--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -156,9 +156,6 @@
     <t xml:space="preserve">Tim Holyk</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Walker Hultgren</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t xml:space="preserve">Rafael Gross</t>
   </si>
   <si>
-    <t xml:space="preserve">Raffi Gross</t>
-  </si>
-  <si>
     <t xml:space="preserve">Samuele Bruno</t>
   </si>
   <si>
@@ -679,9 +673,6 @@
   </si>
   <si>
     <t xml:space="preserve">Eric Pettipiece</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Elliottt</t>
   </si>
   <si>
     <t xml:space="preserve">Garret Day</t>
@@ -982,8 +973,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K166" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K166"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K164" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K164"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -1002,8 +993,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K136" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K135" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K135"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2374,7 +2365,7 @@
         <v>17.1</v>
       </c>
       <c r="G31" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="H31" t="n">
         <v>11.6</v>
@@ -2536,86 +2527,102 @@
       <c r="B36" t="s">
         <v>33</v>
       </c>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
+      <c r="C36" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25</v>
+      </c>
       <c r="G36" t="n">
-        <v>100</v>
-      </c>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
+        <v>28.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C37" t="n">
-        <v>74.2</v>
+        <v>76.1</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="E37" t="n">
-        <v>49.2</v>
+        <v>54.4</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="G37" t="n">
-        <v>28.2</v>
+        <v>34.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="I37" t="n">
-        <v>45.8</v>
+        <v>63.2</v>
       </c>
       <c r="J37" t="n">
-        <v>29.2</v>
+        <v>23.7</v>
       </c>
       <c r="K37" t="n">
-        <v>37.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
         <v>49</v>
       </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
       <c r="C38" t="n">
-        <v>76.1</v>
+        <v>65.3</v>
       </c>
       <c r="D38" t="n">
-        <v>21.7</v>
+        <v>17.5</v>
       </c>
       <c r="E38" t="n">
-        <v>54.4</v>
+        <v>47.8</v>
       </c>
       <c r="F38" t="n">
-        <v>21.7</v>
+        <v>17.5</v>
       </c>
       <c r="G38" t="n">
-        <v>34.8</v>
+        <v>17.6</v>
       </c>
       <c r="H38" t="n">
-        <v>10.5</v>
+        <v>6.9</v>
       </c>
       <c r="I38" t="n">
-        <v>63.2</v>
+        <v>40.7</v>
       </c>
       <c r="J38" t="n">
-        <v>23.7</v>
+        <v>31.9</v>
       </c>
       <c r="K38" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="39">
@@ -2623,34 +2630,34 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="n">
-        <v>65.3</v>
+        <v>78.9</v>
       </c>
       <c r="D39" t="n">
-        <v>17.5</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="n">
-        <v>47.8</v>
+        <v>65.6</v>
       </c>
       <c r="F39" t="n">
-        <v>17.5</v>
+        <v>13.3</v>
       </c>
       <c r="G39" t="n">
         <v>17.6</v>
       </c>
       <c r="H39" t="n">
-        <v>6.9</v>
+        <v>12.5</v>
       </c>
       <c r="I39" t="n">
-        <v>40.7</v>
+        <v>66.7</v>
       </c>
       <c r="J39" t="n">
-        <v>31.9</v>
+        <v>16.7</v>
       </c>
       <c r="K39" t="n">
-        <v>45.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
@@ -2658,34 +2665,28 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" t="n">
-        <v>78.9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>65.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>13.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
       <c r="G40" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2693,28 +2694,34 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" t="n">
-        <v>100</v>
-      </c>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
+        <v>72.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14.3</v>
+      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>51.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="42">
@@ -2722,34 +2729,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" t="n">
-        <v>72.4</v>
+        <v>78.5</v>
       </c>
       <c r="D42" t="n">
-        <v>14.3</v>
+        <v>27.1</v>
       </c>
       <c r="E42" t="n">
-        <v>58.1</v>
+        <v>51.4</v>
       </c>
       <c r="F42" t="n">
-        <v>14.3</v>
+        <v>27.1</v>
       </c>
       <c r="G42" t="n">
-        <v>12.9</v>
+        <v>25.4</v>
       </c>
       <c r="H42" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>51.9</v>
+        <v>48.2</v>
       </c>
       <c r="J42" t="n">
-        <v>24.7</v>
+        <v>31.3</v>
       </c>
       <c r="K42" t="n">
-        <v>25.9</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="43">
@@ -2757,34 +2764,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>78.5</v>
+        <v>67.3</v>
       </c>
       <c r="D43" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="E43" t="n">
-        <v>51.4</v>
+        <v>39.2</v>
       </c>
       <c r="F43" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="G43" t="n">
-        <v>25.4</v>
+        <v>13.2</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="I43" t="n">
-        <v>48.2</v>
+        <v>36</v>
       </c>
       <c r="J43" t="n">
-        <v>31.3</v>
+        <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>38.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="44">
@@ -2792,34 +2799,30 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" t="n">
-        <v>67.3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C44"/>
       <c r="D44" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>39.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E44"/>
       <c r="F44" t="n">
-        <v>28.1</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>29.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -2827,30 +2830,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45"/>
+        <v>49</v>
+      </c>
+      <c r="C45" t="n">
+        <v>65.7</v>
+      </c>
       <c r="D45" t="n">
-        <v>100</v>
-      </c>
-      <c r="E45"/>
+        <v>25.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>39.9</v>
+      </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>25.8</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>53.2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="46">
@@ -2858,34 +2865,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>65.7</v>
+        <v>77.3</v>
       </c>
       <c r="D46" t="n">
-        <v>25.8</v>
+        <v>22.5</v>
       </c>
       <c r="E46" t="n">
-        <v>39.9</v>
+        <v>54.8</v>
       </c>
       <c r="F46" t="n">
-        <v>25.8</v>
+        <v>22.5</v>
       </c>
       <c r="G46" t="n">
-        <v>22</v>
+        <v>41.2</v>
       </c>
       <c r="H46" t="n">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="I46" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="J46" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="K46" t="n">
-        <v>20.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="47">
@@ -2893,34 +2900,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>77.3</v>
+        <v>79.4</v>
       </c>
       <c r="D47" t="n">
-        <v>22.5</v>
+        <v>37</v>
       </c>
       <c r="E47" t="n">
-        <v>54.8</v>
+        <v>42.4</v>
       </c>
       <c r="F47" t="n">
-        <v>22.5</v>
+        <v>37</v>
       </c>
       <c r="G47" t="n">
-        <v>41.2</v>
+        <v>39.1</v>
       </c>
       <c r="H47" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>55.6</v>
+        <v>48.1</v>
       </c>
       <c r="J47" t="n">
-        <v>22.2</v>
+        <v>29.6</v>
       </c>
       <c r="K47" t="n">
-        <v>25.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="48">
@@ -2928,34 +2935,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" t="n">
-        <v>79.4</v>
+        <v>50.7</v>
       </c>
       <c r="D48" t="n">
-        <v>37</v>
+        <v>17.9</v>
       </c>
       <c r="E48" t="n">
-        <v>42.4</v>
+        <v>32.8</v>
       </c>
       <c r="F48" t="n">
-        <v>37</v>
+        <v>17.9</v>
       </c>
       <c r="G48" t="n">
-        <v>39.1</v>
+        <v>18.3</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>17.1</v>
       </c>
       <c r="I48" t="n">
-        <v>48.1</v>
+        <v>38.5</v>
       </c>
       <c r="J48" t="n">
-        <v>29.6</v>
+        <v>30.8</v>
       </c>
       <c r="K48" t="n">
-        <v>40.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="49">
@@ -2963,34 +2970,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>50.7</v>
+        <v>69.3</v>
       </c>
       <c r="D49" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="E49" t="n">
-        <v>32.8</v>
+        <v>54.5</v>
       </c>
       <c r="F49" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="G49" t="n">
-        <v>18.3</v>
+        <v>31.2</v>
       </c>
       <c r="H49" t="n">
-        <v>17.1</v>
+        <v>12.5</v>
       </c>
       <c r="I49" t="n">
-        <v>38.5</v>
+        <v>36.7</v>
       </c>
       <c r="J49" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -2998,34 +3005,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>69.3</v>
+        <v>68.1</v>
       </c>
       <c r="D50" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="E50" t="n">
-        <v>54.5</v>
+        <v>42.6</v>
       </c>
       <c r="F50" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="G50" t="n">
-        <v>31.2</v>
+        <v>51.6</v>
       </c>
       <c r="H50" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="I50" t="n">
-        <v>36.7</v>
+        <v>47.1</v>
       </c>
       <c r="J50" t="n">
-        <v>40</v>
+        <v>17.6</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="51">
@@ -3033,34 +3040,34 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>68.1</v>
+        <v>70.7</v>
       </c>
       <c r="D51" t="n">
-        <v>25.5</v>
+        <v>14.3</v>
       </c>
       <c r="E51" t="n">
-        <v>42.6</v>
+        <v>56.4</v>
       </c>
       <c r="F51" t="n">
-        <v>25.5</v>
+        <v>14.3</v>
       </c>
       <c r="G51" t="n">
-        <v>51.6</v>
+        <v>21.6</v>
       </c>
       <c r="H51" t="n">
-        <v>6.5</v>
+        <v>13.3</v>
       </c>
       <c r="I51" t="n">
-        <v>47.1</v>
+        <v>61.9</v>
       </c>
       <c r="J51" t="n">
-        <v>17.6</v>
+        <v>14.3</v>
       </c>
       <c r="K51" t="n">
-        <v>29.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="52">
@@ -3068,34 +3075,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C52" t="n">
-        <v>70.7</v>
+        <v>69.3</v>
       </c>
       <c r="D52" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="n">
-        <v>56.4</v>
+        <v>54.7</v>
       </c>
       <c r="F52" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="H52" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
       <c r="I52" t="n">
-        <v>61.9</v>
+        <v>38.8</v>
       </c>
       <c r="J52" t="n">
-        <v>14.3</v>
+        <v>32.8</v>
       </c>
       <c r="K52" t="n">
-        <v>21.4</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="53">
@@ -3103,34 +3110,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53" t="n">
-        <v>69.3</v>
+        <v>77.8</v>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="E53" t="n">
-        <v>54.7</v>
+        <v>65.6</v>
       </c>
       <c r="F53" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="G53" t="n">
-        <v>25.6</v>
+        <v>33.8</v>
       </c>
       <c r="H53" t="n">
-        <v>9.6</v>
+        <v>13.6</v>
       </c>
       <c r="I53" t="n">
-        <v>38.8</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>32.8</v>
+        <v>41.5</v>
       </c>
       <c r="K53" t="n">
-        <v>38.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="54">
@@ -3138,69 +3145,69 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
-        <v>77.8</v>
+        <v>76.8</v>
       </c>
       <c r="D54" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="E54" t="n">
-        <v>65.6</v>
+        <v>53.5</v>
       </c>
       <c r="F54" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="G54" t="n">
-        <v>33.8</v>
+        <v>30.6</v>
       </c>
       <c r="H54" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>52.1</v>
       </c>
       <c r="J54" t="n">
-        <v>41.5</v>
+        <v>18.8</v>
       </c>
       <c r="K54" t="n">
-        <v>50.8</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
         <v>67</v>
       </c>
-      <c r="B55" t="s">
-        <v>68</v>
-      </c>
       <c r="C55" t="n">
-        <v>76.8</v>
+        <v>78.9</v>
       </c>
       <c r="D55" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="E55" t="n">
-        <v>53.5</v>
+        <v>45.6</v>
       </c>
       <c r="F55" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="G55" t="n">
-        <v>30.6</v>
+        <v>23.5</v>
       </c>
       <c r="H55" t="n">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
       <c r="I55" t="n">
-        <v>52.1</v>
+        <v>40.8</v>
       </c>
       <c r="J55" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="K55" t="n">
-        <v>43.8</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="56">
@@ -3208,34 +3215,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
-        <v>78.9</v>
+        <v>59.6</v>
       </c>
       <c r="D56" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="E56" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="F56" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="G56" t="n">
-        <v>23.5</v>
+        <v>26.1</v>
       </c>
       <c r="H56" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="I56" t="n">
-        <v>40.8</v>
+        <v>54.9</v>
       </c>
       <c r="J56" t="n">
-        <v>22.4</v>
+        <v>17.6</v>
       </c>
       <c r="K56" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
@@ -3243,34 +3250,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
-        <v>59.6</v>
+        <v>69.2</v>
       </c>
       <c r="D57" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="n">
-        <v>46.3</v>
+        <v>52.5</v>
       </c>
       <c r="F57" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="G57" t="n">
-        <v>26.1</v>
+        <v>42.9</v>
       </c>
       <c r="H57" t="n">
-        <v>13.6</v>
+        <v>23.1</v>
       </c>
       <c r="I57" t="n">
-        <v>54.9</v>
+        <v>42.9</v>
       </c>
       <c r="J57" t="n">
-        <v>17.6</v>
+        <v>57.1</v>
       </c>
       <c r="K57" t="n">
-        <v>34</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="58">
@@ -3278,98 +3285,98 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="E58" t="n">
-        <v>52.5</v>
+        <v>-100</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="J58" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>28.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>57.8</v>
       </c>
       <c r="D59" t="n">
-        <v>100</v>
+        <v>45.7</v>
       </c>
       <c r="E59" t="n">
-        <v>-100</v>
+        <v>12.1</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>45.7</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
+        <v>3.4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
-        <v>57.8</v>
+        <v>57.1</v>
       </c>
       <c r="D60" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="n">
-        <v>12.1</v>
+        <v>44.6</v>
       </c>
       <c r="F60" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="G60" t="n">
-        <v>31</v>
+        <v>14.3</v>
       </c>
       <c r="H60" t="n">
-        <v>3.4</v>
+        <v>16.7</v>
       </c>
       <c r="I60" t="n">
-        <v>47.4</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>42.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -3377,34 +3384,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E61" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G61" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="H61" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I61" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -3412,34 +3419,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D62" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F62" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G62" t="n">
-        <v>38.1</v>
+        <v>41.2</v>
       </c>
       <c r="H62" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I62" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -3447,34 +3454,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>72.4</v>
+        <v>46.4</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="n">
-        <v>62.4</v>
+        <v>33.2</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="G63" t="n">
-        <v>41.2</v>
+        <v>14.3</v>
       </c>
       <c r="H63" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I63" t="n">
+        <v>30</v>
+      </c>
+      <c r="J63" t="n">
+        <v>40</v>
+      </c>
+      <c r="K63" t="n">
         <v>50</v>
-      </c>
-      <c r="J63" t="n">
-        <v>30</v>
-      </c>
-      <c r="K63" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3482,34 +3489,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>46.4</v>
+        <v>70.2</v>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>17.8</v>
       </c>
       <c r="E64" t="n">
-        <v>33.2</v>
+        <v>52.4</v>
       </c>
       <c r="F64" t="n">
-        <v>13.2</v>
+        <v>17.8</v>
       </c>
       <c r="G64" t="n">
-        <v>14.3</v>
+        <v>23.5</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>15.7</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>50.6</v>
       </c>
       <c r="J64" t="n">
-        <v>40</v>
+        <v>20.8</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="65">
@@ -3517,34 +3524,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E65" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F65" t="n">
-        <v>17.8</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
       <c r="G65" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>50.6</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>20.8</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -3552,28 +3553,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
+        <v>81</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>64.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>16.1</v>
+      </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>15.4</v>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="67">
@@ -3581,34 +3588,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="E67" t="n">
-        <v>64.9</v>
+        <v>50</v>
       </c>
       <c r="F67" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="H67" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -3616,19 +3623,19 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G68" t="n">
         <v>25</v>
@@ -3637,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -3651,34 +3658,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69" t="n">
+        <v>74.4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G69" t="n">
         <v>33.3</v>
       </c>
-      <c r="D69" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25</v>
-      </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="70">
@@ -3686,34 +3693,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C70" t="n">
-        <v>74.4</v>
+        <v>69.6</v>
       </c>
       <c r="D70" t="n">
-        <v>3.1</v>
+        <v>33.3</v>
       </c>
       <c r="E70" t="n">
-        <v>71.3</v>
+        <v>36.3</v>
       </c>
       <c r="F70" t="n">
-        <v>3.1</v>
+        <v>33.3</v>
       </c>
       <c r="G70" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="H70" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="I70" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="J70" t="n">
-        <v>11.1</v>
+        <v>30.8</v>
       </c>
       <c r="K70" t="n">
-        <v>11.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="71">
@@ -3721,34 +3728,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" t="n">
-        <v>69.6</v>
+        <v>61.1</v>
       </c>
       <c r="D71" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="E71" t="n">
-        <v>36.3</v>
+        <v>38</v>
       </c>
       <c r="F71" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="G71" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
-        <v>11.8</v>
+        <v>14.3</v>
       </c>
       <c r="I71" t="n">
-        <v>46.2</v>
+        <v>37.5</v>
       </c>
       <c r="J71" t="n">
-        <v>30.8</v>
+        <v>37.5</v>
       </c>
       <c r="K71" t="n">
-        <v>53.8</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="72">
@@ -3756,34 +3763,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" t="n">
-        <v>61.1</v>
+        <v>68.6</v>
       </c>
       <c r="D72" t="n">
-        <v>23.1</v>
+        <v>31.8</v>
       </c>
       <c r="E72" t="n">
-        <v>38</v>
+        <v>36.8</v>
       </c>
       <c r="F72" t="n">
-        <v>23.1</v>
+        <v>31.8</v>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>14.3</v>
+        <v>3.4</v>
       </c>
       <c r="I72" t="n">
-        <v>37.5</v>
+        <v>47.6</v>
       </c>
       <c r="J72" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="K72" t="n">
-        <v>71.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="73">
@@ -3791,34 +3798,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" t="n">
-        <v>68.6</v>
+        <v>66.4</v>
       </c>
       <c r="D73" t="n">
-        <v>31.8</v>
+        <v>14.9</v>
       </c>
       <c r="E73" t="n">
-        <v>36.8</v>
+        <v>51.5</v>
       </c>
       <c r="F73" t="n">
-        <v>31.8</v>
+        <v>14.9</v>
       </c>
       <c r="G73" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="H73" t="n">
-        <v>3.4</v>
+        <v>10.3</v>
       </c>
       <c r="I73" t="n">
-        <v>47.6</v>
+        <v>38.7</v>
       </c>
       <c r="J73" t="n">
-        <v>28.6</v>
+        <v>34.7</v>
       </c>
       <c r="K73" t="n">
-        <v>38.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="74">
@@ -3826,34 +3833,34 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" t="n">
-        <v>66.4</v>
+        <v>80.8</v>
       </c>
       <c r="D74" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="E74" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="F74" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="G74" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="H74" t="n">
-        <v>10.3</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="n">
-        <v>38.7</v>
+        <v>42.9</v>
       </c>
       <c r="J74" t="n">
-        <v>34.7</v>
+        <v>35.2</v>
       </c>
       <c r="K74" t="n">
-        <v>47.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="75">
@@ -3861,34 +3868,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C75" t="n">
-        <v>80.8</v>
+        <v>56.1</v>
       </c>
       <c r="D75" t="n">
-        <v>33.3</v>
+        <v>9.8</v>
       </c>
       <c r="E75" t="n">
-        <v>47.5</v>
+        <v>46.3</v>
       </c>
       <c r="F75" t="n">
-        <v>33.3</v>
+        <v>9.8</v>
       </c>
       <c r="G75" t="n">
-        <v>26.1</v>
+        <v>30.6</v>
       </c>
       <c r="H75" t="n">
-        <v>3.2</v>
+        <v>17.7</v>
       </c>
       <c r="I75" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="J75" t="n">
-        <v>35.2</v>
+        <v>21.8</v>
       </c>
       <c r="K75" t="n">
-        <v>50.5</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="76">
@@ -3896,34 +3903,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C76" t="n">
-        <v>56.1</v>
+        <v>66.7</v>
       </c>
       <c r="D76" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>46.3</v>
+        <v>66.7</v>
       </c>
       <c r="F76" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>30.6</v>
+        <v>26.7</v>
       </c>
       <c r="H76" t="n">
-        <v>17.7</v>
+        <v>16.7</v>
       </c>
       <c r="I76" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K76" t="n">
         <v>54.5</v>
-      </c>
-      <c r="J76" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K76" t="n">
-        <v>30.8</v>
       </c>
     </row>
     <row r="77">
@@ -3931,34 +3938,34 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C77" t="n">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="E77" t="n">
-        <v>66.7</v>
+        <v>58.7</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="G77" t="n">
-        <v>26.7</v>
+        <v>30.4</v>
       </c>
       <c r="H77" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="I77" t="n">
-        <v>27.3</v>
+        <v>46.9</v>
       </c>
       <c r="J77" t="n">
-        <v>36.4</v>
+        <v>29.7</v>
       </c>
       <c r="K77" t="n">
-        <v>54.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="78">
@@ -3966,69 +3973,69 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C78" t="n">
-        <v>77.3</v>
+        <v>85.7</v>
       </c>
       <c r="D78" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="E78" t="n">
-        <v>58.7</v>
+        <v>70.4</v>
       </c>
       <c r="F78" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="G78" t="n">
-        <v>30.4</v>
+        <v>37.7</v>
       </c>
       <c r="H78" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="I78" t="n">
-        <v>46.9</v>
+        <v>38.9</v>
       </c>
       <c r="J78" t="n">
-        <v>29.7</v>
+        <v>41.7</v>
       </c>
       <c r="K78" t="n">
-        <v>58.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" t="s">
         <v>92</v>
       </c>
-      <c r="B79" t="s">
-        <v>93</v>
-      </c>
       <c r="C79" t="n">
-        <v>85.7</v>
+        <v>72.6</v>
       </c>
       <c r="D79" t="n">
-        <v>15.3</v>
+        <v>30</v>
       </c>
       <c r="E79" t="n">
-        <v>70.4</v>
+        <v>42.6</v>
       </c>
       <c r="F79" t="n">
-        <v>15.3</v>
+        <v>30</v>
       </c>
       <c r="G79" t="n">
-        <v>37.7</v>
+        <v>20.4</v>
       </c>
       <c r="H79" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="I79" t="n">
-        <v>38.9</v>
+        <v>59.1</v>
       </c>
       <c r="J79" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="K79" t="n">
-        <v>47.4</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="80">
@@ -4036,34 +4043,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C80" t="n">
-        <v>72.6</v>
+        <v>72.2</v>
       </c>
       <c r="D80" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="E80" t="n">
-        <v>42.6</v>
+        <v>44.3</v>
       </c>
       <c r="F80" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="G80" t="n">
-        <v>20.4</v>
+        <v>31.7</v>
       </c>
       <c r="H80" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="I80" t="n">
-        <v>59.1</v>
+        <v>41.3</v>
       </c>
       <c r="J80" t="n">
-        <v>16.7</v>
+        <v>21.3</v>
       </c>
       <c r="K80" t="n">
-        <v>42.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="81">
@@ -4071,34 +4078,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C81" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="D81" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="E81" t="n">
-        <v>44.3</v>
+        <v>46.9</v>
       </c>
       <c r="F81" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="G81" t="n">
-        <v>31.7</v>
+        <v>26</v>
       </c>
       <c r="H81" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I81" t="n">
-        <v>41.3</v>
+        <v>45.5</v>
       </c>
       <c r="J81" t="n">
-        <v>21.3</v>
+        <v>23.4</v>
       </c>
       <c r="K81" t="n">
-        <v>57.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82">
@@ -4106,34 +4113,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C82" t="n">
-        <v>76.5</v>
+        <v>78.6</v>
       </c>
       <c r="D82" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>46.9</v>
+        <v>78.6</v>
       </c>
       <c r="F82" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="H82" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="I82" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>23.4</v>
+        <v>37.5</v>
       </c>
       <c r="K82" t="n">
-        <v>48</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="83">
@@ -4141,34 +4148,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C83" t="n">
-        <v>78.6</v>
+        <v>78.9</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="E83" t="n">
-        <v>78.6</v>
+        <v>48.2</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="G83" t="n">
-        <v>5.3</v>
+        <v>25.7</v>
       </c>
       <c r="H83" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>43.5</v>
       </c>
       <c r="J83" t="n">
-        <v>37.5</v>
+        <v>27.2</v>
       </c>
       <c r="K83" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="84">
@@ -4176,34 +4183,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C84" t="n">
-        <v>78.9</v>
+        <v>73.8</v>
       </c>
       <c r="D84" t="n">
-        <v>30.7</v>
+        <v>17.8</v>
       </c>
       <c r="E84" t="n">
-        <v>48.2</v>
+        <v>56</v>
       </c>
       <c r="F84" t="n">
-        <v>30.7</v>
+        <v>17.8</v>
       </c>
       <c r="G84" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I84" t="n">
-        <v>43.5</v>
+        <v>32.9</v>
       </c>
       <c r="J84" t="n">
-        <v>27.2</v>
+        <v>39.7</v>
       </c>
       <c r="K84" t="n">
-        <v>63.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
@@ -4211,34 +4218,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C85" t="n">
-        <v>73.8</v>
+        <v>72.2</v>
       </c>
       <c r="D85" t="n">
-        <v>17.8</v>
+        <v>21.3</v>
       </c>
       <c r="E85" t="n">
-        <v>56</v>
+        <v>50.9</v>
       </c>
       <c r="F85" t="n">
-        <v>17.8</v>
+        <v>21.3</v>
       </c>
       <c r="G85" t="n">
-        <v>26.6</v>
+        <v>30</v>
       </c>
       <c r="H85" t="n">
-        <v>11.3</v>
+        <v>6.8</v>
       </c>
       <c r="I85" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="J85" t="n">
-        <v>39.7</v>
+        <v>24.5</v>
       </c>
       <c r="K85" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86">
@@ -4246,34 +4253,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C86" t="n">
-        <v>72.2</v>
+        <v>40</v>
       </c>
       <c r="D86" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="E86" t="n">
-        <v>50.9</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="G86" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>6.8</v>
+        <v>21.1</v>
       </c>
       <c r="I86" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="J86" t="n">
-        <v>24.5</v>
+        <v>12.5</v>
       </c>
       <c r="K86" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87">
@@ -4281,34 +4288,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C87" t="n">
-        <v>40</v>
+        <v>70.8</v>
       </c>
       <c r="D87" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>44.1</v>
       </c>
       <c r="F87" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="G87" t="n">
-        <v>36</v>
+        <v>18.4</v>
       </c>
       <c r="H87" t="n">
-        <v>21.1</v>
+        <v>6.9</v>
       </c>
       <c r="I87" t="n">
-        <v>62.5</v>
+        <v>54.3</v>
       </c>
       <c r="J87" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="K87" t="n">
-        <v>50</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="88">
@@ -4316,34 +4323,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C88" t="n">
-        <v>70.8</v>
+        <v>72.5</v>
       </c>
       <c r="D88" t="n">
-        <v>26.7</v>
+        <v>32.4</v>
       </c>
       <c r="E88" t="n">
-        <v>44.1</v>
+        <v>40.1</v>
       </c>
       <c r="F88" t="n">
-        <v>26.7</v>
+        <v>32.4</v>
       </c>
       <c r="G88" t="n">
-        <v>18.4</v>
+        <v>26</v>
       </c>
       <c r="H88" t="n">
-        <v>6.9</v>
+        <v>9.3</v>
       </c>
       <c r="I88" t="n">
-        <v>54.3</v>
+        <v>44.4</v>
       </c>
       <c r="J88" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K88" t="n">
-        <v>39.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="89">
@@ -4351,34 +4358,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>72.5</v>
+        <v>83.3</v>
       </c>
       <c r="D89" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="E89" t="n">
-        <v>40.1</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="G89" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="H89" t="n">
-        <v>9.3</v>
+        <v>20</v>
       </c>
       <c r="I89" t="n">
-        <v>44.4</v>
+        <v>70</v>
       </c>
       <c r="J89" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K89" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -4386,34 +4393,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C90" t="n">
-        <v>83.3</v>
+        <v>65.2</v>
       </c>
       <c r="D90" t="n">
-        <v>27.3</v>
+        <v>14.5</v>
       </c>
       <c r="E90" t="n">
-        <v>56</v>
+        <v>50.7</v>
       </c>
       <c r="F90" t="n">
-        <v>27.3</v>
+        <v>14.5</v>
       </c>
       <c r="G90" t="n">
-        <v>26.1</v>
+        <v>21.2</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>12.1</v>
       </c>
       <c r="I90" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J90" t="n">
-        <v>10</v>
+        <v>14.1</v>
       </c>
       <c r="K90" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="91">
@@ -4421,34 +4428,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C91" t="n">
-        <v>65.2</v>
+        <v>53.6</v>
       </c>
       <c r="D91" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="E91" t="n">
-        <v>50.7</v>
+        <v>38</v>
       </c>
       <c r="F91" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="G91" t="n">
-        <v>21.2</v>
+        <v>30.9</v>
       </c>
       <c r="H91" t="n">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
       <c r="I91" t="n">
-        <v>62</v>
+        <v>67.7</v>
       </c>
       <c r="J91" t="n">
-        <v>14.1</v>
+        <v>25.8</v>
       </c>
       <c r="K91" t="n">
-        <v>42.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="92">
@@ -4456,57 +4463,51 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C92" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="D92" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="E92" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="G92" t="n">
-        <v>30.9</v>
+        <v>100</v>
       </c>
       <c r="H92" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J92" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K92" t="n">
-        <v>26.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" t="s">
         <v>107</v>
       </c>
-      <c r="B93" t="s">
-        <v>108</v>
-      </c>
       <c r="C93" t="n">
+        <v>100</v>
+      </c>
+      <c r="D93" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G93" t="n">
         <v>50</v>
-      </c>
-      <c r="D93" t="n">
-        <v>50</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>50</v>
-      </c>
-      <c r="G93" t="n">
-        <v>100</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4517,66 +4518,72 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C94" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D94" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="E94" t="n">
-        <v>66.7</v>
+        <v>47</v>
       </c>
       <c r="F94" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="G94" t="n">
-        <v>50</v>
+        <v>25.4</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94"/>
-      <c r="J94"/>
-      <c r="K94"/>
+        <v>12.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J94" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K94" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C95" t="n">
-        <v>57.8</v>
+        <v>71.4</v>
       </c>
       <c r="D95" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="E95" t="n">
-        <v>47</v>
+        <v>51.4</v>
       </c>
       <c r="F95" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>25.4</v>
+        <v>16.7</v>
       </c>
       <c r="H95" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I95" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4584,34 +4591,34 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C96" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D96" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>51.4</v>
+        <v>75</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
@@ -4619,34 +4626,28 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C97" t="n">
-        <v>75</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>75</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
       <c r="G97" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H97" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4654,28 +4655,34 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C98" t="n">
-        <v>50</v>
-      </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
+        <v>60</v>
+      </c>
+      <c r="D98" t="n">
+        <v>40</v>
+      </c>
+      <c r="E98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F98" t="n">
+        <v>40</v>
+      </c>
       <c r="G98" t="n">
-        <v>50</v>
+        <v>28.8</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -4683,34 +4690,34 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C99" t="n">
-        <v>60</v>
+        <v>75.9</v>
       </c>
       <c r="D99" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="E99" t="n">
-        <v>20</v>
+        <v>37.2</v>
       </c>
       <c r="F99" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="G99" t="n">
-        <v>28.8</v>
+        <v>42.4</v>
       </c>
       <c r="H99" t="n">
-        <v>2.8</v>
+        <v>9.4</v>
       </c>
       <c r="I99" t="n">
-        <v>39.1</v>
+        <v>54.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="K99" t="n">
-        <v>13</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="100">
@@ -4718,34 +4725,34 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C100" t="n">
-        <v>75.9</v>
+        <v>73.2</v>
       </c>
       <c r="D100" t="n">
-        <v>38.7</v>
+        <v>22</v>
       </c>
       <c r="E100" t="n">
-        <v>37.2</v>
+        <v>51.2</v>
       </c>
       <c r="F100" t="n">
-        <v>38.7</v>
+        <v>22</v>
       </c>
       <c r="G100" t="n">
-        <v>42.4</v>
+        <v>14.7</v>
       </c>
       <c r="H100" t="n">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="I100" t="n">
-        <v>54.3</v>
+        <v>45.5</v>
       </c>
       <c r="J100" t="n">
-        <v>14.3</v>
+        <v>19.5</v>
       </c>
       <c r="K100" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="101">
@@ -4753,34 +4760,34 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C101" t="n">
-        <v>73.2</v>
+        <v>65.5</v>
       </c>
       <c r="D101" t="n">
-        <v>22</v>
+        <v>9.7</v>
       </c>
       <c r="E101" t="n">
-        <v>51.2</v>
+        <v>55.8</v>
       </c>
       <c r="F101" t="n">
-        <v>22</v>
+        <v>9.7</v>
       </c>
       <c r="G101" t="n">
-        <v>14.7</v>
+        <v>31.4</v>
       </c>
       <c r="H101" t="n">
-        <v>8.1</v>
+        <v>21.8</v>
       </c>
       <c r="I101" t="n">
-        <v>45.5</v>
+        <v>28.3</v>
       </c>
       <c r="J101" t="n">
-        <v>19.5</v>
+        <v>35</v>
       </c>
       <c r="K101" t="n">
-        <v>27.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102">
@@ -4788,34 +4795,34 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C102" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="D102" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="E102" t="n">
-        <v>55.8</v>
+        <v>48.5</v>
       </c>
       <c r="F102" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="G102" t="n">
-        <v>31.4</v>
+        <v>46.7</v>
       </c>
       <c r="H102" t="n">
-        <v>21.8</v>
+        <v>33.3</v>
       </c>
       <c r="I102" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>39</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="103">
@@ -4823,25 +4830,25 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C103" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D103" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="F103" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -4850,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4858,34 +4865,26 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
-      </c>
-      <c r="C104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
         <v>100</v>
       </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
         <v>100</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4893,26 +4892,34 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
-      </c>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
+        <v>107</v>
+      </c>
+      <c r="C105" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="D105" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>25.2</v>
+      </c>
       <c r="G105" t="n">
-        <v>16.7</v>
+        <v>22.7</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I105" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="K105" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="106">
@@ -4920,34 +4927,34 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C106" t="n">
-        <v>71.7</v>
+        <v>80</v>
       </c>
       <c r="D106" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="E106" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="F106" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="G106" t="n">
-        <v>22.7</v>
+        <v>35.1</v>
       </c>
       <c r="H106" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="I106" t="n">
-        <v>43.8</v>
+        <v>36.1</v>
       </c>
       <c r="J106" t="n">
-        <v>28.7</v>
+        <v>31.1</v>
       </c>
       <c r="K106" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="107">
@@ -4955,34 +4962,34 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" t="n">
-        <v>80</v>
+        <v>71.4</v>
       </c>
       <c r="D107" t="n">
-        <v>25.8</v>
+        <v>35.7</v>
       </c>
       <c r="E107" t="n">
-        <v>54.2</v>
+        <v>35.7</v>
       </c>
       <c r="F107" t="n">
-        <v>25.8</v>
+        <v>35.7</v>
       </c>
       <c r="G107" t="n">
-        <v>33.9</v>
+        <v>5.3</v>
       </c>
       <c r="H107" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="I107" t="n">
-        <v>33.9</v>
+        <v>42.9</v>
       </c>
       <c r="J107" t="n">
-        <v>32.2</v>
+        <v>14.3</v>
       </c>
       <c r="K107" t="n">
-        <v>49.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="108">
@@ -4990,34 +4997,34 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>59.1</v>
       </c>
       <c r="D108" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="E108" t="n">
-        <v>-20</v>
+        <v>40.6</v>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="G108" t="n">
-        <v>54.5</v>
+        <v>31.2</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I108" t="n">
-        <v>100</v>
+        <v>34.6</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>34.6</v>
       </c>
       <c r="K108" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="109">
@@ -5025,34 +5032,34 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C109" t="n">
-        <v>71.4</v>
+        <v>79.8</v>
       </c>
       <c r="D109" t="n">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="E109" t="n">
-        <v>35.7</v>
+        <v>53.1</v>
       </c>
       <c r="F109" t="n">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="G109" t="n">
-        <v>5.3</v>
+        <v>35.4</v>
       </c>
       <c r="H109" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="I109" t="n">
-        <v>42.9</v>
+        <v>39.3</v>
       </c>
       <c r="J109" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="K109" t="n">
-        <v>33.3</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="110">
@@ -5060,34 +5067,34 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C110" t="n">
-        <v>59.1</v>
+        <v>66.2</v>
       </c>
       <c r="D110" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="E110" t="n">
-        <v>40.6</v>
+        <v>49.6</v>
       </c>
       <c r="F110" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="G110" t="n">
-        <v>31.2</v>
+        <v>17.2</v>
       </c>
       <c r="H110" t="n">
-        <v>4.2</v>
+        <v>10.2</v>
       </c>
       <c r="I110" t="n">
-        <v>34.6</v>
+        <v>39.8</v>
       </c>
       <c r="J110" t="n">
-        <v>34.6</v>
+        <v>21.5</v>
       </c>
       <c r="K110" t="n">
-        <v>42.3</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="111">
@@ -5095,34 +5102,34 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C111" t="n">
-        <v>79.8</v>
+        <v>57.8</v>
       </c>
       <c r="D111" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="E111" t="n">
-        <v>53.1</v>
+        <v>35.6</v>
       </c>
       <c r="F111" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="G111" t="n">
-        <v>35.4</v>
+        <v>18.9</v>
       </c>
       <c r="H111" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="I111" t="n">
-        <v>39.3</v>
+        <v>41.6</v>
       </c>
       <c r="J111" t="n">
-        <v>28.6</v>
+        <v>23.4</v>
       </c>
       <c r="K111" t="n">
-        <v>39.3</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="112">
@@ -5130,34 +5137,34 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" t="n">
-        <v>66.2</v>
+        <v>66</v>
       </c>
       <c r="D112" t="n">
-        <v>16.6</v>
+        <v>15.7</v>
       </c>
       <c r="E112" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
       <c r="F112" t="n">
-        <v>16.6</v>
+        <v>15.7</v>
       </c>
       <c r="G112" t="n">
-        <v>17.2</v>
+        <v>25.1</v>
       </c>
       <c r="H112" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="I112" t="n">
-        <v>39.8</v>
+        <v>53.3</v>
       </c>
       <c r="J112" t="n">
-        <v>21.5</v>
+        <v>26.7</v>
       </c>
       <c r="K112" t="n">
-        <v>45.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="113">
@@ -5165,104 +5172,96 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C113" t="n">
-        <v>57.8</v>
+        <v>66.2</v>
       </c>
       <c r="D113" t="n">
-        <v>22.2</v>
+        <v>36.1</v>
       </c>
       <c r="E113" t="n">
-        <v>35.6</v>
+        <v>30.1</v>
       </c>
       <c r="F113" t="n">
-        <v>22.2</v>
+        <v>36.1</v>
       </c>
       <c r="G113" t="n">
-        <v>18.9</v>
+        <v>27.9</v>
       </c>
       <c r="H113" t="n">
-        <v>11.2</v>
+        <v>7.9</v>
       </c>
       <c r="I113" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="J113" t="n">
-        <v>23.4</v>
+        <v>33.3</v>
       </c>
       <c r="K113" t="n">
-        <v>40.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>129</v>
+      </c>
+      <c r="B114" t="s">
         <v>128</v>
       </c>
-      <c r="B114" t="s">
-        <v>108</v>
-      </c>
-      <c r="C114" t="n">
-        <v>66</v>
-      </c>
-      <c r="D114" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="E114" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="F114" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
       <c r="G114" t="n">
-        <v>25.1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="J114" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="K114" t="n">
-        <v>51.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C115" t="n">
-        <v>66.2</v>
+        <v>80</v>
       </c>
       <c r="D115" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>30.1</v>
+        <v>80</v>
       </c>
       <c r="F115" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5270,26 +5269,34 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
-      </c>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
+        <v>128</v>
+      </c>
+      <c r="C116" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E116" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="F116" t="n">
+        <v>21.9</v>
+      </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>9.8</v>
       </c>
       <c r="I116" t="n">
-        <v>33.3</v>
+        <v>39.3</v>
       </c>
       <c r="J116" t="n">
-        <v>33.3</v>
+        <v>31.1</v>
       </c>
       <c r="K116" t="n">
-        <v>33.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="117">
@@ -5297,34 +5304,34 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C117" t="n">
-        <v>80</v>
+        <v>68.2</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="E117" t="n">
-        <v>80</v>
+        <v>43.7</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="G117" t="n">
-        <v>25</v>
+        <v>29.5</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="J117" t="n">
-        <v>100</v>
+        <v>25.5</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="118">
@@ -5332,34 +5339,34 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C118" t="n">
-        <v>71.3</v>
+        <v>79.5</v>
       </c>
       <c r="D118" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="E118" t="n">
-        <v>49.4</v>
+        <v>47.6</v>
       </c>
       <c r="F118" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="G118" t="n">
-        <v>14.4</v>
+        <v>25.8</v>
       </c>
       <c r="H118" t="n">
-        <v>9.8</v>
+        <v>6</v>
       </c>
       <c r="I118" t="n">
-        <v>39.3</v>
+        <v>42.7</v>
       </c>
       <c r="J118" t="n">
-        <v>31.1</v>
+        <v>25.6</v>
       </c>
       <c r="K118" t="n">
-        <v>50.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="119">
@@ -5367,34 +5374,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C119" t="n">
-        <v>68.2</v>
+        <v>59.2</v>
       </c>
       <c r="D119" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="E119" t="n">
-        <v>43.7</v>
+        <v>35.7</v>
       </c>
       <c r="F119" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="G119" t="n">
-        <v>29.5</v>
+        <v>23.2</v>
       </c>
       <c r="H119" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I119" t="n">
-        <v>43.6</v>
+        <v>62.3</v>
       </c>
       <c r="J119" t="n">
-        <v>25.5</v>
+        <v>15.1</v>
       </c>
       <c r="K119" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="120">
@@ -5402,34 +5409,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C120" t="n">
-        <v>79.5</v>
+        <v>54.7</v>
       </c>
       <c r="D120" t="n">
-        <v>31.9</v>
+        <v>19.6</v>
       </c>
       <c r="E120" t="n">
-        <v>47.6</v>
+        <v>35.1</v>
       </c>
       <c r="F120" t="n">
-        <v>31.9</v>
+        <v>19.6</v>
       </c>
       <c r="G120" t="n">
-        <v>25.8</v>
+        <v>9.5</v>
       </c>
       <c r="H120" t="n">
-        <v>6</v>
+        <v>11.6</v>
       </c>
       <c r="I120" t="n">
-        <v>42.7</v>
+        <v>63.4</v>
       </c>
       <c r="J120" t="n">
-        <v>25.6</v>
+        <v>11.8</v>
       </c>
       <c r="K120" t="n">
-        <v>30.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121">
@@ -5437,34 +5444,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C121" t="n">
-        <v>59.2</v>
+        <v>80</v>
       </c>
       <c r="D121" t="n">
-        <v>23.5</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="n">
-        <v>35.7</v>
+        <v>68.9</v>
       </c>
       <c r="F121" t="n">
-        <v>23.5</v>
+        <v>11.1</v>
       </c>
       <c r="G121" t="n">
-        <v>23.2</v>
+        <v>39.5</v>
       </c>
       <c r="H121" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I121" t="n">
-        <v>62.3</v>
+        <v>63.6</v>
       </c>
       <c r="J121" t="n">
-        <v>15.1</v>
+        <v>9.1</v>
       </c>
       <c r="K121" t="n">
-        <v>47.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="122">
@@ -5472,34 +5479,34 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C122" t="n">
-        <v>54.7</v>
+        <v>70.6</v>
       </c>
       <c r="D122" t="n">
-        <v>19.6</v>
+        <v>28.7</v>
       </c>
       <c r="E122" t="n">
-        <v>35.1</v>
+        <v>41.9</v>
       </c>
       <c r="F122" t="n">
-        <v>19.6</v>
+        <v>28.7</v>
       </c>
       <c r="G122" t="n">
-        <v>9.5</v>
+        <v>21.8</v>
       </c>
       <c r="H122" t="n">
-        <v>11.6</v>
+        <v>4.9</v>
       </c>
       <c r="I122" t="n">
-        <v>63.4</v>
+        <v>39.6</v>
       </c>
       <c r="J122" t="n">
-        <v>11.8</v>
+        <v>31.5</v>
       </c>
       <c r="K122" t="n">
-        <v>25</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="123">
@@ -5507,34 +5514,34 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C123" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="E123" t="n">
-        <v>68.9</v>
+        <v>43.3</v>
       </c>
       <c r="F123" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="G123" t="n">
-        <v>39.5</v>
+        <v>14.8</v>
       </c>
       <c r="H123" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I123" t="n">
+        <v>60</v>
+      </c>
+      <c r="J123" t="n">
+        <v>30</v>
+      </c>
+      <c r="K123" t="n">
         <v>10</v>
-      </c>
-      <c r="I123" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J123" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K123" t="n">
-        <v>45.5</v>
       </c>
     </row>
     <row r="124">
@@ -5542,34 +5549,34 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C124" t="n">
-        <v>70.6</v>
+        <v>56.9</v>
       </c>
       <c r="D124" t="n">
-        <v>28.7</v>
+        <v>19.7</v>
       </c>
       <c r="E124" t="n">
-        <v>41.9</v>
+        <v>37.2</v>
       </c>
       <c r="F124" t="n">
-        <v>28.7</v>
+        <v>19.7</v>
       </c>
       <c r="G124" t="n">
-        <v>21.8</v>
+        <v>15.2</v>
       </c>
       <c r="H124" t="n">
-        <v>4.9</v>
+        <v>13.3</v>
       </c>
       <c r="I124" t="n">
-        <v>39.6</v>
+        <v>48.1</v>
       </c>
       <c r="J124" t="n">
-        <v>31.5</v>
+        <v>29.6</v>
       </c>
       <c r="K124" t="n">
-        <v>39.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="125">
@@ -5577,34 +5584,34 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>70</v>
+        <v>72.6</v>
       </c>
       <c r="D125" t="n">
-        <v>26.7</v>
+        <v>21.1</v>
       </c>
       <c r="E125" t="n">
-        <v>43.3</v>
+        <v>51.5</v>
       </c>
       <c r="F125" t="n">
-        <v>26.7</v>
+        <v>21.1</v>
       </c>
       <c r="G125" t="n">
-        <v>14.8</v>
+        <v>32.9</v>
       </c>
       <c r="H125" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I125" t="n">
-        <v>60</v>
+        <v>48.6</v>
       </c>
       <c r="J125" t="n">
-        <v>30</v>
+        <v>18.9</v>
       </c>
       <c r="K125" t="n">
-        <v>10</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="126">
@@ -5612,34 +5619,34 @@
         <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C126" t="n">
-        <v>56.9</v>
+        <v>74.7</v>
       </c>
       <c r="D126" t="n">
-        <v>19.7</v>
+        <v>24.3</v>
       </c>
       <c r="E126" t="n">
-        <v>37.2</v>
+        <v>50.4</v>
       </c>
       <c r="F126" t="n">
-        <v>19.7</v>
+        <v>24.3</v>
       </c>
       <c r="G126" t="n">
-        <v>15.2</v>
+        <v>32</v>
       </c>
       <c r="H126" t="n">
-        <v>13.3</v>
+        <v>8.3</v>
       </c>
       <c r="I126" t="n">
-        <v>48.1</v>
+        <v>38.6</v>
       </c>
       <c r="J126" t="n">
-        <v>29.6</v>
+        <v>26.5</v>
       </c>
       <c r="K126" t="n">
-        <v>53.8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127">
@@ -5647,34 +5654,34 @@
         <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C127" t="n">
-        <v>72.6</v>
+        <v>75.2</v>
       </c>
       <c r="D127" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="E127" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="F127" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="G127" t="n">
-        <v>32.9</v>
+        <v>24.8</v>
       </c>
       <c r="H127" t="n">
-        <v>12.9</v>
+        <v>8.2</v>
       </c>
       <c r="I127" t="n">
-        <v>48.6</v>
+        <v>41.1</v>
       </c>
       <c r="J127" t="n">
-        <v>18.9</v>
+        <v>33.7</v>
       </c>
       <c r="K127" t="n">
-        <v>41.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="128">
@@ -5682,34 +5689,34 @@
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C128" t="n">
-        <v>74.7</v>
+        <v>68.2</v>
       </c>
       <c r="D128" t="n">
-        <v>24.3</v>
+        <v>18.2</v>
       </c>
       <c r="E128" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>24.3</v>
+        <v>18.2</v>
       </c>
       <c r="G128" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="H128" t="n">
-        <v>8.3</v>
+        <v>11.9</v>
       </c>
       <c r="I128" t="n">
-        <v>38.6</v>
+        <v>48.3</v>
       </c>
       <c r="J128" t="n">
-        <v>26.5</v>
+        <v>17.2</v>
       </c>
       <c r="K128" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129">
@@ -5717,104 +5724,104 @@
         <v>144</v>
       </c>
       <c r="B129" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C129" t="n">
-        <v>75.2</v>
+        <v>72</v>
       </c>
       <c r="D129" t="n">
         <v>23.1</v>
       </c>
       <c r="E129" t="n">
-        <v>52.1</v>
+        <v>48.9</v>
       </c>
       <c r="F129" t="n">
         <v>23.1</v>
       </c>
       <c r="G129" t="n">
-        <v>24.8</v>
+        <v>14.3</v>
       </c>
       <c r="H129" t="n">
-        <v>8.2</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>41.1</v>
+        <v>36.4</v>
       </c>
       <c r="J129" t="n">
-        <v>33.7</v>
+        <v>18.2</v>
       </c>
       <c r="K129" t="n">
-        <v>49.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>146</v>
+      </c>
+      <c r="B130" t="s">
         <v>145</v>
       </c>
-      <c r="B130" t="s">
-        <v>130</v>
-      </c>
       <c r="C130" t="n">
-        <v>68.2</v>
+        <v>66.7</v>
       </c>
       <c r="D130" t="n">
-        <v>18.2</v>
+        <v>60</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>6.7</v>
       </c>
       <c r="F130" t="n">
-        <v>18.2</v>
+        <v>60</v>
       </c>
       <c r="G130" t="n">
-        <v>21.5</v>
+        <v>33.3</v>
       </c>
       <c r="H130" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="I130" t="n">
-        <v>48.3</v>
+        <v>25</v>
       </c>
       <c r="J130" t="n">
-        <v>17.2</v>
+        <v>25</v>
       </c>
       <c r="K130" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C131" t="n">
-        <v>72</v>
+        <v>66.2</v>
       </c>
       <c r="D131" t="n">
-        <v>23.1</v>
+        <v>20</v>
       </c>
       <c r="E131" t="n">
-        <v>48.9</v>
+        <v>46.2</v>
       </c>
       <c r="F131" t="n">
-        <v>23.1</v>
+        <v>20</v>
       </c>
       <c r="G131" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I131" t="n">
-        <v>36.4</v>
+        <v>43.9</v>
       </c>
       <c r="J131" t="n">
-        <v>18.2</v>
+        <v>24.6</v>
       </c>
       <c r="K131" t="n">
-        <v>27.3</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="132">
@@ -5822,31 +5829,31 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C132" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="D132" t="n">
-        <v>60</v>
+        <v>13.3</v>
       </c>
       <c r="E132" t="n">
-        <v>6.7</v>
+        <v>21.7</v>
       </c>
       <c r="F132" t="n">
-        <v>60</v>
+        <v>13.3</v>
       </c>
       <c r="G132" t="n">
         <v>33.3</v>
       </c>
       <c r="H132" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J132" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5857,34 +5864,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C133" t="n">
-        <v>66.2</v>
+        <v>72.2</v>
       </c>
       <c r="D133" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E133" t="n">
-        <v>46.2</v>
+        <v>44.2</v>
       </c>
       <c r="F133" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G133" t="n">
-        <v>14.1</v>
+        <v>32.4</v>
       </c>
       <c r="H133" t="n">
-        <v>5.1</v>
+        <v>9.8</v>
       </c>
       <c r="I133" t="n">
-        <v>43.9</v>
+        <v>50</v>
       </c>
       <c r="J133" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="K133" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="134">
@@ -5892,31 +5899,25 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C134" t="n">
-        <v>35</v>
-      </c>
-      <c r="D134" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E134" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" t="n">
-        <v>13.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
       <c r="G134" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5927,34 +5928,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C135" t="n">
-        <v>72.2</v>
+        <v>74.5</v>
       </c>
       <c r="D135" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="E135" t="n">
-        <v>44.2</v>
+        <v>47.3</v>
       </c>
       <c r="F135" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="G135" t="n">
-        <v>32.4</v>
+        <v>30.8</v>
       </c>
       <c r="H135" t="n">
         <v>9.8</v>
       </c>
       <c r="I135" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="J135" t="n">
-        <v>23.7</v>
+        <v>26.3</v>
       </c>
       <c r="K135" t="n">
-        <v>42.1</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="136">
@@ -5962,28 +5963,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C136" t="n">
-        <v>100</v>
-      </c>
-      <c r="D136"/>
-      <c r="E136"/>
-      <c r="F136"/>
+        <v>48.1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>25</v>
+      </c>
+      <c r="E136" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>25</v>
+      </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="J136" t="n">
-        <v>100</v>
+        <v>22.2</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="137">
@@ -5991,34 +5998,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C137" t="n">
-        <v>74.5</v>
+        <v>66</v>
       </c>
       <c r="D137" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
       <c r="E137" t="n">
-        <v>47.3</v>
+        <v>41.7</v>
       </c>
       <c r="F137" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
       <c r="G137" t="n">
-        <v>30.8</v>
+        <v>21.9</v>
       </c>
       <c r="H137" t="n">
-        <v>9.8</v>
+        <v>7.7</v>
       </c>
       <c r="I137" t="n">
-        <v>47.4</v>
+        <v>54.3</v>
       </c>
       <c r="J137" t="n">
-        <v>26.3</v>
+        <v>15.7</v>
       </c>
       <c r="K137" t="n">
-        <v>39.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="138">
@@ -6026,34 +6033,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C138" t="n">
-        <v>48.1</v>
+        <v>66.7</v>
       </c>
       <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>75</v>
+      </c>
+      <c r="J138" t="n">
         <v>25</v>
       </c>
-      <c r="E138" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F138" t="n">
-        <v>25</v>
-      </c>
-      <c r="G138" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="H138" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I138" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J138" t="n">
-        <v>22.2</v>
-      </c>
       <c r="K138" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -6061,34 +6068,34 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C139" t="n">
-        <v>66</v>
+        <v>72.2</v>
       </c>
       <c r="D139" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="E139" t="n">
-        <v>41.7</v>
+        <v>52.8</v>
       </c>
       <c r="F139" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="G139" t="n">
-        <v>21.9</v>
+        <v>27.4</v>
       </c>
       <c r="H139" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="I139" t="n">
-        <v>54.3</v>
+        <v>69.2</v>
       </c>
       <c r="J139" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>31.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="140">
@@ -6096,25 +6103,25 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C140" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E140" t="n">
-        <v>66.7</v>
+        <v>35.7</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G140" t="n">
-        <v>18.2</v>
+        <v>28.6</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I140" t="n">
         <v>75</v>
@@ -6123,7 +6130,7 @@
         <v>25</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141">
@@ -6131,34 +6138,34 @@
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C141" t="n">
-        <v>72.2</v>
+        <v>68.5</v>
       </c>
       <c r="D141" t="n">
-        <v>19.4</v>
+        <v>29</v>
       </c>
       <c r="E141" t="n">
-        <v>52.8</v>
+        <v>39.5</v>
       </c>
       <c r="F141" t="n">
-        <v>19.4</v>
+        <v>29</v>
       </c>
       <c r="G141" t="n">
-        <v>27.4</v>
+        <v>31.8</v>
       </c>
       <c r="H141" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="I141" t="n">
-        <v>69.2</v>
+        <v>35.9</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="K141" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="142">
@@ -6166,139 +6173,139 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="D142" t="n">
-        <v>14.3</v>
+        <v>24</v>
       </c>
       <c r="E142" t="n">
-        <v>35.7</v>
+        <v>41.8</v>
       </c>
       <c r="F142" t="n">
-        <v>14.3</v>
+        <v>24</v>
       </c>
       <c r="G142" t="n">
-        <v>28.6</v>
+        <v>21.9</v>
       </c>
       <c r="H142" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="I142" t="n">
-        <v>75</v>
+        <v>59.7</v>
       </c>
       <c r="J142" t="n">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="K142" t="n">
-        <v>50</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C143" t="n">
-        <v>68.5</v>
+        <v>56.1</v>
       </c>
       <c r="D143" t="n">
-        <v>29</v>
+        <v>19.2</v>
       </c>
       <c r="E143" t="n">
-        <v>39.5</v>
+        <v>36.9</v>
       </c>
       <c r="F143" t="n">
-        <v>29</v>
+        <v>19.2</v>
       </c>
       <c r="G143" t="n">
-        <v>31.8</v>
+        <v>22.5</v>
       </c>
       <c r="H143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>35.9</v>
+        <v>40.5</v>
       </c>
       <c r="J143" t="n">
-        <v>28.1</v>
+        <v>27</v>
       </c>
       <c r="K143" t="n">
-        <v>43.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C144" t="n">
-        <v>65.8</v>
+        <v>79.6</v>
       </c>
       <c r="D144" t="n">
-        <v>24</v>
+        <v>36.8</v>
       </c>
       <c r="E144" t="n">
-        <v>41.8</v>
+        <v>42.8</v>
       </c>
       <c r="F144" t="n">
-        <v>24</v>
+        <v>36.8</v>
       </c>
       <c r="G144" t="n">
-        <v>21.9</v>
+        <v>34.2</v>
       </c>
       <c r="H144" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="I144" t="n">
-        <v>59.7</v>
+        <v>44</v>
       </c>
       <c r="J144" t="n">
-        <v>23.9</v>
+        <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>30.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C145" t="n">
-        <v>56.1</v>
+        <v>57.8</v>
       </c>
       <c r="D145" t="n">
-        <v>19.2</v>
+        <v>14.1</v>
       </c>
       <c r="E145" t="n">
-        <v>36.9</v>
+        <v>43.7</v>
       </c>
       <c r="F145" t="n">
-        <v>19.2</v>
+        <v>14.1</v>
       </c>
       <c r="G145" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="I145" t="n">
-        <v>40.5</v>
+        <v>52.8</v>
       </c>
       <c r="J145" t="n">
-        <v>27</v>
+        <v>9.7</v>
       </c>
       <c r="K145" t="n">
-        <v>40.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="146">
@@ -6306,34 +6313,34 @@
         <v>161</v>
       </c>
       <c r="B146" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>79.6</v>
+        <v>63.2</v>
       </c>
       <c r="D146" t="n">
-        <v>36.8</v>
+        <v>45</v>
       </c>
       <c r="E146" t="n">
-        <v>42.8</v>
+        <v>18.2</v>
       </c>
       <c r="F146" t="n">
-        <v>36.8</v>
+        <v>45</v>
       </c>
       <c r="G146" t="n">
-        <v>34.2</v>
+        <v>26.9</v>
       </c>
       <c r="H146" t="n">
-        <v>2.9</v>
+        <v>7.7</v>
       </c>
       <c r="I146" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K146" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147">
@@ -6341,34 +6348,34 @@
         <v>162</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C147" t="n">
-        <v>57.8</v>
+        <v>74.2</v>
       </c>
       <c r="D147" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="E147" t="n">
-        <v>43.7</v>
+        <v>62.1</v>
       </c>
       <c r="F147" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="G147" t="n">
-        <v>12.5</v>
+        <v>23.4</v>
       </c>
       <c r="H147" t="n">
-        <v>10.2</v>
+        <v>14.8</v>
       </c>
       <c r="I147" t="n">
-        <v>52.8</v>
+        <v>32.9</v>
       </c>
       <c r="J147" t="n">
-        <v>9.7</v>
+        <v>37</v>
       </c>
       <c r="K147" t="n">
-        <v>35.7</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="148">
@@ -6376,34 +6383,34 @@
         <v>163</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C148" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="D148" t="n">
-        <v>45</v>
+        <v>26.1</v>
       </c>
       <c r="E148" t="n">
-        <v>18.2</v>
+        <v>48.1</v>
       </c>
       <c r="F148" t="n">
-        <v>45</v>
+        <v>26.1</v>
       </c>
       <c r="G148" t="n">
-        <v>26.9</v>
+        <v>9.2</v>
       </c>
       <c r="H148" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="J148" t="n">
-        <v>25</v>
+        <v>20.8</v>
       </c>
       <c r="K148" t="n">
-        <v>25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="149">
@@ -6411,104 +6418,104 @@
         <v>164</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C149" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="D149" t="n">
-        <v>12.1</v>
+        <v>20.5</v>
       </c>
       <c r="E149" t="n">
-        <v>62.1</v>
+        <v>50</v>
       </c>
       <c r="F149" t="n">
-        <v>12.1</v>
+        <v>20.5</v>
       </c>
       <c r="G149" t="n">
-        <v>23.4</v>
+        <v>37.7</v>
       </c>
       <c r="H149" t="n">
-        <v>14.8</v>
+        <v>9.2</v>
       </c>
       <c r="I149" t="n">
-        <v>32.9</v>
+        <v>51.9</v>
       </c>
       <c r="J149" t="n">
-        <v>37</v>
+        <v>21.2</v>
       </c>
       <c r="K149" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
+        <v>166</v>
+      </c>
+      <c r="B150" t="s">
         <v>165</v>
       </c>
-      <c r="B150" t="s">
-        <v>147</v>
-      </c>
       <c r="C150" t="n">
-        <v>74.2</v>
+        <v>68.6</v>
       </c>
       <c r="D150" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="E150" t="n">
         <v>48.1</v>
       </c>
       <c r="F150" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="G150" t="n">
-        <v>9.2</v>
+        <v>14.9</v>
       </c>
       <c r="H150" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="I150" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
       <c r="J150" t="n">
-        <v>20.8</v>
+        <v>18.7</v>
       </c>
       <c r="K150" t="n">
-        <v>32.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C151" t="n">
-        <v>70.5</v>
+        <v>64.6</v>
       </c>
       <c r="D151" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E151" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="F151" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="G151" t="n">
         <v>37.7</v>
       </c>
       <c r="H151" t="n">
-        <v>9.2</v>
+        <v>12.5</v>
       </c>
       <c r="I151" t="n">
-        <v>51.9</v>
+        <v>29.6</v>
       </c>
       <c r="J151" t="n">
-        <v>21.2</v>
+        <v>48.1</v>
       </c>
       <c r="K151" t="n">
-        <v>39.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="152">
@@ -6516,34 +6523,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C152" t="n">
-        <v>68.6</v>
+        <v>60</v>
       </c>
       <c r="D152" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="E152" t="n">
-        <v>48.1</v>
+        <v>38.9</v>
       </c>
       <c r="F152" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="G152" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="H152" t="n">
         <v>14.9</v>
       </c>
-      <c r="H152" t="n">
-        <v>6.6</v>
-      </c>
       <c r="I152" t="n">
-        <v>57.3</v>
+        <v>34.8</v>
       </c>
       <c r="J152" t="n">
-        <v>18.7</v>
+        <v>30.4</v>
       </c>
       <c r="K152" t="n">
-        <v>45.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="153">
@@ -6551,34 +6558,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C153" t="n">
-        <v>64.6</v>
+        <v>66.3</v>
       </c>
       <c r="D153" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E153" t="n">
-        <v>47.9</v>
+        <v>51.9</v>
       </c>
       <c r="F153" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="G153" t="n">
-        <v>37.7</v>
+        <v>9</v>
       </c>
       <c r="H153" t="n">
-        <v>12.5</v>
+        <v>18.2</v>
       </c>
       <c r="I153" t="n">
-        <v>29.6</v>
+        <v>62.2</v>
       </c>
       <c r="J153" t="n">
-        <v>48.1</v>
+        <v>17.3</v>
       </c>
       <c r="K153" t="n">
-        <v>38.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="154">
@@ -6586,34 +6593,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C154" t="n">
-        <v>60</v>
+        <v>80.4</v>
       </c>
       <c r="D154" t="n">
-        <v>21.1</v>
+        <v>16.5</v>
       </c>
       <c r="E154" t="n">
-        <v>38.9</v>
+        <v>63.9</v>
       </c>
       <c r="F154" t="n">
-        <v>21.1</v>
+        <v>16.5</v>
       </c>
       <c r="G154" t="n">
-        <v>32.4</v>
+        <v>23.3</v>
       </c>
       <c r="H154" t="n">
-        <v>14.9</v>
+        <v>9.4</v>
       </c>
       <c r="I154" t="n">
-        <v>34.8</v>
+        <v>36.2</v>
       </c>
       <c r="J154" t="n">
-        <v>30.4</v>
+        <v>34</v>
       </c>
       <c r="K154" t="n">
-        <v>33.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="155">
@@ -6621,34 +6628,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C155" t="n">
-        <v>66.3</v>
+        <v>55.6</v>
       </c>
       <c r="D155" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="E155" t="n">
-        <v>51.9</v>
+        <v>38</v>
       </c>
       <c r="F155" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="G155" t="n">
-        <v>9</v>
+        <v>25.7</v>
       </c>
       <c r="H155" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="I155" t="n">
-        <v>62.2</v>
+        <v>47.4</v>
       </c>
       <c r="J155" t="n">
-        <v>17.3</v>
+        <v>22.8</v>
       </c>
       <c r="K155" t="n">
-        <v>36.2</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="156">
@@ -6656,34 +6663,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C156" t="n">
-        <v>80.4</v>
+        <v>75</v>
       </c>
       <c r="D156" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>63.9</v>
+        <v>75</v>
       </c>
       <c r="F156" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>23.3</v>
+        <v>66.7</v>
       </c>
       <c r="H156" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>44.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6691,34 +6698,34 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C157" t="n">
-        <v>55.6</v>
+        <v>56.2</v>
       </c>
       <c r="D157" t="n">
         <v>17.6</v>
       </c>
       <c r="E157" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="F157" t="n">
         <v>17.6</v>
       </c>
       <c r="G157" t="n">
-        <v>25.7</v>
+        <v>14.6</v>
       </c>
       <c r="H157" t="n">
-        <v>12.6</v>
+        <v>16.5</v>
       </c>
       <c r="I157" t="n">
-        <v>47.4</v>
+        <v>37</v>
       </c>
       <c r="J157" t="n">
-        <v>22.8</v>
+        <v>28.8</v>
       </c>
       <c r="K157" t="n">
-        <v>26.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="158">
@@ -6726,34 +6733,34 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C158" t="n">
-        <v>75</v>
+        <v>61.4</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="E158" t="n">
-        <v>75</v>
+        <v>40.6</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="G158" t="n">
-        <v>66.7</v>
+        <v>9.8</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>60.4</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="159">
@@ -6761,34 +6768,34 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C159" t="n">
-        <v>56.2</v>
+        <v>71.5</v>
       </c>
       <c r="D159" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="E159" t="n">
-        <v>38.6</v>
+        <v>54.8</v>
       </c>
       <c r="F159" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="G159" t="n">
-        <v>14.6</v>
+        <v>24.7</v>
       </c>
       <c r="H159" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="I159" t="n">
-        <v>37</v>
+        <v>34.8</v>
       </c>
       <c r="J159" t="n">
-        <v>28.8</v>
+        <v>31.5</v>
       </c>
       <c r="K159" t="n">
-        <v>49.3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160">
@@ -6796,34 +6803,34 @@
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C160" t="n">
-        <v>61.4</v>
+        <v>77.2</v>
       </c>
       <c r="D160" t="n">
-        <v>20.8</v>
+        <v>29.9</v>
       </c>
       <c r="E160" t="n">
-        <v>40.6</v>
+        <v>47.3</v>
       </c>
       <c r="F160" t="n">
-        <v>20.8</v>
+        <v>29.9</v>
       </c>
       <c r="G160" t="n">
-        <v>9.8</v>
+        <v>41.7</v>
       </c>
       <c r="H160" t="n">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="I160" t="n">
-        <v>60.4</v>
+        <v>44.4</v>
       </c>
       <c r="J160" t="n">
-        <v>18</v>
+        <v>22.2</v>
       </c>
       <c r="K160" t="n">
-        <v>29.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="161">
@@ -6831,34 +6838,34 @@
         <v>177</v>
       </c>
       <c r="B161" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C161" t="n">
-        <v>71.5</v>
+        <v>75.5</v>
       </c>
       <c r="D161" t="n">
-        <v>16.7</v>
+        <v>20.4</v>
       </c>
       <c r="E161" t="n">
-        <v>54.8</v>
+        <v>55.1</v>
       </c>
       <c r="F161" t="n">
-        <v>16.7</v>
+        <v>20.4</v>
       </c>
       <c r="G161" t="n">
-        <v>24.7</v>
+        <v>19.7</v>
       </c>
       <c r="H161" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="I161" t="n">
-        <v>34.8</v>
+        <v>27.9</v>
       </c>
       <c r="J161" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="K161" t="n">
-        <v>56</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="162">
@@ -6866,160 +6873,90 @@
         <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C162" t="n">
-        <v>77.2</v>
+        <v>37.5</v>
       </c>
       <c r="D162" t="n">
-        <v>29.9</v>
+        <v>33.3</v>
       </c>
       <c r="E162" t="n">
-        <v>47.3</v>
+        <v>4.2</v>
       </c>
       <c r="F162" t="n">
-        <v>29.9</v>
+        <v>33.3</v>
       </c>
       <c r="G162" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I162" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J162" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K162" t="n">
-        <v>66.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
     </row>
     <row r="163">
       <c r="A163" t="s">
         <v>179</v>
       </c>
       <c r="B163" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C163" t="n">
-        <v>75.5</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="E163" t="n">
-        <v>55.1</v>
+        <v>-33.3</v>
       </c>
       <c r="F163" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="G163" t="n">
-        <v>19.7</v>
+        <v>100</v>
       </c>
       <c r="H163" t="n">
-        <v>11</v>
-      </c>
-      <c r="I163" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J163" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K163" t="n">
-        <v>46.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="K163"/>
     </row>
     <row r="164">
-      <c r="A164" t="s">
+      <c r="A164"/>
+      <c r="B164" t="s">
         <v>180</v>
       </c>
-      <c r="B164" t="s">
-        <v>167</v>
-      </c>
       <c r="C164" t="n">
-        <v>37.5</v>
+        <v>68</v>
       </c>
       <c r="D164" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="E164" t="n">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="F164" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164"/>
-      <c r="J164"/>
-      <c r="K164"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>181</v>
-      </c>
-      <c r="B165" t="s">
-        <v>167</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E165" t="n">
-        <v>-33.3</v>
-      </c>
-      <c r="F165" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G165" t="n">
-        <v>100</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165"/>
-      <c r="J165"/>
-      <c r="K165"/>
-    </row>
-    <row r="166">
-      <c r="A166"/>
-      <c r="B166" t="s">
-        <v>182</v>
-      </c>
-      <c r="C166" t="n">
-        <v>68.1</v>
-      </c>
-      <c r="D166" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E166" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="F166" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G166" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H166" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I166" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="J166" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K166" t="n">
-        <v>39.4</v>
+        <v>9.5</v>
+      </c>
+      <c r="I164" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K164" t="n">
+        <v>39.3</v>
       </c>
     </row>
   </sheetData>
@@ -7051,22 +6988,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7075,18 +7012,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7121,7 +7058,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7156,7 +7093,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7226,7 +7163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7261,7 +7198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7296,7 +7233,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7331,7 +7268,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7366,7 +7303,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -7436,7 +7373,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7471,7 +7408,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7506,7 +7443,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7541,7 +7478,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -7576,7 +7513,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -7644,7 +7581,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -7679,7 +7616,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -7714,7 +7651,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
@@ -7784,7 +7721,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
@@ -7819,7 +7756,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -7854,7 +7791,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -7889,7 +7826,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -7924,7 +7861,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
@@ -7959,7 +7896,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -7994,7 +7931,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -8029,7 +7966,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
@@ -8064,7 +8001,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -8099,7 +8036,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -8134,7 +8071,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -8169,7 +8106,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -8204,10 +8141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="n">
         <v>78.6</v>
@@ -8239,10 +8176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" t="n">
         <v>52.5</v>
@@ -8274,10 +8211,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="n">
         <v>45.8</v>
@@ -8309,10 +8246,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" t="n">
         <v>52.9</v>
@@ -8344,10 +8281,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" t="n">
         <v>47.8</v>
@@ -8379,10 +8316,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="n">
         <v>48.8</v>
@@ -8414,10 +8351,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" t="n">
         <v>59</v>
@@ -8449,10 +8386,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" t="n">
         <v>54.8</v>
@@ -8484,10 +8421,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" t="n">
         <v>100</v>
@@ -8517,10 +8454,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
         <v>66.3</v>
@@ -8552,10 +8489,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" t="n">
         <v>57</v>
@@ -8587,10 +8524,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" t="n">
         <v>60.4</v>
@@ -8622,10 +8559,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="n">
         <v>55.4</v>
@@ -8657,10 +8594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" t="n">
         <v>81.2</v>
@@ -8692,10 +8629,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" t="n">
         <v>58</v>
@@ -8727,10 +8664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
         <v>44.4</v>
@@ -8760,10 +8697,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
         <v>51.8</v>
@@ -8795,10 +8732,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" t="n">
         <v>60</v>
@@ -8830,10 +8767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" t="n">
         <v>70.9</v>
@@ -8865,10 +8802,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" t="n">
         <v>60.6</v>
@@ -8900,10 +8837,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
         <v>66.7</v>
@@ -8933,10 +8870,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C55" t="n">
         <v>77.8</v>
@@ -8968,10 +8905,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
         <v>65.6</v>
@@ -9003,10 +8940,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
         <v>57.3</v>
@@ -9038,10 +8975,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
         <v>67.6</v>
@@ -9073,10 +9010,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
         <v>61.1</v>
@@ -9108,10 +9045,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
         <v>62</v>
@@ -9143,10 +9080,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
         <v>56.5</v>
@@ -9178,10 +9115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
         <v>65.7</v>
@@ -9213,10 +9150,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
         <v>62.3</v>
@@ -9248,10 +9185,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
         <v>30</v>
@@ -9283,10 +9220,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
         <v>44.4</v>
@@ -9318,10 +9255,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
         <v>62.5</v>
@@ -9353,10 +9290,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C67" t="n">
         <v>72.4</v>
@@ -9388,10 +9325,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C68" t="n">
         <v>66.7</v>
@@ -9423,10 +9360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C69" t="n">
         <v>50</v>
@@ -9458,10 +9395,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C70" t="n">
         <v>55.6</v>
@@ -9493,10 +9430,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C71" t="n">
         <v>54.8</v>
@@ -9528,10 +9465,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C72" t="n">
         <v>61.1</v>
@@ -9563,10 +9500,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73" t="n">
         <v>63.8</v>
@@ -9598,10 +9535,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" t="n">
         <v>51.6</v>
@@ -9633,10 +9570,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C75" t="n">
         <v>58.8</v>
@@ -9668,10 +9605,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C76" t="n">
         <v>69.4</v>
@@ -9703,10 +9640,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77" t="n">
         <v>60.3</v>
@@ -9738,10 +9675,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C78" t="n">
         <v>61.5</v>
@@ -9773,10 +9710,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C79" t="n">
         <v>42</v>
@@ -9808,10 +9745,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" t="n">
         <v>64.6</v>
@@ -9843,10 +9780,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" t="n">
         <v>50</v>
@@ -9878,10 +9815,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C82" t="n">
         <v>28.6</v>
@@ -9911,10 +9848,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C83" t="n">
         <v>63.6</v>
@@ -9946,10 +9883,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84" t="n">
         <v>48.6</v>
@@ -9981,10 +9918,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" t="n">
         <v>57.6</v>
@@ -10016,1780 +9953,1745 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C86" t="n">
-        <v>71.4</v>
+        <v>61.6</v>
       </c>
       <c r="D86" t="n">
-        <v>70.6</v>
+        <v>66.2</v>
       </c>
       <c r="E86" t="n">
-        <v>22.2</v>
+        <v>26.6</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6</v>
+        <v>37.4</v>
       </c>
       <c r="G86" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="H86" t="n">
-        <v>45.5</v>
+        <v>44.6</v>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J86" t="n">
-        <v>10.7</v>
+        <v>21.4</v>
       </c>
       <c r="K86" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C87" t="n">
-        <v>61</v>
+        <v>45.8</v>
       </c>
       <c r="D87" t="n">
-        <v>65.9</v>
+        <v>55.1</v>
       </c>
       <c r="E87" t="n">
-        <v>27</v>
+        <v>10.4</v>
       </c>
       <c r="F87" t="n">
-        <v>38</v>
+        <v>26.3</v>
       </c>
       <c r="G87" t="n">
-        <v>5.6</v>
+        <v>15.3</v>
       </c>
       <c r="H87" t="n">
-        <v>44.5</v>
+        <v>47.1</v>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
-        <v>22.2</v>
+        <v>33.9</v>
       </c>
       <c r="K87" t="n">
-        <v>10.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C88" t="n">
-        <v>45.8</v>
+        <v>67.3</v>
       </c>
       <c r="D88" t="n">
-        <v>55.1</v>
+        <v>65.4</v>
       </c>
       <c r="E88" t="n">
-        <v>10.4</v>
+        <v>27.7</v>
       </c>
       <c r="F88" t="n">
-        <v>26.3</v>
+        <v>39.3</v>
       </c>
       <c r="G88" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="H88" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="I88" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
-        <v>33.9</v>
+        <v>29</v>
       </c>
       <c r="K88" t="n">
-        <v>1.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" t="n">
-        <v>67.3</v>
+        <v>59.3</v>
       </c>
       <c r="D89" t="n">
-        <v>65.4</v>
+        <v>61.4</v>
       </c>
       <c r="E89" t="n">
-        <v>27.7</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>39.3</v>
+        <v>35</v>
       </c>
       <c r="G89" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="H89" t="n">
-        <v>46.7</v>
+        <v>56.4</v>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="K89" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C90" t="n">
-        <v>59.3</v>
+        <v>52.6</v>
       </c>
       <c r="D90" t="n">
-        <v>61.4</v>
+        <v>55.6</v>
       </c>
       <c r="E90" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="F90" t="n">
-        <v>35</v>
+        <v>38.5</v>
       </c>
       <c r="G90" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="H90" t="n">
-        <v>56.4</v>
+        <v>30</v>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J90" t="n">
-        <v>28.2</v>
+        <v>24.9</v>
       </c>
       <c r="K90" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C91" t="n">
-        <v>52.6</v>
+        <v>57.9</v>
       </c>
       <c r="D91" t="n">
-        <v>55.6</v>
+        <v>61.6</v>
       </c>
       <c r="E91" t="n">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="F91" t="n">
-        <v>38.5</v>
+        <v>39.4</v>
       </c>
       <c r="G91" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="H91" t="n">
-        <v>30</v>
+        <v>51.2</v>
       </c>
       <c r="I91" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J91" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="K91" t="n">
-        <v>3.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C92" t="n">
-        <v>57.9</v>
+        <v>74.2</v>
       </c>
       <c r="D92" t="n">
-        <v>61.6</v>
+        <v>69.7</v>
       </c>
       <c r="E92" t="n">
-        <v>21.3</v>
+        <v>39.1</v>
       </c>
       <c r="F92" t="n">
-        <v>39.4</v>
+        <v>33.3</v>
       </c>
       <c r="G92" t="n">
-        <v>7.6</v>
+        <v>9.7</v>
       </c>
       <c r="H92" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>24.8</v>
+        <v>22.9</v>
       </c>
       <c r="K92" t="n">
-        <v>14.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C93" t="n">
-        <v>74.2</v>
+        <v>64.4</v>
       </c>
       <c r="D93" t="n">
-        <v>69.7</v>
+        <v>57.5</v>
       </c>
       <c r="E93" t="n">
-        <v>39.1</v>
+        <v>17.9</v>
       </c>
       <c r="F93" t="n">
-        <v>33.3</v>
+        <v>41.9</v>
       </c>
       <c r="G93" t="n">
-        <v>9.7</v>
+        <v>15.3</v>
       </c>
       <c r="H93" t="n">
-        <v>52.2</v>
+        <v>40.5</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
-        <v>22.9</v>
+        <v>27.2</v>
       </c>
       <c r="K93" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B94" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C94" t="n">
-        <v>64.4</v>
+        <v>57.5</v>
       </c>
       <c r="D94" t="n">
-        <v>57.5</v>
+        <v>63.9</v>
       </c>
       <c r="E94" t="n">
-        <v>17.9</v>
+        <v>26.6</v>
       </c>
       <c r="F94" t="n">
-        <v>41.9</v>
+        <v>36.8</v>
       </c>
       <c r="G94" t="n">
-        <v>15.3</v>
+        <v>7.4</v>
       </c>
       <c r="H94" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
-        <v>27.2</v>
+        <v>22.5</v>
       </c>
       <c r="K94" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B95" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C95" t="n">
-        <v>57.5</v>
+        <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>63.9</v>
+        <v>68.6</v>
       </c>
       <c r="E95" t="n">
-        <v>26.6</v>
+        <v>21.4</v>
       </c>
       <c r="F95" t="n">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="G95" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="K95" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C96" t="n">
-        <v>80</v>
+        <v>62.1</v>
       </c>
       <c r="D96" t="n">
-        <v>68.6</v>
+        <v>64.9</v>
       </c>
       <c r="E96" t="n">
-        <v>21.4</v>
+        <v>29.3</v>
       </c>
       <c r="F96" t="n">
-        <v>25</v>
+        <v>52.2</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H96" t="n">
-        <v>25</v>
+        <v>63.5</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
-        <v>15</v>
+        <v>33.1</v>
       </c>
       <c r="K96" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C97" t="n">
-        <v>62.1</v>
+        <v>62.7</v>
       </c>
       <c r="D97" t="n">
-        <v>64.9</v>
+        <v>65.6</v>
       </c>
       <c r="E97" t="n">
-        <v>29.3</v>
+        <v>32.5</v>
       </c>
       <c r="F97" t="n">
-        <v>52.2</v>
+        <v>58.6</v>
       </c>
       <c r="G97" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="H97" t="n">
-        <v>63.5</v>
+        <v>55.6</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="K97" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B98" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C98" t="n">
-        <v>62.7</v>
+        <v>74.3</v>
       </c>
       <c r="D98" t="n">
-        <v>65.6</v>
+        <v>71.8</v>
       </c>
       <c r="E98" t="n">
-        <v>32.5</v>
+        <v>28.1</v>
       </c>
       <c r="F98" t="n">
-        <v>58.6</v>
+        <v>42.9</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="H98" t="n">
-        <v>55.6</v>
+        <v>73.1</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
-        <v>33</v>
+        <v>24.6</v>
       </c>
       <c r="K98" t="n">
-        <v>20.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B99" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C99" t="n">
-        <v>74.3</v>
+        <v>60.6</v>
       </c>
       <c r="D99" t="n">
-        <v>71.8</v>
+        <v>64.6</v>
       </c>
       <c r="E99" t="n">
-        <v>28.1</v>
+        <v>21.7</v>
       </c>
       <c r="F99" t="n">
-        <v>42.9</v>
+        <v>26.5</v>
       </c>
       <c r="G99" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H99" t="n">
-        <v>73.1</v>
+        <v>67.9</v>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="K99" t="n">
-        <v>11.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B100" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C100" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D100" t="n">
-        <v>64.6</v>
+        <v>67.5</v>
       </c>
       <c r="E100" t="n">
-        <v>21.7</v>
+        <v>31</v>
       </c>
       <c r="F100" t="n">
-        <v>26.5</v>
+        <v>54.5</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="H100" t="n">
-        <v>67.9</v>
+        <v>42.3</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J100" t="n">
-        <v>19.3</v>
+        <v>37.3</v>
       </c>
       <c r="K100" t="n">
-        <v>7.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B101" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C101" t="n">
-        <v>66.7</v>
+        <v>65.8</v>
       </c>
       <c r="D101" t="n">
-        <v>67.5</v>
+        <v>65.6</v>
       </c>
       <c r="E101" t="n">
-        <v>31</v>
+        <v>23.1</v>
       </c>
       <c r="F101" t="n">
-        <v>54.5</v>
+        <v>37.2</v>
       </c>
       <c r="G101" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="n">
-        <v>42.3</v>
+        <v>41.3</v>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>37.3</v>
+        <v>21.5</v>
       </c>
       <c r="K101" t="n">
-        <v>19.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B102" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C102" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="D102" t="n">
-        <v>65.6</v>
+        <v>68.8</v>
       </c>
       <c r="E102" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="F102" t="n">
-        <v>37.2</v>
+        <v>46.5</v>
       </c>
       <c r="G102" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="H102" t="n">
-        <v>41.3</v>
+        <v>42.3</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="K102" t="n">
-        <v>6.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B103" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C103" t="n">
-        <v>66.2</v>
+        <v>64.4</v>
       </c>
       <c r="D103" t="n">
-        <v>68.8</v>
+        <v>61.4</v>
       </c>
       <c r="E103" t="n">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="F103" t="n">
-        <v>46.5</v>
+        <v>58</v>
       </c>
       <c r="G103" t="n">
-        <v>1.9</v>
+        <v>16.4</v>
       </c>
       <c r="H103" t="n">
-        <v>42.3</v>
+        <v>32.3</v>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
-        <v>21.9</v>
+        <v>36.4</v>
       </c>
       <c r="K103" t="n">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C104" t="n">
-        <v>64.4</v>
+        <v>33.3</v>
       </c>
       <c r="D104" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E104" t="n">
-        <v>13.4</v>
+        <v>36.4</v>
       </c>
       <c r="F104" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="H104" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>33.3</v>
       </c>
       <c r="J104" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>23.3</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C105" t="n">
-        <v>33.3</v>
+        <v>58.8</v>
       </c>
       <c r="D105" t="n">
-        <v>56.2</v>
+        <v>59.6</v>
       </c>
       <c r="E105" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G105" t="n">
-        <v>33.3</v>
+        <v>13.7</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="I105" t="n">
-        <v>33.3</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="K105" t="n">
-        <v>-33.3</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="B106" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C106" t="n">
-        <v>58.8</v>
+        <v>51.6</v>
       </c>
       <c r="D106" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="E106" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F106" t="n">
-        <v>14.3</v>
+        <v>40.9</v>
       </c>
       <c r="G106" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="H106" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J106" t="n">
-        <v>14.5</v>
+        <v>24.4</v>
       </c>
       <c r="K106" t="n">
-        <v>-7.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>146</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C107" t="n">
-        <v>51.6</v>
+        <v>62</v>
       </c>
       <c r="D107" t="n">
-        <v>58.9</v>
+        <v>65.2</v>
       </c>
       <c r="E107" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="F107" t="n">
-        <v>40.9</v>
+        <v>35.7</v>
       </c>
       <c r="G107" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="H107" t="n">
-        <v>44.4</v>
+        <v>37.7</v>
       </c>
       <c r="I107" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J107" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K107" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B108" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C108" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D108" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="E108" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F108" t="n">
-        <v>35.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F108"/>
       <c r="G108" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
       <c r="H108" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>5.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B109" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C109" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="D109" t="n">
-        <v>45.5</v>
+        <v>62.4</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109"/>
+        <v>23.5</v>
+      </c>
+      <c r="F109" t="n">
+        <v>30.5</v>
+      </c>
       <c r="G109" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>49.4</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="K109" t="n">
-        <v>-25</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C110" t="n">
-        <v>65.8</v>
+        <v>51</v>
       </c>
       <c r="D110" t="n">
-        <v>62.4</v>
+        <v>58.9</v>
       </c>
       <c r="E110" t="n">
-        <v>23.5</v>
+        <v>13.2</v>
       </c>
       <c r="F110" t="n">
-        <v>30.5</v>
+        <v>25</v>
       </c>
       <c r="G110" t="n">
-        <v>12.9</v>
+        <v>6.4</v>
       </c>
       <c r="H110" t="n">
-        <v>49.4</v>
+        <v>41.7</v>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J110" t="n">
-        <v>25.9</v>
+        <v>19.2</v>
       </c>
       <c r="K110" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>282</v>
+        <v>156</v>
       </c>
       <c r="B111" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C111" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="D111" t="n">
-        <v>58.9</v>
+        <v>59.9</v>
       </c>
       <c r="E111" t="n">
-        <v>13.2</v>
+        <v>30.4</v>
       </c>
       <c r="F111" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="G111" t="n">
-        <v>6.4</v>
+        <v>13.4</v>
       </c>
       <c r="H111" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="I111" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="J111" t="n">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="K111" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="B112" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C112" t="n">
-        <v>51.5</v>
+        <v>63.3</v>
       </c>
       <c r="D112" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="E112" t="n">
-        <v>30.4</v>
+        <v>20.5</v>
       </c>
       <c r="F112" t="n">
-        <v>42.9</v>
+        <v>34.6</v>
       </c>
       <c r="G112" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="H112" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="I112" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
-        <v>28</v>
+        <v>22.8</v>
       </c>
       <c r="K112" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C113" t="n">
-        <v>63.3</v>
+        <v>52.6</v>
       </c>
       <c r="D113" t="n">
-        <v>60.1</v>
+        <v>56.2</v>
       </c>
       <c r="E113" t="n">
-        <v>20.5</v>
+        <v>30</v>
       </c>
       <c r="F113" t="n">
-        <v>34.6</v>
+        <v>10</v>
       </c>
       <c r="G113" t="n">
         <v>16.7</v>
       </c>
       <c r="H113" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="I113" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J113" t="n">
-        <v>22.8</v>
+        <v>15.2</v>
       </c>
       <c r="K113" t="n">
-        <v>2.1</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C114" t="n">
-        <v>52.6</v>
+        <v>65.9</v>
       </c>
       <c r="D114" t="n">
-        <v>56.2</v>
+        <v>64.2</v>
       </c>
       <c r="E114" t="n">
-        <v>30</v>
+        <v>20.5</v>
       </c>
       <c r="F114" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="G114" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="H114" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="I114" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
-        <v>15.2</v>
+        <v>28.1</v>
       </c>
       <c r="K114" t="n">
-        <v>-11.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C115" t="n">
-        <v>65.9</v>
+        <v>60</v>
       </c>
       <c r="D115" t="n">
-        <v>64.2</v>
+        <v>61.5</v>
       </c>
       <c r="E115" t="n">
-        <v>20.5</v>
+        <v>18.9</v>
       </c>
       <c r="F115" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G115" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H115" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>28.1</v>
+        <v>35.6</v>
       </c>
       <c r="K115" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B116" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C116" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D116" t="n">
-        <v>61.5</v>
+        <v>56.3</v>
       </c>
       <c r="E116" t="n">
-        <v>18.9</v>
+        <v>23.1</v>
       </c>
       <c r="F116" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="G116" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H116" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J116" t="n">
-        <v>35.6</v>
+        <v>26.5</v>
       </c>
       <c r="K116" t="n">
-        <v>15.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C117" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="D117" t="n">
-        <v>56.3</v>
+        <v>52</v>
       </c>
       <c r="E117" t="n">
-        <v>23.1</v>
+        <v>16.3</v>
       </c>
       <c r="F117" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G117" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H117" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J117" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="K117" t="n">
-        <v>12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C118" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="D118" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="E118" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="F118" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G118" t="n">
-        <v>27.8</v>
+        <v>30</v>
       </c>
       <c r="H118" t="n">
-        <v>22.2</v>
+        <v>60</v>
       </c>
       <c r="I118" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
       <c r="K118" t="n">
-        <v>-11.1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B119" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C119" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D119" t="n">
-        <v>48.8</v>
+        <v>61.8</v>
       </c>
       <c r="E119" t="n">
-        <v>13.6</v>
+        <v>19.7</v>
       </c>
       <c r="F119" t="n">
-        <v>50</v>
+        <v>29.1</v>
       </c>
       <c r="G119" t="n">
-        <v>30</v>
+        <v>7.7</v>
       </c>
       <c r="H119" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
       <c r="K119" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B120" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C120" t="n">
-        <v>57.7</v>
+        <v>58</v>
       </c>
       <c r="D120" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="E120" t="n">
-        <v>19.7</v>
+        <v>24.1</v>
       </c>
       <c r="F120" t="n">
-        <v>29.1</v>
+        <v>32.9</v>
       </c>
       <c r="G120" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="H120" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I120" t="n">
         <v>7.7</v>
       </c>
-      <c r="H120" t="n">
-        <v>57</v>
-      </c>
-      <c r="I120" t="n">
-        <v>2.7</v>
-      </c>
       <c r="J120" t="n">
-        <v>21.6</v>
+        <v>18.6</v>
       </c>
       <c r="K120" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C121" t="n">
-        <v>58</v>
+        <v>70.1</v>
       </c>
       <c r="D121" t="n">
-        <v>58.3</v>
+        <v>66.4</v>
       </c>
       <c r="E121" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="F121" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="G121" t="n">
-        <v>8.7</v>
+        <v>5.4</v>
       </c>
       <c r="H121" t="n">
-        <v>43.1</v>
+        <v>52.7</v>
       </c>
       <c r="I121" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="K121" t="n">
-        <v>3.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B122" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C122" t="n">
-        <v>70.1</v>
+        <v>61.6</v>
       </c>
       <c r="D122" t="n">
-        <v>66.4</v>
+        <v>65.8</v>
       </c>
       <c r="E122" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="F122" t="n">
-        <v>42.9</v>
+        <v>41.8</v>
       </c>
       <c r="G122" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="H122" t="n">
-        <v>52.7</v>
+        <v>47.1</v>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
-        <v>22.3</v>
+        <v>20.1</v>
       </c>
       <c r="K122" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B123" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C123" t="n">
-        <v>61.6</v>
+        <v>60.7</v>
       </c>
       <c r="D123" t="n">
-        <v>65.8</v>
+        <v>64.8</v>
       </c>
       <c r="E123" t="n">
-        <v>20.2</v>
+        <v>11.2</v>
       </c>
       <c r="F123" t="n">
-        <v>41.8</v>
+        <v>32.4</v>
       </c>
       <c r="G123" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="H123" t="n">
-        <v>47.1</v>
+        <v>29.6</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J123" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="K123" t="n">
-        <v>13.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B124" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C124" t="n">
-        <v>60.7</v>
+        <v>58.2</v>
       </c>
       <c r="D124" t="n">
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E124" t="n">
-        <v>11.2</v>
+        <v>27.7</v>
       </c>
       <c r="F124" t="n">
-        <v>32.4</v>
+        <v>65.9</v>
       </c>
       <c r="G124" t="n">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
       <c r="H124" t="n">
-        <v>29.6</v>
+        <v>42.3</v>
       </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J124" t="n">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="K124" t="n">
-        <v>5.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="B125" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C125" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="D125" t="n">
-        <v>62.1</v>
+        <v>58.7</v>
       </c>
       <c r="E125" t="n">
-        <v>27.7</v>
+        <v>12.8</v>
       </c>
       <c r="F125" t="n">
-        <v>65.9</v>
+        <v>34.1</v>
       </c>
       <c r="G125" t="n">
         <v>11.1</v>
       </c>
       <c r="H125" t="n">
-        <v>42.3</v>
+        <v>35.5</v>
       </c>
       <c r="I125" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J125" t="n">
-        <v>37</v>
+        <v>23.9</v>
       </c>
       <c r="K125" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="B126" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C126" t="n">
-        <v>59.3</v>
+        <v>73.6</v>
       </c>
       <c r="D126" t="n">
-        <v>58.7</v>
+        <v>64.6</v>
       </c>
       <c r="E126" t="n">
-        <v>12.8</v>
+        <v>31</v>
       </c>
       <c r="F126" t="n">
-        <v>34.1</v>
+        <v>56.9</v>
       </c>
       <c r="G126" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="H126" t="n">
-        <v>35.5</v>
+        <v>44.1</v>
       </c>
       <c r="I126" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
-        <v>23.9</v>
+        <v>49.6</v>
       </c>
       <c r="K126" t="n">
-        <v>5.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B127" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C127" t="n">
-        <v>73.6</v>
+        <v>78.6</v>
       </c>
       <c r="D127" t="n">
-        <v>64.6</v>
-      </c>
-      <c r="E127" t="n">
-        <v>31</v>
-      </c>
+        <v>72.9</v>
+      </c>
+      <c r="E127"/>
       <c r="F127" t="n">
-        <v>56.9</v>
+        <v>45.5</v>
       </c>
       <c r="G127" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>44.1</v>
+        <v>46.5</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J127" t="n">
-        <v>49.6</v>
+        <v>26.7</v>
       </c>
       <c r="K127" t="n">
-        <v>34.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B128" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C128" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D128" t="n">
-        <v>72.9</v>
-      </c>
-      <c r="E128"/>
+        <v>45.1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
       <c r="F128" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H128" t="n">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="I128" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J128" t="n">
-        <v>26.7</v>
+        <v>31.2</v>
       </c>
       <c r="K128" t="n">
-        <v>18.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B129" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C129" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F129" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H129" t="n">
         <v>50</v>
       </c>
-      <c r="D129" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>25</v>
-      </c>
-      <c r="G129" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H129" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I129" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J129" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="K129" t="n">
-        <v>-23.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B130" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C130" t="n">
-        <v>61.3</v>
+        <v>65.8</v>
       </c>
       <c r="D130" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E130" t="n">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="F130" t="n">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="G130" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H130" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I130" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="K130" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B131" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C131" t="n">
-        <v>65.8</v>
+        <v>50.9</v>
       </c>
       <c r="D131" t="n">
-        <v>67.5</v>
+        <v>60.7</v>
       </c>
       <c r="E131" t="n">
-        <v>36.4</v>
+        <v>24.6</v>
       </c>
       <c r="F131" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G131" t="n">
-        <v>7.9</v>
+        <v>9.7</v>
       </c>
       <c r="H131" t="n">
-        <v>53.8</v>
+        <v>54.4</v>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
-        <v>26.8</v>
+        <v>21.7</v>
       </c>
       <c r="K131" t="n">
-        <v>13.2</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B132" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C132" t="n">
-        <v>50.9</v>
+        <v>66.7</v>
       </c>
       <c r="D132" t="n">
-        <v>60.7</v>
+        <v>56.7</v>
       </c>
       <c r="E132" t="n">
-        <v>24.6</v>
+        <v>14.3</v>
       </c>
       <c r="F132" t="n">
-        <v>38.6</v>
+        <v>50</v>
       </c>
       <c r="G132" t="n">
-        <v>9.7</v>
+        <v>22.2</v>
       </c>
       <c r="H132" t="n">
-        <v>54.4</v>
+        <v>20</v>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="K132" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C133" t="n">
-        <v>66.7</v>
+        <v>69.5</v>
       </c>
       <c r="D133" t="n">
-        <v>56.7</v>
+        <v>70.3</v>
       </c>
       <c r="E133" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="F133" t="n">
         <v>50</v>
       </c>
       <c r="G133" t="n">
-        <v>22.2</v>
+        <v>4.1</v>
       </c>
       <c r="H133" t="n">
-        <v>20</v>
+        <v>41.9</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B134" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C134" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
       <c r="D134" t="n">
-        <v>70.3</v>
+        <v>63</v>
       </c>
       <c r="E134" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F134" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G134" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H134" t="n">
         <v>50</v>
       </c>
-      <c r="G134" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H134" t="n">
-        <v>41.9</v>
-      </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
-        <v>26.3</v>
+        <v>21</v>
       </c>
       <c r="K134" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
-        <v>304</v>
-      </c>
+      <c r="A135"/>
       <c r="B135" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C135" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="D135" t="n">
-        <v>63</v>
+        <v>61.3</v>
       </c>
       <c r="E135" t="n">
-        <v>27</v>
+        <v>20.7</v>
       </c>
       <c r="F135" t="n">
-        <v>42.2</v>
+        <v>37.3</v>
       </c>
       <c r="G135" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="H135" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J135" t="n">
-        <v>21</v>
+        <v>24.9</v>
       </c>
       <c r="K135" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136"/>
-      <c r="B136" t="s">
-        <v>182</v>
-      </c>
-      <c r="C136" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="D136" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="E136" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F136" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="G136" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H136" t="n">
-        <v>46</v>
-      </c>
-      <c r="I136" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J136" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="K136" t="n">
         <v>8</v>
       </c>
     </row>

--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -465,9 +465,6 @@
     <t xml:space="preserve">Crixtian Taveras</t>
   </si>
   <si>
-    <t xml:space="preserve">Denis Dei Banning</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dennis Dei Baning</t>
   </si>
   <si>
@@ -585,9 +582,6 @@
     <t xml:space="preserve">Brady Encarnacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Braeden Pakkala</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brett Reid</t>
   </si>
   <si>
@@ -837,7 +831,7 @@
     <t xml:space="preserve">Zachary Laird</t>
   </si>
   <si>
-    <t xml:space="preserve">Alex Gerard</t>
+    <t xml:space="preserve">Alex Gerrard</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Lanigan</t>
@@ -973,8 +967,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K164" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K164"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K163" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K163"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -993,8 +987,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K135" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K134" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K134"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -5902,25 +5896,31 @@
         <v>145</v>
       </c>
       <c r="C134" t="n">
-        <v>100</v>
-      </c>
-      <c r="D134"/>
-      <c r="E134"/>
-      <c r="F134"/>
+        <v>74.6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E134" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="F134" t="n">
+        <v>27.2</v>
+      </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>9.7</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="J134" t="n">
-        <v>100</v>
+        <v>27.6</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="135">
@@ -5931,31 +5931,31 @@
         <v>145</v>
       </c>
       <c r="C135" t="n">
-        <v>74.5</v>
+        <v>48.1</v>
       </c>
       <c r="D135" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="E135" t="n">
-        <v>47.3</v>
+        <v>23.1</v>
       </c>
       <c r="F135" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="G135" t="n">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="H135" t="n">
-        <v>9.8</v>
+        <v>18.8</v>
       </c>
       <c r="I135" t="n">
-        <v>47.4</v>
+        <v>44.4</v>
       </c>
       <c r="J135" t="n">
-        <v>26.3</v>
+        <v>22.2</v>
       </c>
       <c r="K135" t="n">
-        <v>39.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="136">
@@ -5966,31 +5966,31 @@
         <v>145</v>
       </c>
       <c r="C136" t="n">
-        <v>48.1</v>
+        <v>66</v>
       </c>
       <c r="D136" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="E136" t="n">
-        <v>23.1</v>
+        <v>41.7</v>
       </c>
       <c r="F136" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="G136" t="n">
-        <v>15.4</v>
+        <v>21.9</v>
       </c>
       <c r="H136" t="n">
-        <v>18.8</v>
+        <v>7.7</v>
       </c>
       <c r="I136" t="n">
-        <v>44.4</v>
+        <v>54.3</v>
       </c>
       <c r="J136" t="n">
-        <v>22.2</v>
+        <v>15.7</v>
       </c>
       <c r="K136" t="n">
-        <v>11.1</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="137">
@@ -6001,31 +6001,31 @@
         <v>145</v>
       </c>
       <c r="C137" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="D137" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="F137" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>21.9</v>
+        <v>18.2</v>
       </c>
       <c r="H137" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>54.3</v>
+        <v>75</v>
       </c>
       <c r="J137" t="n">
-        <v>15.7</v>
+        <v>25</v>
       </c>
       <c r="K137" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6036,31 +6036,31 @@
         <v>145</v>
       </c>
       <c r="C138" t="n">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="E138" t="n">
-        <v>66.7</v>
+        <v>52.8</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="G138" t="n">
-        <v>18.2</v>
+        <v>27.4</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I138" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="139">
@@ -6071,31 +6071,31 @@
         <v>145</v>
       </c>
       <c r="C139" t="n">
-        <v>72.2</v>
+        <v>50</v>
       </c>
       <c r="D139" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="E139" t="n">
-        <v>52.8</v>
+        <v>35.7</v>
       </c>
       <c r="F139" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="G139" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="H139" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="I139" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K139" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140">
@@ -6106,31 +6106,31 @@
         <v>145</v>
       </c>
       <c r="C140" t="n">
-        <v>50</v>
+        <v>68.5</v>
       </c>
       <c r="D140" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="E140" t="n">
-        <v>35.7</v>
+        <v>39.5</v>
       </c>
       <c r="F140" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="G140" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="H140" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="I140" t="n">
-        <v>75</v>
+        <v>35.9</v>
       </c>
       <c r="J140" t="n">
-        <v>25</v>
+        <v>28.1</v>
       </c>
       <c r="K140" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="141">
@@ -6141,101 +6141,101 @@
         <v>145</v>
       </c>
       <c r="C141" t="n">
-        <v>68.5</v>
+        <v>65.8</v>
       </c>
       <c r="D141" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E141" t="n">
-        <v>39.5</v>
+        <v>41.8</v>
       </c>
       <c r="F141" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G141" t="n">
-        <v>31.8</v>
+        <v>21.9</v>
       </c>
       <c r="H141" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="I141" t="n">
-        <v>35.9</v>
+        <v>59.7</v>
       </c>
       <c r="J141" t="n">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
       <c r="K141" t="n">
-        <v>43.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="B142" t="s">
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>65.8</v>
+        <v>56.1</v>
       </c>
       <c r="D142" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="E142" t="n">
-        <v>41.8</v>
+        <v>36.9</v>
       </c>
       <c r="F142" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="G142" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="H142" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>59.7</v>
+        <v>40.5</v>
       </c>
       <c r="J142" t="n">
-        <v>23.9</v>
+        <v>27</v>
       </c>
       <c r="K142" t="n">
-        <v>30.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="B143" t="s">
         <v>145</v>
       </c>
       <c r="C143" t="n">
-        <v>56.1</v>
+        <v>79.6</v>
       </c>
       <c r="D143" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="E143" t="n">
-        <v>36.9</v>
+        <v>42.8</v>
       </c>
       <c r="F143" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="G143" t="n">
-        <v>22.5</v>
+        <v>34.2</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I143" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
       <c r="J143" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144">
@@ -6246,31 +6246,31 @@
         <v>145</v>
       </c>
       <c r="C144" t="n">
-        <v>79.6</v>
+        <v>57.8</v>
       </c>
       <c r="D144" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="E144" t="n">
-        <v>42.8</v>
+        <v>43.7</v>
       </c>
       <c r="F144" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="G144" t="n">
-        <v>34.2</v>
+        <v>12.5</v>
       </c>
       <c r="H144" t="n">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="I144" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="J144" t="n">
-        <v>20</v>
+        <v>9.7</v>
       </c>
       <c r="K144" t="n">
-        <v>44</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="145">
@@ -6281,31 +6281,31 @@
         <v>145</v>
       </c>
       <c r="C145" t="n">
-        <v>57.8</v>
+        <v>63.2</v>
       </c>
       <c r="D145" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="E145" t="n">
-        <v>43.7</v>
+        <v>18.2</v>
       </c>
       <c r="F145" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="G145" t="n">
-        <v>12.5</v>
+        <v>26.9</v>
       </c>
       <c r="H145" t="n">
-        <v>10.2</v>
+        <v>7.7</v>
       </c>
       <c r="I145" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>9.7</v>
+        <v>25</v>
       </c>
       <c r="K145" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146">
@@ -6316,31 +6316,31 @@
         <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="D146" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="E146" t="n">
-        <v>18.2</v>
+        <v>62.1</v>
       </c>
       <c r="F146" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="G146" t="n">
-        <v>26.9</v>
+        <v>23.4</v>
       </c>
       <c r="H146" t="n">
-        <v>7.7</v>
+        <v>14.8</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="J146" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K146" t="n">
-        <v>25</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="147">
@@ -6354,28 +6354,28 @@
         <v>74.2</v>
       </c>
       <c r="D147" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="E147" t="n">
-        <v>62.1</v>
+        <v>48.1</v>
       </c>
       <c r="F147" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="G147" t="n">
-        <v>23.4</v>
+        <v>9.2</v>
       </c>
       <c r="H147" t="n">
-        <v>14.8</v>
+        <v>2.2</v>
       </c>
       <c r="I147" t="n">
-        <v>32.9</v>
+        <v>48.1</v>
       </c>
       <c r="J147" t="n">
-        <v>37</v>
+        <v>20.8</v>
       </c>
       <c r="K147" t="n">
-        <v>38.4</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="148">
@@ -6383,69 +6383,69 @@
         <v>163</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C148" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="D148" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="E148" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="G148" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H148" t="n">
         <v>9.2</v>
       </c>
-      <c r="H148" t="n">
-        <v>2.2</v>
-      </c>
       <c r="I148" t="n">
-        <v>48.1</v>
+        <v>51.9</v>
       </c>
       <c r="J148" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="K148" t="n">
-        <v>32.5</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
+        <v>165</v>
+      </c>
+      <c r="B149" t="s">
         <v>164</v>
       </c>
-      <c r="B149" t="s">
-        <v>165</v>
-      </c>
       <c r="C149" t="n">
-        <v>70.5</v>
+        <v>68.6</v>
       </c>
       <c r="D149" t="n">
         <v>20.5</v>
       </c>
       <c r="E149" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F149" t="n">
         <v>20.5</v>
       </c>
       <c r="G149" t="n">
-        <v>37.7</v>
+        <v>14.9</v>
       </c>
       <c r="H149" t="n">
-        <v>9.2</v>
+        <v>6.6</v>
       </c>
       <c r="I149" t="n">
-        <v>51.9</v>
+        <v>57.3</v>
       </c>
       <c r="J149" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="K149" t="n">
-        <v>39.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="150">
@@ -6453,34 +6453,34 @@
         <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C150" t="n">
-        <v>68.6</v>
+        <v>64.6</v>
       </c>
       <c r="D150" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E150" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F150" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G150" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H150" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J150" t="n">
         <v>48.1</v>
       </c>
-      <c r="F150" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G150" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H150" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I150" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J150" t="n">
-        <v>18.7</v>
-      </c>
       <c r="K150" t="n">
-        <v>45.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="151">
@@ -6488,34 +6488,34 @@
         <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C151" t="n">
-        <v>64.6</v>
+        <v>60</v>
       </c>
       <c r="D151" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E151" t="n">
-        <v>47.9</v>
+        <v>38.9</v>
       </c>
       <c r="F151" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G151" t="n">
-        <v>37.7</v>
+        <v>32.4</v>
       </c>
       <c r="H151" t="n">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="I151" t="n">
-        <v>29.6</v>
+        <v>34.8</v>
       </c>
       <c r="J151" t="n">
-        <v>48.1</v>
+        <v>30.4</v>
       </c>
       <c r="K151" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="152">
@@ -6523,34 +6523,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C152" t="n">
-        <v>60</v>
+        <v>66.3</v>
       </c>
       <c r="D152" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E152" t="n">
-        <v>38.9</v>
+        <v>51.9</v>
       </c>
       <c r="F152" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="G152" t="n">
-        <v>32.4</v>
+        <v>9</v>
       </c>
       <c r="H152" t="n">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="I152" t="n">
-        <v>34.8</v>
+        <v>62.2</v>
       </c>
       <c r="J152" t="n">
-        <v>30.4</v>
+        <v>17.3</v>
       </c>
       <c r="K152" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="153">
@@ -6558,34 +6558,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C153" t="n">
-        <v>66.3</v>
+        <v>80.4</v>
       </c>
       <c r="D153" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="E153" t="n">
-        <v>51.9</v>
+        <v>63.9</v>
       </c>
       <c r="F153" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="G153" t="n">
-        <v>9</v>
+        <v>23.3</v>
       </c>
       <c r="H153" t="n">
-        <v>18.2</v>
+        <v>9.4</v>
       </c>
       <c r="I153" t="n">
-        <v>62.2</v>
+        <v>36.2</v>
       </c>
       <c r="J153" t="n">
-        <v>17.3</v>
+        <v>34</v>
       </c>
       <c r="K153" t="n">
-        <v>36.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="154">
@@ -6593,34 +6593,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C154" t="n">
-        <v>80.4</v>
+        <v>55.6</v>
       </c>
       <c r="D154" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="E154" t="n">
-        <v>63.9</v>
+        <v>38</v>
       </c>
       <c r="F154" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="G154" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="H154" t="n">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="I154" t="n">
-        <v>36.2</v>
+        <v>47.4</v>
       </c>
       <c r="J154" t="n">
-        <v>34</v>
+        <v>22.8</v>
       </c>
       <c r="K154" t="n">
-        <v>44.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="155">
@@ -6628,34 +6628,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C155" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D155" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F155" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>25.7</v>
+        <v>66.7</v>
       </c>
       <c r="H155" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -6663,34 +6663,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C156" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E156" t="n">
-        <v>75</v>
+        <v>38.6</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G156" t="n">
-        <v>66.7</v>
+        <v>14.6</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="157">
@@ -6698,34 +6698,34 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C157" t="n">
-        <v>56.2</v>
+        <v>61.4</v>
       </c>
       <c r="D157" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="E157" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="F157" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="G157" t="n">
-        <v>14.6</v>
+        <v>9.8</v>
       </c>
       <c r="H157" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="I157" t="n">
-        <v>37</v>
+        <v>60.4</v>
       </c>
       <c r="J157" t="n">
-        <v>28.8</v>
+        <v>18</v>
       </c>
       <c r="K157" t="n">
-        <v>49.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="158">
@@ -6733,34 +6733,34 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C158" t="n">
-        <v>61.4</v>
+        <v>71.5</v>
       </c>
       <c r="D158" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E158" t="n">
-        <v>40.6</v>
+        <v>54.8</v>
       </c>
       <c r="F158" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="G158" t="n">
-        <v>9.8</v>
+        <v>24.7</v>
       </c>
       <c r="H158" t="n">
-        <v>8.5</v>
+        <v>11.8</v>
       </c>
       <c r="I158" t="n">
-        <v>60.4</v>
+        <v>34.8</v>
       </c>
       <c r="J158" t="n">
-        <v>18</v>
+        <v>31.5</v>
       </c>
       <c r="K158" t="n">
-        <v>29.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="159">
@@ -6768,34 +6768,34 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C159" t="n">
-        <v>71.5</v>
+        <v>77.2</v>
       </c>
       <c r="D159" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="E159" t="n">
-        <v>54.8</v>
+        <v>47.3</v>
       </c>
       <c r="F159" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="G159" t="n">
-        <v>24.7</v>
+        <v>41.7</v>
       </c>
       <c r="H159" t="n">
-        <v>11.8</v>
+        <v>6.9</v>
       </c>
       <c r="I159" t="n">
-        <v>34.8</v>
+        <v>44.4</v>
       </c>
       <c r="J159" t="n">
-        <v>31.5</v>
+        <v>22.2</v>
       </c>
       <c r="K159" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="160">
@@ -6803,34 +6803,34 @@
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C160" t="n">
-        <v>77.2</v>
+        <v>75.5</v>
       </c>
       <c r="D160" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="E160" t="n">
-        <v>47.3</v>
+        <v>55.1</v>
       </c>
       <c r="F160" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="G160" t="n">
-        <v>41.7</v>
+        <v>19.7</v>
       </c>
       <c r="H160" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="I160" t="n">
-        <v>44.4</v>
+        <v>27.9</v>
       </c>
       <c r="J160" t="n">
-        <v>22.2</v>
+        <v>33.7</v>
       </c>
       <c r="K160" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="161">
@@ -6838,57 +6838,51 @@
         <v>177</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C161" t="n">
-        <v>75.5</v>
+        <v>37.5</v>
       </c>
       <c r="D161" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="E161" t="n">
-        <v>55.1</v>
+        <v>4.2</v>
       </c>
       <c r="F161" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="G161" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>11</v>
-      </c>
-      <c r="I161" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J161" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K161" t="n">
-        <v>46.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I161"/>
+      <c r="J161"/>
+      <c r="K161"/>
     </row>
     <row r="162">
       <c r="A162" t="s">
         <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C162" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
         <v>33.3</v>
       </c>
       <c r="E162" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F162" t="n">
         <v>33.3</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -6898,65 +6892,36 @@
       <c r="K162"/>
     </row>
     <row r="163">
-      <c r="A163" t="s">
+      <c r="A163"/>
+      <c r="B163" t="s">
         <v>179</v>
       </c>
-      <c r="B163" t="s">
-        <v>165</v>
-      </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>67.8</v>
       </c>
       <c r="D163" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="E163" t="n">
-        <v>-33.3</v>
+        <v>46</v>
       </c>
       <c r="F163" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="G163" t="n">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163"/>
-      <c r="J163"/>
-      <c r="K163"/>
-    </row>
-    <row r="164">
-      <c r="A164"/>
-      <c r="B164" t="s">
-        <v>180</v>
-      </c>
-      <c r="C164" t="n">
-        <v>68</v>
-      </c>
-      <c r="D164" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E164" t="n">
-        <v>46</v>
-      </c>
-      <c r="F164" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G164" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H164" t="n">
         <v>9.5</v>
       </c>
-      <c r="I164" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J164" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="K164" t="n">
-        <v>39.3</v>
+      <c r="I163" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J163" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K163" t="n">
+        <v>39.6</v>
       </c>
     </row>
   </sheetData>
@@ -6988,22 +6953,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7012,18 +6977,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7058,7 +7023,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7093,7 +7058,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7134,559 +7099,559 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>57.7</v>
+        <v>58.4</v>
       </c>
       <c r="D5" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="E5" t="n">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="F5" t="n">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="G5" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="H5" t="n">
-        <v>52.3</v>
+        <v>45.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>27.7</v>
+        <v>24.6</v>
       </c>
       <c r="K5" t="n">
-        <v>10.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>60.9</v>
+        <v>49.2</v>
       </c>
       <c r="D6" t="n">
-        <v>58.5</v>
+        <v>56.4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>19.7</v>
       </c>
       <c r="F6" t="n">
-        <v>27.3</v>
+        <v>35.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H6" t="n">
-        <v>26.7</v>
+        <v>41.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>11.8</v>
+        <v>26.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>49.2</v>
+        <v>71.4</v>
       </c>
       <c r="D7" t="n">
-        <v>56.4</v>
+        <v>55.6</v>
       </c>
       <c r="E7" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="n">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>16.7</v>
       </c>
       <c r="H7" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>26.5</v>
+        <v>36.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>71.4</v>
+        <v>70.5</v>
       </c>
       <c r="D8" t="n">
-        <v>55.6</v>
+        <v>69.6</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>35.1</v>
       </c>
       <c r="G8" t="n">
-        <v>16.7</v>
+        <v>8.1</v>
       </c>
       <c r="H8" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>36.4</v>
+        <v>28.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>70.5</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>69.6</v>
+        <v>64.9</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>35.1</v>
+        <v>32.3</v>
       </c>
       <c r="G9" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="K9" t="n">
-        <v>14.5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>63.3</v>
       </c>
       <c r="D10" t="n">
-        <v>64.9</v>
+        <v>64.3</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="F10" t="n">
-        <v>32.3</v>
+        <v>35.3</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>81.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>21.9</v>
+        <v>18.8</v>
       </c>
       <c r="K10" t="n">
-        <v>9.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>63.3</v>
+        <v>59.4</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>13.5</v>
+        <v>16.6</v>
       </c>
       <c r="F11" t="n">
-        <v>35.3</v>
+        <v>27.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>81.8</v>
+        <v>41.7</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>18.8</v>
+        <v>17.2</v>
       </c>
       <c r="K11" t="n">
-        <v>13.3</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>59.4</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6</v>
+        <v>19.6</v>
       </c>
       <c r="F12" t="n">
-        <v>27.8</v>
+        <v>47.3</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="H12" t="n">
-        <v>41.7</v>
+        <v>53</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
-        <v>17.2</v>
+        <v>33.7</v>
       </c>
       <c r="K12" t="n">
-        <v>8.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>42.2</v>
       </c>
       <c r="G13" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>33.7</v>
+        <v>34.4</v>
       </c>
       <c r="K13" t="n">
-        <v>17.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>58.3</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>52.3</v>
       </c>
       <c r="E14" t="n">
-        <v>17.8</v>
+        <v>8.3</v>
       </c>
       <c r="F14" t="n">
-        <v>42.2</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>34.4</v>
+        <v>23.5</v>
       </c>
       <c r="K14" t="n">
-        <v>14.1</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>58.3</v>
+        <v>57.2</v>
       </c>
       <c r="D15" t="n">
-        <v>52.3</v>
+        <v>63.9</v>
       </c>
       <c r="E15" t="n">
-        <v>8.3</v>
+        <v>18.3</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>48.9</v>
       </c>
       <c r="G15" t="n">
-        <v>16.7</v>
+        <v>7.1</v>
       </c>
       <c r="H15" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>23.5</v>
+        <v>28.6</v>
       </c>
       <c r="K15" t="n">
-        <v>8.3</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>57.2</v>
+        <v>33.3</v>
       </c>
       <c r="D16" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>18.3</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="E16"/>
       <c r="F16" t="n">
-        <v>48.9</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="D17" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="E17"/>
+        <v>52.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.5</v>
+      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H17" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-21.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>42.9</v>
+        <v>51.6</v>
       </c>
       <c r="D18" t="n">
-        <v>52.2</v>
+        <v>56.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10.5</v>
+        <v>17.4</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="G18" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="H18" t="n">
-        <v>55.6</v>
+        <v>46.9</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>51.6</v>
+        <v>52.9</v>
       </c>
       <c r="D19" t="n">
-        <v>56.1</v>
+        <v>39.1</v>
       </c>
       <c r="E19" t="n">
-        <v>17.4</v>
+        <v>10.4</v>
       </c>
       <c r="F19" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>23.6</v>
+        <v>35.3</v>
       </c>
       <c r="H19" t="n">
-        <v>46.9</v>
+        <v>55.6</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>22.4</v>
+        <v>8.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-9</v>
+        <v>-35.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>39.1</v>
+        <v>59.6</v>
       </c>
       <c r="E20" t="n">
-        <v>10.4</v>
+        <v>7.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>35.3</v>
+        <v>17.4</v>
       </c>
       <c r="H20" t="n">
-        <v>55.6</v>
+        <v>38.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
-        <v>8.3</v>
+        <v>27.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-35.3</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
@@ -7695,4004 +7660,3969 @@
         <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>59.6</v>
+        <v>56.2</v>
       </c>
       <c r="E21" t="n">
-        <v>7.9</v>
+        <v>14.7</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>17.4</v>
+        <v>12.1</v>
       </c>
       <c r="H21" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>27.8</v>
+        <v>17.3</v>
       </c>
       <c r="K21" t="n">
-        <v>8.7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>56.2</v>
+        <v>62.6</v>
       </c>
       <c r="E22" t="n">
-        <v>14.7</v>
+        <v>29.5</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>38.5</v>
       </c>
       <c r="G22" t="n">
-        <v>12.1</v>
+        <v>9.3</v>
       </c>
       <c r="H22" t="n">
-        <v>38.6</v>
+        <v>45.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>17.3</v>
+        <v>25.8</v>
       </c>
       <c r="K22" t="n">
-        <v>-3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>66.7</v>
       </c>
       <c r="D23" t="n">
-        <v>62.6</v>
+        <v>80</v>
       </c>
       <c r="E23" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>45.7</v>
+        <v>75</v>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>25.8</v>
+        <v>14.3</v>
       </c>
       <c r="K23" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>61.5</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>33.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>52.6</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>14.3</v>
+        <v>20.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>55.6</v>
+        <v>58</v>
       </c>
       <c r="D25" t="n">
-        <v>61.5</v>
+        <v>60.6</v>
       </c>
       <c r="E25" t="n">
-        <v>33.8</v>
+        <v>12.1</v>
       </c>
       <c r="F25" t="n">
-        <v>33.3</v>
+        <v>48.5</v>
       </c>
       <c r="G25" t="n">
-        <v>7.4</v>
+        <v>17.9</v>
       </c>
       <c r="H25" t="n">
-        <v>52.6</v>
+        <v>46.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>20.5</v>
+        <v>37.3</v>
       </c>
       <c r="K25" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>58</v>
+        <v>43.3</v>
       </c>
       <c r="D26" t="n">
-        <v>60.6</v>
+        <v>51.2</v>
       </c>
       <c r="E26" t="n">
-        <v>12.1</v>
+        <v>15.9</v>
       </c>
       <c r="F26" t="n">
-        <v>48.5</v>
+        <v>37.9</v>
       </c>
       <c r="G26" t="n">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="H26" t="n">
-        <v>46.2</v>
+        <v>42.4</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>37.3</v>
+        <v>29.2</v>
       </c>
       <c r="K26" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>43.3</v>
+        <v>66.7</v>
       </c>
       <c r="D27" t="n">
-        <v>51.2</v>
+        <v>68.1</v>
       </c>
       <c r="E27" t="n">
-        <v>15.9</v>
+        <v>37.8</v>
       </c>
       <c r="F27" t="n">
-        <v>37.9</v>
+        <v>54.5</v>
       </c>
       <c r="G27" t="n">
-        <v>18.6</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
-        <v>42.4</v>
+        <v>45.5</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>29.2</v>
+        <v>40.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>66.7</v>
+        <v>55.4</v>
       </c>
       <c r="D28" t="n">
-        <v>68.1</v>
+        <v>65.5</v>
       </c>
       <c r="E28" t="n">
-        <v>37.8</v>
+        <v>26.7</v>
       </c>
       <c r="F28" t="n">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
       <c r="G28" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>45.5</v>
+        <v>58.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>40.2</v>
+        <v>24.1</v>
       </c>
       <c r="K28" t="n">
-        <v>33.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
       </c>
       <c r="C29" t="n">
-        <v>55.4</v>
+        <v>55.7</v>
       </c>
       <c r="D29" t="n">
-        <v>65.5</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>26.7</v>
+        <v>21.3</v>
       </c>
       <c r="F29" t="n">
-        <v>45.5</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>17.4</v>
       </c>
       <c r="H29" t="n">
-        <v>58.1</v>
+        <v>53.7</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="K29" t="n">
-        <v>14.4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>55.7</v>
+        <v>59.1</v>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>57.8</v>
       </c>
       <c r="E30" t="n">
-        <v>21.3</v>
+        <v>18.5</v>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>17.1</v>
       </c>
       <c r="G30" t="n">
-        <v>17.4</v>
+        <v>13.8</v>
       </c>
       <c r="H30" t="n">
-        <v>53.7</v>
+        <v>44.6</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.1</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>59.1</v>
+        <v>56.7</v>
       </c>
       <c r="D31" t="n">
-        <v>57.8</v>
+        <v>60.8</v>
       </c>
       <c r="E31" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>17.1</v>
+        <v>41.7</v>
       </c>
       <c r="G31" t="n">
-        <v>13.8</v>
+        <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>44.6</v>
+        <v>41.2</v>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="J31" t="n">
-        <v>22.8</v>
+        <v>27.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
       <c r="C32" t="n">
-        <v>56.7</v>
+        <v>58.2</v>
       </c>
       <c r="D32" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
         <v>41.7</v>
       </c>
       <c r="G32" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="H32" t="n">
-        <v>41.2</v>
+        <v>43.9</v>
       </c>
       <c r="I32" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C33" t="n">
-        <v>58.2</v>
+        <v>78.6</v>
       </c>
       <c r="D33" t="n">
-        <v>60.5</v>
+        <v>79.1</v>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>30.8</v>
       </c>
       <c r="F33" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="G33" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>43.9</v>
+        <v>30.8</v>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>21.4</v>
       </c>
       <c r="J33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>16.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="n">
-        <v>78.6</v>
+        <v>52.5</v>
       </c>
       <c r="D34" t="n">
-        <v>79.1</v>
+        <v>59.1</v>
       </c>
       <c r="E34" t="n">
-        <v>30.8</v>
+        <v>15.9</v>
       </c>
       <c r="F34" t="n">
-        <v>16.7</v>
+        <v>29.4</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H34" t="n">
-        <v>30.8</v>
+        <v>46</v>
       </c>
       <c r="I34" t="n">
-        <v>21.4</v>
+        <v>8.5</v>
       </c>
       <c r="J34" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="K34" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
       </c>
       <c r="C35" t="n">
-        <v>52.5</v>
+        <v>45.8</v>
       </c>
       <c r="D35" t="n">
-        <v>59.1</v>
+        <v>57</v>
       </c>
       <c r="E35" t="n">
-        <v>15.9</v>
+        <v>17.6</v>
       </c>
       <c r="F35" t="n">
-        <v>29.4</v>
+        <v>28.6</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3</v>
+        <v>20.8</v>
       </c>
       <c r="H35" t="n">
-        <v>46</v>
+        <v>42.9</v>
       </c>
       <c r="I35" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
-        <v>18.8</v>
+        <v>24.4</v>
       </c>
       <c r="K35" t="n">
-        <v>2.5</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B36" t="s">
         <v>49</v>
       </c>
       <c r="C36" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H36" t="n">
         <v>45.8</v>
       </c>
-      <c r="D36" t="n">
-        <v>57</v>
-      </c>
-      <c r="E36" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F36" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>42.9</v>
-      </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
       </c>
       <c r="C37" t="n">
-        <v>52.9</v>
+        <v>47.8</v>
       </c>
       <c r="D37" t="n">
-        <v>57.7</v>
+        <v>53.7</v>
       </c>
       <c r="E37" t="n">
-        <v>11.1</v>
+        <v>12.1</v>
       </c>
       <c r="F37" t="n">
-        <v>35.3</v>
+        <v>28.6</v>
       </c>
       <c r="G37" t="n">
-        <v>11.6</v>
+        <v>15.2</v>
       </c>
       <c r="H37" t="n">
-        <v>45.8</v>
+        <v>53.3</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
-        <v>23.1</v>
+        <v>19.4</v>
       </c>
       <c r="K37" t="n">
-        <v>5.8</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
       </c>
       <c r="C38" t="n">
-        <v>47.8</v>
+        <v>48.8</v>
       </c>
       <c r="D38" t="n">
-        <v>53.7</v>
+        <v>55.8</v>
       </c>
       <c r="E38" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="F38" t="n">
-        <v>28.6</v>
+        <v>37.3</v>
       </c>
       <c r="G38" t="n">
-        <v>15.2</v>
+        <v>11.7</v>
       </c>
       <c r="H38" t="n">
-        <v>53.3</v>
+        <v>54.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
-        <v>19.4</v>
+        <v>24.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
       </c>
       <c r="C39" t="n">
-        <v>48.8</v>
+        <v>59</v>
       </c>
       <c r="D39" t="n">
-        <v>55.8</v>
+        <v>63.6</v>
       </c>
       <c r="E39" t="n">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="F39" t="n">
-        <v>37.3</v>
+        <v>21.9</v>
       </c>
       <c r="G39" t="n">
-        <v>11.7</v>
+        <v>9.1</v>
       </c>
       <c r="H39" t="n">
-        <v>54.7</v>
+        <v>34.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
-        <v>24.9</v>
+        <v>20.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B40" t="s">
         <v>49</v>
       </c>
       <c r="C40" t="n">
-        <v>59</v>
+        <v>54.8</v>
       </c>
       <c r="D40" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="E40" t="n">
-        <v>16.7</v>
+        <v>23.7</v>
       </c>
       <c r="F40" t="n">
-        <v>21.9</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="H40" t="n">
-        <v>34.5</v>
+        <v>38.1</v>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
       </c>
       <c r="C41" t="n">
-        <v>54.8</v>
+        <v>100</v>
       </c>
       <c r="D41" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>50</v>
       </c>
-      <c r="G41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20.8</v>
-      </c>
       <c r="K41" t="n">
-        <v>16.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42" t="n">
-        <v>100</v>
+        <v>66.3</v>
       </c>
       <c r="D42" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>52.9</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42"/>
+        <v>2.4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>62.3</v>
+      </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>19.1</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>66.3</v>
+        <v>57</v>
       </c>
       <c r="D43" t="n">
-        <v>65</v>
+        <v>61.8</v>
       </c>
       <c r="E43" t="n">
-        <v>15.5</v>
+        <v>18.4</v>
       </c>
       <c r="F43" t="n">
-        <v>52.9</v>
+        <v>48.6</v>
       </c>
       <c r="G43" t="n">
-        <v>2.4</v>
+        <v>11.6</v>
       </c>
       <c r="H43" t="n">
-        <v>62.3</v>
+        <v>47.3</v>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
-        <v>19.1</v>
+        <v>27.3</v>
       </c>
       <c r="K43" t="n">
-        <v>19</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
       </c>
       <c r="C44" t="n">
-        <v>57</v>
+        <v>60.4</v>
       </c>
       <c r="D44" t="n">
-        <v>61.8</v>
+        <v>66.4</v>
       </c>
       <c r="E44" t="n">
-        <v>18.4</v>
+        <v>20.3</v>
       </c>
       <c r="F44" t="n">
-        <v>48.6</v>
+        <v>45.3</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6</v>
+        <v>4.9</v>
       </c>
       <c r="H44" t="n">
-        <v>47.3</v>
+        <v>35.2</v>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
-        <v>27.3</v>
+        <v>25.9</v>
       </c>
       <c r="K44" t="n">
-        <v>8.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
       </c>
       <c r="C45" t="n">
-        <v>60.4</v>
+        <v>55.4</v>
       </c>
       <c r="D45" t="n">
-        <v>66.4</v>
+        <v>62.1</v>
       </c>
       <c r="E45" t="n">
-        <v>20.3</v>
+        <v>22.8</v>
       </c>
       <c r="F45" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="G45" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="H45" t="n">
-        <v>35.2</v>
+        <v>48.9</v>
       </c>
       <c r="I45" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="J45" t="n">
-        <v>25.9</v>
+        <v>31.8</v>
       </c>
       <c r="K45" t="n">
-        <v>21.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>55.4</v>
+        <v>81.2</v>
       </c>
       <c r="D46" t="n">
-        <v>62.1</v>
+        <v>72.9</v>
       </c>
       <c r="E46" t="n">
-        <v>22.8</v>
+        <v>25</v>
       </c>
       <c r="F46" t="n">
-        <v>45.2</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H46" t="n">
-        <v>48.9</v>
+        <v>54.5</v>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>31.8</v>
+        <v>29.2</v>
       </c>
       <c r="K46" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s">
         <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>81.2</v>
+        <v>58</v>
       </c>
       <c r="D47" t="n">
-        <v>72.9</v>
+        <v>64</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>16.3</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>44.7</v>
       </c>
       <c r="G47" t="n">
         <v>6.2</v>
       </c>
       <c r="H47" t="n">
-        <v>54.5</v>
+        <v>52.8</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J47" t="n">
-        <v>29.2</v>
+        <v>26.6</v>
       </c>
       <c r="K47" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
         <v>49</v>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>44.4</v>
       </c>
       <c r="D48" t="n">
-        <v>64</v>
-      </c>
-      <c r="E48" t="n">
-        <v>16.3</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E48"/>
       <c r="F48" t="n">
-        <v>44.7</v>
+        <v>25</v>
       </c>
       <c r="G48" t="n">
-        <v>6.2</v>
+        <v>33.3</v>
       </c>
       <c r="H48" t="n">
-        <v>52.8</v>
+        <v>20</v>
       </c>
       <c r="I48" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s">
         <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>44.4</v>
+        <v>51.8</v>
       </c>
       <c r="D49" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E49"/>
+        <v>57</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15.4</v>
+      </c>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>22.8</v>
       </c>
       <c r="G49" t="n">
-        <v>33.3</v>
+        <v>9.6</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>38.4</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>27.3</v>
+        <v>12.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-22.2</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C50" t="n">
-        <v>51.8</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="E50" t="n">
-        <v>15.4</v>
+        <v>16.9</v>
       </c>
       <c r="F50" t="n">
-        <v>22.8</v>
+        <v>38.1</v>
       </c>
       <c r="G50" t="n">
-        <v>9.6</v>
+        <v>14.6</v>
       </c>
       <c r="H50" t="n">
-        <v>38.4</v>
+        <v>31.2</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
-        <v>12.9</v>
+        <v>28.4</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
         <v>67</v>
       </c>
       <c r="C51" t="n">
-        <v>60</v>
+        <v>70.9</v>
       </c>
       <c r="D51" t="n">
-        <v>56.5</v>
+        <v>74</v>
       </c>
       <c r="E51" t="n">
-        <v>16.9</v>
+        <v>40.8</v>
       </c>
       <c r="F51" t="n">
-        <v>38.1</v>
+        <v>71.4</v>
       </c>
       <c r="G51" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>31.2</v>
+        <v>41.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
-        <v>28.4</v>
+        <v>43.3</v>
       </c>
       <c r="K51" t="n">
-        <v>4.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s">
         <v>67</v>
       </c>
       <c r="C52" t="n">
-        <v>70.9</v>
+        <v>60.6</v>
       </c>
       <c r="D52" t="n">
-        <v>74</v>
+        <v>61.2</v>
       </c>
       <c r="E52" t="n">
-        <v>40.8</v>
+        <v>21.5</v>
       </c>
       <c r="F52" t="n">
-        <v>71.4</v>
+        <v>47.8</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H52" t="n">
-        <v>41.4</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
-        <v>43.3</v>
+        <v>35.1</v>
       </c>
       <c r="K52" t="n">
-        <v>38.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
       </c>
       <c r="C53" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>21.5</v>
-      </c>
+        <v>71.4</v>
+      </c>
+      <c r="E53"/>
       <c r="F53" t="n">
-        <v>47.8</v>
+        <v>33.3</v>
       </c>
       <c r="G53" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>35.1</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>20.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>231</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
         <v>67</v>
       </c>
       <c r="C54" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>72.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F54" t="n">
         <v>66.7</v>
       </c>
-      <c r="D54" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="E54"/>
-      <c r="F54" t="n">
-        <v>33.3</v>
-      </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>33.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
         <v>67</v>
       </c>
       <c r="C55" t="n">
-        <v>77.8</v>
+        <v>65.6</v>
       </c>
       <c r="D55" t="n">
-        <v>72.9</v>
+        <v>67</v>
       </c>
       <c r="E55" t="n">
-        <v>42.9</v>
+        <v>18.2</v>
       </c>
       <c r="F55" t="n">
-        <v>66.7</v>
+        <v>34.1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="H55" t="n">
-        <v>55.6</v>
+        <v>40.4</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>47.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
       </c>
       <c r="C56" t="n">
-        <v>65.6</v>
+        <v>57.3</v>
       </c>
       <c r="D56" t="n">
-        <v>67</v>
+        <v>60.4</v>
       </c>
       <c r="E56" t="n">
-        <v>18.2</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>34.1</v>
+        <v>44</v>
       </c>
       <c r="G56" t="n">
-        <v>4.4</v>
+        <v>12.6</v>
       </c>
       <c r="H56" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
-        <v>22</v>
+        <v>35.9</v>
       </c>
       <c r="K56" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
       </c>
       <c r="C57" t="n">
+        <v>67.6</v>
+      </c>
+      <c r="D57" t="n">
         <v>57.3</v>
       </c>
-      <c r="D57" t="n">
-        <v>60.4</v>
-      </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="F57" t="n">
-        <v>44</v>
+        <v>57.1</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6</v>
+        <v>22.9</v>
       </c>
       <c r="H57" t="n">
-        <v>38.6</v>
+        <v>33.3</v>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>35.9</v>
+        <v>39.7</v>
       </c>
       <c r="K57" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
       <c r="C58" t="n">
-        <v>67.6</v>
+        <v>61.1</v>
       </c>
       <c r="D58" t="n">
-        <v>57.3</v>
+        <v>62.7</v>
       </c>
       <c r="E58" t="n">
-        <v>11.6</v>
+        <v>23.4</v>
       </c>
       <c r="F58" t="n">
-        <v>57.1</v>
+        <v>35.4</v>
       </c>
       <c r="G58" t="n">
-        <v>22.9</v>
+        <v>8.3</v>
       </c>
       <c r="H58" t="n">
-        <v>33.3</v>
+        <v>34.6</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
-        <v>39.7</v>
+        <v>15.7</v>
       </c>
       <c r="K58" t="n">
-        <v>11.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
       </c>
       <c r="C59" t="n">
-        <v>61.1</v>
+        <v>62</v>
       </c>
       <c r="D59" t="n">
-        <v>62.7</v>
+        <v>65</v>
       </c>
       <c r="E59" t="n">
-        <v>23.4</v>
+        <v>20.7</v>
       </c>
       <c r="F59" t="n">
-        <v>35.4</v>
+        <v>48.8</v>
       </c>
       <c r="G59" t="n">
-        <v>8.3</v>
+        <v>6.3</v>
       </c>
       <c r="H59" t="n">
-        <v>34.6</v>
+        <v>62</v>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J59" t="n">
-        <v>15.7</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>4.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
       </c>
       <c r="C60" t="n">
-        <v>62</v>
+        <v>56.5</v>
       </c>
       <c r="D60" t="n">
-        <v>65</v>
+        <v>61.6</v>
       </c>
       <c r="E60" t="n">
-        <v>20.7</v>
+        <v>6.5</v>
       </c>
       <c r="F60" t="n">
-        <v>48.8</v>
+        <v>42.9</v>
       </c>
       <c r="G60" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="H60" t="n">
-        <v>62</v>
+        <v>56.2</v>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
-        <v>33.3</v>
+        <v>23.8</v>
       </c>
       <c r="K60" t="n">
-        <v>19</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>56.5</v>
+        <v>65.7</v>
       </c>
       <c r="D61" t="n">
-        <v>61.6</v>
+        <v>66.9</v>
       </c>
       <c r="E61" t="n">
-        <v>6.5</v>
+        <v>29.4</v>
       </c>
       <c r="F61" t="n">
-        <v>42.9</v>
+        <v>34.5</v>
       </c>
       <c r="G61" t="n">
-        <v>8.9</v>
+        <v>5.2</v>
       </c>
       <c r="H61" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
-        <v>23.8</v>
+        <v>19.6</v>
       </c>
       <c r="K61" t="n">
-        <v>11.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
       </c>
       <c r="C62" t="n">
-        <v>65.7</v>
+        <v>62.3</v>
       </c>
       <c r="D62" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="E62" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="F62" t="n">
-        <v>34.5</v>
+        <v>37.5</v>
       </c>
       <c r="G62" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="H62" t="n">
-        <v>55.8</v>
+        <v>22.9</v>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="K62" t="n">
-        <v>9.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>238</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>62.3</v>
+        <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>64.6</v>
+        <v>60.6</v>
       </c>
       <c r="E63" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
         <v>25</v>
       </c>
-      <c r="F63" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G63" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H63" t="n">
-        <v>22.9</v>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>237</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>30</v>
+        <v>44.4</v>
       </c>
       <c r="D64" t="n">
-        <v>60.6</v>
+        <v>48.6</v>
       </c>
       <c r="E64" t="n">
-        <v>46.7</v>
+        <v>15.7</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H64" t="n">
-        <v>25</v>
+        <v>54.2</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="B65" t="s">
         <v>67</v>
       </c>
       <c r="C65" t="n">
-        <v>44.4</v>
+        <v>62.5</v>
       </c>
       <c r="D65" t="n">
-        <v>48.6</v>
+        <v>64</v>
       </c>
       <c r="E65" t="n">
-        <v>15.7</v>
+        <v>33.3</v>
       </c>
       <c r="F65" t="n">
-        <v>23.8</v>
+        <v>66.7</v>
       </c>
       <c r="G65" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>54.2</v>
+        <v>16.7</v>
       </c>
       <c r="I65" t="n">
-        <v>8.9</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>31.1</v>
+        <v>16.7</v>
       </c>
       <c r="K65" t="n">
-        <v>-15.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>238</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C66" t="n">
-        <v>62.5</v>
+        <v>72.4</v>
       </c>
       <c r="D66" t="n">
-        <v>64</v>
+        <v>71.8</v>
       </c>
       <c r="E66" t="n">
-        <v>33.3</v>
+        <v>16.4</v>
       </c>
       <c r="F66" t="n">
-        <v>66.7</v>
+        <v>37.8</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H66" t="n">
-        <v>16.7</v>
+        <v>45.8</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
-        <v>16.7</v>
+        <v>22.8</v>
       </c>
       <c r="K66" t="n">
-        <v>25</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B67" t="s">
         <v>92</v>
       </c>
       <c r="C67" t="n">
-        <v>72.4</v>
+        <v>66.7</v>
       </c>
       <c r="D67" t="n">
-        <v>71.8</v>
+        <v>66</v>
       </c>
       <c r="E67" t="n">
-        <v>16.4</v>
+        <v>13.5</v>
       </c>
       <c r="F67" t="n">
-        <v>37.8</v>
+        <v>22.2</v>
       </c>
       <c r="G67" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H67" t="n">
-        <v>45.8</v>
+        <v>37.9</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J67" t="n">
-        <v>22.8</v>
+        <v>9.3</v>
       </c>
       <c r="K67" t="n">
-        <v>17.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B68" t="s">
         <v>92</v>
       </c>
       <c r="C68" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>66</v>
+        <v>68.3</v>
       </c>
       <c r="E68" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
       <c r="F68" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="H68" t="n">
-        <v>37.9</v>
+        <v>38.9</v>
       </c>
       <c r="I68" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>9.3</v>
+        <v>8.9</v>
       </c>
       <c r="K68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B69" t="s">
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D69" t="n">
-        <v>68.3</v>
+        <v>60.5</v>
       </c>
       <c r="E69" t="n">
-        <v>26.5</v>
+        <v>20</v>
       </c>
       <c r="F69" t="n">
-        <v>16.7</v>
+        <v>38.9</v>
       </c>
       <c r="G69" t="n">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
       <c r="H69" t="n">
-        <v>38.9</v>
+        <v>46.7</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
-        <v>8.9</v>
+        <v>18.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>92</v>
       </c>
       <c r="C70" t="n">
-        <v>55.6</v>
+        <v>54.8</v>
       </c>
       <c r="D70" t="n">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="E70" t="n">
         <v>20</v>
       </c>
       <c r="F70" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="H70" t="n">
-        <v>46.7</v>
+        <v>54.2</v>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>18.5</v>
+        <v>25.5</v>
       </c>
       <c r="K70" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" t="s">
         <v>92</v>
       </c>
       <c r="C71" t="n">
-        <v>54.8</v>
+        <v>61.1</v>
       </c>
       <c r="D71" t="n">
-        <v>62.4</v>
+        <v>63</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G71" t="n">
-        <v>14.3</v>
+        <v>7.2</v>
       </c>
       <c r="H71" t="n">
-        <v>54.2</v>
+        <v>56.5</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
-        <v>25.5</v>
+        <v>36.2</v>
       </c>
       <c r="K71" t="n">
-        <v>4.7</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" t="s">
         <v>92</v>
       </c>
       <c r="C72" t="n">
-        <v>61.1</v>
+        <v>63.8</v>
       </c>
       <c r="D72" t="n">
-        <v>63</v>
+        <v>61.7</v>
       </c>
       <c r="E72" t="n">
-        <v>17.6</v>
+        <v>26.4</v>
       </c>
       <c r="F72" t="n">
-        <v>55</v>
+        <v>57.6</v>
       </c>
       <c r="G72" t="n">
-        <v>7.2</v>
+        <v>8.2</v>
       </c>
       <c r="H72" t="n">
-        <v>56.5</v>
+        <v>53.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
-        <v>36.2</v>
+        <v>38.4</v>
       </c>
       <c r="K72" t="n">
-        <v>22.5</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B73" t="s">
         <v>92</v>
       </c>
       <c r="C73" t="n">
-        <v>63.8</v>
+        <v>51.6</v>
       </c>
       <c r="D73" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="E73" t="n">
-        <v>26.4</v>
+        <v>34.5</v>
       </c>
       <c r="F73" t="n">
-        <v>57.6</v>
+        <v>18.8</v>
       </c>
       <c r="G73" t="n">
-        <v>8.2</v>
+        <v>12.9</v>
       </c>
       <c r="H73" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
-        <v>38.4</v>
+        <v>21.7</v>
       </c>
       <c r="K73" t="n">
-        <v>27.9</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B74" t="s">
         <v>92</v>
       </c>
       <c r="C74" t="n">
-        <v>51.6</v>
+        <v>58.8</v>
       </c>
       <c r="D74" t="n">
-        <v>62.4</v>
+        <v>60.7</v>
       </c>
       <c r="E74" t="n">
-        <v>34.5</v>
+        <v>23.5</v>
       </c>
       <c r="F74" t="n">
-        <v>18.8</v>
+        <v>36.4</v>
       </c>
       <c r="G74" t="n">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="H74" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>21.7</v>
+        <v>30.5</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
         <v>92</v>
       </c>
       <c r="C75" t="n">
-        <v>58.8</v>
+        <v>69.4</v>
       </c>
       <c r="D75" t="n">
-        <v>60.7</v>
+        <v>69.9</v>
       </c>
       <c r="E75" t="n">
-        <v>23.5</v>
+        <v>26.9</v>
       </c>
       <c r="F75" t="n">
-        <v>36.4</v>
+        <v>44.9</v>
       </c>
       <c r="G75" t="n">
-        <v>15.2</v>
+        <v>7.4</v>
       </c>
       <c r="H75" t="n">
-        <v>44.4</v>
+        <v>51.9</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
-        <v>30.5</v>
+        <v>25.1</v>
       </c>
       <c r="K75" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
         <v>92</v>
       </c>
       <c r="C76" t="n">
-        <v>69.4</v>
+        <v>60.3</v>
       </c>
       <c r="D76" t="n">
-        <v>69.9</v>
+        <v>63.2</v>
       </c>
       <c r="E76" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="F76" t="n">
-        <v>44.9</v>
+        <v>54.4</v>
       </c>
       <c r="G76" t="n">
-        <v>7.4</v>
+        <v>8.3</v>
       </c>
       <c r="H76" t="n">
-        <v>51.9</v>
+        <v>42.6</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
-        <v>25.1</v>
+        <v>29.9</v>
       </c>
       <c r="K76" t="n">
-        <v>13</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
         <v>92</v>
       </c>
       <c r="C77" t="n">
-        <v>60.3</v>
+        <v>61.5</v>
       </c>
       <c r="D77" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="E77" t="n">
-        <v>24.5</v>
+        <v>21.1</v>
       </c>
       <c r="F77" t="n">
-        <v>54.4</v>
+        <v>47.6</v>
       </c>
       <c r="G77" t="n">
-        <v>8.3</v>
+        <v>10</v>
       </c>
       <c r="H77" t="n">
-        <v>42.6</v>
+        <v>61.3</v>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
-        <v>29.9</v>
+        <v>21.7</v>
       </c>
       <c r="K77" t="n">
-        <v>18.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C78" t="n">
-        <v>61.5</v>
+        <v>42</v>
       </c>
       <c r="D78" t="n">
-        <v>62.9</v>
+        <v>44.7</v>
       </c>
       <c r="E78" t="n">
-        <v>21.1</v>
+        <v>6.3</v>
       </c>
       <c r="F78" t="n">
-        <v>47.6</v>
+        <v>46.4</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>32.4</v>
       </c>
       <c r="H78" t="n">
-        <v>61.3</v>
+        <v>41.4</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
-        <v>21.7</v>
+        <v>30.4</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>-13.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
         <v>107</v>
       </c>
       <c r="C79" t="n">
-        <v>42</v>
+        <v>64.6</v>
       </c>
       <c r="D79" t="n">
-        <v>44.7</v>
+        <v>63.3</v>
       </c>
       <c r="E79" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>49</v>
+      </c>
+      <c r="G79" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I79" t="n">
         <v>6.3</v>
       </c>
-      <c r="F79" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G79" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="H79" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2.9</v>
-      </c>
       <c r="J79" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="K79" t="n">
-        <v>-13.3</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>189</v>
       </c>
       <c r="B80" t="s">
         <v>107</v>
       </c>
       <c r="C80" t="n">
-        <v>64.6</v>
+        <v>50</v>
       </c>
       <c r="D80" t="n">
-        <v>63.3</v>
+        <v>53.1</v>
       </c>
       <c r="E80" t="n">
-        <v>27.6</v>
+        <v>10.1</v>
       </c>
       <c r="F80" t="n">
-        <v>49</v>
+        <v>46.4</v>
       </c>
       <c r="G80" t="n">
-        <v>10.5</v>
+        <v>14.1</v>
       </c>
       <c r="H80" t="n">
-        <v>51.7</v>
+        <v>38.5</v>
       </c>
       <c r="I80" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
-        <v>29.7</v>
+        <v>22.1</v>
       </c>
       <c r="K80" t="n">
-        <v>14.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="B81" t="s">
         <v>107</v>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="D81" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>10.1</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E81"/>
       <c r="F81" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>14.1</v>
+        <v>42.9</v>
       </c>
       <c r="H81" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>22.1</v>
+        <v>14.3</v>
       </c>
       <c r="K81" t="n">
-        <v>6.2</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s">
         <v>107</v>
       </c>
       <c r="C82" t="n">
-        <v>28.6</v>
+        <v>63.6</v>
       </c>
       <c r="D82" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E82"/>
+        <v>64.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>25.5</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="G82" t="n">
-        <v>42.9</v>
+        <v>12.1</v>
       </c>
       <c r="H82" t="n">
-        <v>25</v>
+        <v>39.1</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>14.3</v>
+        <v>24.6</v>
       </c>
       <c r="K82" t="n">
-        <v>-42.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
         <v>107</v>
       </c>
       <c r="C83" t="n">
-        <v>63.6</v>
+        <v>48.6</v>
       </c>
       <c r="D83" t="n">
-        <v>64.4</v>
+        <v>56.4</v>
       </c>
       <c r="E83" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="F83" t="n">
-        <v>31.2</v>
+        <v>41.5</v>
       </c>
       <c r="G83" t="n">
-        <v>12.1</v>
+        <v>14.9</v>
       </c>
       <c r="H83" t="n">
-        <v>39.1</v>
+        <v>32.6</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
-        <v>24.6</v>
+        <v>33.6</v>
       </c>
       <c r="K83" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="B84" t="s">
         <v>107</v>
       </c>
       <c r="C84" t="n">
-        <v>48.6</v>
+        <v>57.6</v>
       </c>
       <c r="D84" t="n">
-        <v>56.4</v>
+        <v>58.9</v>
       </c>
       <c r="E84" t="n">
-        <v>22.6</v>
+        <v>16.9</v>
       </c>
       <c r="F84" t="n">
-        <v>41.5</v>
+        <v>23.5</v>
       </c>
       <c r="G84" t="n">
-        <v>14.9</v>
+        <v>6.2</v>
       </c>
       <c r="H84" t="n">
-        <v>32.6</v>
+        <v>43.1</v>
       </c>
       <c r="I84" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J84" t="n">
-        <v>33.6</v>
+        <v>21.1</v>
       </c>
       <c r="K84" t="n">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B85" t="s">
         <v>107</v>
       </c>
       <c r="C85" t="n">
-        <v>57.6</v>
+        <v>61.6</v>
       </c>
       <c r="D85" t="n">
-        <v>58.9</v>
+        <v>66.2</v>
       </c>
       <c r="E85" t="n">
-        <v>16.9</v>
+        <v>26.6</v>
       </c>
       <c r="F85" t="n">
-        <v>23.5</v>
+        <v>37.4</v>
       </c>
       <c r="G85" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H85" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="I85" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="K85" t="n">
-        <v>6.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="B86" t="s">
         <v>107</v>
       </c>
       <c r="C86" t="n">
-        <v>61.6</v>
+        <v>45.8</v>
       </c>
       <c r="D86" t="n">
-        <v>66.2</v>
+        <v>55.1</v>
       </c>
       <c r="E86" t="n">
-        <v>26.6</v>
+        <v>10.4</v>
       </c>
       <c r="F86" t="n">
-        <v>37.4</v>
+        <v>26.3</v>
       </c>
       <c r="G86" t="n">
-        <v>5.7</v>
+        <v>15.3</v>
       </c>
       <c r="H86" t="n">
-        <v>44.6</v>
+        <v>47.1</v>
       </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J86" t="n">
-        <v>21.4</v>
+        <v>33.9</v>
       </c>
       <c r="K86" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
       </c>
       <c r="C87" t="n">
-        <v>45.8</v>
+        <v>67.3</v>
       </c>
       <c r="D87" t="n">
-        <v>55.1</v>
+        <v>65.4</v>
       </c>
       <c r="E87" t="n">
-        <v>10.4</v>
+        <v>27.7</v>
       </c>
       <c r="F87" t="n">
-        <v>26.3</v>
+        <v>39.3</v>
       </c>
       <c r="G87" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
-        <v>33.9</v>
+        <v>29</v>
       </c>
       <c r="K87" t="n">
-        <v>1.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B88" t="s">
         <v>107</v>
       </c>
       <c r="C88" t="n">
-        <v>67.3</v>
+        <v>59.3</v>
       </c>
       <c r="D88" t="n">
-        <v>65.4</v>
+        <v>61.4</v>
       </c>
       <c r="E88" t="n">
-        <v>27.7</v>
+        <v>20</v>
       </c>
       <c r="F88" t="n">
-        <v>39.3</v>
+        <v>35</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="H88" t="n">
-        <v>46.7</v>
+        <v>56.4</v>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="K88" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B89" t="s">
         <v>107</v>
       </c>
       <c r="C89" t="n">
-        <v>59.3</v>
+        <v>52.6</v>
       </c>
       <c r="D89" t="n">
-        <v>61.4</v>
+        <v>55.6</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="F89" t="n">
-        <v>35</v>
+        <v>38.5</v>
       </c>
       <c r="G89" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="H89" t="n">
-        <v>56.4</v>
+        <v>30</v>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J89" t="n">
-        <v>28.2</v>
+        <v>24.9</v>
       </c>
       <c r="K89" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B90" t="s">
         <v>107</v>
       </c>
       <c r="C90" t="n">
-        <v>52.6</v>
+        <v>57.9</v>
       </c>
       <c r="D90" t="n">
-        <v>55.6</v>
+        <v>61.6</v>
       </c>
       <c r="E90" t="n">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="F90" t="n">
-        <v>38.5</v>
+        <v>39.4</v>
       </c>
       <c r="G90" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="H90" t="n">
-        <v>30</v>
+        <v>51.2</v>
       </c>
       <c r="I90" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J90" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="K90" t="n">
-        <v>3.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B91" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C91" t="n">
-        <v>57.9</v>
+        <v>74.2</v>
       </c>
       <c r="D91" t="n">
-        <v>61.6</v>
+        <v>69.7</v>
       </c>
       <c r="E91" t="n">
-        <v>21.3</v>
+        <v>39.1</v>
       </c>
       <c r="F91" t="n">
-        <v>39.4</v>
+        <v>33.3</v>
       </c>
       <c r="G91" t="n">
-        <v>7.6</v>
+        <v>9.7</v>
       </c>
       <c r="H91" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="I91" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>24.8</v>
+        <v>22.9</v>
       </c>
       <c r="K91" t="n">
-        <v>14.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B92" t="s">
         <v>128</v>
       </c>
       <c r="C92" t="n">
-        <v>74.2</v>
+        <v>64.4</v>
       </c>
       <c r="D92" t="n">
-        <v>69.7</v>
+        <v>57.5</v>
       </c>
       <c r="E92" t="n">
-        <v>39.1</v>
+        <v>17.9</v>
       </c>
       <c r="F92" t="n">
-        <v>33.3</v>
+        <v>41.9</v>
       </c>
       <c r="G92" t="n">
-        <v>9.7</v>
+        <v>15.3</v>
       </c>
       <c r="H92" t="n">
-        <v>52.2</v>
+        <v>40.5</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
-        <v>22.9</v>
+        <v>27.2</v>
       </c>
       <c r="K92" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B93" t="s">
         <v>128</v>
       </c>
       <c r="C93" t="n">
-        <v>64.4</v>
+        <v>57.5</v>
       </c>
       <c r="D93" t="n">
-        <v>57.5</v>
+        <v>63.9</v>
       </c>
       <c r="E93" t="n">
-        <v>17.9</v>
+        <v>26.6</v>
       </c>
       <c r="F93" t="n">
-        <v>41.9</v>
+        <v>36.8</v>
       </c>
       <c r="G93" t="n">
-        <v>15.3</v>
+        <v>7.4</v>
       </c>
       <c r="H93" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
-        <v>27.2</v>
+        <v>22.5</v>
       </c>
       <c r="K93" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B94" t="s">
         <v>128</v>
       </c>
       <c r="C94" t="n">
-        <v>57.5</v>
+        <v>80</v>
       </c>
       <c r="D94" t="n">
-        <v>63.9</v>
+        <v>68.6</v>
       </c>
       <c r="E94" t="n">
-        <v>26.6</v>
+        <v>21.4</v>
       </c>
       <c r="F94" t="n">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="G94" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="K94" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B95" t="s">
         <v>128</v>
       </c>
       <c r="C95" t="n">
-        <v>80</v>
+        <v>62.1</v>
       </c>
       <c r="D95" t="n">
-        <v>68.6</v>
+        <v>64.9</v>
       </c>
       <c r="E95" t="n">
-        <v>21.4</v>
+        <v>29.3</v>
       </c>
       <c r="F95" t="n">
-        <v>25</v>
+        <v>52.2</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H95" t="n">
-        <v>25</v>
+        <v>63.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
-        <v>15</v>
+        <v>33.1</v>
       </c>
       <c r="K95" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B96" t="s">
         <v>128</v>
       </c>
       <c r="C96" t="n">
-        <v>62.1</v>
+        <v>62.7</v>
       </c>
       <c r="D96" t="n">
-        <v>64.9</v>
+        <v>65.6</v>
       </c>
       <c r="E96" t="n">
-        <v>29.3</v>
+        <v>32.5</v>
       </c>
       <c r="F96" t="n">
-        <v>52.2</v>
+        <v>58.6</v>
       </c>
       <c r="G96" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="H96" t="n">
-        <v>63.5</v>
+        <v>55.6</v>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="K96" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B97" t="s">
         <v>128</v>
       </c>
       <c r="C97" t="n">
-        <v>62.7</v>
+        <v>74.3</v>
       </c>
       <c r="D97" t="n">
-        <v>65.6</v>
+        <v>71.8</v>
       </c>
       <c r="E97" t="n">
-        <v>32.5</v>
+        <v>28.1</v>
       </c>
       <c r="F97" t="n">
-        <v>58.6</v>
+        <v>42.9</v>
       </c>
       <c r="G97" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="H97" t="n">
-        <v>55.6</v>
+        <v>73.1</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
-        <v>33</v>
+        <v>24.6</v>
       </c>
       <c r="K97" t="n">
-        <v>20.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
       </c>
       <c r="C98" t="n">
-        <v>74.3</v>
+        <v>60.6</v>
       </c>
       <c r="D98" t="n">
-        <v>71.8</v>
+        <v>64.6</v>
       </c>
       <c r="E98" t="n">
-        <v>28.1</v>
+        <v>21.7</v>
       </c>
       <c r="F98" t="n">
-        <v>42.9</v>
+        <v>26.5</v>
       </c>
       <c r="G98" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
-        <v>73.1</v>
+        <v>67.9</v>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="K98" t="n">
-        <v>11.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B99" t="s">
         <v>128</v>
       </c>
       <c r="C99" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D99" t="n">
-        <v>64.6</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>21.7</v>
+        <v>31</v>
       </c>
       <c r="F99" t="n">
-        <v>26.5</v>
+        <v>54.5</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="H99" t="n">
-        <v>67.9</v>
+        <v>42.3</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
-        <v>19.3</v>
+        <v>37.3</v>
       </c>
       <c r="K99" t="n">
-        <v>7.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B100" t="s">
         <v>128</v>
       </c>
       <c r="C100" t="n">
-        <v>66.7</v>
+        <v>65.8</v>
       </c>
       <c r="D100" t="n">
-        <v>67.5</v>
+        <v>65.6</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>23.1</v>
       </c>
       <c r="F100" t="n">
-        <v>54.5</v>
+        <v>37.2</v>
       </c>
       <c r="G100" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H100" t="n">
-        <v>42.3</v>
+        <v>41.3</v>
       </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>37.3</v>
+        <v>21.5</v>
       </c>
       <c r="K100" t="n">
-        <v>19.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B101" t="s">
         <v>128</v>
       </c>
       <c r="C101" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="D101" t="n">
-        <v>65.6</v>
+        <v>68.8</v>
       </c>
       <c r="E101" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="F101" t="n">
-        <v>37.2</v>
+        <v>46.5</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="H101" t="n">
-        <v>41.3</v>
+        <v>42.3</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="K101" t="n">
-        <v>6.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
         <v>128</v>
       </c>
       <c r="C102" t="n">
-        <v>66.2</v>
+        <v>64.4</v>
       </c>
       <c r="D102" t="n">
-        <v>68.8</v>
+        <v>61.4</v>
       </c>
       <c r="E102" t="n">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="F102" t="n">
-        <v>46.5</v>
+        <v>58</v>
       </c>
       <c r="G102" t="n">
-        <v>1.9</v>
+        <v>16.4</v>
       </c>
       <c r="H102" t="n">
-        <v>42.3</v>
+        <v>32.3</v>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J102" t="n">
-        <v>21.9</v>
+        <v>36.4</v>
       </c>
       <c r="K102" t="n">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C103" t="n">
-        <v>64.4</v>
+        <v>33.3</v>
       </c>
       <c r="D103" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E103" t="n">
-        <v>13.4</v>
+        <v>36.4</v>
       </c>
       <c r="F103" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="H103" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>33.3</v>
       </c>
       <c r="J103" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>23.3</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B104" t="s">
         <v>145</v>
       </c>
       <c r="C104" t="n">
-        <v>33.3</v>
+        <v>58.8</v>
       </c>
       <c r="D104" t="n">
-        <v>56.2</v>
+        <v>59.6</v>
       </c>
       <c r="E104" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G104" t="n">
-        <v>33.3</v>
+        <v>13.7</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="I104" t="n">
-        <v>33.3</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="K104" t="n">
-        <v>-33.3</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>275</v>
+        <v>144</v>
       </c>
       <c r="B105" t="s">
         <v>145</v>
       </c>
       <c r="C105" t="n">
-        <v>58.8</v>
+        <v>51.6</v>
       </c>
       <c r="D105" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="E105" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F105" t="n">
-        <v>14.3</v>
+        <v>40.9</v>
       </c>
       <c r="G105" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="H105" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J105" t="n">
-        <v>14.5</v>
+        <v>24.4</v>
       </c>
       <c r="K105" t="n">
-        <v>-7.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>144</v>
+        <v>274</v>
       </c>
       <c r="B106" t="s">
         <v>145</v>
       </c>
       <c r="C106" t="n">
-        <v>51.6</v>
+        <v>62</v>
       </c>
       <c r="D106" t="n">
-        <v>58.9</v>
+        <v>65.2</v>
       </c>
       <c r="E106" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="F106" t="n">
-        <v>40.9</v>
+        <v>35.7</v>
       </c>
       <c r="G106" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="H106" t="n">
-        <v>44.4</v>
+        <v>37.7</v>
       </c>
       <c r="I106" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J106" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K106" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B107" t="s">
         <v>145</v>
       </c>
       <c r="C107" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D107" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="E107" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F107" t="n">
-        <v>35.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F107"/>
       <c r="G107" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
       <c r="H107" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>5.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B108" t="s">
         <v>145</v>
       </c>
       <c r="C108" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="D108" t="n">
-        <v>45.5</v>
+        <v>62.4</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108"/>
+        <v>23.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>30.5</v>
+      </c>
       <c r="G108" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>49.4</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="K108" t="n">
-        <v>-25</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B109" t="s">
         <v>145</v>
       </c>
       <c r="C109" t="n">
-        <v>65.8</v>
+        <v>51</v>
       </c>
       <c r="D109" t="n">
-        <v>62.4</v>
+        <v>58.9</v>
       </c>
       <c r="E109" t="n">
-        <v>23.5</v>
+        <v>13.2</v>
       </c>
       <c r="F109" t="n">
-        <v>30.5</v>
+        <v>25</v>
       </c>
       <c r="G109" t="n">
-        <v>12.9</v>
+        <v>6.4</v>
       </c>
       <c r="H109" t="n">
-        <v>49.4</v>
+        <v>41.7</v>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J109" t="n">
-        <v>25.9</v>
+        <v>19.2</v>
       </c>
       <c r="K109" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>279</v>
+        <v>155</v>
       </c>
       <c r="B110" t="s">
         <v>145</v>
       </c>
       <c r="C110" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="D110" t="n">
-        <v>58.9</v>
+        <v>59.9</v>
       </c>
       <c r="E110" t="n">
-        <v>13.2</v>
+        <v>30.4</v>
       </c>
       <c r="F110" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="G110" t="n">
-        <v>6.4</v>
+        <v>13.4</v>
       </c>
       <c r="H110" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="I110" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="J110" t="n">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="K110" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="B111" t="s">
         <v>145</v>
       </c>
       <c r="C111" t="n">
-        <v>51.5</v>
+        <v>63.3</v>
       </c>
       <c r="D111" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="E111" t="n">
-        <v>30.4</v>
+        <v>20.5</v>
       </c>
       <c r="F111" t="n">
-        <v>42.9</v>
+        <v>34.6</v>
       </c>
       <c r="G111" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="H111" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="I111" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
-        <v>28</v>
+        <v>22.8</v>
       </c>
       <c r="K111" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B112" t="s">
         <v>145</v>
       </c>
       <c r="C112" t="n">
-        <v>63.3</v>
+        <v>52.6</v>
       </c>
       <c r="D112" t="n">
-        <v>60.1</v>
+        <v>56.2</v>
       </c>
       <c r="E112" t="n">
-        <v>20.5</v>
+        <v>30</v>
       </c>
       <c r="F112" t="n">
-        <v>34.6</v>
+        <v>10</v>
       </c>
       <c r="G112" t="n">
         <v>16.7</v>
       </c>
       <c r="H112" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J112" t="n">
-        <v>22.8</v>
+        <v>15.2</v>
       </c>
       <c r="K112" t="n">
-        <v>2.1</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B113" t="s">
         <v>145</v>
       </c>
       <c r="C113" t="n">
-        <v>52.6</v>
+        <v>65.9</v>
       </c>
       <c r="D113" t="n">
-        <v>56.2</v>
+        <v>64.2</v>
       </c>
       <c r="E113" t="n">
-        <v>30</v>
+        <v>20.5</v>
       </c>
       <c r="F113" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="G113" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="H113" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="I113" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
-        <v>15.2</v>
+        <v>28.1</v>
       </c>
       <c r="K113" t="n">
-        <v>-11.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B114" t="s">
         <v>145</v>
       </c>
       <c r="C114" t="n">
-        <v>65.9</v>
+        <v>60</v>
       </c>
       <c r="D114" t="n">
-        <v>64.2</v>
+        <v>61.5</v>
       </c>
       <c r="E114" t="n">
-        <v>20.5</v>
+        <v>18.9</v>
       </c>
       <c r="F114" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G114" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H114" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="I114" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>28.1</v>
+        <v>35.6</v>
       </c>
       <c r="K114" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B115" t="s">
         <v>145</v>
       </c>
       <c r="C115" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D115" t="n">
-        <v>61.5</v>
+        <v>56.3</v>
       </c>
       <c r="E115" t="n">
-        <v>18.9</v>
+        <v>23.1</v>
       </c>
       <c r="F115" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="G115" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H115" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J115" t="n">
-        <v>35.6</v>
+        <v>26.5</v>
       </c>
       <c r="K115" t="n">
-        <v>15.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B116" t="s">
         <v>145</v>
       </c>
       <c r="C116" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="D116" t="n">
-        <v>56.3</v>
+        <v>52</v>
       </c>
       <c r="E116" t="n">
-        <v>23.1</v>
+        <v>16.3</v>
       </c>
       <c r="F116" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G116" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H116" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="I116" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J116" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="K116" t="n">
-        <v>12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B117" t="s">
         <v>145</v>
       </c>
       <c r="C117" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="D117" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="E117" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="F117" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G117" t="n">
-        <v>27.8</v>
+        <v>30</v>
       </c>
       <c r="H117" t="n">
-        <v>22.2</v>
+        <v>60</v>
       </c>
       <c r="I117" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
       <c r="K117" t="n">
-        <v>-11.1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B118" t="s">
         <v>145</v>
       </c>
       <c r="C118" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D118" t="n">
-        <v>48.8</v>
+        <v>61.8</v>
       </c>
       <c r="E118" t="n">
-        <v>13.6</v>
+        <v>19.7</v>
       </c>
       <c r="F118" t="n">
-        <v>50</v>
+        <v>29.1</v>
       </c>
       <c r="G118" t="n">
-        <v>30</v>
+        <v>7.7</v>
       </c>
       <c r="H118" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
       <c r="K118" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B119" t="s">
         <v>145</v>
       </c>
       <c r="C119" t="n">
-        <v>57.7</v>
+        <v>58</v>
       </c>
       <c r="D119" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="E119" t="n">
-        <v>19.7</v>
+        <v>24.1</v>
       </c>
       <c r="F119" t="n">
-        <v>29.1</v>
+        <v>32.9</v>
       </c>
       <c r="G119" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I119" t="n">
         <v>7.7</v>
       </c>
-      <c r="H119" t="n">
-        <v>57</v>
-      </c>
-      <c r="I119" t="n">
-        <v>2.7</v>
-      </c>
       <c r="J119" t="n">
-        <v>21.6</v>
+        <v>18.6</v>
       </c>
       <c r="K119" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B120" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C120" t="n">
-        <v>58</v>
+        <v>70.1</v>
       </c>
       <c r="D120" t="n">
-        <v>58.3</v>
+        <v>66.4</v>
       </c>
       <c r="E120" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="F120" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="G120" t="n">
-        <v>8.7</v>
+        <v>5.4</v>
       </c>
       <c r="H120" t="n">
-        <v>43.1</v>
+        <v>52.7</v>
       </c>
       <c r="I120" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="K120" t="n">
-        <v>3.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C121" t="n">
-        <v>70.1</v>
+        <v>61.6</v>
       </c>
       <c r="D121" t="n">
-        <v>66.4</v>
+        <v>65.8</v>
       </c>
       <c r="E121" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="F121" t="n">
-        <v>42.9</v>
+        <v>41.8</v>
       </c>
       <c r="G121" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="H121" t="n">
-        <v>52.7</v>
+        <v>47.1</v>
       </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
-        <v>22.3</v>
+        <v>20.1</v>
       </c>
       <c r="K121" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B122" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C122" t="n">
-        <v>61.6</v>
+        <v>60.7</v>
       </c>
       <c r="D122" t="n">
-        <v>65.8</v>
+        <v>64.8</v>
       </c>
       <c r="E122" t="n">
-        <v>20.2</v>
+        <v>11.2</v>
       </c>
       <c r="F122" t="n">
-        <v>41.8</v>
+        <v>32.4</v>
       </c>
       <c r="G122" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="H122" t="n">
-        <v>47.1</v>
+        <v>29.6</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="K122" t="n">
-        <v>13.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C123" t="n">
-        <v>60.7</v>
+        <v>58.2</v>
       </c>
       <c r="D123" t="n">
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E123" t="n">
-        <v>11.2</v>
+        <v>27.7</v>
       </c>
       <c r="F123" t="n">
-        <v>32.4</v>
+        <v>65.9</v>
       </c>
       <c r="G123" t="n">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
       <c r="H123" t="n">
-        <v>29.6</v>
+        <v>42.3</v>
       </c>
       <c r="I123" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J123" t="n">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="K123" t="n">
-        <v>5.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>292</v>
+        <v>217</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C124" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="D124" t="n">
-        <v>62.1</v>
+        <v>58.7</v>
       </c>
       <c r="E124" t="n">
-        <v>27.7</v>
+        <v>12.8</v>
       </c>
       <c r="F124" t="n">
-        <v>65.9</v>
+        <v>34.1</v>
       </c>
       <c r="G124" t="n">
         <v>11.1</v>
       </c>
       <c r="H124" t="n">
-        <v>42.3</v>
+        <v>35.5</v>
       </c>
       <c r="I124" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
-        <v>37</v>
+        <v>23.9</v>
       </c>
       <c r="K124" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C125" t="n">
-        <v>59.3</v>
+        <v>73.6</v>
       </c>
       <c r="D125" t="n">
-        <v>58.7</v>
+        <v>64.6</v>
       </c>
       <c r="E125" t="n">
-        <v>12.8</v>
+        <v>31</v>
       </c>
       <c r="F125" t="n">
-        <v>34.1</v>
+        <v>56.9</v>
       </c>
       <c r="G125" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="H125" t="n">
-        <v>35.5</v>
+        <v>44.1</v>
       </c>
       <c r="I125" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
-        <v>23.9</v>
+        <v>49.6</v>
       </c>
       <c r="K125" t="n">
-        <v>5.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C126" t="n">
-        <v>73.6</v>
+        <v>78.6</v>
       </c>
       <c r="D126" t="n">
-        <v>64.6</v>
-      </c>
-      <c r="E126" t="n">
-        <v>31</v>
-      </c>
+        <v>72.9</v>
+      </c>
+      <c r="E126"/>
       <c r="F126" t="n">
-        <v>56.9</v>
+        <v>45.5</v>
       </c>
       <c r="G126" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>44.1</v>
+        <v>46.5</v>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
-        <v>49.6</v>
+        <v>26.7</v>
       </c>
       <c r="K126" t="n">
-        <v>34.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B127" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C127" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D127" t="n">
-        <v>72.9</v>
-      </c>
-      <c r="E127"/>
+        <v>45.1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
       <c r="F127" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H127" t="n">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J127" t="n">
-        <v>26.7</v>
+        <v>31.2</v>
       </c>
       <c r="K127" t="n">
-        <v>18.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C128" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D128" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E128" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F128" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H128" t="n">
         <v>50</v>
       </c>
-      <c r="D128" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>25</v>
-      </c>
-      <c r="G128" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H128" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I128" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J128" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="K128" t="n">
-        <v>-23.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C129" t="n">
-        <v>61.3</v>
+        <v>65.8</v>
       </c>
       <c r="D129" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E129" t="n">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="F129" t="n">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="G129" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H129" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I129" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="K129" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B130" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C130" t="n">
-        <v>65.8</v>
+        <v>50.9</v>
       </c>
       <c r="D130" t="n">
-        <v>67.5</v>
+        <v>60.7</v>
       </c>
       <c r="E130" t="n">
-        <v>36.4</v>
+        <v>24.6</v>
       </c>
       <c r="F130" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G130" t="n">
-        <v>7.9</v>
+        <v>9.7</v>
       </c>
       <c r="H130" t="n">
-        <v>53.8</v>
+        <v>54.4</v>
       </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J130" t="n">
-        <v>26.8</v>
+        <v>21.7</v>
       </c>
       <c r="K130" t="n">
-        <v>13.2</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C131" t="n">
-        <v>50.9</v>
+        <v>66.7</v>
       </c>
       <c r="D131" t="n">
-        <v>60.7</v>
+        <v>56.7</v>
       </c>
       <c r="E131" t="n">
-        <v>24.6</v>
+        <v>14.3</v>
       </c>
       <c r="F131" t="n">
-        <v>38.6</v>
+        <v>50</v>
       </c>
       <c r="G131" t="n">
-        <v>9.7</v>
+        <v>22.2</v>
       </c>
       <c r="H131" t="n">
-        <v>54.4</v>
+        <v>20</v>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="K131" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C132" t="n">
-        <v>66.7</v>
+        <v>69.5</v>
       </c>
       <c r="D132" t="n">
-        <v>56.7</v>
+        <v>70.3</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="F132" t="n">
         <v>50</v>
       </c>
       <c r="G132" t="n">
-        <v>22.2</v>
+        <v>4.1</v>
       </c>
       <c r="H132" t="n">
-        <v>20</v>
+        <v>41.9</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C133" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
       <c r="D133" t="n">
-        <v>70.3</v>
+        <v>63</v>
       </c>
       <c r="E133" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F133" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G133" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H133" t="n">
         <v>50</v>
       </c>
-      <c r="G133" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H133" t="n">
-        <v>41.9</v>
-      </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
-        <v>26.3</v>
+        <v>21</v>
       </c>
       <c r="K133" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
-        <v>301</v>
-      </c>
+      <c r="A134"/>
       <c r="B134" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C134" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="D134" t="n">
-        <v>63</v>
+        <v>61.4</v>
       </c>
       <c r="E134" t="n">
-        <v>27</v>
+        <v>20.8</v>
       </c>
       <c r="F134" t="n">
-        <v>42.2</v>
+        <v>37.3</v>
       </c>
       <c r="G134" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="H134" t="n">
-        <v>50</v>
+        <v>46.1</v>
       </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
-        <v>21</v>
+        <v>24.9</v>
       </c>
       <c r="K134" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135"/>
-      <c r="B135" t="s">
-        <v>180</v>
-      </c>
-      <c r="C135" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="D135" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="E135" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F135" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="G135" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H135" t="n">
-        <v>46</v>
-      </c>
-      <c r="I135" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J135" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="K135" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>

--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -400,9 +400,6 @@
   </si>
   <si>
     <t xml:space="preserve">London Majors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Inoa</t>
   </si>
   <si>
     <t xml:space="preserve">Cleveland Brownlee</t>
@@ -967,8 +964,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K163" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K162" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K162"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -5203,24 +5200,32 @@
       <c r="B114" t="s">
         <v>128</v>
       </c>
-      <c r="C114"/>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
+      <c r="C114" t="n">
+        <v>80</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>80</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K114" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5231,31 +5236,31 @@
         <v>128</v>
       </c>
       <c r="C115" t="n">
-        <v>80</v>
+        <v>71.3</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="E115" t="n">
-        <v>80</v>
+        <v>49.4</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="G115" t="n">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="J115" t="n">
-        <v>100</v>
+        <v>31.2</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116">
@@ -5266,31 +5271,31 @@
         <v>128</v>
       </c>
       <c r="C116" t="n">
-        <v>71.3</v>
+        <v>68.2</v>
       </c>
       <c r="D116" t="n">
-        <v>21.9</v>
+        <v>24.5</v>
       </c>
       <c r="E116" t="n">
-        <v>49.4</v>
+        <v>43.7</v>
       </c>
       <c r="F116" t="n">
-        <v>21.9</v>
+        <v>24.5</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4</v>
+        <v>29.5</v>
       </c>
       <c r="H116" t="n">
-        <v>9.8</v>
+        <v>7.1</v>
       </c>
       <c r="I116" t="n">
-        <v>39.3</v>
+        <v>43.6</v>
       </c>
       <c r="J116" t="n">
-        <v>31.1</v>
+        <v>25.5</v>
       </c>
       <c r="K116" t="n">
-        <v>50.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="117">
@@ -5301,31 +5306,31 @@
         <v>128</v>
       </c>
       <c r="C117" t="n">
-        <v>68.2</v>
+        <v>79.5</v>
       </c>
       <c r="D117" t="n">
-        <v>24.5</v>
+        <v>31.9</v>
       </c>
       <c r="E117" t="n">
-        <v>43.7</v>
+        <v>47.6</v>
       </c>
       <c r="F117" t="n">
-        <v>24.5</v>
+        <v>31.9</v>
       </c>
       <c r="G117" t="n">
-        <v>29.5</v>
+        <v>25.8</v>
       </c>
       <c r="H117" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="I117" t="n">
-        <v>43.6</v>
+        <v>42.7</v>
       </c>
       <c r="J117" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="K117" t="n">
-        <v>47.3</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="118">
@@ -5336,31 +5341,31 @@
         <v>128</v>
       </c>
       <c r="C118" t="n">
-        <v>79.5</v>
+        <v>59.2</v>
       </c>
       <c r="D118" t="n">
-        <v>31.9</v>
+        <v>23.5</v>
       </c>
       <c r="E118" t="n">
-        <v>47.6</v>
+        <v>35.7</v>
       </c>
       <c r="F118" t="n">
-        <v>31.9</v>
+        <v>23.5</v>
       </c>
       <c r="G118" t="n">
-        <v>25.8</v>
+        <v>23.2</v>
       </c>
       <c r="H118" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="I118" t="n">
-        <v>42.7</v>
+        <v>62.3</v>
       </c>
       <c r="J118" t="n">
-        <v>25.6</v>
+        <v>15.1</v>
       </c>
       <c r="K118" t="n">
-        <v>30.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="119">
@@ -5371,31 +5376,31 @@
         <v>128</v>
       </c>
       <c r="C119" t="n">
-        <v>59.2</v>
+        <v>54.7</v>
       </c>
       <c r="D119" t="n">
-        <v>23.5</v>
+        <v>19.6</v>
       </c>
       <c r="E119" t="n">
-        <v>35.7</v>
+        <v>35.1</v>
       </c>
       <c r="F119" t="n">
-        <v>23.5</v>
+        <v>19.6</v>
       </c>
       <c r="G119" t="n">
-        <v>23.2</v>
+        <v>9.5</v>
       </c>
       <c r="H119" t="n">
-        <v>7.9</v>
+        <v>11.6</v>
       </c>
       <c r="I119" t="n">
-        <v>62.3</v>
+        <v>63.4</v>
       </c>
       <c r="J119" t="n">
-        <v>15.1</v>
+        <v>11.8</v>
       </c>
       <c r="K119" t="n">
-        <v>47.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120">
@@ -5406,31 +5411,31 @@
         <v>128</v>
       </c>
       <c r="C120" t="n">
-        <v>54.7</v>
+        <v>80</v>
       </c>
       <c r="D120" t="n">
-        <v>19.6</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="n">
-        <v>35.1</v>
+        <v>68.9</v>
       </c>
       <c r="F120" t="n">
-        <v>19.6</v>
+        <v>11.1</v>
       </c>
       <c r="G120" t="n">
-        <v>9.5</v>
+        <v>39.5</v>
       </c>
       <c r="H120" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="I120" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="J120" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="K120" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="121">
@@ -5441,31 +5446,31 @@
         <v>128</v>
       </c>
       <c r="C121" t="n">
-        <v>80</v>
+        <v>70.6</v>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>28.7</v>
       </c>
       <c r="E121" t="n">
-        <v>68.9</v>
+        <v>41.9</v>
       </c>
       <c r="F121" t="n">
-        <v>11.1</v>
+        <v>28.7</v>
       </c>
       <c r="G121" t="n">
-        <v>39.5</v>
+        <v>21.8</v>
       </c>
       <c r="H121" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="I121" t="n">
-        <v>63.6</v>
+        <v>39.6</v>
       </c>
       <c r="J121" t="n">
-        <v>9.1</v>
+        <v>31.5</v>
       </c>
       <c r="K121" t="n">
-        <v>45.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="122">
@@ -5476,31 +5481,31 @@
         <v>128</v>
       </c>
       <c r="C122" t="n">
-        <v>70.6</v>
+        <v>70</v>
       </c>
       <c r="D122" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="E122" t="n">
-        <v>41.9</v>
+        <v>43.3</v>
       </c>
       <c r="F122" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="G122" t="n">
-        <v>21.8</v>
+        <v>14.8</v>
       </c>
       <c r="H122" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="I122" t="n">
-        <v>39.6</v>
+        <v>60</v>
       </c>
       <c r="J122" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="K122" t="n">
-        <v>39.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
@@ -5511,31 +5516,31 @@
         <v>128</v>
       </c>
       <c r="C123" t="n">
-        <v>70</v>
+        <v>56.9</v>
       </c>
       <c r="D123" t="n">
-        <v>26.7</v>
+        <v>19.7</v>
       </c>
       <c r="E123" t="n">
-        <v>43.3</v>
+        <v>37.2</v>
       </c>
       <c r="F123" t="n">
-        <v>26.7</v>
+        <v>19.7</v>
       </c>
       <c r="G123" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="H123" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="I123" t="n">
-        <v>60</v>
+        <v>48.1</v>
       </c>
       <c r="J123" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="K123" t="n">
-        <v>10</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="124">
@@ -5546,31 +5551,31 @@
         <v>128</v>
       </c>
       <c r="C124" t="n">
-        <v>56.9</v>
+        <v>72.6</v>
       </c>
       <c r="D124" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
       </c>
       <c r="E124" t="n">
-        <v>37.2</v>
+        <v>51.5</v>
       </c>
       <c r="F124" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
       </c>
       <c r="G124" t="n">
-        <v>15.2</v>
+        <v>32.9</v>
       </c>
       <c r="H124" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="I124" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="J124" t="n">
-        <v>29.6</v>
+        <v>18.9</v>
       </c>
       <c r="K124" t="n">
-        <v>53.8</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="125">
@@ -5581,31 +5586,31 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>72.6</v>
+        <v>74.7</v>
       </c>
       <c r="D125" t="n">
-        <v>21.1</v>
+        <v>24.3</v>
       </c>
       <c r="E125" t="n">
-        <v>51.5</v>
+        <v>50.4</v>
       </c>
       <c r="F125" t="n">
-        <v>21.1</v>
+        <v>24.3</v>
       </c>
       <c r="G125" t="n">
-        <v>32.9</v>
+        <v>32</v>
       </c>
       <c r="H125" t="n">
-        <v>12.9</v>
+        <v>8.3</v>
       </c>
       <c r="I125" t="n">
-        <v>48.6</v>
+        <v>38.6</v>
       </c>
       <c r="J125" t="n">
-        <v>18.9</v>
+        <v>26.5</v>
       </c>
       <c r="K125" t="n">
-        <v>41.3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="126">
@@ -5616,31 +5621,31 @@
         <v>128</v>
       </c>
       <c r="C126" t="n">
-        <v>74.7</v>
+        <v>75.2</v>
       </c>
       <c r="D126" t="n">
-        <v>24.3</v>
+        <v>23.1</v>
       </c>
       <c r="E126" t="n">
-        <v>50.4</v>
+        <v>52.1</v>
       </c>
       <c r="F126" t="n">
-        <v>24.3</v>
+        <v>23.1</v>
       </c>
       <c r="G126" t="n">
-        <v>32</v>
+        <v>24.8</v>
       </c>
       <c r="H126" t="n">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="I126" t="n">
-        <v>38.6</v>
+        <v>41.1</v>
       </c>
       <c r="J126" t="n">
-        <v>26.5</v>
+        <v>33.7</v>
       </c>
       <c r="K126" t="n">
-        <v>39</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="127">
@@ -5651,31 +5656,31 @@
         <v>128</v>
       </c>
       <c r="C127" t="n">
-        <v>75.2</v>
+        <v>68.2</v>
       </c>
       <c r="D127" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="E127" t="n">
-        <v>52.1</v>
+        <v>50</v>
       </c>
       <c r="F127" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="G127" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="H127" t="n">
-        <v>8.2</v>
+        <v>11.9</v>
       </c>
       <c r="I127" t="n">
-        <v>41.1</v>
+        <v>48.3</v>
       </c>
       <c r="J127" t="n">
-        <v>33.7</v>
+        <v>17.2</v>
       </c>
       <c r="K127" t="n">
-        <v>49.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128">
@@ -5683,69 +5688,69 @@
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C128" t="n">
-        <v>68.2</v>
+        <v>72</v>
       </c>
       <c r="D128" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F128" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G128" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J128" t="n">
         <v>18.2</v>
       </c>
-      <c r="E128" t="n">
-        <v>50</v>
-      </c>
-      <c r="F128" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H128" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="I128" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J128" t="n">
-        <v>17.2</v>
-      </c>
       <c r="K128" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>145</v>
+      </c>
+      <c r="B129" t="s">
         <v>144</v>
       </c>
-      <c r="B129" t="s">
-        <v>145</v>
-      </c>
       <c r="C129" t="n">
-        <v>72</v>
+        <v>66.7</v>
       </c>
       <c r="D129" t="n">
-        <v>23.1</v>
+        <v>60</v>
       </c>
       <c r="E129" t="n">
-        <v>48.9</v>
+        <v>6.7</v>
       </c>
       <c r="F129" t="n">
-        <v>23.1</v>
+        <v>60</v>
       </c>
       <c r="G129" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I129" t="n">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="J129" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="K129" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5753,34 +5758,34 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C130" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="D130" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E130" t="n">
-        <v>6.7</v>
+        <v>46.2</v>
       </c>
       <c r="F130" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G130" t="n">
-        <v>33.3</v>
+        <v>14.1</v>
       </c>
       <c r="H130" t="n">
-        <v>11.1</v>
+        <v>5.1</v>
       </c>
       <c r="I130" t="n">
-        <v>25</v>
+        <v>43.9</v>
       </c>
       <c r="J130" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="131">
@@ -5788,34 +5793,34 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C131" t="n">
-        <v>66.2</v>
+        <v>35</v>
       </c>
       <c r="D131" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E131" t="n">
-        <v>46.2</v>
+        <v>21.7</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="G131" t="n">
-        <v>14.1</v>
+        <v>33.3</v>
       </c>
       <c r="H131" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>43.9</v>
+        <v>50</v>
       </c>
       <c r="J131" t="n">
-        <v>24.6</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>41.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5823,34 +5828,34 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C132" t="n">
-        <v>35</v>
+        <v>72.2</v>
       </c>
       <c r="D132" t="n">
-        <v>13.3</v>
+        <v>28</v>
       </c>
       <c r="E132" t="n">
-        <v>21.7</v>
+        <v>44.2</v>
       </c>
       <c r="F132" t="n">
-        <v>13.3</v>
+        <v>28</v>
       </c>
       <c r="G132" t="n">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>9.8</v>
       </c>
       <c r="I132" t="n">
         <v>50</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="133">
@@ -5858,34 +5863,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C133" t="n">
-        <v>72.2</v>
+        <v>74.6</v>
       </c>
       <c r="D133" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="E133" t="n">
-        <v>44.2</v>
+        <v>47.4</v>
       </c>
       <c r="F133" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="G133" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="H133" t="n">
-        <v>9.8</v>
+        <v>9.7</v>
       </c>
       <c r="I133" t="n">
-        <v>50</v>
+        <v>46.6</v>
       </c>
       <c r="J133" t="n">
-        <v>23.7</v>
+        <v>27.6</v>
       </c>
       <c r="K133" t="n">
-        <v>42.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="134">
@@ -5893,34 +5898,34 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C134" t="n">
-        <v>74.6</v>
+        <v>48.1</v>
       </c>
       <c r="D134" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="E134" t="n">
-        <v>47.4</v>
+        <v>23.1</v>
       </c>
       <c r="F134" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="G134" t="n">
-        <v>30.6</v>
+        <v>15.4</v>
       </c>
       <c r="H134" t="n">
-        <v>9.7</v>
+        <v>18.8</v>
       </c>
       <c r="I134" t="n">
-        <v>46.6</v>
+        <v>44.4</v>
       </c>
       <c r="J134" t="n">
-        <v>27.6</v>
+        <v>22.2</v>
       </c>
       <c r="K134" t="n">
-        <v>38.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="135">
@@ -5928,34 +5933,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C135" t="n">
-        <v>48.1</v>
+        <v>66</v>
       </c>
       <c r="D135" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="E135" t="n">
-        <v>23.1</v>
+        <v>41.7</v>
       </c>
       <c r="F135" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="G135" t="n">
-        <v>15.4</v>
+        <v>21.9</v>
       </c>
       <c r="H135" t="n">
-        <v>18.8</v>
+        <v>7.7</v>
       </c>
       <c r="I135" t="n">
-        <v>44.4</v>
+        <v>54.3</v>
       </c>
       <c r="J135" t="n">
-        <v>22.2</v>
+        <v>15.7</v>
       </c>
       <c r="K135" t="n">
-        <v>11.1</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="136">
@@ -5963,34 +5968,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C136" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="D136" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="F136" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>21.9</v>
+        <v>18.2</v>
       </c>
       <c r="H136" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>54.3</v>
+        <v>75</v>
       </c>
       <c r="J136" t="n">
-        <v>15.7</v>
+        <v>25</v>
       </c>
       <c r="K136" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -5998,34 +6003,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C137" t="n">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="E137" t="n">
-        <v>66.7</v>
+        <v>52.8</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="G137" t="n">
-        <v>18.2</v>
+        <v>27.4</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I137" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="J137" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="138">
@@ -6033,34 +6038,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C138" t="n">
-        <v>72.2</v>
+        <v>50</v>
       </c>
       <c r="D138" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="E138" t="n">
-        <v>52.8</v>
+        <v>35.7</v>
       </c>
       <c r="F138" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="G138" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="H138" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="I138" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K138" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139">
@@ -6068,34 +6073,34 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C139" t="n">
-        <v>50</v>
+        <v>68.5</v>
       </c>
       <c r="D139" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="E139" t="n">
-        <v>35.7</v>
+        <v>39.5</v>
       </c>
       <c r="F139" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="G139" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="H139" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="I139" t="n">
-        <v>75</v>
+        <v>35.9</v>
       </c>
       <c r="J139" t="n">
-        <v>25</v>
+        <v>28.1</v>
       </c>
       <c r="K139" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="140">
@@ -6103,104 +6108,104 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C140" t="n">
-        <v>68.5</v>
+        <v>65.8</v>
       </c>
       <c r="D140" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E140" t="n">
-        <v>39.5</v>
+        <v>41.8</v>
       </c>
       <c r="F140" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G140" t="n">
-        <v>31.8</v>
+        <v>21.9</v>
       </c>
       <c r="H140" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="I140" t="n">
-        <v>35.9</v>
+        <v>59.7</v>
       </c>
       <c r="J140" t="n">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
       <c r="K140" t="n">
-        <v>43.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C141" t="n">
-        <v>65.8</v>
+        <v>56.1</v>
       </c>
       <c r="D141" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="E141" t="n">
-        <v>41.8</v>
+        <v>36.9</v>
       </c>
       <c r="F141" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="G141" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="H141" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>59.7</v>
+        <v>40.5</v>
       </c>
       <c r="J141" t="n">
-        <v>23.9</v>
+        <v>27</v>
       </c>
       <c r="K141" t="n">
-        <v>30.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C142" t="n">
-        <v>56.1</v>
+        <v>79.6</v>
       </c>
       <c r="D142" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="E142" t="n">
-        <v>36.9</v>
+        <v>42.8</v>
       </c>
       <c r="F142" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="G142" t="n">
-        <v>22.5</v>
+        <v>34.2</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I142" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
       <c r="J142" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143">
@@ -6208,34 +6213,34 @@
         <v>158</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C143" t="n">
-        <v>79.6</v>
+        <v>57.8</v>
       </c>
       <c r="D143" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="E143" t="n">
-        <v>42.8</v>
+        <v>43.7</v>
       </c>
       <c r="F143" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="G143" t="n">
-        <v>34.2</v>
+        <v>12.5</v>
       </c>
       <c r="H143" t="n">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="I143" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="J143" t="n">
-        <v>20</v>
+        <v>9.7</v>
       </c>
       <c r="K143" t="n">
-        <v>44</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="144">
@@ -6243,34 +6248,34 @@
         <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C144" t="n">
-        <v>57.8</v>
+        <v>63.2</v>
       </c>
       <c r="D144" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="E144" t="n">
-        <v>43.7</v>
+        <v>18.2</v>
       </c>
       <c r="F144" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="G144" t="n">
-        <v>12.5</v>
+        <v>26.9</v>
       </c>
       <c r="H144" t="n">
-        <v>10.2</v>
+        <v>7.7</v>
       </c>
       <c r="I144" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>9.7</v>
+        <v>25</v>
       </c>
       <c r="K144" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145">
@@ -6278,34 +6283,34 @@
         <v>160</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C145" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="D145" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="E145" t="n">
-        <v>18.2</v>
+        <v>62.1</v>
       </c>
       <c r="F145" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="G145" t="n">
-        <v>26.9</v>
+        <v>23.4</v>
       </c>
       <c r="H145" t="n">
-        <v>7.7</v>
+        <v>14.8</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="J145" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K145" t="n">
-        <v>25</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="146">
@@ -6313,34 +6318,34 @@
         <v>161</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C146" t="n">
         <v>74.2</v>
       </c>
       <c r="D146" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="E146" t="n">
-        <v>62.1</v>
+        <v>48.1</v>
       </c>
       <c r="F146" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="G146" t="n">
-        <v>23.4</v>
+        <v>9.2</v>
       </c>
       <c r="H146" t="n">
-        <v>14.8</v>
+        <v>2.2</v>
       </c>
       <c r="I146" t="n">
-        <v>32.9</v>
+        <v>48.1</v>
       </c>
       <c r="J146" t="n">
-        <v>37</v>
+        <v>20.8</v>
       </c>
       <c r="K146" t="n">
-        <v>38.4</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="147">
@@ -6348,69 +6353,69 @@
         <v>162</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C147" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="D147" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="E147" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="F147" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="G147" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H147" t="n">
         <v>9.2</v>
       </c>
-      <c r="H147" t="n">
-        <v>2.2</v>
-      </c>
       <c r="I147" t="n">
-        <v>48.1</v>
+        <v>51.9</v>
       </c>
       <c r="J147" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="K147" t="n">
-        <v>32.5</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>164</v>
+      </c>
+      <c r="B148" t="s">
         <v>163</v>
       </c>
-      <c r="B148" t="s">
-        <v>164</v>
-      </c>
       <c r="C148" t="n">
-        <v>70.5</v>
+        <v>68.6</v>
       </c>
       <c r="D148" t="n">
         <v>20.5</v>
       </c>
       <c r="E148" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F148" t="n">
         <v>20.5</v>
       </c>
       <c r="G148" t="n">
-        <v>37.7</v>
+        <v>14.9</v>
       </c>
       <c r="H148" t="n">
-        <v>9.2</v>
+        <v>6.6</v>
       </c>
       <c r="I148" t="n">
-        <v>51.9</v>
+        <v>57.3</v>
       </c>
       <c r="J148" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="K148" t="n">
-        <v>39.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="149">
@@ -6418,34 +6423,34 @@
         <v>165</v>
       </c>
       <c r="B149" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C149" t="n">
-        <v>68.6</v>
+        <v>64.6</v>
       </c>
       <c r="D149" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E149" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F149" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G149" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H149" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I149" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J149" t="n">
         <v>48.1</v>
       </c>
-      <c r="F149" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G149" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H149" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I149" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J149" t="n">
-        <v>18.7</v>
-      </c>
       <c r="K149" t="n">
-        <v>45.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="150">
@@ -6453,34 +6458,34 @@
         <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C150" t="n">
-        <v>64.6</v>
+        <v>60</v>
       </c>
       <c r="D150" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E150" t="n">
-        <v>47.9</v>
+        <v>38.9</v>
       </c>
       <c r="F150" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G150" t="n">
-        <v>37.7</v>
+        <v>32.4</v>
       </c>
       <c r="H150" t="n">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="I150" t="n">
-        <v>29.6</v>
+        <v>34.8</v>
       </c>
       <c r="J150" t="n">
-        <v>48.1</v>
+        <v>30.4</v>
       </c>
       <c r="K150" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="151">
@@ -6488,34 +6493,34 @@
         <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C151" t="n">
-        <v>60</v>
+        <v>66.3</v>
       </c>
       <c r="D151" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E151" t="n">
-        <v>38.9</v>
+        <v>51.9</v>
       </c>
       <c r="F151" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="G151" t="n">
-        <v>32.4</v>
+        <v>9</v>
       </c>
       <c r="H151" t="n">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="I151" t="n">
-        <v>34.8</v>
+        <v>62.2</v>
       </c>
       <c r="J151" t="n">
-        <v>30.4</v>
+        <v>17.3</v>
       </c>
       <c r="K151" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="152">
@@ -6523,34 +6528,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C152" t="n">
-        <v>66.3</v>
+        <v>80.4</v>
       </c>
       <c r="D152" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="E152" t="n">
-        <v>51.9</v>
+        <v>63.9</v>
       </c>
       <c r="F152" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="G152" t="n">
-        <v>9</v>
+        <v>23.3</v>
       </c>
       <c r="H152" t="n">
-        <v>18.2</v>
+        <v>9.4</v>
       </c>
       <c r="I152" t="n">
-        <v>62.2</v>
+        <v>36.2</v>
       </c>
       <c r="J152" t="n">
-        <v>17.3</v>
+        <v>34</v>
       </c>
       <c r="K152" t="n">
-        <v>36.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="153">
@@ -6558,34 +6563,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C153" t="n">
-        <v>80.4</v>
+        <v>55.6</v>
       </c>
       <c r="D153" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="E153" t="n">
-        <v>63.9</v>
+        <v>38</v>
       </c>
       <c r="F153" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="G153" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="H153" t="n">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="I153" t="n">
-        <v>36.2</v>
+        <v>47.4</v>
       </c>
       <c r="J153" t="n">
-        <v>34</v>
+        <v>22.8</v>
       </c>
       <c r="K153" t="n">
-        <v>44.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="154">
@@ -6593,34 +6598,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C154" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D154" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F154" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>25.7</v>
+        <v>66.7</v>
       </c>
       <c r="H154" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6628,34 +6633,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C155" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E155" t="n">
-        <v>75</v>
+        <v>38.6</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G155" t="n">
-        <v>66.7</v>
+        <v>14.6</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="156">
@@ -6663,34 +6668,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C156" t="n">
-        <v>56.2</v>
+        <v>61.4</v>
       </c>
       <c r="D156" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="E156" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="F156" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="G156" t="n">
-        <v>14.6</v>
+        <v>9.8</v>
       </c>
       <c r="H156" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="I156" t="n">
-        <v>37</v>
+        <v>60.4</v>
       </c>
       <c r="J156" t="n">
-        <v>28.8</v>
+        <v>18</v>
       </c>
       <c r="K156" t="n">
-        <v>49.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="157">
@@ -6698,34 +6703,34 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C157" t="n">
-        <v>61.4</v>
+        <v>71.5</v>
       </c>
       <c r="D157" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E157" t="n">
-        <v>40.6</v>
+        <v>54.8</v>
       </c>
       <c r="F157" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="G157" t="n">
-        <v>9.8</v>
+        <v>24.7</v>
       </c>
       <c r="H157" t="n">
-        <v>8.5</v>
+        <v>11.8</v>
       </c>
       <c r="I157" t="n">
-        <v>60.4</v>
+        <v>34.8</v>
       </c>
       <c r="J157" t="n">
-        <v>18</v>
+        <v>31.5</v>
       </c>
       <c r="K157" t="n">
-        <v>29.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="158">
@@ -6733,34 +6738,34 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C158" t="n">
-        <v>71.5</v>
+        <v>77.2</v>
       </c>
       <c r="D158" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="E158" t="n">
-        <v>54.8</v>
+        <v>47.3</v>
       </c>
       <c r="F158" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="G158" t="n">
-        <v>24.7</v>
+        <v>41.7</v>
       </c>
       <c r="H158" t="n">
-        <v>11.8</v>
+        <v>6.9</v>
       </c>
       <c r="I158" t="n">
-        <v>34.8</v>
+        <v>44.4</v>
       </c>
       <c r="J158" t="n">
-        <v>31.5</v>
+        <v>22.2</v>
       </c>
       <c r="K158" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="159">
@@ -6768,34 +6773,34 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C159" t="n">
-        <v>77.2</v>
+        <v>75.5</v>
       </c>
       <c r="D159" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="E159" t="n">
-        <v>47.3</v>
+        <v>55.1</v>
       </c>
       <c r="F159" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="G159" t="n">
-        <v>41.7</v>
+        <v>19.7</v>
       </c>
       <c r="H159" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="I159" t="n">
-        <v>44.4</v>
+        <v>27.9</v>
       </c>
       <c r="J159" t="n">
-        <v>22.2</v>
+        <v>33.7</v>
       </c>
       <c r="K159" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="160">
@@ -6803,57 +6808,51 @@
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C160" t="n">
-        <v>75.5</v>
+        <v>37.5</v>
       </c>
       <c r="D160" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="E160" t="n">
-        <v>55.1</v>
+        <v>4.2</v>
       </c>
       <c r="F160" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="G160" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>11</v>
-      </c>
-      <c r="I160" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J160" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K160" t="n">
-        <v>46.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I160"/>
+      <c r="J160"/>
+      <c r="K160"/>
     </row>
     <row r="161">
       <c r="A161" t="s">
         <v>177</v>
       </c>
       <c r="B161" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C161" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
         <v>33.3</v>
       </c>
       <c r="E161" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F161" t="n">
         <v>33.3</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -6863,64 +6862,35 @@
       <c r="K161"/>
     </row>
     <row r="162">
-      <c r="A162" t="s">
+      <c r="A162"/>
+      <c r="B162" t="s">
         <v>178</v>
       </c>
-      <c r="B162" t="s">
-        <v>164</v>
-      </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>67.8</v>
       </c>
       <c r="D162" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="E162" t="n">
-        <v>-33.3</v>
+        <v>46</v>
       </c>
       <c r="F162" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="G162" t="n">
-        <v>100</v>
+        <v>27.1</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162"/>
-      <c r="J162"/>
-      <c r="K162"/>
-    </row>
-    <row r="163">
-      <c r="A163"/>
-      <c r="B163" t="s">
-        <v>179</v>
-      </c>
-      <c r="C163" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="D163" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E163" t="n">
-        <v>46</v>
-      </c>
-      <c r="F163" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G163" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="H163" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I163" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="J163" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I162" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J162" t="n">
         <v>24.3</v>
       </c>
-      <c r="K163" t="n">
+      <c r="K162" t="n">
         <v>39.6</v>
       </c>
     </row>
@@ -6953,22 +6923,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6977,18 +6947,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7023,7 +6993,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7058,7 +7028,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7163,7 +7133,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7198,7 +7168,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7233,7 +7203,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7303,7 +7273,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7338,7 +7308,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7373,7 +7343,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7408,7 +7378,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7443,7 +7413,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -7511,7 +7481,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -7546,7 +7516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -7581,7 +7551,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -7651,7 +7621,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
@@ -7686,7 +7656,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
@@ -7721,7 +7691,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -7756,7 +7726,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -7791,7 +7761,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -7826,7 +7796,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
@@ -7861,7 +7831,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -7896,7 +7866,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -7931,7 +7901,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
@@ -7966,7 +7936,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -8001,7 +7971,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -8036,7 +8006,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -8071,7 +8041,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
@@ -8106,7 +8076,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
@@ -8141,7 +8111,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
@@ -8176,7 +8146,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B36" t="s">
         <v>49</v>
@@ -8246,7 +8216,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
@@ -8281,7 +8251,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
@@ -8316,7 +8286,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
         <v>49</v>
@@ -8384,7 +8354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
@@ -8419,7 +8389,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -8454,7 +8424,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
@@ -8489,7 +8459,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -8524,7 +8494,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
@@ -8559,7 +8529,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s">
         <v>49</v>
@@ -8594,7 +8564,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
         <v>49</v>
@@ -8627,7 +8597,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
         <v>49</v>
@@ -8662,7 +8632,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s">
         <v>67</v>
@@ -8697,7 +8667,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
         <v>67</v>
@@ -8732,7 +8702,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
         <v>67</v>
@@ -8767,7 +8737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
@@ -8835,7 +8805,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s">
         <v>67</v>
@@ -8870,7 +8840,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
@@ -8940,7 +8910,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
@@ -8975,7 +8945,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
@@ -9010,7 +8980,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
@@ -9045,7 +9015,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -9080,7 +9050,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
@@ -9150,7 +9120,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -9220,7 +9190,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B66" t="s">
         <v>92</v>
@@ -9255,7 +9225,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" t="s">
         <v>92</v>
@@ -9290,7 +9260,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B68" t="s">
         <v>92</v>
@@ -9325,7 +9295,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B69" t="s">
         <v>92</v>
@@ -9360,7 +9330,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" t="s">
         <v>92</v>
@@ -9395,7 +9365,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B71" t="s">
         <v>92</v>
@@ -9430,7 +9400,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
         <v>92</v>
@@ -9465,7 +9435,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B73" t="s">
         <v>92</v>
@@ -9500,7 +9470,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" t="s">
         <v>92</v>
@@ -9535,7 +9505,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B75" t="s">
         <v>92</v>
@@ -9570,7 +9540,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
         <v>92</v>
@@ -9605,7 +9575,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" t="s">
         <v>92</v>
@@ -9640,7 +9610,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s">
         <v>107</v>
@@ -9675,7 +9645,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B79" t="s">
         <v>107</v>
@@ -9710,7 +9680,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B80" t="s">
         <v>107</v>
@@ -9745,7 +9715,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
         <v>107</v>
@@ -9778,7 +9748,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
         <v>107</v>
@@ -9813,7 +9783,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
         <v>107</v>
@@ -9918,7 +9888,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B86" t="s">
         <v>107</v>
@@ -9953,7 +9923,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
@@ -9988,7 +9958,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B88" t="s">
         <v>107</v>
@@ -10023,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B89" t="s">
         <v>107</v>
@@ -10058,7 +10028,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B90" t="s">
         <v>107</v>
@@ -10093,7 +10063,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
         <v>128</v>
@@ -10128,7 +10098,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
         <v>128</v>
@@ -10163,7 +10133,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
         <v>128</v>
@@ -10198,7 +10168,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
         <v>128</v>
@@ -10233,7 +10203,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
         <v>128</v>
@@ -10268,7 +10238,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
         <v>128</v>
@@ -10303,7 +10273,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
         <v>128</v>
@@ -10338,7 +10308,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
@@ -10373,7 +10343,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
         <v>128</v>
@@ -10408,7 +10378,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
         <v>128</v>
@@ -10443,7 +10413,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B101" t="s">
         <v>128</v>
@@ -10478,7 +10448,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B102" t="s">
         <v>128</v>
@@ -10513,10 +10483,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C103" t="n">
         <v>33.3</v>
@@ -10548,10 +10518,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B104" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C104" t="n">
         <v>58.8</v>
@@ -10583,10 +10553,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>143</v>
+      </c>
+      <c r="B105" t="s">
         <v>144</v>
-      </c>
-      <c r="B105" t="s">
-        <v>145</v>
       </c>
       <c r="C105" t="n">
         <v>51.6</v>
@@ -10618,10 +10588,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C106" t="n">
         <v>62</v>
@@ -10653,10 +10623,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C107" t="n">
         <v>50</v>
@@ -10686,10 +10656,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C108" t="n">
         <v>65.8</v>
@@ -10721,10 +10691,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C109" t="n">
         <v>51</v>
@@ -10756,10 +10726,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C110" t="n">
         <v>51.5</v>
@@ -10791,10 +10761,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C111" t="n">
         <v>63.3</v>
@@ -10826,10 +10796,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C112" t="n">
         <v>52.6</v>
@@ -10861,10 +10831,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C113" t="n">
         <v>65.9</v>
@@ -10896,10 +10866,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C114" t="n">
         <v>60</v>
@@ -10931,10 +10901,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C115" t="n">
         <v>44</v>
@@ -10966,10 +10936,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C116" t="n">
         <v>38.9</v>
@@ -11001,10 +10971,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C117" t="n">
         <v>50</v>
@@ -11036,10 +11006,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C118" t="n">
         <v>57.7</v>
@@ -11071,10 +11041,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C119" t="n">
         <v>58</v>
@@ -11106,10 +11076,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B120" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C120" t="n">
         <v>70.1</v>
@@ -11141,10 +11111,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B121" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C121" t="n">
         <v>61.6</v>
@@ -11176,10 +11146,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C122" t="n">
         <v>60.7</v>
@@ -11211,10 +11181,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C123" t="n">
         <v>58.2</v>
@@ -11246,10 +11216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B124" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C124" t="n">
         <v>59.3</v>
@@ -11281,10 +11251,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B125" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C125" t="n">
         <v>73.6</v>
@@ -11316,10 +11286,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B126" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C126" t="n">
         <v>78.6</v>
@@ -11349,10 +11319,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B127" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C127" t="n">
         <v>50</v>
@@ -11384,10 +11354,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C128" t="n">
         <v>61.3</v>
@@ -11419,10 +11389,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B129" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C129" t="n">
         <v>65.8</v>
@@ -11454,10 +11424,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B130" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C130" t="n">
         <v>50.9</v>
@@ -11489,10 +11459,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B131" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C131" t="n">
         <v>66.7</v>
@@ -11524,10 +11494,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B132" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C132" t="n">
         <v>69.5</v>
@@ -11559,10 +11529,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B133" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C133" t="n">
         <v>59</v>
@@ -11595,7 +11565,7 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C134" t="n">
         <v>59.3</v>

--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t xml:space="preserve">Brandon Hernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Daley</t>
   </si>
   <si>
     <t xml:space="preserve">Brendon Daley</t>
@@ -964,8 +961,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K162" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K161" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K161"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -1436,31 +1433,31 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3</v>
+        <v>13.6</v>
       </c>
       <c r="E5" t="n">
-        <v>57.9</v>
+        <v>50.2</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3</v>
+        <v>13.6</v>
       </c>
       <c r="G5" t="n">
-        <v>38.5</v>
+        <v>42.1</v>
       </c>
       <c r="H5" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1471,31 +1468,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>64.3</v>
+        <v>80.8</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>44.3</v>
+        <v>63.8</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>44</v>
+        <v>34.8</v>
       </c>
       <c r="H6" t="n">
-        <v>11.8</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="J6" t="n">
-        <v>44.4</v>
+        <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="7">
@@ -1506,31 +1503,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>80.8</v>
+        <v>59.6</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>22.7</v>
       </c>
       <c r="E7" t="n">
-        <v>63.8</v>
+        <v>36.9</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>22.7</v>
       </c>
       <c r="G7" t="n">
-        <v>34.8</v>
+        <v>32.2</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>46.4</v>
+        <v>38.9</v>
       </c>
       <c r="J7" t="n">
-        <v>29</v>
+        <v>44.4</v>
       </c>
       <c r="K7" t="n">
-        <v>31.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="8">
@@ -1541,31 +1538,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>59.6</v>
+        <v>69.6</v>
       </c>
       <c r="D8" t="n">
-        <v>22.7</v>
+        <v>11.9</v>
       </c>
       <c r="E8" t="n">
-        <v>36.9</v>
+        <v>57.7</v>
       </c>
       <c r="F8" t="n">
-        <v>22.7</v>
+        <v>11.9</v>
       </c>
       <c r="G8" t="n">
-        <v>32.2</v>
+        <v>37</v>
       </c>
       <c r="H8" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="I8" t="n">
-        <v>38.9</v>
+        <v>44.1</v>
       </c>
       <c r="J8" t="n">
-        <v>44.4</v>
+        <v>29.4</v>
       </c>
       <c r="K8" t="n">
-        <v>66.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -1576,31 +1573,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>69.6</v>
+        <v>54.6</v>
       </c>
       <c r="D9" t="n">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="E9" t="n">
-        <v>57.7</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="G9" t="n">
-        <v>37</v>
+        <v>22.4</v>
       </c>
       <c r="H9" t="n">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="I9" t="n">
-        <v>44.1</v>
+        <v>56</v>
       </c>
       <c r="J9" t="n">
-        <v>29.4</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="10">
@@ -1611,31 +1608,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>54.6</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>22.4</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1646,31 +1643,31 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>52.2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>24.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="12">
@@ -1681,31 +1678,31 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>52.6</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="E12" t="n">
-        <v>52.2</v>
+        <v>36.8</v>
       </c>
       <c r="F12" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="G12" t="n">
-        <v>24.5</v>
+        <v>22.6</v>
       </c>
       <c r="H12" t="n">
-        <v>15.5</v>
+        <v>9.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.7</v>
+        <v>62.5</v>
       </c>
       <c r="J12" t="n">
-        <v>41.7</v>
+        <v>31.2</v>
       </c>
       <c r="K12" t="n">
-        <v>43.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="13">
@@ -1716,32 +1713,30 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.6</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>36.8</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>22.6</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>33.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -1751,30 +1746,32 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>47.9</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>17.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I14" t="n">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14"/>
+        <v>38.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>61.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -1784,31 +1781,31 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>66.7</v>
+        <v>70.6</v>
       </c>
       <c r="D15" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="n">
-        <v>47.9</v>
+        <v>53.9</v>
       </c>
       <c r="F15" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="G15" t="n">
-        <v>17.2</v>
+        <v>24.3</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>42.2</v>
       </c>
       <c r="J15" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>61.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="16">
@@ -1819,31 +1816,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70.6</v>
+        <v>70.1</v>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>23.9</v>
       </c>
       <c r="E16" t="n">
-        <v>53.9</v>
+        <v>46.2</v>
       </c>
       <c r="F16" t="n">
-        <v>16.7</v>
+        <v>23.9</v>
       </c>
       <c r="G16" t="n">
-        <v>24.3</v>
+        <v>24.8</v>
       </c>
       <c r="H16" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="I16" t="n">
-        <v>42.2</v>
+        <v>65.2</v>
       </c>
       <c r="J16" t="n">
-        <v>40</v>
+        <v>18.2</v>
       </c>
       <c r="K16" t="n">
-        <v>55.6</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="17">
@@ -1854,31 +1851,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>70.1</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
-        <v>23.9</v>
+        <v>20.9</v>
       </c>
       <c r="E17" t="n">
-        <v>46.2</v>
+        <v>54.1</v>
       </c>
       <c r="F17" t="n">
-        <v>23.9</v>
+        <v>20.9</v>
       </c>
       <c r="G17" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="I17" t="n">
-        <v>65.2</v>
+        <v>48.6</v>
       </c>
       <c r="J17" t="n">
-        <v>18.2</v>
+        <v>26.4</v>
       </c>
       <c r="K17" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="18">
@@ -1889,31 +1886,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>75</v>
+        <v>69.7</v>
       </c>
       <c r="D18" t="n">
-        <v>20.9</v>
+        <v>35.7</v>
       </c>
       <c r="E18" t="n">
-        <v>54.1</v>
+        <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>20.9</v>
+        <v>35.7</v>
       </c>
       <c r="G18" t="n">
-        <v>26</v>
+        <v>23.3</v>
       </c>
       <c r="H18" t="n">
-        <v>10.6</v>
+        <v>7.9</v>
       </c>
       <c r="I18" t="n">
-        <v>48.6</v>
+        <v>39.6</v>
       </c>
       <c r="J18" t="n">
-        <v>26.4</v>
+        <v>29.2</v>
       </c>
       <c r="K18" t="n">
-        <v>33.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -1924,31 +1921,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>69.7</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>35.7</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>41.7</v>
       </c>
       <c r="F19" t="n">
-        <v>35.7</v>
+        <v>13.3</v>
       </c>
       <c r="G19" t="n">
-        <v>23.3</v>
+        <v>11.1</v>
       </c>
       <c r="H19" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>39.6</v>
+        <v>33.3</v>
       </c>
       <c r="J19" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
       <c r="K19" t="n">
-        <v>31.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="20">
@@ -1959,31 +1956,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>79.5</v>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>29.8</v>
       </c>
       <c r="E20" t="n">
-        <v>41.7</v>
+        <v>49.7</v>
       </c>
       <c r="F20" t="n">
-        <v>13.3</v>
+        <v>29.8</v>
       </c>
       <c r="G20" t="n">
-        <v>11.1</v>
+        <v>30</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>33.3</v>
+        <v>40.4</v>
       </c>
       <c r="J20" t="n">
         <v>33.3</v>
       </c>
       <c r="K20" t="n">
-        <v>16.7</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="21">
@@ -1991,69 +1988,69 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>79.5</v>
+        <v>62.1</v>
       </c>
       <c r="D21" t="n">
-        <v>29.8</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>49.7</v>
+        <v>37.1</v>
       </c>
       <c r="F21" t="n">
-        <v>29.8</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>40.4</v>
+        <v>46.2</v>
       </c>
       <c r="J21" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="K21" t="n">
-        <v>43.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
         <v>32</v>
       </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
       <c r="C22" t="n">
-        <v>62.1</v>
+        <v>74.7</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="E22" t="n">
-        <v>37.1</v>
+        <v>47.8</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>22.3</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>46.2</v>
+        <v>36.2</v>
       </c>
       <c r="J22" t="n">
-        <v>23.1</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>38.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="23">
@@ -2061,34 +2058,34 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
-        <v>74.7</v>
+        <v>59.9</v>
       </c>
       <c r="D23" t="n">
-        <v>26.9</v>
+        <v>16.9</v>
       </c>
       <c r="E23" t="n">
-        <v>47.8</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>26.9</v>
+        <v>16.9</v>
       </c>
       <c r="G23" t="n">
-        <v>22.3</v>
+        <v>34.3</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2</v>
+        <v>15.9</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>42.3</v>
       </c>
       <c r="J23" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="K23" t="n">
-        <v>46.4</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="24">
@@ -2096,34 +2093,34 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>59.9</v>
+        <v>66.7</v>
       </c>
       <c r="D24" t="n">
-        <v>16.9</v>
+        <v>19.8</v>
       </c>
       <c r="E24" t="n">
-        <v>43</v>
+        <v>46.9</v>
       </c>
       <c r="F24" t="n">
-        <v>16.9</v>
+        <v>19.8</v>
       </c>
       <c r="G24" t="n">
-        <v>34.3</v>
+        <v>28.4</v>
       </c>
       <c r="H24" t="n">
-        <v>15.9</v>
+        <v>3.3</v>
       </c>
       <c r="I24" t="n">
-        <v>42.3</v>
+        <v>54.1</v>
       </c>
       <c r="J24" t="n">
-        <v>30.8</v>
+        <v>9.8</v>
       </c>
       <c r="K24" t="n">
-        <v>35.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="25">
@@ -2131,34 +2128,34 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>66.7</v>
       </c>
       <c r="D25" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>46.9</v>
+        <v>66.7</v>
       </c>
       <c r="F25" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>28.4</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>54.1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>9.8</v>
+        <v>50</v>
       </c>
       <c r="K25" t="n">
-        <v>38.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -2166,34 +2163,34 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>66.7</v>
+        <v>81.1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E26" t="n">
-        <v>66.7</v>
+        <v>58.6</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>50</v>
+        <v>19.4</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="27">
@@ -2201,34 +2198,34 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>81.1</v>
+        <v>76.2</v>
       </c>
       <c r="D27" t="n">
-        <v>22.5</v>
+        <v>27.6</v>
       </c>
       <c r="E27" t="n">
-        <v>58.6</v>
+        <v>48.6</v>
       </c>
       <c r="F27" t="n">
-        <v>22.5</v>
+        <v>27.6</v>
       </c>
       <c r="G27" t="n">
-        <v>22.4</v>
+        <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>46.8</v>
       </c>
       <c r="J27" t="n">
-        <v>19.4</v>
+        <v>24.1</v>
       </c>
       <c r="K27" t="n">
-        <v>48.4</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="28">
@@ -2236,34 +2233,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>76.2</v>
+        <v>47.5</v>
       </c>
       <c r="D28" t="n">
-        <v>27.6</v>
+        <v>6.1</v>
       </c>
       <c r="E28" t="n">
-        <v>48.6</v>
+        <v>41.4</v>
       </c>
       <c r="F28" t="n">
-        <v>27.6</v>
+        <v>6.1</v>
       </c>
       <c r="G28" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>16.7</v>
       </c>
       <c r="I28" t="n">
-        <v>46.8</v>
+        <v>90.9</v>
       </c>
       <c r="J28" t="n">
-        <v>24.1</v>
+        <v>9.1</v>
       </c>
       <c r="K28" t="n">
-        <v>46.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="29">
@@ -2271,34 +2268,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>47.5</v>
+        <v>73.9</v>
       </c>
       <c r="D29" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="E29" t="n">
-        <v>41.4</v>
+        <v>68.3</v>
       </c>
       <c r="F29" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="G29" t="n">
-        <v>17.9</v>
+        <v>22.7</v>
       </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="I29" t="n">
-        <v>90.9</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>9.1</v>
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>18.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="30">
@@ -2306,34 +2303,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>73.9</v>
+        <v>70.4</v>
       </c>
       <c r="D30" t="n">
-        <v>5.6</v>
+        <v>17.1</v>
       </c>
       <c r="E30" t="n">
-        <v>68.3</v>
+        <v>53.3</v>
       </c>
       <c r="F30" t="n">
-        <v>5.6</v>
+        <v>17.1</v>
       </c>
       <c r="G30" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>11.6</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>47.2</v>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
       <c r="K30" t="n">
-        <v>37.5</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="31">
@@ -2341,34 +2338,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>70.4</v>
+        <v>65.5</v>
       </c>
       <c r="D31" t="n">
-        <v>17.1</v>
+        <v>24.2</v>
       </c>
       <c r="E31" t="n">
-        <v>53.3</v>
+        <v>41.3</v>
       </c>
       <c r="F31" t="n">
-        <v>17.1</v>
+        <v>24.2</v>
       </c>
       <c r="G31" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
       </c>
       <c r="H31" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>47.2</v>
+        <v>57.9</v>
       </c>
       <c r="J31" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="K31" t="n">
-        <v>43.7</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="32">
@@ -2376,34 +2373,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>65.5</v>
+        <v>54.2</v>
       </c>
       <c r="D32" t="n">
-        <v>24.2</v>
+        <v>45.8</v>
       </c>
       <c r="E32" t="n">
-        <v>41.3</v>
+        <v>8.4</v>
       </c>
       <c r="F32" t="n">
-        <v>24.2</v>
+        <v>45.8</v>
       </c>
       <c r="G32" t="n">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>57.9</v>
+        <v>47.4</v>
       </c>
       <c r="J32" t="n">
-        <v>21.1</v>
+        <v>31.6</v>
       </c>
       <c r="K32" t="n">
-        <v>29.8</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="33">
@@ -2411,34 +2408,34 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>54.2</v>
+        <v>61.5</v>
       </c>
       <c r="D33" t="n">
-        <v>45.8</v>
+        <v>13.7</v>
       </c>
       <c r="E33" t="n">
-        <v>8.4</v>
+        <v>47.8</v>
       </c>
       <c r="F33" t="n">
-        <v>45.8</v>
+        <v>13.7</v>
       </c>
       <c r="G33" t="n">
-        <v>25.5</v>
+        <v>15.3</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="I33" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="J33" t="n">
-        <v>31.6</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>44.4</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="34">
@@ -2446,34 +2443,34 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>61.5</v>
+        <v>68.2</v>
       </c>
       <c r="D34" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="E34" t="n">
-        <v>47.8</v>
+        <v>47.3</v>
       </c>
       <c r="F34" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="G34" t="n">
-        <v>15.3</v>
+        <v>28.1</v>
       </c>
       <c r="H34" t="n">
-        <v>18.7</v>
+        <v>9.3</v>
       </c>
       <c r="I34" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="J34" t="n">
-        <v>23</v>
+        <v>16.4</v>
       </c>
       <c r="K34" t="n">
-        <v>37.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="35">
@@ -2481,34 +2478,34 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
-        <v>68.2</v>
+        <v>74.2</v>
       </c>
       <c r="D35" t="n">
-        <v>20.9</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>47.3</v>
+        <v>49.2</v>
       </c>
       <c r="F35" t="n">
-        <v>20.9</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="H35" t="n">
-        <v>9.3</v>
+        <v>1.5</v>
       </c>
       <c r="I35" t="n">
-        <v>49.2</v>
+        <v>45.8</v>
       </c>
       <c r="J35" t="n">
-        <v>16.4</v>
+        <v>29.2</v>
       </c>
       <c r="K35" t="n">
-        <v>43.1</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="36">
@@ -2516,69 +2513,69 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C36" t="n">
-        <v>74.2</v>
+        <v>76.1</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="E36" t="n">
-        <v>49.2</v>
+        <v>54.4</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="G36" t="n">
-        <v>28.2</v>
+        <v>34.8</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="I36" t="n">
-        <v>45.8</v>
+        <v>63.2</v>
       </c>
       <c r="J36" t="n">
-        <v>29.2</v>
+        <v>23.7</v>
       </c>
       <c r="K36" t="n">
-        <v>37.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
         <v>48</v>
       </c>
-      <c r="B37" t="s">
-        <v>49</v>
-      </c>
       <c r="C37" t="n">
-        <v>76.1</v>
+        <v>65.3</v>
       </c>
       <c r="D37" t="n">
-        <v>21.7</v>
+        <v>17.5</v>
       </c>
       <c r="E37" t="n">
-        <v>54.4</v>
+        <v>47.8</v>
       </c>
       <c r="F37" t="n">
-        <v>21.7</v>
+        <v>17.5</v>
       </c>
       <c r="G37" t="n">
-        <v>34.8</v>
+        <v>17.6</v>
       </c>
       <c r="H37" t="n">
-        <v>10.5</v>
+        <v>6.9</v>
       </c>
       <c r="I37" t="n">
-        <v>63.2</v>
+        <v>40.7</v>
       </c>
       <c r="J37" t="n">
-        <v>23.7</v>
+        <v>31.9</v>
       </c>
       <c r="K37" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,34 +2583,34 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" t="n">
-        <v>65.3</v>
+        <v>78.9</v>
       </c>
       <c r="D38" t="n">
-        <v>17.5</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="n">
-        <v>47.8</v>
+        <v>65.6</v>
       </c>
       <c r="F38" t="n">
-        <v>17.5</v>
+        <v>13.3</v>
       </c>
       <c r="G38" t="n">
         <v>17.6</v>
       </c>
       <c r="H38" t="n">
-        <v>6.9</v>
+        <v>12.5</v>
       </c>
       <c r="I38" t="n">
-        <v>40.7</v>
+        <v>66.7</v>
       </c>
       <c r="J38" t="n">
-        <v>31.9</v>
+        <v>16.7</v>
       </c>
       <c r="K38" t="n">
-        <v>45.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -2621,34 +2618,28 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" t="n">
-        <v>78.9</v>
-      </c>
-      <c r="D39" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E39" t="n">
-        <v>65.6</v>
-      </c>
-      <c r="F39" t="n">
-        <v>13.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
       <c r="G39" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2656,28 +2647,34 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>100</v>
-      </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
+        <v>72.4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14.3</v>
+      </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I40" t="n">
-        <v>100</v>
+        <v>51.9</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="41">
@@ -2685,34 +2682,34 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" t="n">
-        <v>72.4</v>
+        <v>78.5</v>
       </c>
       <c r="D41" t="n">
-        <v>14.3</v>
+        <v>27.1</v>
       </c>
       <c r="E41" t="n">
-        <v>58.1</v>
+        <v>51.4</v>
       </c>
       <c r="F41" t="n">
-        <v>14.3</v>
+        <v>27.1</v>
       </c>
       <c r="G41" t="n">
-        <v>12.9</v>
+        <v>25.4</v>
       </c>
       <c r="H41" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>51.9</v>
+        <v>48.2</v>
       </c>
       <c r="J41" t="n">
-        <v>24.7</v>
+        <v>31.3</v>
       </c>
       <c r="K41" t="n">
-        <v>25.9</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="42">
@@ -2720,34 +2717,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" t="n">
-        <v>78.5</v>
+        <v>67.3</v>
       </c>
       <c r="D42" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="E42" t="n">
-        <v>51.4</v>
+        <v>39.2</v>
       </c>
       <c r="F42" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="G42" t="n">
-        <v>25.4</v>
+        <v>13.2</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="I42" t="n">
-        <v>48.2</v>
+        <v>36</v>
       </c>
       <c r="J42" t="n">
-        <v>31.3</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>38.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="43">
@@ -2755,34 +2752,30 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" t="n">
-        <v>67.3</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C43"/>
       <c r="D43" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>39.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E43"/>
       <c r="F43" t="n">
-        <v>28.1</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>29.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -2790,30 +2783,34 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44"/>
+        <v>48</v>
+      </c>
+      <c r="C44" t="n">
+        <v>65.7</v>
+      </c>
       <c r="D44" t="n">
-        <v>100</v>
-      </c>
-      <c r="E44"/>
+        <v>25.8</v>
+      </c>
+      <c r="E44" t="n">
+        <v>39.9</v>
+      </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>25.8</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I44" t="n">
-        <v>100</v>
+        <v>53.2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="45">
@@ -2821,34 +2818,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>65.7</v>
+        <v>77.3</v>
       </c>
       <c r="D45" t="n">
-        <v>25.8</v>
+        <v>22.5</v>
       </c>
       <c r="E45" t="n">
-        <v>39.9</v>
+        <v>54.8</v>
       </c>
       <c r="F45" t="n">
-        <v>25.8</v>
+        <v>22.5</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>41.2</v>
       </c>
       <c r="H45" t="n">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="I45" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="J45" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="K45" t="n">
-        <v>20.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="46">
@@ -2856,34 +2853,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" t="n">
-        <v>77.3</v>
+        <v>79.4</v>
       </c>
       <c r="D46" t="n">
-        <v>22.5</v>
+        <v>37</v>
       </c>
       <c r="E46" t="n">
-        <v>54.8</v>
+        <v>42.4</v>
       </c>
       <c r="F46" t="n">
-        <v>22.5</v>
+        <v>37</v>
       </c>
       <c r="G46" t="n">
-        <v>41.2</v>
+        <v>39.1</v>
       </c>
       <c r="H46" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
-        <v>55.6</v>
+        <v>48.1</v>
       </c>
       <c r="J46" t="n">
-        <v>22.2</v>
+        <v>29.6</v>
       </c>
       <c r="K46" t="n">
-        <v>25.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="47">
@@ -2891,34 +2888,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" t="n">
-        <v>79.4</v>
+        <v>50.7</v>
       </c>
       <c r="D47" t="n">
-        <v>37</v>
+        <v>17.9</v>
       </c>
       <c r="E47" t="n">
-        <v>42.4</v>
+        <v>32.8</v>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>17.9</v>
       </c>
       <c r="G47" t="n">
-        <v>39.1</v>
+        <v>18.3</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>17.1</v>
       </c>
       <c r="I47" t="n">
-        <v>48.1</v>
+        <v>38.5</v>
       </c>
       <c r="J47" t="n">
-        <v>29.6</v>
+        <v>30.8</v>
       </c>
       <c r="K47" t="n">
-        <v>40.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="48">
@@ -2926,34 +2923,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" t="n">
-        <v>50.7</v>
+        <v>69.3</v>
       </c>
       <c r="D48" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="E48" t="n">
-        <v>32.8</v>
+        <v>54.5</v>
       </c>
       <c r="F48" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="G48" t="n">
-        <v>18.3</v>
+        <v>31.2</v>
       </c>
       <c r="H48" t="n">
-        <v>17.1</v>
+        <v>12.5</v>
       </c>
       <c r="I48" t="n">
-        <v>38.5</v>
+        <v>36.7</v>
       </c>
       <c r="J48" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="K48" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -2961,34 +2958,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>69.3</v>
+        <v>68.1</v>
       </c>
       <c r="D49" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="E49" t="n">
-        <v>54.5</v>
+        <v>42.6</v>
       </c>
       <c r="F49" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="G49" t="n">
-        <v>31.2</v>
+        <v>51.6</v>
       </c>
       <c r="H49" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="I49" t="n">
-        <v>36.7</v>
+        <v>47.1</v>
       </c>
       <c r="J49" t="n">
-        <v>40</v>
+        <v>17.6</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="50">
@@ -2996,34 +2993,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>68.1</v>
+        <v>70.7</v>
       </c>
       <c r="D50" t="n">
-        <v>25.5</v>
+        <v>14.3</v>
       </c>
       <c r="E50" t="n">
-        <v>42.6</v>
+        <v>56.4</v>
       </c>
       <c r="F50" t="n">
-        <v>25.5</v>
+        <v>14.3</v>
       </c>
       <c r="G50" t="n">
-        <v>51.6</v>
+        <v>21.6</v>
       </c>
       <c r="H50" t="n">
-        <v>6.5</v>
+        <v>13.3</v>
       </c>
       <c r="I50" t="n">
-        <v>47.1</v>
+        <v>61.9</v>
       </c>
       <c r="J50" t="n">
-        <v>17.6</v>
+        <v>14.3</v>
       </c>
       <c r="K50" t="n">
-        <v>29.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="51">
@@ -3031,34 +3028,34 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51" t="n">
-        <v>70.7</v>
+        <v>69.3</v>
       </c>
       <c r="D51" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="n">
-        <v>56.4</v>
+        <v>54.7</v>
       </c>
       <c r="F51" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G51" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="H51" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
       <c r="I51" t="n">
-        <v>61.9</v>
+        <v>38.8</v>
       </c>
       <c r="J51" t="n">
-        <v>14.3</v>
+        <v>32.8</v>
       </c>
       <c r="K51" t="n">
-        <v>21.4</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="52">
@@ -3066,34 +3063,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52" t="n">
-        <v>69.3</v>
+        <v>77.8</v>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="E52" t="n">
-        <v>54.7</v>
+        <v>65.6</v>
       </c>
       <c r="F52" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="G52" t="n">
-        <v>25.6</v>
+        <v>33.8</v>
       </c>
       <c r="H52" t="n">
-        <v>9.6</v>
+        <v>13.6</v>
       </c>
       <c r="I52" t="n">
-        <v>38.8</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>32.8</v>
+        <v>41.5</v>
       </c>
       <c r="K52" t="n">
-        <v>38.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="53">
@@ -3101,69 +3098,69 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C53" t="n">
-        <v>77.8</v>
+        <v>76.8</v>
       </c>
       <c r="D53" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="E53" t="n">
-        <v>65.6</v>
+        <v>53.5</v>
       </c>
       <c r="F53" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="G53" t="n">
-        <v>33.8</v>
+        <v>30.6</v>
       </c>
       <c r="H53" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>52.1</v>
       </c>
       <c r="J53" t="n">
-        <v>41.5</v>
+        <v>18.8</v>
       </c>
       <c r="K53" t="n">
-        <v>50.8</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="B54" t="s">
-        <v>67</v>
-      </c>
       <c r="C54" t="n">
-        <v>76.8</v>
+        <v>78.9</v>
       </c>
       <c r="D54" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="E54" t="n">
-        <v>53.5</v>
+        <v>45.6</v>
       </c>
       <c r="F54" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="G54" t="n">
-        <v>30.6</v>
+        <v>23.5</v>
       </c>
       <c r="H54" t="n">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
       <c r="I54" t="n">
-        <v>52.1</v>
+        <v>40.8</v>
       </c>
       <c r="J54" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="K54" t="n">
-        <v>43.8</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="55">
@@ -3171,34 +3168,34 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="n">
-        <v>78.9</v>
+        <v>59.6</v>
       </c>
       <c r="D55" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="E55" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="F55" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="G55" t="n">
-        <v>23.5</v>
+        <v>26.1</v>
       </c>
       <c r="H55" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="I55" t="n">
-        <v>40.8</v>
+        <v>54.9</v>
       </c>
       <c r="J55" t="n">
-        <v>22.4</v>
+        <v>17.6</v>
       </c>
       <c r="K55" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
@@ -3206,34 +3203,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" t="n">
-        <v>59.6</v>
+        <v>69.2</v>
       </c>
       <c r="D56" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E56" t="n">
-        <v>46.3</v>
+        <v>52.5</v>
       </c>
       <c r="F56" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="G56" t="n">
-        <v>26.1</v>
+        <v>42.9</v>
       </c>
       <c r="H56" t="n">
-        <v>13.6</v>
+        <v>23.1</v>
       </c>
       <c r="I56" t="n">
-        <v>54.9</v>
+        <v>42.9</v>
       </c>
       <c r="J56" t="n">
-        <v>17.6</v>
+        <v>57.1</v>
       </c>
       <c r="K56" t="n">
-        <v>34</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="57">
@@ -3241,98 +3238,98 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="E57" t="n">
-        <v>52.5</v>
+        <v>-100</v>
       </c>
       <c r="F57" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I57" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>28.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>57.8</v>
       </c>
       <c r="D58" t="n">
-        <v>100</v>
+        <v>45.7</v>
       </c>
       <c r="E58" t="n">
-        <v>-100</v>
+        <v>12.1</v>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>45.7</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58"/>
+        <v>3.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" t="n">
-        <v>57.8</v>
+        <v>57.1</v>
       </c>
       <c r="D59" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="n">
-        <v>12.1</v>
+        <v>44.6</v>
       </c>
       <c r="F59" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="G59" t="n">
-        <v>31</v>
+        <v>14.3</v>
       </c>
       <c r="H59" t="n">
-        <v>3.4</v>
+        <v>16.7</v>
       </c>
       <c r="I59" t="n">
-        <v>47.4</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>42.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60">
@@ -3340,34 +3337,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E60" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F60" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G60" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="H60" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I60" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K60" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
@@ -3375,34 +3372,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C61" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D61" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F61" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G61" t="n">
-        <v>38.1</v>
+        <v>41.2</v>
       </c>
       <c r="H61" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I61" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -3410,34 +3407,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" t="n">
-        <v>72.4</v>
+        <v>46.4</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="n">
-        <v>62.4</v>
+        <v>33.2</v>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="G62" t="n">
-        <v>41.2</v>
+        <v>14.3</v>
       </c>
       <c r="H62" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I62" t="n">
+        <v>30</v>
+      </c>
+      <c r="J62" t="n">
+        <v>40</v>
+      </c>
+      <c r="K62" t="n">
         <v>50</v>
-      </c>
-      <c r="J62" t="n">
-        <v>30</v>
-      </c>
-      <c r="K62" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -3445,34 +3442,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>46.4</v>
+        <v>70.2</v>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>17.8</v>
       </c>
       <c r="E63" t="n">
-        <v>33.2</v>
+        <v>52.4</v>
       </c>
       <c r="F63" t="n">
-        <v>13.2</v>
+        <v>17.8</v>
       </c>
       <c r="G63" t="n">
-        <v>14.3</v>
+        <v>23.5</v>
       </c>
       <c r="H63" t="n">
-        <v>20</v>
+        <v>15.7</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>50.6</v>
       </c>
       <c r="J63" t="n">
-        <v>40</v>
+        <v>20.8</v>
       </c>
       <c r="K63" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="64">
@@ -3480,34 +3477,28 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="D64" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E64" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F64" t="n">
-        <v>17.8</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
       <c r="G64" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>50.6</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>20.8</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
@@ -3515,28 +3506,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C65" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
+        <v>81</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>64.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>16.1</v>
+      </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>50</v>
+        <v>15.4</v>
       </c>
       <c r="K65" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="66">
@@ -3544,34 +3541,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C66" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D66" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="E66" t="n">
-        <v>64.9</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="H66" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -3579,19 +3576,19 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D67" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G67" t="n">
         <v>25</v>
@@ -3600,13 +3597,13 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -3614,34 +3611,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C68" t="n">
+        <v>74.4</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G68" t="n">
         <v>33.3</v>
       </c>
-      <c r="D68" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G68" t="n">
-        <v>25</v>
-      </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I68" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="69">
@@ -3649,34 +3646,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C69" t="n">
-        <v>74.4</v>
+        <v>69.6</v>
       </c>
       <c r="D69" t="n">
-        <v>3.1</v>
+        <v>33.3</v>
       </c>
       <c r="E69" t="n">
-        <v>71.3</v>
+        <v>36.3</v>
       </c>
       <c r="F69" t="n">
-        <v>3.1</v>
+        <v>33.3</v>
       </c>
       <c r="G69" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="I69" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="J69" t="n">
-        <v>11.1</v>
+        <v>30.8</v>
       </c>
       <c r="K69" t="n">
-        <v>11.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="70">
@@ -3684,34 +3681,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" t="n">
-        <v>69.6</v>
+        <v>61.1</v>
       </c>
       <c r="D70" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="E70" t="n">
-        <v>36.3</v>
+        <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="G70" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H70" t="n">
-        <v>11.8</v>
+        <v>14.3</v>
       </c>
       <c r="I70" t="n">
-        <v>46.2</v>
+        <v>37.5</v>
       </c>
       <c r="J70" t="n">
-        <v>30.8</v>
+        <v>37.5</v>
       </c>
       <c r="K70" t="n">
-        <v>53.8</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="71">
@@ -3719,34 +3716,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" t="n">
-        <v>61.1</v>
+        <v>68.6</v>
       </c>
       <c r="D71" t="n">
-        <v>23.1</v>
+        <v>31.8</v>
       </c>
       <c r="E71" t="n">
-        <v>38</v>
+        <v>36.8</v>
       </c>
       <c r="F71" t="n">
-        <v>23.1</v>
+        <v>31.8</v>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>14.3</v>
+        <v>3.4</v>
       </c>
       <c r="I71" t="n">
-        <v>37.5</v>
+        <v>47.6</v>
       </c>
       <c r="J71" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="K71" t="n">
-        <v>71.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="72">
@@ -3754,34 +3751,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C72" t="n">
-        <v>68.6</v>
+        <v>66.4</v>
       </c>
       <c r="D72" t="n">
-        <v>31.8</v>
+        <v>14.9</v>
       </c>
       <c r="E72" t="n">
-        <v>36.8</v>
+        <v>51.5</v>
       </c>
       <c r="F72" t="n">
-        <v>31.8</v>
+        <v>14.9</v>
       </c>
       <c r="G72" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="H72" t="n">
-        <v>3.4</v>
+        <v>10.3</v>
       </c>
       <c r="I72" t="n">
-        <v>47.6</v>
+        <v>38.7</v>
       </c>
       <c r="J72" t="n">
-        <v>28.6</v>
+        <v>34.7</v>
       </c>
       <c r="K72" t="n">
-        <v>38.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="73">
@@ -3789,34 +3786,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C73" t="n">
-        <v>66.4</v>
+        <v>80.8</v>
       </c>
       <c r="D73" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="E73" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="F73" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="G73" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="H73" t="n">
-        <v>10.3</v>
+        <v>3.2</v>
       </c>
       <c r="I73" t="n">
-        <v>38.7</v>
+        <v>42.9</v>
       </c>
       <c r="J73" t="n">
-        <v>34.7</v>
+        <v>35.2</v>
       </c>
       <c r="K73" t="n">
-        <v>47.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="74">
@@ -3824,34 +3821,34 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C74" t="n">
-        <v>80.8</v>
+        <v>56.1</v>
       </c>
       <c r="D74" t="n">
-        <v>33.3</v>
+        <v>9.8</v>
       </c>
       <c r="E74" t="n">
-        <v>47.5</v>
+        <v>46.3</v>
       </c>
       <c r="F74" t="n">
-        <v>33.3</v>
+        <v>9.8</v>
       </c>
       <c r="G74" t="n">
-        <v>26.1</v>
+        <v>30.6</v>
       </c>
       <c r="H74" t="n">
-        <v>3.2</v>
+        <v>17.7</v>
       </c>
       <c r="I74" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="J74" t="n">
-        <v>35.2</v>
+        <v>21.8</v>
       </c>
       <c r="K74" t="n">
-        <v>50.5</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="75">
@@ -3859,34 +3856,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C75" t="n">
-        <v>56.1</v>
+        <v>66.7</v>
       </c>
       <c r="D75" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>46.3</v>
+        <v>66.7</v>
       </c>
       <c r="F75" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>30.6</v>
+        <v>26.7</v>
       </c>
       <c r="H75" t="n">
-        <v>17.7</v>
+        <v>16.7</v>
       </c>
       <c r="I75" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K75" t="n">
         <v>54.5</v>
-      </c>
-      <c r="J75" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K75" t="n">
-        <v>30.8</v>
       </c>
     </row>
     <row r="76">
@@ -3894,34 +3891,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C76" t="n">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="E76" t="n">
-        <v>66.7</v>
+        <v>58.7</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="G76" t="n">
-        <v>26.7</v>
+        <v>30.4</v>
       </c>
       <c r="H76" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="I76" t="n">
-        <v>27.3</v>
+        <v>46.9</v>
       </c>
       <c r="J76" t="n">
-        <v>36.4</v>
+        <v>29.7</v>
       </c>
       <c r="K76" t="n">
-        <v>54.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="77">
@@ -3929,69 +3926,69 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C77" t="n">
-        <v>77.3</v>
+        <v>85.7</v>
       </c>
       <c r="D77" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="E77" t="n">
-        <v>58.7</v>
+        <v>70.4</v>
       </c>
       <c r="F77" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="G77" t="n">
-        <v>30.4</v>
+        <v>37.7</v>
       </c>
       <c r="H77" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="I77" t="n">
-        <v>46.9</v>
+        <v>38.9</v>
       </c>
       <c r="J77" t="n">
-        <v>29.7</v>
+        <v>41.7</v>
       </c>
       <c r="K77" t="n">
-        <v>58.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s">
         <v>91</v>
       </c>
-      <c r="B78" t="s">
-        <v>92</v>
-      </c>
       <c r="C78" t="n">
-        <v>85.7</v>
+        <v>72.6</v>
       </c>
       <c r="D78" t="n">
-        <v>15.3</v>
+        <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>70.4</v>
+        <v>42.6</v>
       </c>
       <c r="F78" t="n">
-        <v>15.3</v>
+        <v>30</v>
       </c>
       <c r="G78" t="n">
-        <v>37.7</v>
+        <v>20.4</v>
       </c>
       <c r="H78" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="I78" t="n">
-        <v>38.9</v>
+        <v>59.1</v>
       </c>
       <c r="J78" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="K78" t="n">
-        <v>47.4</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="79">
@@ -3999,34 +3996,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C79" t="n">
-        <v>72.6</v>
+        <v>72.2</v>
       </c>
       <c r="D79" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="E79" t="n">
-        <v>42.6</v>
+        <v>44.3</v>
       </c>
       <c r="F79" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="G79" t="n">
-        <v>20.4</v>
+        <v>31.7</v>
       </c>
       <c r="H79" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="I79" t="n">
-        <v>59.1</v>
+        <v>41.3</v>
       </c>
       <c r="J79" t="n">
-        <v>16.7</v>
+        <v>21.3</v>
       </c>
       <c r="K79" t="n">
-        <v>42.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="80">
@@ -4034,34 +4031,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C80" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="D80" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="E80" t="n">
-        <v>44.3</v>
+        <v>46.9</v>
       </c>
       <c r="F80" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="G80" t="n">
-        <v>31.7</v>
+        <v>26</v>
       </c>
       <c r="H80" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I80" t="n">
-        <v>41.3</v>
+        <v>45.5</v>
       </c>
       <c r="J80" t="n">
-        <v>21.3</v>
+        <v>23.4</v>
       </c>
       <c r="K80" t="n">
-        <v>57.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81">
@@ -4069,34 +4066,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>76.5</v>
+        <v>78.6</v>
       </c>
       <c r="D81" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>46.9</v>
+        <v>78.6</v>
       </c>
       <c r="F81" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="H81" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="I81" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>23.4</v>
+        <v>37.5</v>
       </c>
       <c r="K81" t="n">
-        <v>48</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="82">
@@ -4104,34 +4101,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C82" t="n">
-        <v>78.6</v>
+        <v>78.9</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="E82" t="n">
-        <v>78.6</v>
+        <v>48.2</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="G82" t="n">
-        <v>5.3</v>
+        <v>25.7</v>
       </c>
       <c r="H82" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>43.5</v>
       </c>
       <c r="J82" t="n">
-        <v>37.5</v>
+        <v>27.2</v>
       </c>
       <c r="K82" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="83">
@@ -4139,34 +4136,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83" t="n">
-        <v>78.9</v>
+        <v>73.8</v>
       </c>
       <c r="D83" t="n">
-        <v>30.7</v>
+        <v>17.8</v>
       </c>
       <c r="E83" t="n">
-        <v>48.2</v>
+        <v>56</v>
       </c>
       <c r="F83" t="n">
-        <v>30.7</v>
+        <v>17.8</v>
       </c>
       <c r="G83" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I83" t="n">
-        <v>43.5</v>
+        <v>32.9</v>
       </c>
       <c r="J83" t="n">
-        <v>27.2</v>
+        <v>39.7</v>
       </c>
       <c r="K83" t="n">
-        <v>63.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
@@ -4174,34 +4171,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C84" t="n">
-        <v>73.8</v>
+        <v>72.2</v>
       </c>
       <c r="D84" t="n">
-        <v>17.8</v>
+        <v>21.3</v>
       </c>
       <c r="E84" t="n">
-        <v>56</v>
+        <v>50.9</v>
       </c>
       <c r="F84" t="n">
-        <v>17.8</v>
+        <v>21.3</v>
       </c>
       <c r="G84" t="n">
-        <v>26.6</v>
+        <v>30</v>
       </c>
       <c r="H84" t="n">
-        <v>11.3</v>
+        <v>6.8</v>
       </c>
       <c r="I84" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="J84" t="n">
-        <v>39.7</v>
+        <v>24.5</v>
       </c>
       <c r="K84" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85">
@@ -4209,34 +4206,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>72.2</v>
+        <v>40</v>
       </c>
       <c r="D85" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="E85" t="n">
-        <v>50.9</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="G85" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H85" t="n">
-        <v>6.8</v>
+        <v>21.1</v>
       </c>
       <c r="I85" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="J85" t="n">
-        <v>24.5</v>
+        <v>12.5</v>
       </c>
       <c r="K85" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
@@ -4244,34 +4241,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C86" t="n">
-        <v>40</v>
+        <v>70.8</v>
       </c>
       <c r="D86" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="E86" t="n">
-        <v>15</v>
+        <v>44.1</v>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="G86" t="n">
-        <v>36</v>
+        <v>18.4</v>
       </c>
       <c r="H86" t="n">
-        <v>21.1</v>
+        <v>6.9</v>
       </c>
       <c r="I86" t="n">
-        <v>62.5</v>
+        <v>54.3</v>
       </c>
       <c r="J86" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="K86" t="n">
-        <v>50</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="87">
@@ -4279,34 +4276,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>70.8</v>
+        <v>72.5</v>
       </c>
       <c r="D87" t="n">
-        <v>26.7</v>
+        <v>32.4</v>
       </c>
       <c r="E87" t="n">
-        <v>44.1</v>
+        <v>40.1</v>
       </c>
       <c r="F87" t="n">
-        <v>26.7</v>
+        <v>32.4</v>
       </c>
       <c r="G87" t="n">
-        <v>18.4</v>
+        <v>26</v>
       </c>
       <c r="H87" t="n">
-        <v>6.9</v>
+        <v>9.3</v>
       </c>
       <c r="I87" t="n">
-        <v>54.3</v>
+        <v>44.4</v>
       </c>
       <c r="J87" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K87" t="n">
-        <v>39.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="88">
@@ -4314,34 +4311,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>72.5</v>
+        <v>83.3</v>
       </c>
       <c r="D88" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="E88" t="n">
-        <v>40.1</v>
+        <v>56</v>
       </c>
       <c r="F88" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="G88" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="H88" t="n">
-        <v>9.3</v>
+        <v>20</v>
       </c>
       <c r="I88" t="n">
-        <v>44.4</v>
+        <v>70</v>
       </c>
       <c r="J88" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K88" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -4349,34 +4346,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C89" t="n">
-        <v>83.3</v>
+        <v>65.2</v>
       </c>
       <c r="D89" t="n">
-        <v>27.3</v>
+        <v>14.5</v>
       </c>
       <c r="E89" t="n">
-        <v>56</v>
+        <v>50.7</v>
       </c>
       <c r="F89" t="n">
-        <v>27.3</v>
+        <v>14.5</v>
       </c>
       <c r="G89" t="n">
-        <v>26.1</v>
+        <v>21.2</v>
       </c>
       <c r="H89" t="n">
-        <v>20</v>
+        <v>12.1</v>
       </c>
       <c r="I89" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J89" t="n">
-        <v>10</v>
+        <v>14.1</v>
       </c>
       <c r="K89" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="90">
@@ -4384,34 +4381,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C90" t="n">
-        <v>65.2</v>
+        <v>53.6</v>
       </c>
       <c r="D90" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="E90" t="n">
-        <v>50.7</v>
+        <v>38</v>
       </c>
       <c r="F90" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="G90" t="n">
-        <v>21.2</v>
+        <v>30.9</v>
       </c>
       <c r="H90" t="n">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
       <c r="I90" t="n">
-        <v>62</v>
+        <v>67.7</v>
       </c>
       <c r="J90" t="n">
-        <v>14.1</v>
+        <v>25.8</v>
       </c>
       <c r="K90" t="n">
-        <v>42.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="91">
@@ -4419,57 +4416,51 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C91" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="D91" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="E91" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="G91" t="n">
-        <v>30.9</v>
+        <v>100</v>
       </c>
       <c r="H91" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I91" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J91" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K91" t="n">
-        <v>26.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92" t="s">
         <v>106</v>
       </c>
-      <c r="B92" t="s">
-        <v>107</v>
-      </c>
       <c r="C92" t="n">
+        <v>100</v>
+      </c>
+      <c r="D92" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F92" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G92" t="n">
         <v>50</v>
-      </c>
-      <c r="D92" t="n">
-        <v>50</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>50</v>
-      </c>
-      <c r="G92" t="n">
-        <v>100</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4480,66 +4471,72 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C93" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D93" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="E93" t="n">
-        <v>66.7</v>
+        <v>47</v>
       </c>
       <c r="F93" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="G93" t="n">
-        <v>50</v>
+        <v>25.4</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93"/>
-      <c r="J93"/>
-      <c r="K93"/>
+        <v>12.5</v>
+      </c>
+      <c r="I93" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J93" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K93" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C94" t="n">
-        <v>57.8</v>
+        <v>71.4</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="E94" t="n">
-        <v>47</v>
+        <v>51.4</v>
       </c>
       <c r="F94" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="G94" t="n">
-        <v>25.4</v>
+        <v>16.7</v>
       </c>
       <c r="H94" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I94" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4547,34 +4544,34 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C95" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>51.4</v>
+        <v>75</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="H95" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96">
@@ -4582,34 +4579,28 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C96" t="n">
-        <v>75</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>75</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
       <c r="G96" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H96" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4617,28 +4608,34 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C97" t="n">
-        <v>50</v>
-      </c>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
+        <v>60</v>
+      </c>
+      <c r="D97" t="n">
+        <v>40</v>
+      </c>
+      <c r="E97" t="n">
+        <v>20</v>
+      </c>
+      <c r="F97" t="n">
+        <v>40</v>
+      </c>
       <c r="G97" t="n">
-        <v>50</v>
+        <v>28.8</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -4646,34 +4643,34 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C98" t="n">
-        <v>60</v>
+        <v>75.9</v>
       </c>
       <c r="D98" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="E98" t="n">
-        <v>20</v>
+        <v>37.2</v>
       </c>
       <c r="F98" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="G98" t="n">
-        <v>28.8</v>
+        <v>42.4</v>
       </c>
       <c r="H98" t="n">
-        <v>2.8</v>
+        <v>9.4</v>
       </c>
       <c r="I98" t="n">
-        <v>39.1</v>
+        <v>54.3</v>
       </c>
       <c r="J98" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="K98" t="n">
-        <v>13</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="99">
@@ -4681,34 +4678,34 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C99" t="n">
-        <v>75.9</v>
+        <v>73.2</v>
       </c>
       <c r="D99" t="n">
-        <v>38.7</v>
+        <v>22</v>
       </c>
       <c r="E99" t="n">
-        <v>37.2</v>
+        <v>51.2</v>
       </c>
       <c r="F99" t="n">
-        <v>38.7</v>
+        <v>22</v>
       </c>
       <c r="G99" t="n">
-        <v>42.4</v>
+        <v>14.7</v>
       </c>
       <c r="H99" t="n">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="I99" t="n">
-        <v>54.3</v>
+        <v>45.5</v>
       </c>
       <c r="J99" t="n">
-        <v>14.3</v>
+        <v>19.5</v>
       </c>
       <c r="K99" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="100">
@@ -4716,34 +4713,34 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C100" t="n">
-        <v>73.2</v>
+        <v>65.5</v>
       </c>
       <c r="D100" t="n">
-        <v>22</v>
+        <v>9.7</v>
       </c>
       <c r="E100" t="n">
-        <v>51.2</v>
+        <v>55.8</v>
       </c>
       <c r="F100" t="n">
-        <v>22</v>
+        <v>9.7</v>
       </c>
       <c r="G100" t="n">
-        <v>14.7</v>
+        <v>31.4</v>
       </c>
       <c r="H100" t="n">
-        <v>8.1</v>
+        <v>21.8</v>
       </c>
       <c r="I100" t="n">
-        <v>45.5</v>
+        <v>28.3</v>
       </c>
       <c r="J100" t="n">
-        <v>19.5</v>
+        <v>35</v>
       </c>
       <c r="K100" t="n">
-        <v>27.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101">
@@ -4751,34 +4748,34 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C101" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="D101" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="E101" t="n">
-        <v>55.8</v>
+        <v>48.5</v>
       </c>
       <c r="F101" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="G101" t="n">
-        <v>31.4</v>
+        <v>46.7</v>
       </c>
       <c r="H101" t="n">
-        <v>21.8</v>
+        <v>33.3</v>
       </c>
       <c r="I101" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>39</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="102">
@@ -4786,25 +4783,25 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C102" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D102" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -4813,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4821,34 +4818,26 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>107</v>
-      </c>
-      <c r="C103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
         <v>100</v>
       </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>100</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4856,26 +4845,34 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>107</v>
-      </c>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
+        <v>106</v>
+      </c>
+      <c r="C104" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="D104" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>25.2</v>
+      </c>
       <c r="G104" t="n">
-        <v>16.7</v>
+        <v>22.7</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I104" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="K104" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="105">
@@ -4883,34 +4880,34 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C105" t="n">
-        <v>71.7</v>
+        <v>80</v>
       </c>
       <c r="D105" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="E105" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="F105" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="G105" t="n">
-        <v>22.7</v>
+        <v>35.1</v>
       </c>
       <c r="H105" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="I105" t="n">
-        <v>43.8</v>
+        <v>36.1</v>
       </c>
       <c r="J105" t="n">
-        <v>28.7</v>
+        <v>31.1</v>
       </c>
       <c r="K105" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="106">
@@ -4918,34 +4915,34 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C106" t="n">
-        <v>80</v>
+        <v>71.4</v>
       </c>
       <c r="D106" t="n">
-        <v>28.9</v>
+        <v>35.7</v>
       </c>
       <c r="E106" t="n">
-        <v>51.1</v>
+        <v>35.7</v>
       </c>
       <c r="F106" t="n">
-        <v>28.9</v>
+        <v>35.7</v>
       </c>
       <c r="G106" t="n">
-        <v>35.1</v>
+        <v>5.3</v>
       </c>
       <c r="H106" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="I106" t="n">
-        <v>36.1</v>
+        <v>42.9</v>
       </c>
       <c r="J106" t="n">
-        <v>31.1</v>
+        <v>14.3</v>
       </c>
       <c r="K106" t="n">
-        <v>49.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="107">
@@ -4953,34 +4950,34 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C107" t="n">
-        <v>71.4</v>
+        <v>59.1</v>
       </c>
       <c r="D107" t="n">
-        <v>35.7</v>
+        <v>18.5</v>
       </c>
       <c r="E107" t="n">
-        <v>35.7</v>
+        <v>40.6</v>
       </c>
       <c r="F107" t="n">
-        <v>35.7</v>
+        <v>18.5</v>
       </c>
       <c r="G107" t="n">
-        <v>5.3</v>
+        <v>31.2</v>
       </c>
       <c r="H107" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="I107" t="n">
-        <v>42.9</v>
+        <v>34.6</v>
       </c>
       <c r="J107" t="n">
-        <v>14.3</v>
+        <v>34.6</v>
       </c>
       <c r="K107" t="n">
-        <v>33.3</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="108">
@@ -4988,34 +4985,34 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C108" t="n">
-        <v>59.1</v>
+        <v>79.8</v>
       </c>
       <c r="D108" t="n">
-        <v>18.5</v>
+        <v>26.7</v>
       </c>
       <c r="E108" t="n">
-        <v>40.6</v>
+        <v>53.1</v>
       </c>
       <c r="F108" t="n">
-        <v>18.5</v>
+        <v>26.7</v>
       </c>
       <c r="G108" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="H108" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="I108" t="n">
-        <v>34.6</v>
+        <v>39.3</v>
       </c>
       <c r="J108" t="n">
-        <v>34.6</v>
+        <v>28.6</v>
       </c>
       <c r="K108" t="n">
-        <v>42.3</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="109">
@@ -5023,34 +5020,34 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C109" t="n">
-        <v>79.8</v>
+        <v>66.2</v>
       </c>
       <c r="D109" t="n">
-        <v>26.7</v>
+        <v>16.6</v>
       </c>
       <c r="E109" t="n">
-        <v>53.1</v>
+        <v>49.6</v>
       </c>
       <c r="F109" t="n">
-        <v>26.7</v>
+        <v>16.6</v>
       </c>
       <c r="G109" t="n">
-        <v>35.4</v>
+        <v>17.2</v>
       </c>
       <c r="H109" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="I109" t="n">
-        <v>39.3</v>
+        <v>39.8</v>
       </c>
       <c r="J109" t="n">
-        <v>28.6</v>
+        <v>21.5</v>
       </c>
       <c r="K109" t="n">
-        <v>39.3</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="110">
@@ -5058,34 +5055,34 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C110" t="n">
-        <v>66.2</v>
+        <v>57.8</v>
       </c>
       <c r="D110" t="n">
-        <v>16.6</v>
+        <v>22.2</v>
       </c>
       <c r="E110" t="n">
-        <v>49.6</v>
+        <v>35.6</v>
       </c>
       <c r="F110" t="n">
-        <v>16.6</v>
+        <v>22.2</v>
       </c>
       <c r="G110" t="n">
-        <v>17.2</v>
+        <v>18.9</v>
       </c>
       <c r="H110" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="I110" t="n">
-        <v>39.8</v>
+        <v>41.6</v>
       </c>
       <c r="J110" t="n">
-        <v>21.5</v>
+        <v>23.4</v>
       </c>
       <c r="K110" t="n">
-        <v>45.7</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="111">
@@ -5093,34 +5090,34 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C111" t="n">
-        <v>57.8</v>
+        <v>66</v>
       </c>
       <c r="D111" t="n">
-        <v>22.2</v>
+        <v>15.7</v>
       </c>
       <c r="E111" t="n">
-        <v>35.6</v>
+        <v>50.3</v>
       </c>
       <c r="F111" t="n">
-        <v>22.2</v>
+        <v>15.7</v>
       </c>
       <c r="G111" t="n">
-        <v>18.9</v>
+        <v>25.1</v>
       </c>
       <c r="H111" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="I111" t="n">
-        <v>41.6</v>
+        <v>53.3</v>
       </c>
       <c r="J111" t="n">
-        <v>23.4</v>
+        <v>26.7</v>
       </c>
       <c r="K111" t="n">
-        <v>40.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="112">
@@ -5128,69 +5125,69 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C112" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="D112" t="n">
-        <v>15.7</v>
+        <v>36.1</v>
       </c>
       <c r="E112" t="n">
-        <v>50.3</v>
+        <v>30.1</v>
       </c>
       <c r="F112" t="n">
-        <v>15.7</v>
+        <v>36.1</v>
       </c>
       <c r="G112" t="n">
-        <v>25.1</v>
+        <v>27.9</v>
       </c>
       <c r="H112" t="n">
-        <v>11.5</v>
+        <v>7.9</v>
       </c>
       <c r="I112" t="n">
-        <v>53.3</v>
+        <v>40.7</v>
       </c>
       <c r="J112" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="K112" t="n">
-        <v>51.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>128</v>
+      </c>
+      <c r="B113" t="s">
         <v>127</v>
       </c>
-      <c r="B113" t="s">
-        <v>128</v>
-      </c>
       <c r="C113" t="n">
-        <v>66.2</v>
+        <v>80</v>
       </c>
       <c r="D113" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>30.1</v>
+        <v>80</v>
       </c>
       <c r="F113" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="H113" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K113" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5198,34 +5195,34 @@
         <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C114" t="n">
-        <v>80</v>
+        <v>71.3</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="E114" t="n">
-        <v>80</v>
+        <v>49.4</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="G114" t="n">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="J114" t="n">
-        <v>100</v>
+        <v>31.2</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115">
@@ -5233,34 +5230,34 @@
         <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C115" t="n">
-        <v>71.3</v>
+        <v>68.2</v>
       </c>
       <c r="D115" t="n">
-        <v>21.9</v>
+        <v>24.5</v>
       </c>
       <c r="E115" t="n">
-        <v>49.4</v>
+        <v>43.7</v>
       </c>
       <c r="F115" t="n">
-        <v>21.9</v>
+        <v>24.5</v>
       </c>
       <c r="G115" t="n">
-        <v>13.9</v>
+        <v>29.5</v>
       </c>
       <c r="H115" t="n">
-        <v>9.3</v>
+        <v>7.1</v>
       </c>
       <c r="I115" t="n">
-        <v>39.1</v>
+        <v>43.6</v>
       </c>
       <c r="J115" t="n">
-        <v>31.2</v>
+        <v>25.5</v>
       </c>
       <c r="K115" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="116">
@@ -5268,34 +5265,34 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C116" t="n">
-        <v>68.2</v>
+        <v>79.5</v>
       </c>
       <c r="D116" t="n">
-        <v>24.5</v>
+        <v>31.9</v>
       </c>
       <c r="E116" t="n">
-        <v>43.7</v>
+        <v>47.6</v>
       </c>
       <c r="F116" t="n">
-        <v>24.5</v>
+        <v>31.9</v>
       </c>
       <c r="G116" t="n">
-        <v>29.5</v>
+        <v>25.8</v>
       </c>
       <c r="H116" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>43.6</v>
+        <v>42.7</v>
       </c>
       <c r="J116" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="K116" t="n">
-        <v>47.3</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="117">
@@ -5303,34 +5300,34 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C117" t="n">
-        <v>79.5</v>
+        <v>59.2</v>
       </c>
       <c r="D117" t="n">
-        <v>31.9</v>
+        <v>23.5</v>
       </c>
       <c r="E117" t="n">
-        <v>47.6</v>
+        <v>35.7</v>
       </c>
       <c r="F117" t="n">
-        <v>31.9</v>
+        <v>23.5</v>
       </c>
       <c r="G117" t="n">
-        <v>25.8</v>
+        <v>23.2</v>
       </c>
       <c r="H117" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="I117" t="n">
-        <v>42.7</v>
+        <v>62.3</v>
       </c>
       <c r="J117" t="n">
-        <v>25.6</v>
+        <v>15.1</v>
       </c>
       <c r="K117" t="n">
-        <v>30.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="118">
@@ -5338,34 +5335,34 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C118" t="n">
-        <v>59.2</v>
+        <v>54.7</v>
       </c>
       <c r="D118" t="n">
-        <v>23.5</v>
+        <v>19.6</v>
       </c>
       <c r="E118" t="n">
-        <v>35.7</v>
+        <v>35.1</v>
       </c>
       <c r="F118" t="n">
-        <v>23.5</v>
+        <v>19.6</v>
       </c>
       <c r="G118" t="n">
-        <v>23.2</v>
+        <v>9.5</v>
       </c>
       <c r="H118" t="n">
-        <v>7.9</v>
+        <v>11.6</v>
       </c>
       <c r="I118" t="n">
-        <v>62.3</v>
+        <v>63.4</v>
       </c>
       <c r="J118" t="n">
-        <v>15.1</v>
+        <v>11.8</v>
       </c>
       <c r="K118" t="n">
-        <v>47.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119">
@@ -5373,34 +5370,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C119" t="n">
-        <v>54.7</v>
+        <v>80</v>
       </c>
       <c r="D119" t="n">
-        <v>19.6</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="n">
-        <v>35.1</v>
+        <v>68.9</v>
       </c>
       <c r="F119" t="n">
-        <v>19.6</v>
+        <v>11.1</v>
       </c>
       <c r="G119" t="n">
-        <v>9.5</v>
+        <v>39.5</v>
       </c>
       <c r="H119" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="I119" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="J119" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="K119" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="120">
@@ -5408,34 +5405,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C120" t="n">
-        <v>80</v>
+        <v>70.6</v>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>28.7</v>
       </c>
       <c r="E120" t="n">
-        <v>68.9</v>
+        <v>41.9</v>
       </c>
       <c r="F120" t="n">
-        <v>11.1</v>
+        <v>28.7</v>
       </c>
       <c r="G120" t="n">
-        <v>39.5</v>
+        <v>21.8</v>
       </c>
       <c r="H120" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="I120" t="n">
-        <v>63.6</v>
+        <v>39.6</v>
       </c>
       <c r="J120" t="n">
-        <v>9.1</v>
+        <v>31.5</v>
       </c>
       <c r="K120" t="n">
-        <v>45.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="121">
@@ -5443,34 +5440,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C121" t="n">
-        <v>70.6</v>
+        <v>70</v>
       </c>
       <c r="D121" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="E121" t="n">
-        <v>41.9</v>
+        <v>43.3</v>
       </c>
       <c r="F121" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="G121" t="n">
-        <v>21.8</v>
+        <v>14.8</v>
       </c>
       <c r="H121" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="I121" t="n">
-        <v>39.6</v>
+        <v>60</v>
       </c>
       <c r="J121" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="K121" t="n">
-        <v>39.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
@@ -5478,34 +5475,34 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C122" t="n">
-        <v>70</v>
+        <v>56.9</v>
       </c>
       <c r="D122" t="n">
-        <v>26.7</v>
+        <v>19.7</v>
       </c>
       <c r="E122" t="n">
-        <v>43.3</v>
+        <v>37.2</v>
       </c>
       <c r="F122" t="n">
-        <v>26.7</v>
+        <v>19.7</v>
       </c>
       <c r="G122" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="H122" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="I122" t="n">
-        <v>60</v>
+        <v>48.1</v>
       </c>
       <c r="J122" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="K122" t="n">
-        <v>10</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="123">
@@ -5513,34 +5510,34 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C123" t="n">
-        <v>56.9</v>
+        <v>72.6</v>
       </c>
       <c r="D123" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
       </c>
       <c r="E123" t="n">
-        <v>37.2</v>
+        <v>51.5</v>
       </c>
       <c r="F123" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
       </c>
       <c r="G123" t="n">
-        <v>15.2</v>
+        <v>32.9</v>
       </c>
       <c r="H123" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="I123" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="J123" t="n">
-        <v>29.6</v>
+        <v>18.9</v>
       </c>
       <c r="K123" t="n">
-        <v>53.8</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="124">
@@ -5548,34 +5545,34 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>72.6</v>
+        <v>74.7</v>
       </c>
       <c r="D124" t="n">
-        <v>21.1</v>
+        <v>24.3</v>
       </c>
       <c r="E124" t="n">
-        <v>51.5</v>
+        <v>50.4</v>
       </c>
       <c r="F124" t="n">
-        <v>21.1</v>
+        <v>24.3</v>
       </c>
       <c r="G124" t="n">
-        <v>32.9</v>
+        <v>32</v>
       </c>
       <c r="H124" t="n">
-        <v>12.9</v>
+        <v>8.3</v>
       </c>
       <c r="I124" t="n">
-        <v>48.6</v>
+        <v>38.6</v>
       </c>
       <c r="J124" t="n">
-        <v>18.9</v>
+        <v>26.5</v>
       </c>
       <c r="K124" t="n">
-        <v>41.3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125">
@@ -5583,34 +5580,34 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C125" t="n">
-        <v>74.7</v>
+        <v>75.2</v>
       </c>
       <c r="D125" t="n">
-        <v>24.3</v>
+        <v>23.1</v>
       </c>
       <c r="E125" t="n">
-        <v>50.4</v>
+        <v>52.1</v>
       </c>
       <c r="F125" t="n">
-        <v>24.3</v>
+        <v>23.1</v>
       </c>
       <c r="G125" t="n">
-        <v>32</v>
+        <v>24.8</v>
       </c>
       <c r="H125" t="n">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="I125" t="n">
-        <v>38.6</v>
+        <v>41.1</v>
       </c>
       <c r="J125" t="n">
-        <v>26.5</v>
+        <v>33.7</v>
       </c>
       <c r="K125" t="n">
-        <v>39</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="126">
@@ -5618,34 +5615,34 @@
         <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C126" t="n">
-        <v>75.2</v>
+        <v>68.2</v>
       </c>
       <c r="D126" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="E126" t="n">
-        <v>52.1</v>
+        <v>50</v>
       </c>
       <c r="F126" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="G126" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="H126" t="n">
-        <v>8.2</v>
+        <v>11.9</v>
       </c>
       <c r="I126" t="n">
-        <v>41.1</v>
+        <v>48.3</v>
       </c>
       <c r="J126" t="n">
-        <v>33.7</v>
+        <v>17.2</v>
       </c>
       <c r="K126" t="n">
-        <v>49.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127">
@@ -5653,69 +5650,69 @@
         <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C127" t="n">
-        <v>68.2</v>
+        <v>72</v>
       </c>
       <c r="D127" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G127" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J127" t="n">
         <v>18.2</v>
       </c>
-      <c r="E127" t="n">
-        <v>50</v>
-      </c>
-      <c r="F127" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G127" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H127" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="I127" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J127" t="n">
-        <v>17.2</v>
-      </c>
       <c r="K127" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>144</v>
+      </c>
+      <c r="B128" t="s">
         <v>143</v>
       </c>
-      <c r="B128" t="s">
-        <v>144</v>
-      </c>
       <c r="C128" t="n">
-        <v>72</v>
+        <v>66.7</v>
       </c>
       <c r="D128" t="n">
-        <v>23.1</v>
+        <v>60</v>
       </c>
       <c r="E128" t="n">
-        <v>48.9</v>
+        <v>6.7</v>
       </c>
       <c r="F128" t="n">
-        <v>23.1</v>
+        <v>60</v>
       </c>
       <c r="G128" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I128" t="n">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="J128" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="K128" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5723,34 +5720,34 @@
         <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C129" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="D129" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E129" t="n">
-        <v>6.7</v>
+        <v>46.2</v>
       </c>
       <c r="F129" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G129" t="n">
-        <v>33.3</v>
+        <v>14.1</v>
       </c>
       <c r="H129" t="n">
-        <v>11.1</v>
+        <v>5.1</v>
       </c>
       <c r="I129" t="n">
-        <v>25</v>
+        <v>43.9</v>
       </c>
       <c r="J129" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="130">
@@ -5758,34 +5755,34 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C130" t="n">
-        <v>66.2</v>
+        <v>35</v>
       </c>
       <c r="D130" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E130" t="n">
-        <v>46.2</v>
+        <v>21.7</v>
       </c>
       <c r="F130" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="G130" t="n">
-        <v>14.1</v>
+        <v>33.3</v>
       </c>
       <c r="H130" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>43.9</v>
+        <v>50</v>
       </c>
       <c r="J130" t="n">
-        <v>24.6</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>41.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5793,34 +5790,34 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C131" t="n">
-        <v>35</v>
+        <v>72.2</v>
       </c>
       <c r="D131" t="n">
-        <v>13.3</v>
+        <v>28</v>
       </c>
       <c r="E131" t="n">
-        <v>21.7</v>
+        <v>44.2</v>
       </c>
       <c r="F131" t="n">
-        <v>13.3</v>
+        <v>28</v>
       </c>
       <c r="G131" t="n">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>9.8</v>
       </c>
       <c r="I131" t="n">
         <v>50</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="132">
@@ -5828,34 +5825,34 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C132" t="n">
-        <v>72.2</v>
+        <v>74.6</v>
       </c>
       <c r="D132" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="E132" t="n">
-        <v>44.2</v>
+        <v>47.4</v>
       </c>
       <c r="F132" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="G132" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="H132" t="n">
-        <v>9.8</v>
+        <v>9.7</v>
       </c>
       <c r="I132" t="n">
-        <v>50</v>
+        <v>46.6</v>
       </c>
       <c r="J132" t="n">
-        <v>23.7</v>
+        <v>27.6</v>
       </c>
       <c r="K132" t="n">
-        <v>42.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="133">
@@ -5863,34 +5860,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C133" t="n">
-        <v>74.6</v>
+        <v>48.1</v>
       </c>
       <c r="D133" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="E133" t="n">
-        <v>47.4</v>
+        <v>23.1</v>
       </c>
       <c r="F133" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="G133" t="n">
-        <v>30.6</v>
+        <v>15.4</v>
       </c>
       <c r="H133" t="n">
-        <v>9.7</v>
+        <v>18.8</v>
       </c>
       <c r="I133" t="n">
-        <v>46.6</v>
+        <v>44.4</v>
       </c>
       <c r="J133" t="n">
-        <v>27.6</v>
+        <v>22.2</v>
       </c>
       <c r="K133" t="n">
-        <v>38.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="134">
@@ -5898,34 +5895,34 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C134" t="n">
-        <v>48.1</v>
+        <v>66</v>
       </c>
       <c r="D134" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="E134" t="n">
-        <v>23.1</v>
+        <v>41.7</v>
       </c>
       <c r="F134" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="G134" t="n">
-        <v>15.4</v>
+        <v>21.9</v>
       </c>
       <c r="H134" t="n">
-        <v>18.8</v>
+        <v>7.7</v>
       </c>
       <c r="I134" t="n">
-        <v>44.4</v>
+        <v>54.3</v>
       </c>
       <c r="J134" t="n">
-        <v>22.2</v>
+        <v>15.7</v>
       </c>
       <c r="K134" t="n">
-        <v>11.1</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="135">
@@ -5933,34 +5930,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C135" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="D135" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="F135" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>21.9</v>
+        <v>18.2</v>
       </c>
       <c r="H135" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>54.3</v>
+        <v>75</v>
       </c>
       <c r="J135" t="n">
-        <v>15.7</v>
+        <v>25</v>
       </c>
       <c r="K135" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5968,34 +5965,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C136" t="n">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="E136" t="n">
-        <v>66.7</v>
+        <v>52.8</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="G136" t="n">
-        <v>18.2</v>
+        <v>27.4</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I136" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="J136" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="137">
@@ -6003,34 +6000,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C137" t="n">
-        <v>72.2</v>
+        <v>50</v>
       </c>
       <c r="D137" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="E137" t="n">
-        <v>52.8</v>
+        <v>35.7</v>
       </c>
       <c r="F137" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="G137" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="H137" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="I137" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K137" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138">
@@ -6038,34 +6035,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C138" t="n">
-        <v>50</v>
+        <v>68.5</v>
       </c>
       <c r="D138" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="E138" t="n">
-        <v>35.7</v>
+        <v>39.5</v>
       </c>
       <c r="F138" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="G138" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="H138" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="I138" t="n">
-        <v>75</v>
+        <v>35.9</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>28.1</v>
       </c>
       <c r="K138" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="139">
@@ -6073,104 +6070,104 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C139" t="n">
-        <v>68.5</v>
+        <v>65.8</v>
       </c>
       <c r="D139" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E139" t="n">
-        <v>39.5</v>
+        <v>41.8</v>
       </c>
       <c r="F139" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G139" t="n">
-        <v>31.8</v>
+        <v>21.9</v>
       </c>
       <c r="H139" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="I139" t="n">
-        <v>35.9</v>
+        <v>59.7</v>
       </c>
       <c r="J139" t="n">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
       <c r="K139" t="n">
-        <v>43.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="B140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C140" t="n">
-        <v>65.8</v>
+        <v>56.1</v>
       </c>
       <c r="D140" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="E140" t="n">
-        <v>41.8</v>
+        <v>36.9</v>
       </c>
       <c r="F140" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="G140" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="H140" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>59.7</v>
+        <v>40.5</v>
       </c>
       <c r="J140" t="n">
-        <v>23.9</v>
+        <v>27</v>
       </c>
       <c r="K140" t="n">
-        <v>30.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="B141" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C141" t="n">
-        <v>56.1</v>
+        <v>79.6</v>
       </c>
       <c r="D141" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="E141" t="n">
-        <v>36.9</v>
+        <v>42.8</v>
       </c>
       <c r="F141" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="G141" t="n">
-        <v>22.5</v>
+        <v>34.2</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I141" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
       <c r="J141" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142">
@@ -6178,34 +6175,34 @@
         <v>157</v>
       </c>
       <c r="B142" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C142" t="n">
-        <v>79.6</v>
+        <v>57.8</v>
       </c>
       <c r="D142" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="E142" t="n">
-        <v>42.8</v>
+        <v>43.7</v>
       </c>
       <c r="F142" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="G142" t="n">
-        <v>34.2</v>
+        <v>12.5</v>
       </c>
       <c r="H142" t="n">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="I142" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="J142" t="n">
-        <v>20</v>
+        <v>9.7</v>
       </c>
       <c r="K142" t="n">
-        <v>44</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="143">
@@ -6213,34 +6210,34 @@
         <v>158</v>
       </c>
       <c r="B143" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C143" t="n">
-        <v>57.8</v>
+        <v>63.2</v>
       </c>
       <c r="D143" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="E143" t="n">
-        <v>43.7</v>
+        <v>18.2</v>
       </c>
       <c r="F143" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="G143" t="n">
-        <v>12.5</v>
+        <v>26.9</v>
       </c>
       <c r="H143" t="n">
-        <v>10.2</v>
+        <v>7.7</v>
       </c>
       <c r="I143" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>9.7</v>
+        <v>25</v>
       </c>
       <c r="K143" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144">
@@ -6248,34 +6245,34 @@
         <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C144" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="D144" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="E144" t="n">
-        <v>18.2</v>
+        <v>62.1</v>
       </c>
       <c r="F144" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="G144" t="n">
-        <v>26.9</v>
+        <v>23.4</v>
       </c>
       <c r="H144" t="n">
-        <v>7.7</v>
+        <v>14.8</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="J144" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K144" t="n">
-        <v>25</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="145">
@@ -6283,34 +6280,34 @@
         <v>160</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C145" t="n">
         <v>74.2</v>
       </c>
       <c r="D145" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="E145" t="n">
-        <v>62.1</v>
+        <v>48.1</v>
       </c>
       <c r="F145" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="G145" t="n">
-        <v>23.4</v>
+        <v>9.2</v>
       </c>
       <c r="H145" t="n">
-        <v>14.8</v>
+        <v>2.2</v>
       </c>
       <c r="I145" t="n">
-        <v>32.9</v>
+        <v>48.1</v>
       </c>
       <c r="J145" t="n">
-        <v>37</v>
+        <v>20.8</v>
       </c>
       <c r="K145" t="n">
-        <v>38.4</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="146">
@@ -6318,69 +6315,69 @@
         <v>161</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C146" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="D146" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="E146" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="F146" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="G146" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H146" t="n">
         <v>9.2</v>
       </c>
-      <c r="H146" t="n">
-        <v>2.2</v>
-      </c>
       <c r="I146" t="n">
-        <v>48.1</v>
+        <v>51.9</v>
       </c>
       <c r="J146" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="K146" t="n">
-        <v>32.5</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>163</v>
+      </c>
+      <c r="B147" t="s">
         <v>162</v>
       </c>
-      <c r="B147" t="s">
-        <v>163</v>
-      </c>
       <c r="C147" t="n">
-        <v>70.5</v>
+        <v>68.6</v>
       </c>
       <c r="D147" t="n">
         <v>20.5</v>
       </c>
       <c r="E147" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F147" t="n">
         <v>20.5</v>
       </c>
       <c r="G147" t="n">
-        <v>37.7</v>
+        <v>14.9</v>
       </c>
       <c r="H147" t="n">
-        <v>9.2</v>
+        <v>6.6</v>
       </c>
       <c r="I147" t="n">
-        <v>51.9</v>
+        <v>57.3</v>
       </c>
       <c r="J147" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="K147" t="n">
-        <v>39.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="148">
@@ -6388,34 +6385,34 @@
         <v>164</v>
       </c>
       <c r="B148" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C148" t="n">
-        <v>68.6</v>
+        <v>64.6</v>
       </c>
       <c r="D148" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E148" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G148" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H148" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I148" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J148" t="n">
         <v>48.1</v>
       </c>
-      <c r="F148" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G148" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H148" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I148" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J148" t="n">
-        <v>18.7</v>
-      </c>
       <c r="K148" t="n">
-        <v>45.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="149">
@@ -6423,34 +6420,34 @@
         <v>165</v>
       </c>
       <c r="B149" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C149" t="n">
-        <v>64.6</v>
+        <v>60</v>
       </c>
       <c r="D149" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E149" t="n">
-        <v>47.9</v>
+        <v>38.9</v>
       </c>
       <c r="F149" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G149" t="n">
-        <v>37.7</v>
+        <v>32.4</v>
       </c>
       <c r="H149" t="n">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="I149" t="n">
-        <v>29.6</v>
+        <v>34.8</v>
       </c>
       <c r="J149" t="n">
-        <v>48.1</v>
+        <v>30.4</v>
       </c>
       <c r="K149" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="150">
@@ -6458,34 +6455,34 @@
         <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C150" t="n">
-        <v>60</v>
+        <v>66.3</v>
       </c>
       <c r="D150" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E150" t="n">
-        <v>38.9</v>
+        <v>51.9</v>
       </c>
       <c r="F150" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="G150" t="n">
-        <v>32.4</v>
+        <v>9</v>
       </c>
       <c r="H150" t="n">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="I150" t="n">
-        <v>34.8</v>
+        <v>62.2</v>
       </c>
       <c r="J150" t="n">
-        <v>30.4</v>
+        <v>17.3</v>
       </c>
       <c r="K150" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="151">
@@ -6493,34 +6490,34 @@
         <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C151" t="n">
-        <v>66.3</v>
+        <v>80.4</v>
       </c>
       <c r="D151" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="E151" t="n">
-        <v>51.9</v>
+        <v>63.9</v>
       </c>
       <c r="F151" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="G151" t="n">
-        <v>9</v>
+        <v>23.3</v>
       </c>
       <c r="H151" t="n">
-        <v>18.2</v>
+        <v>9.4</v>
       </c>
       <c r="I151" t="n">
-        <v>62.2</v>
+        <v>36.2</v>
       </c>
       <c r="J151" t="n">
-        <v>17.3</v>
+        <v>34</v>
       </c>
       <c r="K151" t="n">
-        <v>36.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="152">
@@ -6528,34 +6525,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C152" t="n">
-        <v>80.4</v>
+        <v>55.6</v>
       </c>
       <c r="D152" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="E152" t="n">
-        <v>63.9</v>
+        <v>38</v>
       </c>
       <c r="F152" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="G152" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="H152" t="n">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="I152" t="n">
-        <v>36.2</v>
+        <v>47.4</v>
       </c>
       <c r="J152" t="n">
-        <v>34</v>
+        <v>22.8</v>
       </c>
       <c r="K152" t="n">
-        <v>44.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="153">
@@ -6563,34 +6560,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C153" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D153" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F153" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>25.7</v>
+        <v>66.7</v>
       </c>
       <c r="H153" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6598,34 +6595,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C154" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E154" t="n">
-        <v>75</v>
+        <v>38.6</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G154" t="n">
-        <v>66.7</v>
+        <v>14.6</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="155">
@@ -6633,34 +6630,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C155" t="n">
-        <v>56.2</v>
+        <v>61.4</v>
       </c>
       <c r="D155" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="E155" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="F155" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="G155" t="n">
-        <v>14.6</v>
+        <v>9.8</v>
       </c>
       <c r="H155" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="I155" t="n">
-        <v>37</v>
+        <v>60.4</v>
       </c>
       <c r="J155" t="n">
-        <v>28.8</v>
+        <v>18</v>
       </c>
       <c r="K155" t="n">
-        <v>49.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="156">
@@ -6668,34 +6665,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C156" t="n">
-        <v>61.4</v>
+        <v>71.5</v>
       </c>
       <c r="D156" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E156" t="n">
-        <v>40.6</v>
+        <v>54.8</v>
       </c>
       <c r="F156" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="G156" t="n">
-        <v>9.8</v>
+        <v>24.7</v>
       </c>
       <c r="H156" t="n">
-        <v>8.5</v>
+        <v>11.8</v>
       </c>
       <c r="I156" t="n">
-        <v>60.4</v>
+        <v>34.8</v>
       </c>
       <c r="J156" t="n">
-        <v>18</v>
+        <v>31.5</v>
       </c>
       <c r="K156" t="n">
-        <v>29.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="157">
@@ -6703,34 +6700,34 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C157" t="n">
-        <v>71.5</v>
+        <v>77.2</v>
       </c>
       <c r="D157" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="E157" t="n">
-        <v>54.8</v>
+        <v>47.3</v>
       </c>
       <c r="F157" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="G157" t="n">
-        <v>24.7</v>
+        <v>41.7</v>
       </c>
       <c r="H157" t="n">
-        <v>11.8</v>
+        <v>6.9</v>
       </c>
       <c r="I157" t="n">
-        <v>34.8</v>
+        <v>44.4</v>
       </c>
       <c r="J157" t="n">
-        <v>31.5</v>
+        <v>22.2</v>
       </c>
       <c r="K157" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="158">
@@ -6738,34 +6735,34 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C158" t="n">
-        <v>77.2</v>
+        <v>75.5</v>
       </c>
       <c r="D158" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="E158" t="n">
-        <v>47.3</v>
+        <v>55.1</v>
       </c>
       <c r="F158" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="G158" t="n">
-        <v>41.7</v>
+        <v>19.7</v>
       </c>
       <c r="H158" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="I158" t="n">
-        <v>44.4</v>
+        <v>27.9</v>
       </c>
       <c r="J158" t="n">
-        <v>22.2</v>
+        <v>33.7</v>
       </c>
       <c r="K158" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="159">
@@ -6773,57 +6770,51 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C159" t="n">
-        <v>75.5</v>
+        <v>37.5</v>
       </c>
       <c r="D159" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="E159" t="n">
-        <v>55.1</v>
+        <v>4.2</v>
       </c>
       <c r="F159" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="G159" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>11</v>
-      </c>
-      <c r="I159" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J159" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K159" t="n">
-        <v>46.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I159"/>
+      <c r="J159"/>
+      <c r="K159"/>
     </row>
     <row r="160">
       <c r="A160" t="s">
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C160" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
         <v>33.3</v>
       </c>
       <c r="E160" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F160" t="n">
         <v>33.3</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -6833,65 +6824,36 @@
       <c r="K160"/>
     </row>
     <row r="161">
-      <c r="A161" t="s">
+      <c r="A161"/>
+      <c r="B161" t="s">
         <v>177</v>
       </c>
-      <c r="B161" t="s">
-        <v>163</v>
-      </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>67.8</v>
       </c>
       <c r="D161" t="n">
-        <v>33.3</v>
+        <v>22.3</v>
       </c>
       <c r="E161" t="n">
-        <v>-33.3</v>
+        <v>45.9</v>
       </c>
       <c r="F161" t="n">
-        <v>33.3</v>
+        <v>22.3</v>
       </c>
       <c r="G161" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161"/>
-      <c r="J161"/>
-      <c r="K161"/>
-    </row>
-    <row r="162">
-      <c r="A162"/>
-      <c r="B162" t="s">
-        <v>178</v>
-      </c>
-      <c r="C162" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="D162" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E162" t="n">
-        <v>46</v>
-      </c>
-      <c r="F162" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G162" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H162" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="I162" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="J162" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="K162" t="n">
-        <v>39.6</v>
+        <v>9.5</v>
+      </c>
+      <c r="I161" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K161" t="n">
+        <v>39.3</v>
       </c>
     </row>
   </sheetData>
@@ -6923,22 +6885,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6947,18 +6909,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6993,7 +6955,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7028,7 +6990,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7098,7 +7060,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7133,7 +7095,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7168,7 +7130,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7203,7 +7165,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7238,7 +7200,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -7273,7 +7235,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7308,7 +7270,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7343,7 +7305,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7378,7 +7340,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7413,7 +7375,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -7448,7 +7410,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -7481,10 +7443,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
         <v>42.9</v>
@@ -7516,10 +7478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" t="n">
         <v>51.6</v>
@@ -7551,10 +7513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
         <v>52.9</v>
@@ -7586,10 +7548,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
         <v>50</v>
@@ -7621,10 +7583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
         <v>50</v>
@@ -7656,10 +7618,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" t="n">
         <v>64</v>
@@ -7691,10 +7653,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
         <v>66.7</v>
@@ -7726,10 +7688,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
         <v>55.6</v>
@@ -7761,10 +7723,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>58</v>
@@ -7796,10 +7758,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>43.3</v>
@@ -7831,10 +7793,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
         <v>66.7</v>
@@ -7866,10 +7828,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
         <v>55.4</v>
@@ -7901,10 +7863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
         <v>55.7</v>
@@ -7936,10 +7898,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
         <v>59.1</v>
@@ -7971,10 +7933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
         <v>56.7</v>
@@ -8006,10 +7968,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
         <v>58.2</v>
@@ -8041,10 +8003,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" t="n">
         <v>78.6</v>
@@ -8076,10 +8038,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" t="n">
         <v>52.5</v>
@@ -8111,10 +8073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" t="n">
         <v>45.8</v>
@@ -8146,10 +8108,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" t="n">
         <v>52.9</v>
@@ -8181,10 +8143,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37" t="n">
         <v>47.8</v>
@@ -8216,10 +8178,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" t="n">
         <v>48.8</v>
@@ -8251,10 +8213,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" t="n">
         <v>59</v>
@@ -8286,10 +8248,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" t="n">
         <v>54.8</v>
@@ -8321,10 +8283,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" t="n">
         <v>100</v>
@@ -8354,10 +8316,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" t="n">
         <v>66.3</v>
@@ -8389,10 +8351,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" t="n">
         <v>57</v>
@@ -8424,10 +8386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" t="n">
         <v>60.4</v>
@@ -8459,10 +8421,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" t="n">
         <v>55.4</v>
@@ -8494,10 +8456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" t="n">
         <v>81.2</v>
@@ -8529,10 +8491,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" t="n">
         <v>58</v>
@@ -8564,10 +8526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" t="n">
         <v>44.4</v>
@@ -8597,10 +8559,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" t="n">
         <v>51.8</v>
@@ -8632,10 +8594,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C50" t="n">
         <v>60</v>
@@ -8667,10 +8629,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51" t="n">
         <v>70.9</v>
@@ -8702,10 +8664,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C52" t="n">
         <v>60.6</v>
@@ -8737,10 +8699,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="n">
         <v>66.7</v>
@@ -8770,10 +8732,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" t="n">
         <v>77.8</v>
@@ -8805,10 +8767,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="n">
         <v>65.6</v>
@@ -8840,10 +8802,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" t="n">
         <v>57.3</v>
@@ -8875,10 +8837,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" t="n">
         <v>67.6</v>
@@ -8910,10 +8872,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" t="n">
         <v>61.1</v>
@@ -8945,10 +8907,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" t="n">
         <v>62</v>
@@ -8980,10 +8942,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" t="n">
         <v>56.5</v>
@@ -9015,10 +8977,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C61" t="n">
         <v>65.7</v>
@@ -9050,10 +9012,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" t="n">
         <v>62.3</v>
@@ -9085,10 +9047,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" t="n">
         <v>30</v>
@@ -9120,10 +9082,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" t="n">
         <v>44.4</v>
@@ -9155,10 +9117,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C65" t="n">
         <v>62.5</v>
@@ -9190,10 +9152,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" t="n">
         <v>72.4</v>
@@ -9225,10 +9187,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C67" t="n">
         <v>66.7</v>
@@ -9260,10 +9222,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C68" t="n">
         <v>50</v>
@@ -9295,10 +9257,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C69" t="n">
         <v>55.6</v>
@@ -9330,10 +9292,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C70" t="n">
         <v>54.8</v>
@@ -9365,10 +9327,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C71" t="n">
         <v>61.1</v>
@@ -9400,10 +9362,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C72" t="n">
         <v>63.8</v>
@@ -9435,10 +9397,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" t="n">
         <v>51.6</v>
@@ -9470,10 +9432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C74" t="n">
         <v>58.8</v>
@@ -9505,10 +9467,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C75" t="n">
         <v>69.4</v>
@@ -9540,10 +9502,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C76" t="n">
         <v>60.3</v>
@@ -9575,10 +9537,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C77" t="n">
         <v>61.5</v>
@@ -9610,10 +9572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C78" t="n">
         <v>42</v>
@@ -9645,10 +9607,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" t="n">
         <v>64.6</v>
@@ -9680,10 +9642,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C80" t="n">
         <v>50</v>
@@ -9715,10 +9677,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C81" t="n">
         <v>28.6</v>
@@ -9748,10 +9710,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C82" t="n">
         <v>63.6</v>
@@ -9783,10 +9745,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C83" t="n">
         <v>48.6</v>
@@ -9818,10 +9780,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C84" t="n">
         <v>57.6</v>
@@ -9853,10 +9815,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C85" t="n">
         <v>61.6</v>
@@ -9888,10 +9850,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C86" t="n">
         <v>45.8</v>
@@ -9923,10 +9885,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" t="n">
         <v>67.3</v>
@@ -9958,10 +9920,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C88" t="n">
         <v>59.3</v>
@@ -9993,10 +9955,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C89" t="n">
         <v>52.6</v>
@@ -10028,10 +9990,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C90" t="n">
         <v>57.9</v>
@@ -10063,10 +10025,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C91" t="n">
         <v>74.2</v>
@@ -10098,10 +10060,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C92" t="n">
         <v>64.4</v>
@@ -10133,10 +10095,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B93" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C93" t="n">
         <v>57.5</v>
@@ -10168,10 +10130,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B94" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C94" t="n">
         <v>80</v>
@@ -10203,10 +10165,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C95" t="n">
         <v>62.1</v>
@@ -10238,10 +10200,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C96" t="n">
         <v>62.7</v>
@@ -10273,10 +10235,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B97" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C97" t="n">
         <v>74.3</v>
@@ -10308,10 +10270,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B98" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C98" t="n">
         <v>60.6</v>
@@ -10343,10 +10305,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C99" t="n">
         <v>66.7</v>
@@ -10378,10 +10340,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C100" t="n">
         <v>65.8</v>
@@ -10413,10 +10375,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B101" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C101" t="n">
         <v>66.2</v>
@@ -10448,10 +10410,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C102" t="n">
         <v>64.4</v>
@@ -10483,10 +10445,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B103" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C103" t="n">
         <v>33.3</v>
@@ -10518,10 +10480,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B104" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C104" t="n">
         <v>58.8</v>
@@ -10553,10 +10515,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>142</v>
+      </c>
+      <c r="B105" t="s">
         <v>143</v>
-      </c>
-      <c r="B105" t="s">
-        <v>144</v>
       </c>
       <c r="C105" t="n">
         <v>51.6</v>
@@ -10588,10 +10550,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C106" t="n">
         <v>62</v>
@@ -10623,10 +10585,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C107" t="n">
         <v>50</v>
@@ -10656,10 +10618,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C108" t="n">
         <v>65.8</v>
@@ -10691,10 +10653,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B109" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C109" t="n">
         <v>51</v>
@@ -10726,10 +10688,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B110" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C110" t="n">
         <v>51.5</v>
@@ -10761,10 +10723,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B111" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C111" t="n">
         <v>63.3</v>
@@ -10796,10 +10758,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B112" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C112" t="n">
         <v>52.6</v>
@@ -10831,10 +10793,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B113" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C113" t="n">
         <v>65.9</v>
@@ -10866,10 +10828,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B114" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C114" t="n">
         <v>60</v>
@@ -10901,10 +10863,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B115" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C115" t="n">
         <v>44</v>
@@ -10936,10 +10898,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B116" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C116" t="n">
         <v>38.9</v>
@@ -10971,10 +10933,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B117" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C117" t="n">
         <v>50</v>
@@ -11006,10 +10968,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C118" t="n">
         <v>57.7</v>
@@ -11041,10 +11003,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B119" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C119" t="n">
         <v>58</v>
@@ -11076,10 +11038,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B120" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C120" t="n">
         <v>70.1</v>
@@ -11111,10 +11073,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B121" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C121" t="n">
         <v>61.6</v>
@@ -11146,10 +11108,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B122" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C122" t="n">
         <v>60.7</v>
@@ -11181,10 +11143,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C123" t="n">
         <v>58.2</v>
@@ -11216,10 +11178,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C124" t="n">
         <v>59.3</v>
@@ -11251,10 +11213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B125" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C125" t="n">
         <v>73.6</v>
@@ -11286,10 +11248,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B126" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C126" t="n">
         <v>78.6</v>
@@ -11319,10 +11281,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B127" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C127" t="n">
         <v>50</v>
@@ -11354,10 +11316,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C128" t="n">
         <v>61.3</v>
@@ -11389,10 +11351,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B129" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C129" t="n">
         <v>65.8</v>
@@ -11424,10 +11386,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B130" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C130" t="n">
         <v>50.9</v>
@@ -11459,10 +11421,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B131" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C131" t="n">
         <v>66.7</v>
@@ -11494,10 +11456,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B132" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C132" t="n">
         <v>69.5</v>
@@ -11529,10 +11491,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C133" t="n">
         <v>59</v>
@@ -11565,7 +11527,7 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C134" t="n">
         <v>59.3</v>

--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -180,364 +180,364 @@
     <t xml:space="preserve">Evan Morrison</t>
   </si>
   <si>
+    <t xml:space="preserve">Iyad Ansari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Valle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julien Monks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kian Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee Kucera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsuki Fukuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Constantineau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Mackie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Morin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yushin Ohta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andy Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guelph Royals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antony Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Patterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carson Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claudio Custodio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conner Morro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damon Topolie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deivis Nadal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drew Donaldson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin Torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garrett Takamatsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleyvin Pineda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.D. Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Sanford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeff MacLeod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Kush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Boscarino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcos Castillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miguel Hiraldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathaniel Ochoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Dos Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taeg Gollert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Mascai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anderson Feliz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Cardinals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angel Guerrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Nicoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Dominguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dario Borrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darlin German</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Magill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremie Veilleux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jommer Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk Gibson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reyny Reyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanner Rempel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor Nicoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breidy Encarnacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchener Panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ernesto Punales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Cooke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Cabral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malik Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mateo Zeppieri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Fabian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Hoyt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Boughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petey Kiefer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuele Bruno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Lawson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yosuke Fujie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yosvani Penalver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yunior Ibarra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Skansi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Thuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London Majors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleveland Brownlee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristian Inoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Draayers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduardo De Oleo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Babiuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarrett Burney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis Jean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maikol Escotto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberto Caro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryder Hancock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starling Joseph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Lenihan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucker Zdunich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Whittle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Sitarenios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto Maple Leafs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Sterritt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brando Leroux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Tomkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crixtian Taveras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dennis Dei Baning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dionysius Chialtas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JJ Dutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Bonzon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Poapst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Knecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Brandt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Cecchetto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spenser Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vasilios Kaloudis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasiel Puig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yolki Pena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yordan Manduley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Hupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welland Jackfish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Luther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryce Arnold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carson Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiki Abe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gianfranco Morello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Greyson Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyad Ansari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Valle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julien Monks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kian Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee Kucera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsuki Fukuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Constantineau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Mackie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Morin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yushin Ohta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andy Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guelph Royals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antony Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Patterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carson Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claudio Custodio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conner Morro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damon Topolie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deivis Nadal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drew Donaldson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franklin Torres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garrett Takamatsu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gleyvin Pineda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J.D. Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Sanford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeff MacLeod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Kush</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Boscarino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcos Castillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miguel Hiraldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathaniel Ochoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Dos Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taeg Gollert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Mascai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anderson Feliz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamilton Cardinals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angel Guerrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Nicoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Dominguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dario Borrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darlin German</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Magill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremie Veilleux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jommer Hernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirk Gibson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reyny Reyes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanner Rempel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor Nicoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yolki Pena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breidy Encarnacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchener Panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ernesto Punales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Cooke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Cabral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malik Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mateo Zeppieri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Fabian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Hoyt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Boughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petey Kiefer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Gross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuele Bruno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Lawson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yosuke Fujie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yosvani Penalver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yunior Ibarra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Skansi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Thuss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London Majors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleveland Brownlee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristian Inoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Draayers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eduardo De Oleo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Babiuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarrett Burney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Lewis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis Jean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maikol Escotto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberto Caro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryder Hancock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starling Joseph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Lenihan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucker Zdunich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Whittle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Sitarenios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto Maple Leafs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Sterritt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brando Leroux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Tomkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crixtian Taveras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dennis Dei Baning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dionysius Chialtas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JJ Dutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Bonzon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Poapst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Knecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Brandt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mike Cecchetto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spenser Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vasilios Kaloudis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yasiel Puig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yordan Manduley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Hupe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welland Jackfish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Luther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryce Arnold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carson Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daiki Abe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gianfranco Morello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marco</t>
   </si>
   <si>
     <t xml:space="preserve">James Smibert</t>
@@ -985,8 +985,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K169" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K169"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K164" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K164"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -2155,31 +2155,31 @@
         <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>75</v>
+        <v>60.4</v>
       </c>
       <c r="D25" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="n">
-        <v>65.9</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="G25" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J25" t="n">
-        <v>66.7</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>66.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -2779,31 +2779,31 @@
         <v>48</v>
       </c>
       <c r="C43" t="n">
-        <v>78.9</v>
+        <v>68.6</v>
       </c>
       <c r="D43" t="n">
-        <v>29.1</v>
+        <v>21.3</v>
       </c>
       <c r="E43" t="n">
-        <v>49.8</v>
+        <v>47.3</v>
       </c>
       <c r="F43" t="n">
-        <v>29.1</v>
+        <v>21.3</v>
       </c>
       <c r="G43" t="n">
-        <v>26.3</v>
+        <v>14.3</v>
       </c>
       <c r="H43" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>47.2</v>
+        <v>33.3</v>
       </c>
       <c r="J43" t="n">
-        <v>32.6</v>
+        <v>43.3</v>
       </c>
       <c r="K43" t="n">
-        <v>37.9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
@@ -2813,32 +2813,28 @@
       <c r="B44" t="s">
         <v>48</v>
       </c>
-      <c r="C44" t="n">
-        <v>68.6</v>
-      </c>
+      <c r="C44"/>
       <c r="D44" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>47.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E44"/>
       <c r="F44" t="n">
-        <v>21.3</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>43.3</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -2848,28 +2844,32 @@
       <c r="B45" t="s">
         <v>48</v>
       </c>
-      <c r="C45"/>
+      <c r="C45" t="n">
+        <v>66.5</v>
+      </c>
       <c r="D45" t="n">
-        <v>100</v>
-      </c>
-      <c r="E45"/>
+        <v>26</v>
+      </c>
+      <c r="E45" t="n">
+        <v>40.5</v>
+      </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>53.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="46">
@@ -2880,31 +2880,31 @@
         <v>48</v>
       </c>
       <c r="C46" t="n">
-        <v>66.5</v>
+        <v>77.3</v>
       </c>
       <c r="D46" t="n">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="E46" t="n">
-        <v>40.5</v>
+        <v>54.8</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="G46" t="n">
-        <v>21.5</v>
+        <v>41.2</v>
       </c>
       <c r="H46" t="n">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="I46" t="n">
-        <v>53.5</v>
+        <v>55.6</v>
       </c>
       <c r="J46" t="n">
-        <v>17.4</v>
+        <v>22.2</v>
       </c>
       <c r="K46" t="n">
-        <v>22.1</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="47">
@@ -2915,31 +2915,31 @@
         <v>48</v>
       </c>
       <c r="C47" t="n">
-        <v>77.3</v>
+        <v>81.2</v>
       </c>
       <c r="D47" t="n">
-        <v>22.5</v>
+        <v>37.6</v>
       </c>
       <c r="E47" t="n">
-        <v>54.8</v>
+        <v>43.6</v>
       </c>
       <c r="F47" t="n">
-        <v>22.5</v>
+        <v>37.6</v>
       </c>
       <c r="G47" t="n">
-        <v>41.2</v>
+        <v>34.8</v>
       </c>
       <c r="H47" t="n">
-        <v>8.2</v>
+        <v>5.4</v>
       </c>
       <c r="I47" t="n">
-        <v>55.6</v>
+        <v>47.5</v>
       </c>
       <c r="J47" t="n">
-        <v>22.2</v>
+        <v>27.5</v>
       </c>
       <c r="K47" t="n">
-        <v>25.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -2950,31 +2950,31 @@
         <v>48</v>
       </c>
       <c r="C48" t="n">
-        <v>81.2</v>
+        <v>50.7</v>
       </c>
       <c r="D48" t="n">
-        <v>37.6</v>
+        <v>17.9</v>
       </c>
       <c r="E48" t="n">
-        <v>43.6</v>
+        <v>32.8</v>
       </c>
       <c r="F48" t="n">
-        <v>37.6</v>
+        <v>17.9</v>
       </c>
       <c r="G48" t="n">
-        <v>34.8</v>
+        <v>18.3</v>
       </c>
       <c r="H48" t="n">
-        <v>5.4</v>
+        <v>17.1</v>
       </c>
       <c r="I48" t="n">
-        <v>47.5</v>
+        <v>38.5</v>
       </c>
       <c r="J48" t="n">
-        <v>27.5</v>
+        <v>30.8</v>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="49">
@@ -2985,31 +2985,31 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>50.7</v>
+        <v>70.8</v>
       </c>
       <c r="D49" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="E49" t="n">
-        <v>32.8</v>
+        <v>53.3</v>
       </c>
       <c r="F49" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="G49" t="n">
-        <v>18.3</v>
+        <v>32.2</v>
       </c>
       <c r="H49" t="n">
-        <v>17.1</v>
+        <v>10.9</v>
       </c>
       <c r="I49" t="n">
-        <v>38.5</v>
+        <v>40.3</v>
       </c>
       <c r="J49" t="n">
-        <v>30.8</v>
+        <v>35.8</v>
       </c>
       <c r="K49" t="n">
-        <v>16.7</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="50">
@@ -3020,31 +3020,31 @@
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>70.8</v>
+        <v>66.1</v>
       </c>
       <c r="D50" t="n">
-        <v>17.5</v>
+        <v>25.3</v>
       </c>
       <c r="E50" t="n">
-        <v>53.3</v>
+        <v>40.8</v>
       </c>
       <c r="F50" t="n">
-        <v>17.5</v>
+        <v>25.3</v>
       </c>
       <c r="G50" t="n">
-        <v>32.2</v>
+        <v>53.9</v>
       </c>
       <c r="H50" t="n">
-        <v>10.9</v>
+        <v>9.8</v>
       </c>
       <c r="I50" t="n">
-        <v>40.3</v>
+        <v>47.4</v>
       </c>
       <c r="J50" t="n">
-        <v>35.8</v>
+        <v>21.1</v>
       </c>
       <c r="K50" t="n">
-        <v>26.9</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="51">
@@ -3055,31 +3055,31 @@
         <v>48</v>
       </c>
       <c r="C51" t="n">
-        <v>66.1</v>
+        <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>25.3</v>
+        <v>14.8</v>
       </c>
       <c r="E51" t="n">
-        <v>40.8</v>
+        <v>57.2</v>
       </c>
       <c r="F51" t="n">
-        <v>25.3</v>
+        <v>14.8</v>
       </c>
       <c r="G51" t="n">
-        <v>53.9</v>
+        <v>21.1</v>
       </c>
       <c r="H51" t="n">
-        <v>9.8</v>
+        <v>13.3</v>
       </c>
       <c r="I51" t="n">
-        <v>47.4</v>
+        <v>63.8</v>
       </c>
       <c r="J51" t="n">
-        <v>21.1</v>
+        <v>14.9</v>
       </c>
       <c r="K51" t="n">
-        <v>31.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="52">
@@ -3090,31 +3090,31 @@
         <v>48</v>
       </c>
       <c r="C52" t="n">
-        <v>72</v>
+        <v>69.3</v>
       </c>
       <c r="D52" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="n">
-        <v>57.2</v>
+        <v>54.7</v>
       </c>
       <c r="F52" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="H52" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
       <c r="I52" t="n">
-        <v>63.8</v>
+        <v>38.8</v>
       </c>
       <c r="J52" t="n">
-        <v>14.9</v>
+        <v>32.8</v>
       </c>
       <c r="K52" t="n">
-        <v>21.3</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="53">
@@ -3125,31 +3125,31 @@
         <v>48</v>
       </c>
       <c r="C53" t="n">
-        <v>69.3</v>
+        <v>77.4</v>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="E53" t="n">
-        <v>54.7</v>
+        <v>63</v>
       </c>
       <c r="F53" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G53" t="n">
-        <v>25.6</v>
+        <v>35.1</v>
       </c>
       <c r="H53" t="n">
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
       <c r="I53" t="n">
-        <v>38.8</v>
+        <v>21.3</v>
       </c>
       <c r="J53" t="n">
-        <v>32.8</v>
+        <v>41.3</v>
       </c>
       <c r="K53" t="n">
-        <v>38.8</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="54">
@@ -3157,69 +3157,69 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
-        <v>77.4</v>
+        <v>77.7</v>
       </c>
       <c r="D54" t="n">
-        <v>14.4</v>
+        <v>24</v>
       </c>
       <c r="E54" t="n">
-        <v>63</v>
+        <v>53.7</v>
       </c>
       <c r="F54" t="n">
-        <v>14.4</v>
+        <v>24</v>
       </c>
       <c r="G54" t="n">
-        <v>35.1</v>
+        <v>30.5</v>
       </c>
       <c r="H54" t="n">
-        <v>14.4</v>
+        <v>10.1</v>
       </c>
       <c r="I54" t="n">
-        <v>21.3</v>
+        <v>53.4</v>
       </c>
       <c r="J54" t="n">
-        <v>41.3</v>
+        <v>20.7</v>
       </c>
       <c r="K54" t="n">
-        <v>50.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
         <v>67</v>
       </c>
-      <c r="B55" t="s">
-        <v>68</v>
-      </c>
       <c r="C55" t="n">
-        <v>77.7</v>
+        <v>79.9</v>
       </c>
       <c r="D55" t="n">
-        <v>24</v>
+        <v>30.3</v>
       </c>
       <c r="E55" t="n">
-        <v>53.7</v>
+        <v>49.6</v>
       </c>
       <c r="F55" t="n">
-        <v>24</v>
+        <v>30.3</v>
       </c>
       <c r="G55" t="n">
-        <v>30.5</v>
+        <v>25</v>
       </c>
       <c r="H55" t="n">
-        <v>10.1</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>53.4</v>
+        <v>41.5</v>
       </c>
       <c r="J55" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="K55" t="n">
-        <v>39.7</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="56">
@@ -3227,34 +3227,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
-        <v>79.9</v>
+        <v>59.8</v>
       </c>
       <c r="D56" t="n">
-        <v>30.3</v>
+        <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>49.6</v>
+        <v>46.8</v>
       </c>
       <c r="F56" t="n">
-        <v>30.3</v>
+        <v>13</v>
       </c>
       <c r="G56" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I56" t="n">
-        <v>41.5</v>
+        <v>53.4</v>
       </c>
       <c r="J56" t="n">
-        <v>22.3</v>
+        <v>17.2</v>
       </c>
       <c r="K56" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="57">
@@ -3262,34 +3262,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
-        <v>59.8</v>
+        <v>66.7</v>
       </c>
       <c r="D57" t="n">
-        <v>13</v>
+        <v>22.2</v>
       </c>
       <c r="E57" t="n">
-        <v>46.8</v>
+        <v>44.5</v>
       </c>
       <c r="F57" t="n">
-        <v>13</v>
+        <v>22.2</v>
       </c>
       <c r="G57" t="n">
-        <v>26.3</v>
+        <v>41.4</v>
       </c>
       <c r="H57" t="n">
-        <v>13</v>
+        <v>17.6</v>
       </c>
       <c r="I57" t="n">
-        <v>53.4</v>
+        <v>50</v>
       </c>
       <c r="J57" t="n">
-        <v>17.2</v>
+        <v>50</v>
       </c>
       <c r="K57" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -3297,98 +3297,98 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
+        <v>40</v>
+      </c>
+      <c r="D58" t="n">
+        <v>50</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" t="n">
         <v>66.7</v>
       </c>
-      <c r="D58" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G58" t="n">
-        <v>41.4</v>
-      </c>
       <c r="H58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I58" t="n">
-        <v>50</v>
-      </c>
-      <c r="J58" t="n">
-        <v>50</v>
-      </c>
-      <c r="K58" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>63.5</v>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="E59" t="n">
-        <v>-10</v>
+        <v>21.4</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="G59" t="n">
-        <v>66.7</v>
+        <v>26.1</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
+        <v>3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="K59" t="n">
+        <v>43.5</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
-        <v>63.5</v>
+        <v>57.1</v>
       </c>
       <c r="D60" t="n">
-        <v>42.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="n">
-        <v>21.4</v>
+        <v>44.6</v>
       </c>
       <c r="F60" t="n">
-        <v>42.1</v>
+        <v>12.5</v>
       </c>
       <c r="G60" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>16.7</v>
       </c>
       <c r="I60" t="n">
-        <v>43.5</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>43.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -3396,34 +3396,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E61" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G61" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="H61" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I61" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -3431,34 +3431,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D62" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F62" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G62" t="n">
-        <v>38.1</v>
+        <v>41.2</v>
       </c>
       <c r="H62" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I62" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -3466,34 +3466,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>72.4</v>
+        <v>46.4</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>12.8</v>
       </c>
       <c r="E63" t="n">
-        <v>62.4</v>
+        <v>33.6</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>12.8</v>
       </c>
       <c r="G63" t="n">
-        <v>41.2</v>
+        <v>17.2</v>
       </c>
       <c r="H63" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I63" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="J63" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="K63" t="n">
-        <v>30</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="64">
@@ -3501,34 +3501,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>46.4</v>
+        <v>70.5</v>
       </c>
       <c r="D64" t="n">
-        <v>12.8</v>
+        <v>18.5</v>
       </c>
       <c r="E64" t="n">
-        <v>33.6</v>
+        <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>12.8</v>
+        <v>18.5</v>
       </c>
       <c r="G64" t="n">
-        <v>17.2</v>
+        <v>22.8</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>13.9</v>
       </c>
       <c r="I64" t="n">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="J64" t="n">
-        <v>30.8</v>
+        <v>23.9</v>
       </c>
       <c r="K64" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="65">
@@ -3536,34 +3536,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="D65" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E65" t="n">
-        <v>52</v>
-      </c>
-      <c r="F65" t="n">
-        <v>18.5</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
       <c r="G65" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>23.9</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>38.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -3571,28 +3565,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
+        <v>78.7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E66" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F66" t="n">
+        <v>13.9</v>
+      </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="67">
@@ -3600,34 +3600,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" t="n">
-        <v>78.7</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>50</v>
       </c>
       <c r="E67" t="n">
-        <v>64.8</v>
+        <v>50</v>
       </c>
       <c r="F67" t="n">
-        <v>13.9</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H67" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -3635,19 +3635,19 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G68" t="n">
         <v>25</v>
@@ -3656,13 +3656,13 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -3670,34 +3670,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69" t="n">
-        <v>33.3</v>
+        <v>72.9</v>
       </c>
       <c r="D69" t="n">
-        <v>33.3</v>
+        <v>2.6</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>70.3</v>
       </c>
       <c r="F69" t="n">
-        <v>33.3</v>
+        <v>2.6</v>
       </c>
       <c r="G69" t="n">
-        <v>25</v>
+        <v>31.4</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -3705,34 +3705,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C70" t="n">
-        <v>72.9</v>
+        <v>69.6</v>
       </c>
       <c r="D70" t="n">
-        <v>2.6</v>
+        <v>33.3</v>
       </c>
       <c r="E70" t="n">
-        <v>70.3</v>
+        <v>36.3</v>
       </c>
       <c r="F70" t="n">
-        <v>2.6</v>
+        <v>33.3</v>
       </c>
       <c r="G70" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="H70" t="n">
-        <v>22.7</v>
+        <v>11.8</v>
       </c>
       <c r="I70" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="J70" t="n">
-        <v>20</v>
+        <v>30.8</v>
       </c>
       <c r="K70" t="n">
-        <v>10</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="71">
@@ -3740,34 +3740,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" t="n">
-        <v>69.6</v>
+        <v>70.8</v>
       </c>
       <c r="D71" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="E71" t="n">
-        <v>36.3</v>
+        <v>50.8</v>
       </c>
       <c r="F71" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="G71" t="n">
-        <v>20</v>
+        <v>44.8</v>
       </c>
       <c r="H71" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="I71" t="n">
-        <v>46.2</v>
+        <v>38.5</v>
       </c>
       <c r="J71" t="n">
-        <v>30.8</v>
+        <v>38.5</v>
       </c>
       <c r="K71" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -3775,34 +3775,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" t="n">
-        <v>70.8</v>
+        <v>68.6</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>31.8</v>
       </c>
       <c r="E72" t="n">
-        <v>50.8</v>
+        <v>36.8</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>31.8</v>
       </c>
       <c r="G72" t="n">
-        <v>44.8</v>
+        <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="I72" t="n">
-        <v>38.5</v>
+        <v>47.6</v>
       </c>
       <c r="J72" t="n">
-        <v>38.5</v>
+        <v>28.6</v>
       </c>
       <c r="K72" t="n">
-        <v>50</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="73">
@@ -3810,34 +3810,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" t="n">
-        <v>68.6</v>
+        <v>67.3</v>
       </c>
       <c r="D73" t="n">
-        <v>31.8</v>
+        <v>12.8</v>
       </c>
       <c r="E73" t="n">
-        <v>36.8</v>
+        <v>54.5</v>
       </c>
       <c r="F73" t="n">
-        <v>31.8</v>
+        <v>12.8</v>
       </c>
       <c r="G73" t="n">
-        <v>11.1</v>
+        <v>26.4</v>
       </c>
       <c r="H73" t="n">
-        <v>3.4</v>
+        <v>10.9</v>
       </c>
       <c r="I73" t="n">
-        <v>47.6</v>
+        <v>38.6</v>
       </c>
       <c r="J73" t="n">
-        <v>28.6</v>
+        <v>36.4</v>
       </c>
       <c r="K73" t="n">
-        <v>38.1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
@@ -3845,34 +3845,34 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" t="n">
-        <v>67.3</v>
+        <v>79.3</v>
       </c>
       <c r="D74" t="n">
-        <v>12.8</v>
+        <v>30.5</v>
       </c>
       <c r="E74" t="n">
-        <v>54.5</v>
+        <v>48.8</v>
       </c>
       <c r="F74" t="n">
-        <v>12.8</v>
+        <v>30.5</v>
       </c>
       <c r="G74" t="n">
-        <v>26.4</v>
+        <v>26.1</v>
       </c>
       <c r="H74" t="n">
-        <v>10.9</v>
+        <v>4.9</v>
       </c>
       <c r="I74" t="n">
-        <v>38.6</v>
+        <v>43.8</v>
       </c>
       <c r="J74" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="K74" t="n">
-        <v>46</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="75">
@@ -3880,34 +3880,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C75" t="n">
-        <v>79.3</v>
+        <v>85.7</v>
       </c>
       <c r="D75" t="n">
-        <v>30.5</v>
+        <v>18.2</v>
       </c>
       <c r="E75" t="n">
-        <v>48.8</v>
+        <v>67.5</v>
       </c>
       <c r="F75" t="n">
-        <v>30.5</v>
+        <v>18.2</v>
       </c>
       <c r="G75" t="n">
-        <v>26.1</v>
+        <v>27.8</v>
       </c>
       <c r="H75" t="n">
-        <v>4.9</v>
+        <v>13.3</v>
       </c>
       <c r="I75" t="n">
-        <v>43.8</v>
+        <v>60</v>
       </c>
       <c r="J75" t="n">
-        <v>35.2</v>
+        <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76">
@@ -3915,34 +3915,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C76" t="n">
-        <v>85.7</v>
+        <v>55.3</v>
       </c>
       <c r="D76" t="n">
-        <v>18.2</v>
+        <v>9.8</v>
       </c>
       <c r="E76" t="n">
-        <v>67.5</v>
+        <v>45.5</v>
       </c>
       <c r="F76" t="n">
-        <v>18.2</v>
+        <v>9.8</v>
       </c>
       <c r="G76" t="n">
-        <v>27.8</v>
+        <v>29.9</v>
       </c>
       <c r="H76" t="n">
-        <v>13.3</v>
+        <v>19.7</v>
       </c>
       <c r="I76" t="n">
-        <v>60</v>
+        <v>51.6</v>
       </c>
       <c r="J76" t="n">
-        <v>20</v>
+        <v>27.4</v>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="77">
@@ -3950,34 +3950,34 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C77" t="n">
-        <v>55.3</v>
+        <v>66.7</v>
       </c>
       <c r="D77" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="F77" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>29.9</v>
+        <v>26.7</v>
       </c>
       <c r="H77" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="I77" t="n">
-        <v>51.6</v>
+        <v>27.3</v>
       </c>
       <c r="J77" t="n">
-        <v>27.4</v>
+        <v>36.4</v>
       </c>
       <c r="K77" t="n">
-        <v>28.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="78">
@@ -3985,34 +3985,34 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C78" t="n">
-        <v>66.7</v>
+        <v>78.4</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E78" t="n">
-        <v>66.7</v>
+        <v>60.4</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G78" t="n">
-        <v>26.7</v>
+        <v>32.2</v>
       </c>
       <c r="H78" t="n">
-        <v>16.7</v>
+        <v>10.5</v>
       </c>
       <c r="I78" t="n">
-        <v>27.3</v>
+        <v>42.5</v>
       </c>
       <c r="J78" t="n">
-        <v>36.4</v>
+        <v>30.1</v>
       </c>
       <c r="K78" t="n">
-        <v>54.5</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="79">
@@ -4020,69 +4020,69 @@
         <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C79" t="n">
-        <v>78.4</v>
+        <v>85.7</v>
       </c>
       <c r="D79" t="n">
-        <v>18</v>
+        <v>15.3</v>
       </c>
       <c r="E79" t="n">
-        <v>60.4</v>
+        <v>70.4</v>
       </c>
       <c r="F79" t="n">
-        <v>18</v>
+        <v>15.3</v>
       </c>
       <c r="G79" t="n">
-        <v>32.2</v>
+        <v>37.7</v>
       </c>
       <c r="H79" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I79" t="n">
-        <v>42.5</v>
+        <v>38.9</v>
       </c>
       <c r="J79" t="n">
-        <v>30.1</v>
+        <v>41.7</v>
       </c>
       <c r="K79" t="n">
-        <v>56.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" t="s">
         <v>93</v>
       </c>
-      <c r="B80" t="s">
-        <v>94</v>
-      </c>
       <c r="C80" t="n">
-        <v>85.7</v>
+        <v>73.7</v>
       </c>
       <c r="D80" t="n">
-        <v>15.3</v>
+        <v>30.4</v>
       </c>
       <c r="E80" t="n">
-        <v>70.4</v>
+        <v>43.3</v>
       </c>
       <c r="F80" t="n">
-        <v>15.3</v>
+        <v>30.4</v>
       </c>
       <c r="G80" t="n">
-        <v>37.7</v>
+        <v>20.5</v>
       </c>
       <c r="H80" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="I80" t="n">
-        <v>38.9</v>
+        <v>58.8</v>
       </c>
       <c r="J80" t="n">
-        <v>41.7</v>
+        <v>17.6</v>
       </c>
       <c r="K80" t="n">
-        <v>47.4</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="81">
@@ -4090,34 +4090,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C81" t="n">
-        <v>73.7</v>
+        <v>75.2</v>
       </c>
       <c r="D81" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
       <c r="E81" t="n">
-        <v>43.3</v>
+        <v>47.7</v>
       </c>
       <c r="F81" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
       <c r="G81" t="n">
-        <v>20.5</v>
+        <v>32.2</v>
       </c>
       <c r="H81" t="n">
-        <v>4.4</v>
+        <v>7.9</v>
       </c>
       <c r="I81" t="n">
-        <v>58.8</v>
+        <v>42.4</v>
       </c>
       <c r="J81" t="n">
-        <v>17.6</v>
+        <v>21.2</v>
       </c>
       <c r="K81" t="n">
-        <v>43.9</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="82">
@@ -4125,34 +4125,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C82" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="D82" t="n">
-        <v>27.5</v>
+        <v>29.1</v>
       </c>
       <c r="E82" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="F82" t="n">
-        <v>27.5</v>
+        <v>29.1</v>
       </c>
       <c r="G82" t="n">
-        <v>32.2</v>
+        <v>27.2</v>
       </c>
       <c r="H82" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="I82" t="n">
-        <v>42.4</v>
+        <v>45.2</v>
       </c>
       <c r="J82" t="n">
-        <v>21.2</v>
+        <v>23.8</v>
       </c>
       <c r="K82" t="n">
-        <v>57.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="83">
@@ -4160,34 +4160,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C83" t="n">
-        <v>76.2</v>
+        <v>83.3</v>
       </c>
       <c r="D83" t="n">
-        <v>29.1</v>
+        <v>23.1</v>
       </c>
       <c r="E83" t="n">
-        <v>47.1</v>
+        <v>60.2</v>
       </c>
       <c r="F83" t="n">
-        <v>29.1</v>
+        <v>23.1</v>
       </c>
       <c r="G83" t="n">
-        <v>27.2</v>
+        <v>11.5</v>
       </c>
       <c r="H83" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="I83" t="n">
-        <v>45.2</v>
+        <v>30.8</v>
       </c>
       <c r="J83" t="n">
-        <v>23.8</v>
+        <v>30.8</v>
       </c>
       <c r="K83" t="n">
-        <v>47.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="84">
@@ -4195,34 +4195,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" t="n">
-        <v>83.3</v>
+        <v>77.9</v>
       </c>
       <c r="D84" t="n">
-        <v>23.1</v>
+        <v>31.7</v>
       </c>
       <c r="E84" t="n">
-        <v>60.2</v>
+        <v>46.2</v>
       </c>
       <c r="F84" t="n">
-        <v>23.1</v>
+        <v>31.7</v>
       </c>
       <c r="G84" t="n">
-        <v>11.5</v>
+        <v>25.4</v>
       </c>
       <c r="H84" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="I84" t="n">
-        <v>30.8</v>
+        <v>45.5</v>
       </c>
       <c r="J84" t="n">
-        <v>30.8</v>
+        <v>26.7</v>
       </c>
       <c r="K84" t="n">
-        <v>53.8</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="85">
@@ -4230,34 +4230,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C85" t="n">
-        <v>77.9</v>
+        <v>74.4</v>
       </c>
       <c r="D85" t="n">
-        <v>31.7</v>
+        <v>19.9</v>
       </c>
       <c r="E85" t="n">
-        <v>46.2</v>
+        <v>54.5</v>
       </c>
       <c r="F85" t="n">
-        <v>31.7</v>
+        <v>19.9</v>
       </c>
       <c r="G85" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="H85" t="n">
-        <v>1.6</v>
+        <v>10.7</v>
       </c>
       <c r="I85" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="J85" t="n">
-        <v>26.7</v>
+        <v>38.1</v>
       </c>
       <c r="K85" t="n">
-        <v>62.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="86">
@@ -4265,34 +4265,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C86" t="n">
-        <v>74.4</v>
+        <v>74</v>
       </c>
       <c r="D86" t="n">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="E86" t="n">
-        <v>54.5</v>
+        <v>51.3</v>
       </c>
       <c r="F86" t="n">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="G86" t="n">
-        <v>26.3</v>
+        <v>30.3</v>
       </c>
       <c r="H86" t="n">
-        <v>10.7</v>
+        <v>6</v>
       </c>
       <c r="I86" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>25</v>
+      </c>
+      <c r="K86" t="n">
         <v>33.3</v>
-      </c>
-      <c r="J86" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>32.9</v>
       </c>
     </row>
     <row r="87">
@@ -4300,34 +4300,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C87" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="D87" t="n">
-        <v>22.7</v>
+        <v>25</v>
       </c>
       <c r="E87" t="n">
-        <v>51.3</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>22.7</v>
+        <v>25</v>
       </c>
       <c r="G87" t="n">
-        <v>30.3</v>
+        <v>36</v>
       </c>
       <c r="H87" t="n">
-        <v>6</v>
+        <v>21.1</v>
       </c>
       <c r="I87" t="n">
-        <v>44.6</v>
+        <v>62.5</v>
       </c>
       <c r="J87" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K87" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
@@ -4335,31 +4335,31 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C88" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="D88" t="n">
-        <v>25</v>
+        <v>29.6</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>45.4</v>
       </c>
       <c r="F88" t="n">
-        <v>25</v>
+        <v>29.6</v>
       </c>
       <c r="G88" t="n">
-        <v>36</v>
+        <v>36.7</v>
       </c>
       <c r="H88" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J88" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>50</v>
@@ -4370,34 +4370,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C89" t="n">
-        <v>75</v>
+        <v>72.3</v>
       </c>
       <c r="D89" t="n">
-        <v>29.6</v>
+        <v>20.9</v>
       </c>
       <c r="E89" t="n">
-        <v>45.4</v>
+        <v>51.4</v>
       </c>
       <c r="F89" t="n">
-        <v>29.6</v>
+        <v>20.9</v>
       </c>
       <c r="G89" t="n">
-        <v>36.7</v>
+        <v>26.5</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I89" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="90">
@@ -4405,34 +4405,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>66.7</v>
+        <v>70.5</v>
       </c>
       <c r="D90" t="n">
-        <v>33.3</v>
+        <v>28.8</v>
       </c>
       <c r="E90" t="n">
-        <v>33.4</v>
+        <v>41.7</v>
       </c>
       <c r="F90" t="n">
-        <v>33.3</v>
+        <v>28.8</v>
       </c>
       <c r="G90" t="n">
-        <v>40</v>
+        <v>19.6</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="I90" t="n">
-        <v>66.7</v>
+        <v>55.7</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="K90" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="91">
@@ -4440,34 +4440,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C91" t="n">
-        <v>70.5</v>
+        <v>72.5</v>
       </c>
       <c r="D91" t="n">
-        <v>28.8</v>
+        <v>32.4</v>
       </c>
       <c r="E91" t="n">
-        <v>41.7</v>
+        <v>40.1</v>
       </c>
       <c r="F91" t="n">
-        <v>28.8</v>
+        <v>32.4</v>
       </c>
       <c r="G91" t="n">
-        <v>19.6</v>
+        <v>26</v>
       </c>
       <c r="H91" t="n">
-        <v>6.1</v>
+        <v>9.3</v>
       </c>
       <c r="I91" t="n">
-        <v>55.7</v>
+        <v>44.4</v>
       </c>
       <c r="J91" t="n">
-        <v>20.5</v>
+        <v>37</v>
       </c>
       <c r="K91" t="n">
-        <v>37.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="92">
@@ -4475,34 +4475,34 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C92" t="n">
-        <v>72.5</v>
+        <v>78.6</v>
       </c>
       <c r="D92" t="n">
-        <v>32.4</v>
+        <v>20</v>
       </c>
       <c r="E92" t="n">
-        <v>40.1</v>
+        <v>58.6</v>
       </c>
       <c r="F92" t="n">
-        <v>32.4</v>
+        <v>20</v>
       </c>
       <c r="G92" t="n">
-        <v>26</v>
+        <v>36.7</v>
       </c>
       <c r="H92" t="n">
-        <v>9.3</v>
+        <v>21.1</v>
       </c>
       <c r="I92" t="n">
-        <v>44.4</v>
+        <v>72.7</v>
       </c>
       <c r="J92" t="n">
-        <v>37</v>
+        <v>9.1</v>
       </c>
       <c r="K92" t="n">
-        <v>55.6</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="93">
@@ -4510,34 +4510,34 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C93" t="n">
-        <v>78.6</v>
+        <v>67.8</v>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="E93" t="n">
-        <v>58.6</v>
+        <v>52.6</v>
       </c>
       <c r="F93" t="n">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="G93" t="n">
-        <v>36.7</v>
+        <v>21.8</v>
       </c>
       <c r="H93" t="n">
-        <v>21.1</v>
+        <v>11.5</v>
       </c>
       <c r="I93" t="n">
-        <v>72.7</v>
+        <v>58</v>
       </c>
       <c r="J93" t="n">
-        <v>9.1</v>
+        <v>16</v>
       </c>
       <c r="K93" t="n">
-        <v>36.4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94">
@@ -4545,991 +4545,991 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="C94" t="n">
-        <v>67.8</v>
+        <v>50</v>
       </c>
       <c r="D94" t="n">
-        <v>15.2</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>52.6</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>15.2</v>
+        <v>50</v>
       </c>
       <c r="G94" t="n">
-        <v>21.8</v>
+        <v>100</v>
       </c>
       <c r="H94" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I94" t="n">
-        <v>58</v>
-      </c>
-      <c r="J94" t="n">
-        <v>16</v>
-      </c>
-      <c r="K94" t="n">
-        <v>42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>110</v>
+      </c>
+      <c r="B95" t="s">
         <v>109</v>
       </c>
-      <c r="B95" t="s">
-        <v>94</v>
-      </c>
       <c r="C95" t="n">
-        <v>53.6</v>
+        <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>15.6</v>
+        <v>33.3</v>
       </c>
       <c r="E95" t="n">
-        <v>38</v>
+        <v>66.7</v>
       </c>
       <c r="F95" t="n">
-        <v>15.6</v>
+        <v>33.3</v>
       </c>
       <c r="G95" t="n">
-        <v>30.9</v>
+        <v>50</v>
       </c>
       <c r="H95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I95" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J95" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K95" t="n">
-        <v>26.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I95"/>
+      <c r="J95"/>
+      <c r="K95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C96" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D96" t="n">
+        <v>20</v>
+      </c>
+      <c r="E96" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>20</v>
+      </c>
+      <c r="G96" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H96" t="n">
         <v>50</v>
       </c>
-      <c r="D96" t="n">
-        <v>50</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>50</v>
-      </c>
-      <c r="G96" t="n">
-        <v>100</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96"/>
-      <c r="J96"/>
-      <c r="K96"/>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C97" t="n">
+        <v>75</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>75</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>40</v>
+      </c>
+      <c r="H97" t="n">
+        <v>25</v>
+      </c>
+      <c r="I97" t="n">
         <v>100</v>
       </c>
-      <c r="D97" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E97" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F97" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G97" t="n">
-        <v>50</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97"/>
-      <c r="J97"/>
-      <c r="K97"/>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C98" t="n">
-        <v>57.8</v>
+        <v>45.5</v>
       </c>
       <c r="D98" t="n">
-        <v>10.8</v>
+        <v>18.2</v>
       </c>
       <c r="E98" t="n">
-        <v>47</v>
+        <v>27.3</v>
       </c>
       <c r="F98" t="n">
-        <v>10.8</v>
+        <v>18.2</v>
       </c>
       <c r="G98" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="H98" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I98" t="n">
-        <v>40.9</v>
+        <v>66.7</v>
       </c>
       <c r="J98" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C99" t="n">
-        <v>71.4</v>
+        <v>59.5</v>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E99" t="n">
-        <v>51.4</v>
+        <v>19.5</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G99" t="n">
-        <v>16.7</v>
+        <v>28.4</v>
       </c>
       <c r="H99" t="n">
-        <v>50</v>
+        <v>2.7</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C100" t="n">
-        <v>75</v>
+        <v>74.3</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="E100" t="n">
-        <v>75</v>
+        <v>40.6</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="G100" t="n">
-        <v>40</v>
+        <v>42.1</v>
       </c>
       <c r="H100" t="n">
-        <v>25</v>
+        <v>8.5</v>
       </c>
       <c r="I100" t="n">
-        <v>100</v>
+        <v>54.1</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="K100" t="n">
-        <v>100</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C101" t="n">
-        <v>45.5</v>
+        <v>71.3</v>
       </c>
       <c r="D101" t="n">
-        <v>18.2</v>
+        <v>21.6</v>
       </c>
       <c r="E101" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G101" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>8</v>
+      </c>
+      <c r="I101" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="J101" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K101" t="n">
         <v>27.3</v>
-      </c>
-      <c r="F101" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G101" t="n">
-        <v>25</v>
-      </c>
-      <c r="H101" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I101" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C102" t="n">
-        <v>59.5</v>
+        <v>66.4</v>
       </c>
       <c r="D102" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="E102" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="G102" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="H102" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I102" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K102" t="n">
         <v>40</v>
-      </c>
-      <c r="E102" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F102" t="n">
-        <v>40</v>
-      </c>
-      <c r="G102" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="H102" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I102" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J102" t="n">
-        <v>25</v>
-      </c>
-      <c r="K102" t="n">
-        <v>12.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C103" t="n">
-        <v>74.3</v>
+        <v>61.7</v>
       </c>
       <c r="D103" t="n">
-        <v>33.7</v>
+        <v>17.7</v>
       </c>
       <c r="E103" t="n">
-        <v>40.6</v>
+        <v>44</v>
       </c>
       <c r="F103" t="n">
-        <v>33.7</v>
+        <v>17.7</v>
       </c>
       <c r="G103" t="n">
-        <v>42.1</v>
+        <v>29.3</v>
       </c>
       <c r="H103" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="I103" t="n">
-        <v>54.1</v>
+        <v>41.3</v>
       </c>
       <c r="J103" t="n">
-        <v>13.5</v>
+        <v>23.9</v>
       </c>
       <c r="K103" t="n">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C104" t="n">
-        <v>71.3</v>
+        <v>100</v>
       </c>
       <c r="D104" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>49.7</v>
+        <v>100</v>
       </c>
       <c r="F104" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>42.7</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
-      </c>
-      <c r="C105" t="n">
-        <v>66.4</v>
-      </c>
-      <c r="D105" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="E105" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F105" t="n">
-        <v>9.3</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
       <c r="G105" t="n">
-        <v>30.4</v>
+        <v>16.7</v>
       </c>
       <c r="H105" t="n">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>30.3</v>
+        <v>100</v>
       </c>
       <c r="J105" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>73.7</v>
+        <v>72.8</v>
       </c>
       <c r="D106" t="n">
-        <v>14.3</v>
+        <v>24.7</v>
       </c>
       <c r="E106" t="n">
-        <v>59.4</v>
+        <v>48.1</v>
       </c>
       <c r="F106" t="n">
-        <v>14.3</v>
+        <v>24.7</v>
       </c>
       <c r="G106" t="n">
-        <v>44.4</v>
+        <v>21.3</v>
       </c>
       <c r="H106" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="I106" t="n">
-        <v>44.4</v>
+        <v>45.8</v>
       </c>
       <c r="J106" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="K106" t="n">
-        <v>30</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C107" t="n">
-        <v>100</v>
+        <v>79.2</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="E107" t="n">
-        <v>100</v>
+        <v>51.9</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>37.3</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>111</v>
-      </c>
-      <c r="C108"/>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
+        <v>109</v>
+      </c>
+      <c r="C108" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D108" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E108" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F108" t="n">
+        <v>35.7</v>
+      </c>
       <c r="G108" t="n">
-        <v>16.7</v>
+        <v>5.3</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I108" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K108" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C109" t="n">
-        <v>72.8</v>
+        <v>59.5</v>
       </c>
       <c r="D109" t="n">
-        <v>24.7</v>
+        <v>15.7</v>
       </c>
       <c r="E109" t="n">
-        <v>48.1</v>
+        <v>43.8</v>
       </c>
       <c r="F109" t="n">
-        <v>24.7</v>
+        <v>15.7</v>
       </c>
       <c r="G109" t="n">
-        <v>21.3</v>
+        <v>33.3</v>
       </c>
       <c r="H109" t="n">
-        <v>8.3</v>
+        <v>4.8</v>
       </c>
       <c r="I109" t="n">
-        <v>45.8</v>
+        <v>29.4</v>
       </c>
       <c r="J109" t="n">
-        <v>25</v>
+        <v>38.2</v>
       </c>
       <c r="K109" t="n">
-        <v>42.7</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>79.2</v>
+        <v>80.8</v>
       </c>
       <c r="D110" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="E110" t="n">
-        <v>51.9</v>
+        <v>54.2</v>
       </c>
       <c r="F110" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="G110" t="n">
-        <v>33.8</v>
+        <v>37.7</v>
       </c>
       <c r="H110" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="I110" t="n">
-        <v>37.3</v>
+        <v>39.7</v>
       </c>
       <c r="J110" t="n">
-        <v>32</v>
+        <v>29.3</v>
       </c>
       <c r="K110" t="n">
-        <v>46.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C111" t="n">
-        <v>71.4</v>
+        <v>67.9</v>
       </c>
       <c r="D111" t="n">
-        <v>35.7</v>
+        <v>16</v>
       </c>
       <c r="E111" t="n">
-        <v>35.7</v>
+        <v>51.9</v>
       </c>
       <c r="F111" t="n">
-        <v>35.7</v>
+        <v>16</v>
       </c>
       <c r="G111" t="n">
-        <v>5.3</v>
+        <v>16.6</v>
       </c>
       <c r="H111" t="n">
-        <v>5.9</v>
+        <v>9.9</v>
       </c>
       <c r="I111" t="n">
-        <v>42.9</v>
+        <v>38.8</v>
       </c>
       <c r="J111" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="K111" t="n">
-        <v>33.3</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C112" t="n">
-        <v>59.5</v>
+        <v>58.1</v>
       </c>
       <c r="D112" t="n">
-        <v>15.7</v>
+        <v>21.7</v>
       </c>
       <c r="E112" t="n">
-        <v>43.8</v>
+        <v>36.4</v>
       </c>
       <c r="F112" t="n">
-        <v>15.7</v>
+        <v>21.7</v>
       </c>
       <c r="G112" t="n">
-        <v>33.3</v>
+        <v>18.3</v>
       </c>
       <c r="H112" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="I112" t="n">
-        <v>29.4</v>
+        <v>40.4</v>
       </c>
       <c r="J112" t="n">
-        <v>38.2</v>
+        <v>22.5</v>
       </c>
       <c r="K112" t="n">
-        <v>35.3</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C113" t="n">
-        <v>80.8</v>
+        <v>61.7</v>
       </c>
       <c r="D113" t="n">
-        <v>26.6</v>
+        <v>15.2</v>
       </c>
       <c r="E113" t="n">
-        <v>54.2</v>
+        <v>46.5</v>
       </c>
       <c r="F113" t="n">
-        <v>26.6</v>
+        <v>15.2</v>
       </c>
       <c r="G113" t="n">
-        <v>37.7</v>
+        <v>26.1</v>
       </c>
       <c r="H113" t="n">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="I113" t="n">
-        <v>39.7</v>
+        <v>53</v>
       </c>
       <c r="J113" t="n">
-        <v>29.3</v>
+        <v>25.8</v>
       </c>
       <c r="K113" t="n">
-        <v>39.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C114" t="n">
-        <v>67.9</v>
+        <v>66.2</v>
       </c>
       <c r="D114" t="n">
-        <v>16</v>
+        <v>36.1</v>
       </c>
       <c r="E114" t="n">
-        <v>51.9</v>
+        <v>30.1</v>
       </c>
       <c r="F114" t="n">
-        <v>16</v>
+        <v>36.1</v>
       </c>
       <c r="G114" t="n">
-        <v>16.6</v>
+        <v>27.9</v>
       </c>
       <c r="H114" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="I114" t="n">
-        <v>38.8</v>
+        <v>40.7</v>
       </c>
       <c r="J114" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="K114" t="n">
-        <v>46.2</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C115" t="n">
-        <v>58.1</v>
+        <v>80</v>
       </c>
       <c r="D115" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>36.4</v>
+        <v>80</v>
       </c>
       <c r="F115" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>18.3</v>
+        <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>40.4</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>22.5</v>
+        <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>132</v>
+      </c>
+      <c r="B116" t="s">
         <v>130</v>
       </c>
-      <c r="B116" t="s">
-        <v>111</v>
-      </c>
       <c r="C116" t="n">
-        <v>61.7</v>
+        <v>68.5</v>
       </c>
       <c r="D116" t="n">
-        <v>15.2</v>
+        <v>18.9</v>
       </c>
       <c r="E116" t="n">
-        <v>46.5</v>
+        <v>49.6</v>
       </c>
       <c r="F116" t="n">
-        <v>15.2</v>
+        <v>18.9</v>
       </c>
       <c r="G116" t="n">
-        <v>26.1</v>
+        <v>12.5</v>
       </c>
       <c r="H116" t="n">
-        <v>10.1</v>
+        <v>12</v>
       </c>
       <c r="I116" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J116" t="n">
-        <v>25.8</v>
+        <v>32.9</v>
       </c>
       <c r="K116" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C117" t="n">
-        <v>66.2</v>
+        <v>68.9</v>
       </c>
       <c r="D117" t="n">
-        <v>36.1</v>
+        <v>22.2</v>
       </c>
       <c r="E117" t="n">
-        <v>30.1</v>
+        <v>46.7</v>
       </c>
       <c r="F117" t="n">
-        <v>36.1</v>
+        <v>22.2</v>
       </c>
       <c r="G117" t="n">
-        <v>27.9</v>
+        <v>29.5</v>
       </c>
       <c r="H117" t="n">
-        <v>7.9</v>
+        <v>8.2</v>
       </c>
       <c r="I117" t="n">
-        <v>40.7</v>
+        <v>47.6</v>
       </c>
       <c r="J117" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="K117" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B118" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C118" t="n">
-        <v>80</v>
+        <v>79.4</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="E118" t="n">
-        <v>80</v>
+        <v>49.7</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="G118" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="J118" t="n">
-        <v>100</v>
+        <v>24.2</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C119" t="n">
-        <v>68.5</v>
+        <v>61.1</v>
       </c>
       <c r="D119" t="n">
-        <v>18.9</v>
+        <v>26.1</v>
       </c>
       <c r="E119" t="n">
-        <v>49.6</v>
+        <v>35</v>
       </c>
       <c r="F119" t="n">
-        <v>18.9</v>
+        <v>26.1</v>
       </c>
       <c r="G119" t="n">
-        <v>12.5</v>
+        <v>23.1</v>
       </c>
       <c r="H119" t="n">
-        <v>12</v>
+        <v>7.7</v>
       </c>
       <c r="I119" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="J119" t="n">
-        <v>32.9</v>
+        <v>14.5</v>
       </c>
       <c r="K119" t="n">
-        <v>49.3</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B120" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C120" t="n">
-        <v>68.9</v>
+        <v>55.7</v>
       </c>
       <c r="D120" t="n">
-        <v>22.2</v>
+        <v>19</v>
       </c>
       <c r="E120" t="n">
-        <v>46.7</v>
+        <v>36.7</v>
       </c>
       <c r="F120" t="n">
-        <v>22.2</v>
+        <v>19</v>
       </c>
       <c r="G120" t="n">
-        <v>29.5</v>
+        <v>9.6</v>
       </c>
       <c r="H120" t="n">
-        <v>8.2</v>
+        <v>11.9</v>
       </c>
       <c r="I120" t="n">
-        <v>47.6</v>
+        <v>64.7</v>
       </c>
       <c r="J120" t="n">
-        <v>22.2</v>
+        <v>10.8</v>
       </c>
       <c r="K120" t="n">
-        <v>47.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C121" t="n">
-        <v>79.4</v>
+        <v>78.6</v>
       </c>
       <c r="D121" t="n">
-        <v>29.7</v>
+        <v>26.9</v>
       </c>
       <c r="E121" t="n">
-        <v>49.7</v>
+        <v>51.7</v>
       </c>
       <c r="F121" t="n">
-        <v>29.7</v>
+        <v>26.9</v>
       </c>
       <c r="G121" t="n">
-        <v>25.6</v>
+        <v>20.7</v>
       </c>
       <c r="H121" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>46.2</v>
+        <v>55.6</v>
       </c>
       <c r="J121" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="K121" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C122" t="n">
-        <v>61.1</v>
+        <v>80</v>
       </c>
       <c r="D122" t="n">
-        <v>26.1</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="n">
-        <v>35</v>
+        <v>68.9</v>
       </c>
       <c r="F122" t="n">
-        <v>26.1</v>
+        <v>11.1</v>
       </c>
       <c r="G122" t="n">
-        <v>23.1</v>
+        <v>39.5</v>
       </c>
       <c r="H122" t="n">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I122" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="J122" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
       </c>
       <c r="K122" t="n">
         <v>45.5</v>
@@ -5537,1627 +5537,1458 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C123" t="n">
-        <v>55.7</v>
+        <v>68.7</v>
       </c>
       <c r="D123" t="n">
-        <v>19</v>
+        <v>28.6</v>
       </c>
       <c r="E123" t="n">
-        <v>36.7</v>
+        <v>40.1</v>
       </c>
       <c r="F123" t="n">
-        <v>19</v>
+        <v>28.6</v>
       </c>
       <c r="G123" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="H123" t="n">
-        <v>11.9</v>
+        <v>4.4</v>
       </c>
       <c r="I123" t="n">
-        <v>64.7</v>
+        <v>37.9</v>
       </c>
       <c r="J123" t="n">
-        <v>10.8</v>
+        <v>32.3</v>
       </c>
       <c r="K123" t="n">
-        <v>25.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C124" t="n">
-        <v>78.6</v>
+        <v>70</v>
       </c>
       <c r="D124" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="E124" t="n">
-        <v>51.7</v>
+        <v>43.3</v>
       </c>
       <c r="F124" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="G124" t="n">
-        <v>20.7</v>
+        <v>14.8</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I124" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="J124" t="n">
-        <v>22.2</v>
+        <v>30</v>
       </c>
       <c r="K124" t="n">
-        <v>22.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C125" t="n">
-        <v>80</v>
+        <v>58.1</v>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>19.4</v>
       </c>
       <c r="E125" t="n">
-        <v>68.9</v>
+        <v>38.7</v>
       </c>
       <c r="F125" t="n">
-        <v>11.1</v>
+        <v>19.4</v>
       </c>
       <c r="G125" t="n">
-        <v>39.5</v>
+        <v>14.7</v>
       </c>
       <c r="H125" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I125" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="J125" t="n">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="K125" t="n">
-        <v>45.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C126" t="n">
-        <v>68.7</v>
+        <v>73.1</v>
       </c>
       <c r="D126" t="n">
-        <v>28.6</v>
+        <v>20.3</v>
       </c>
       <c r="E126" t="n">
-        <v>40.1</v>
+        <v>52.8</v>
       </c>
       <c r="F126" t="n">
-        <v>28.6</v>
+        <v>20.3</v>
       </c>
       <c r="G126" t="n">
-        <v>22</v>
+        <v>32.6</v>
       </c>
       <c r="H126" t="n">
-        <v>4.4</v>
+        <v>12.2</v>
       </c>
       <c r="I126" t="n">
-        <v>37.9</v>
+        <v>49.4</v>
       </c>
       <c r="J126" t="n">
-        <v>32.3</v>
+        <v>20</v>
       </c>
       <c r="K126" t="n">
-        <v>37.9</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>70</v>
+        <v>77.1</v>
       </c>
       <c r="D127" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="E127" t="n">
-        <v>43.3</v>
+        <v>52.7</v>
       </c>
       <c r="F127" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="G127" t="n">
-        <v>14.8</v>
+        <v>30.3</v>
       </c>
       <c r="H127" t="n">
-        <v>12.5</v>
+        <v>8.1</v>
       </c>
       <c r="I127" t="n">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="J127" t="n">
-        <v>30</v>
+        <v>27.1</v>
       </c>
       <c r="K127" t="n">
-        <v>10</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C128" t="n">
-        <v>58.1</v>
+        <v>75.6</v>
       </c>
       <c r="D128" t="n">
-        <v>19.4</v>
+        <v>24.7</v>
       </c>
       <c r="E128" t="n">
-        <v>38.7</v>
+        <v>50.9</v>
       </c>
       <c r="F128" t="n">
-        <v>19.4</v>
+        <v>24.7</v>
       </c>
       <c r="G128" t="n">
-        <v>14.7</v>
+        <v>25.2</v>
       </c>
       <c r="H128" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="I128" t="n">
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="J128" t="n">
-        <v>28.6</v>
+        <v>32.1</v>
       </c>
       <c r="K128" t="n">
-        <v>51.9</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C129" t="n">
-        <v>73.1</v>
+        <v>68.2</v>
       </c>
       <c r="D129" t="n">
-        <v>20.3</v>
+        <v>18.2</v>
       </c>
       <c r="E129" t="n">
-        <v>52.8</v>
+        <v>50</v>
       </c>
       <c r="F129" t="n">
-        <v>20.3</v>
+        <v>18.2</v>
       </c>
       <c r="G129" t="n">
-        <v>32.6</v>
+        <v>21.5</v>
       </c>
       <c r="H129" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="I129" t="n">
-        <v>49.4</v>
+        <v>48.3</v>
       </c>
       <c r="J129" t="n">
-        <v>20</v>
+        <v>17.2</v>
       </c>
       <c r="K129" t="n">
-        <v>38.4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C130" t="n">
-        <v>77.1</v>
+        <v>59.3</v>
       </c>
       <c r="D130" t="n">
-        <v>24.4</v>
+        <v>21.8</v>
       </c>
       <c r="E130" t="n">
-        <v>52.7</v>
+        <v>37.5</v>
       </c>
       <c r="F130" t="n">
-        <v>24.4</v>
+        <v>21.8</v>
       </c>
       <c r="G130" t="n">
-        <v>30.3</v>
+        <v>22.7</v>
       </c>
       <c r="H130" t="n">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
       <c r="I130" t="n">
-        <v>38.5</v>
+        <v>40.9</v>
       </c>
       <c r="J130" t="n">
-        <v>27.1</v>
+        <v>18.2</v>
       </c>
       <c r="K130" t="n">
-        <v>42.1</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C131" t="n">
-        <v>75.6</v>
+        <v>66.7</v>
       </c>
       <c r="D131" t="n">
-        <v>24.7</v>
+        <v>60</v>
       </c>
       <c r="E131" t="n">
-        <v>50.9</v>
+        <v>6.7</v>
       </c>
       <c r="F131" t="n">
-        <v>24.7</v>
+        <v>60</v>
       </c>
       <c r="G131" t="n">
-        <v>25.2</v>
+        <v>33.3</v>
       </c>
       <c r="H131" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="I131" t="n">
-        <v>42.5</v>
+        <v>25</v>
       </c>
       <c r="J131" t="n">
-        <v>32.1</v>
+        <v>25</v>
       </c>
       <c r="K131" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" t="s">
         <v>147</v>
       </c>
-      <c r="B132" t="s">
-        <v>132</v>
-      </c>
       <c r="C132" t="n">
-        <v>68.2</v>
+        <v>66.5</v>
       </c>
       <c r="D132" t="n">
-        <v>18.2</v>
+        <v>16.1</v>
       </c>
       <c r="E132" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F132" t="n">
-        <v>18.2</v>
+        <v>16.1</v>
       </c>
       <c r="G132" t="n">
-        <v>21.5</v>
+        <v>14.1</v>
       </c>
       <c r="H132" t="n">
-        <v>11.9</v>
+        <v>7.8</v>
       </c>
       <c r="I132" t="n">
-        <v>48.3</v>
+        <v>43.8</v>
       </c>
       <c r="J132" t="n">
-        <v>17.2</v>
+        <v>21.9</v>
       </c>
       <c r="K132" t="n">
-        <v>31</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C133" t="n">
-        <v>59.3</v>
+        <v>35</v>
       </c>
       <c r="D133" t="n">
-        <v>21.8</v>
+        <v>13.3</v>
       </c>
       <c r="E133" t="n">
-        <v>37.5</v>
+        <v>21.7</v>
       </c>
       <c r="F133" t="n">
-        <v>21.8</v>
+        <v>13.3</v>
       </c>
       <c r="G133" t="n">
-        <v>22.7</v>
+        <v>33.3</v>
       </c>
       <c r="H133" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>40.9</v>
+        <v>50</v>
       </c>
       <c r="J133" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C134" t="n">
-        <v>66.7</v>
+        <v>70.2</v>
       </c>
       <c r="D134" t="n">
-        <v>60</v>
+        <v>23.3</v>
       </c>
       <c r="E134" t="n">
-        <v>6.7</v>
+        <v>46.9</v>
       </c>
       <c r="F134" t="n">
-        <v>60</v>
+        <v>23.3</v>
       </c>
       <c r="G134" t="n">
-        <v>33.3</v>
+        <v>28.5</v>
       </c>
       <c r="H134" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="I134" t="n">
-        <v>25</v>
+        <v>45.1</v>
       </c>
       <c r="J134" t="n">
-        <v>25</v>
+        <v>29.4</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B135" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C135" t="n">
-        <v>66.5</v>
+        <v>70.6</v>
       </c>
       <c r="D135" t="n">
-        <v>16.1</v>
+        <v>27.1</v>
       </c>
       <c r="E135" t="n">
-        <v>50.4</v>
+        <v>43.5</v>
       </c>
       <c r="F135" t="n">
-        <v>16.1</v>
+        <v>27.1</v>
       </c>
       <c r="G135" t="n">
-        <v>14.1</v>
+        <v>31.9</v>
       </c>
       <c r="H135" t="n">
-        <v>7.8</v>
+        <v>11.4</v>
       </c>
       <c r="I135" t="n">
-        <v>43.8</v>
+        <v>45.9</v>
       </c>
       <c r="J135" t="n">
-        <v>21.9</v>
+        <v>26.2</v>
       </c>
       <c r="K135" t="n">
-        <v>45.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B136" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C136" t="n">
-        <v>35</v>
+        <v>48.1</v>
       </c>
       <c r="D136" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="E136" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="F136" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="G136" t="n">
-        <v>33.3</v>
+        <v>15.4</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I136" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B137" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C137" t="n">
-        <v>70.2</v>
+        <v>66.3</v>
       </c>
       <c r="D137" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="E137" t="n">
-        <v>46.9</v>
+        <v>44</v>
       </c>
       <c r="F137" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="G137" t="n">
-        <v>28.5</v>
+        <v>21.1</v>
       </c>
       <c r="H137" t="n">
-        <v>11.2</v>
+        <v>8</v>
       </c>
       <c r="I137" t="n">
-        <v>45.1</v>
+        <v>55.3</v>
       </c>
       <c r="J137" t="n">
-        <v>29.4</v>
+        <v>14.5</v>
       </c>
       <c r="K137" t="n">
-        <v>39.2</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B138" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C138" t="n">
-        <v>70.6</v>
+        <v>66.7</v>
       </c>
       <c r="D138" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>43.5</v>
+        <v>66.7</v>
       </c>
       <c r="F138" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>31.9</v>
+        <v>18.2</v>
       </c>
       <c r="H138" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>45.9</v>
+        <v>75</v>
       </c>
       <c r="J138" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="K138" t="n">
-        <v>38.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B139" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C139" t="n">
-        <v>48.1</v>
+        <v>55.6</v>
       </c>
       <c r="D139" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="n">
-        <v>23.1</v>
+        <v>44.5</v>
       </c>
       <c r="F139" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="G139" t="n">
-        <v>15.4</v>
+        <v>26.9</v>
       </c>
       <c r="H139" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="I139" t="n">
-        <v>44.4</v>
+        <v>80</v>
       </c>
       <c r="J139" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="K139" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B140" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C140" t="n">
-        <v>66.3</v>
+        <v>69.1</v>
       </c>
       <c r="D140" t="n">
-        <v>22.3</v>
+        <v>26.6</v>
       </c>
       <c r="E140" t="n">
-        <v>44</v>
+        <v>42.5</v>
       </c>
       <c r="F140" t="n">
-        <v>22.3</v>
+        <v>26.6</v>
       </c>
       <c r="G140" t="n">
-        <v>21.1</v>
+        <v>30.4</v>
       </c>
       <c r="H140" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="I140" t="n">
-        <v>55.3</v>
+        <v>37.8</v>
       </c>
       <c r="J140" t="n">
-        <v>14.5</v>
+        <v>24.3</v>
       </c>
       <c r="K140" t="n">
-        <v>31.6</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C141" t="n">
-        <v>66.7</v>
+        <v>65.4</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E141" t="n">
-        <v>66.7</v>
+        <v>40.4</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G141" t="n">
-        <v>18.2</v>
+        <v>20.6</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I141" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="J141" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C142" t="n">
-        <v>72.7</v>
+        <v>80</v>
       </c>
       <c r="D142" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E142" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="F142" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="H142" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I142" t="n">
+        <v>44</v>
+      </c>
+      <c r="J142" t="n">
         <v>20</v>
       </c>
-      <c r="E142" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="F142" t="n">
-        <v>20</v>
-      </c>
-      <c r="G142" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H142" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I142" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
       <c r="K142" t="n">
-        <v>39.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B143" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C143" t="n">
-        <v>55.6</v>
+        <v>58.1</v>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="E143" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="F143" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="G143" t="n">
-        <v>26.9</v>
+        <v>14.1</v>
       </c>
       <c r="H143" t="n">
-        <v>15.8</v>
+        <v>11</v>
       </c>
       <c r="I143" t="n">
-        <v>80</v>
+        <v>52.9</v>
       </c>
       <c r="J143" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="K143" t="n">
-        <v>50</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C144" t="n">
-        <v>69.1</v>
+        <v>63.2</v>
       </c>
       <c r="D144" t="n">
-        <v>26.6</v>
+        <v>45</v>
       </c>
       <c r="E144" t="n">
-        <v>42.5</v>
+        <v>18.2</v>
       </c>
       <c r="F144" t="n">
-        <v>26.6</v>
+        <v>45</v>
       </c>
       <c r="G144" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H144" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I144" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="K144" t="n">
-        <v>39.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C145" t="n">
-        <v>65.4</v>
+        <v>75.1</v>
       </c>
       <c r="D145" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="E145" t="n">
-        <v>40.4</v>
+        <v>63.6</v>
       </c>
       <c r="F145" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="G145" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="H145" t="n">
-        <v>2.8</v>
+        <v>14.2</v>
       </c>
       <c r="I145" t="n">
-        <v>62.5</v>
+        <v>30</v>
       </c>
       <c r="J145" t="n">
-        <v>22.5</v>
+        <v>37.8</v>
       </c>
       <c r="K145" t="n">
-        <v>32.9</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C146" t="n">
-        <v>56.1</v>
+        <v>52.7</v>
       </c>
       <c r="D146" t="n">
-        <v>19.2</v>
+        <v>14.7</v>
       </c>
       <c r="E146" t="n">
-        <v>36.9</v>
+        <v>38</v>
       </c>
       <c r="F146" t="n">
-        <v>19.2</v>
+        <v>14.7</v>
       </c>
       <c r="G146" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I146" t="n">
-        <v>40.5</v>
+        <v>67.7</v>
       </c>
       <c r="J146" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="K146" t="n">
-        <v>40.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C147" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D147" t="n">
-        <v>33.8</v>
+        <v>27.4</v>
       </c>
       <c r="E147" t="n">
-        <v>46.2</v>
+        <v>44.6</v>
       </c>
       <c r="F147" t="n">
-        <v>33.8</v>
+        <v>27.4</v>
       </c>
       <c r="G147" t="n">
-        <v>33.8</v>
+        <v>10.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="I147" t="n">
-        <v>44</v>
+        <v>45.3</v>
       </c>
       <c r="J147" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="K147" t="n">
-        <v>44</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C148" t="n">
-        <v>58.1</v>
+        <v>70.5</v>
       </c>
       <c r="D148" t="n">
-        <v>12.7</v>
+        <v>20.5</v>
       </c>
       <c r="E148" t="n">
-        <v>45.4</v>
+        <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>12.7</v>
+        <v>20.5</v>
       </c>
       <c r="G148" t="n">
-        <v>14.1</v>
+        <v>37.7</v>
       </c>
       <c r="H148" t="n">
-        <v>11</v>
+        <v>9.2</v>
       </c>
       <c r="I148" t="n">
-        <v>52.9</v>
+        <v>51.9</v>
       </c>
       <c r="J148" t="n">
-        <v>11.8</v>
+        <v>21.2</v>
       </c>
       <c r="K148" t="n">
-        <v>34.9</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C149" t="n">
-        <v>63.2</v>
+        <v>69.8</v>
       </c>
       <c r="D149" t="n">
-        <v>45</v>
+        <v>19.1</v>
       </c>
       <c r="E149" t="n">
-        <v>18.2</v>
+        <v>50.7</v>
       </c>
       <c r="F149" t="n">
-        <v>45</v>
+        <v>19.1</v>
       </c>
       <c r="G149" t="n">
-        <v>26.9</v>
+        <v>14.5</v>
       </c>
       <c r="H149" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J149" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="K149" t="n">
-        <v>25</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C150" t="n">
-        <v>75.1</v>
+        <v>64.6</v>
       </c>
       <c r="D150" t="n">
-        <v>11.5</v>
+        <v>16.7</v>
       </c>
       <c r="E150" t="n">
-        <v>63.6</v>
+        <v>47.9</v>
       </c>
       <c r="F150" t="n">
-        <v>11.5</v>
+        <v>16.7</v>
       </c>
       <c r="G150" t="n">
-        <v>21.3</v>
+        <v>37.7</v>
       </c>
       <c r="H150" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="I150" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="J150" t="n">
-        <v>37.8</v>
+        <v>48.1</v>
       </c>
       <c r="K150" t="n">
-        <v>41.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C151" t="n">
-        <v>40</v>
+        <v>60.5</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E151" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="H151" t="n">
-        <v>50</v>
-      </c>
-      <c r="I151"/>
-      <c r="J151"/>
-      <c r="K151"/>
+        <v>13.7</v>
+      </c>
+      <c r="I151" t="n">
+        <v>32</v>
+      </c>
+      <c r="J151" t="n">
+        <v>28</v>
+      </c>
+      <c r="K151" t="n">
+        <v>34.8</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B152" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C152" t="n">
-        <v>72</v>
+        <v>65.6</v>
       </c>
       <c r="D152" t="n">
-        <v>27.4</v>
+        <v>14.4</v>
       </c>
       <c r="E152" t="n">
-        <v>44.6</v>
+        <v>51.2</v>
       </c>
       <c r="F152" t="n">
-        <v>27.4</v>
+        <v>14.4</v>
       </c>
       <c r="G152" t="n">
-        <v>10.2</v>
+        <v>9.2</v>
       </c>
       <c r="H152" t="n">
-        <v>2.7</v>
+        <v>16.6</v>
       </c>
       <c r="I152" t="n">
-        <v>45.3</v>
+        <v>60.6</v>
       </c>
       <c r="J152" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="K152" t="n">
-        <v>28.4</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
+        <v>171</v>
+      </c>
+      <c r="B153" t="s">
         <v>166</v>
       </c>
-      <c r="B153" t="s">
-        <v>167</v>
-      </c>
       <c r="C153" t="n">
-        <v>70.5</v>
+        <v>80.5</v>
       </c>
       <c r="D153" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="E153" t="n">
-        <v>50</v>
+        <v>63.5</v>
       </c>
       <c r="F153" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="G153" t="n">
-        <v>37.7</v>
+        <v>22.6</v>
       </c>
       <c r="H153" t="n">
-        <v>9.2</v>
+        <v>8.5</v>
       </c>
       <c r="I153" t="n">
-        <v>51.9</v>
+        <v>36.4</v>
       </c>
       <c r="J153" t="n">
-        <v>21.2</v>
+        <v>33.6</v>
       </c>
       <c r="K153" t="n">
-        <v>39.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C154" t="n">
-        <v>69.8</v>
+        <v>58.4</v>
       </c>
       <c r="D154" t="n">
-        <v>19.1</v>
+        <v>17.5</v>
       </c>
       <c r="E154" t="n">
-        <v>50.7</v>
+        <v>40.9</v>
       </c>
       <c r="F154" t="n">
-        <v>19.1</v>
+        <v>17.5</v>
       </c>
       <c r="G154" t="n">
-        <v>14.5</v>
+        <v>25.9</v>
       </c>
       <c r="H154" t="n">
-        <v>7.1</v>
+        <v>12.1</v>
       </c>
       <c r="I154" t="n">
-        <v>58</v>
+        <v>49.3</v>
       </c>
       <c r="J154" t="n">
-        <v>18.5</v>
+        <v>23.9</v>
       </c>
       <c r="K154" t="n">
-        <v>42.1</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C155" t="n">
-        <v>64.6</v>
+        <v>75</v>
       </c>
       <c r="D155" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>47.9</v>
+        <v>75</v>
       </c>
       <c r="F155" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>37.7</v>
+        <v>66.7</v>
       </c>
       <c r="H155" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C156" t="n">
-        <v>60.5</v>
+        <v>79.7</v>
       </c>
       <c r="D156" t="n">
-        <v>20</v>
+        <v>27.8</v>
       </c>
       <c r="E156" t="n">
-        <v>40.5</v>
+        <v>51.9</v>
       </c>
       <c r="F156" t="n">
-        <v>20</v>
+        <v>27.8</v>
       </c>
       <c r="G156" t="n">
-        <v>32.9</v>
+        <v>26.5</v>
       </c>
       <c r="H156" t="n">
-        <v>13.7</v>
+        <v>4.3</v>
       </c>
       <c r="I156" t="n">
-        <v>32</v>
+        <v>46.8</v>
       </c>
       <c r="J156" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K156" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C157" t="n">
-        <v>65.6</v>
+        <v>57.7</v>
       </c>
       <c r="D157" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E157" t="n">
-        <v>51.2</v>
+        <v>41</v>
       </c>
       <c r="F157" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="G157" t="n">
-        <v>9.2</v>
+        <v>13.7</v>
       </c>
       <c r="H157" t="n">
-        <v>16.6</v>
+        <v>14.5</v>
       </c>
       <c r="I157" t="n">
-        <v>60.6</v>
+        <v>36.9</v>
       </c>
       <c r="J157" t="n">
-        <v>17.4</v>
+        <v>29.8</v>
       </c>
       <c r="K157" t="n">
-        <v>37.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C158" t="n">
-        <v>80.5</v>
+        <v>61.9</v>
       </c>
       <c r="D158" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="E158" t="n">
-        <v>63.5</v>
+        <v>41.4</v>
       </c>
       <c r="F158" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="G158" t="n">
-        <v>22.6</v>
+        <v>10.5</v>
       </c>
       <c r="H158" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="I158" t="n">
-        <v>36.4</v>
+        <v>60.3</v>
       </c>
       <c r="J158" t="n">
-        <v>33.6</v>
+        <v>17.4</v>
       </c>
       <c r="K158" t="n">
-        <v>43.1</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C159" t="n">
-        <v>58.4</v>
+        <v>71</v>
       </c>
       <c r="D159" t="n">
-        <v>17.5</v>
+        <v>15.6</v>
       </c>
       <c r="E159" t="n">
-        <v>40.9</v>
+        <v>55.4</v>
       </c>
       <c r="F159" t="n">
-        <v>17.5</v>
+        <v>15.6</v>
       </c>
       <c r="G159" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="H159" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
       <c r="I159" t="n">
-        <v>49.3</v>
+        <v>35.1</v>
       </c>
       <c r="J159" t="n">
-        <v>23.9</v>
+        <v>32</v>
       </c>
       <c r="K159" t="n">
-        <v>25.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C160" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="E160" t="n">
-        <v>75</v>
+        <v>48.6</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="G160" t="n">
-        <v>66.7</v>
+        <v>42.4</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>46.4</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="B161" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C161" t="n">
-        <v>87</v>
+        <v>75.6</v>
       </c>
       <c r="D161" t="n">
-        <v>9.1</v>
+        <v>19.3</v>
       </c>
       <c r="E161" t="n">
-        <v>77.9</v>
+        <v>56.3</v>
       </c>
       <c r="F161" t="n">
-        <v>9.1</v>
+        <v>19.3</v>
       </c>
       <c r="G161" t="n">
-        <v>28.6</v>
+        <v>19.7</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I161" t="n">
-        <v>40</v>
+        <v>29.9</v>
       </c>
       <c r="J161" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="K161" t="n">
-        <v>20</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C162" t="n">
-        <v>57.7</v>
+        <v>37.5</v>
       </c>
       <c r="D162" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="E162" t="n">
-        <v>41</v>
+        <v>4.2</v>
       </c>
       <c r="F162" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="G162" t="n">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I162" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J162" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="K162" t="n">
-        <v>52.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B163" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C163" t="n">
-        <v>61.9</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>20.5</v>
+        <v>33.3</v>
       </c>
       <c r="E163" t="n">
-        <v>41.4</v>
+        <v>-33.3</v>
       </c>
       <c r="F163" t="n">
-        <v>20.5</v>
+        <v>33.3</v>
       </c>
       <c r="G163" t="n">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="H163" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I163" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J163" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K163" t="n">
-        <v>31.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="K163"/>
     </row>
     <row r="164">
-      <c r="A164" t="s">
-        <v>177</v>
-      </c>
+      <c r="A164"/>
       <c r="B164" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C164" t="n">
-        <v>71</v>
+        <v>68.7</v>
       </c>
       <c r="D164" t="n">
-        <v>15.6</v>
+        <v>22</v>
       </c>
       <c r="E164" t="n">
-        <v>55.4</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>15.6</v>
+        <v>22</v>
       </c>
       <c r="G164" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="H164" t="n">
-        <v>13.4</v>
+        <v>9.7</v>
       </c>
       <c r="I164" t="n">
-        <v>35.1</v>
+        <v>47.6</v>
       </c>
       <c r="J164" t="n">
-        <v>32</v>
+        <v>24.1</v>
       </c>
       <c r="K164" t="n">
-        <v>53.9</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>178</v>
-      </c>
-      <c r="B165" t="s">
-        <v>167</v>
-      </c>
-      <c r="C165" t="n">
-        <v>76</v>
-      </c>
-      <c r="D165" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E165" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="F165" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G165" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H165" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I165" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="J165" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K165" t="n">
-        <v>64.3</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>179</v>
-      </c>
-      <c r="B166" t="s">
-        <v>167</v>
-      </c>
-      <c r="C166" t="n">
-        <v>75.6</v>
-      </c>
-      <c r="D166" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="E166" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="F166" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G166" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H166" t="n">
-        <v>10</v>
-      </c>
-      <c r="I166" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="J166" t="n">
-        <v>33</v>
-      </c>
-      <c r="K166" t="n">
-        <v>47.2</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>180</v>
-      </c>
-      <c r="B167" t="s">
-        <v>167</v>
-      </c>
-      <c r="C167" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D167" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E167" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167"/>
-      <c r="J167"/>
-      <c r="K167"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>181</v>
-      </c>
-      <c r="B168" t="s">
-        <v>167</v>
-      </c>
-      <c r="C168" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E168" t="n">
-        <v>-33.3</v>
-      </c>
-      <c r="F168" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G168" t="n">
-        <v>100</v>
-      </c>
-      <c r="H168" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168"/>
-      <c r="J168"/>
-      <c r="K168"/>
-    </row>
-    <row r="169">
-      <c r="A169"/>
-      <c r="B169" t="s">
-        <v>182</v>
-      </c>
-      <c r="C169" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="D169" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E169" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G169" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H169" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I169" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="J169" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="K169" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
     </row>
   </sheetData>
@@ -7364,7 +7195,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -8657,7 +8488,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
@@ -8971,7 +8802,7 @@
         <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" t="n">
         <v>60</v>
@@ -9006,7 +8837,7 @@
         <v>231</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" t="n">
         <v>70.5</v>
@@ -9041,7 +8872,7 @@
         <v>232</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
         <v>55.7</v>
@@ -9076,7 +8907,7 @@
         <v>233</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C55" t="n">
         <v>66.7</v>
@@ -9106,10 +8937,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
         <v>73</v>
@@ -9144,7 +8975,7 @@
         <v>234</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
         <v>65.5</v>
@@ -9179,7 +9010,7 @@
         <v>235</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
         <v>59.7</v>
@@ -9211,10 +9042,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
         <v>70.8</v>
@@ -9249,7 +9080,7 @@
         <v>236</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
         <v>62</v>
@@ -9284,7 +9115,7 @@
         <v>237</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
         <v>63.6</v>
@@ -9319,7 +9150,7 @@
         <v>238</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
         <v>58.7</v>
@@ -9354,7 +9185,7 @@
         <v>239</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
         <v>64</v>
@@ -9389,7 +9220,7 @@
         <v>240</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
         <v>62.3</v>
@@ -9421,10 +9252,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
         <v>30</v>
@@ -9456,10 +9287,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
         <v>40</v>
@@ -9494,7 +9325,7 @@
         <v>241</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" t="n">
         <v>43.8</v>
@@ -9526,10 +9357,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" t="n">
         <v>62.5</v>
@@ -9564,7 +9395,7 @@
         <v>242</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C69" t="n">
         <v>70.7</v>
@@ -9599,7 +9430,7 @@
         <v>243</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C70" t="n">
         <v>59.5</v>
@@ -9634,7 +9465,7 @@
         <v>244</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C71" t="n">
         <v>48.1</v>
@@ -9669,7 +9500,7 @@
         <v>245</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C72" t="n">
         <v>58.5</v>
@@ -9704,7 +9535,7 @@
         <v>246</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C73" t="n">
         <v>54.9</v>
@@ -9739,7 +9570,7 @@
         <v>247</v>
       </c>
       <c r="B74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C74" t="n">
         <v>61.6</v>
@@ -9774,7 +9605,7 @@
         <v>248</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C75" t="n">
         <v>63.8</v>
@@ -9809,7 +9640,7 @@
         <v>249</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C76" t="n">
         <v>51.6</v>
@@ -9844,7 +9675,7 @@
         <v>250</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C77" t="n">
         <v>61</v>
@@ -9879,7 +9710,7 @@
         <v>251</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C78" t="n">
         <v>67.4</v>
@@ -9914,7 +9745,7 @@
         <v>252</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C79" t="n">
         <v>62.6</v>
@@ -9949,7 +9780,7 @@
         <v>253</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C80" t="n">
         <v>57.1</v>
@@ -9984,7 +9815,7 @@
         <v>254</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C81" t="n">
         <v>60.7</v>
@@ -10019,7 +9850,7 @@
         <v>255</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C82" t="n">
         <v>42</v>
@@ -10054,7 +9885,7 @@
         <v>256</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C83" t="n">
         <v>65.9</v>
@@ -10089,7 +9920,7 @@
         <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C84" t="n">
         <v>50</v>
@@ -10124,7 +9955,7 @@
         <v>257</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C85" t="n">
         <v>28.6</v>
@@ -10157,7 +9988,7 @@
         <v>258</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C86" t="n">
         <v>61.7</v>
@@ -10192,7 +10023,7 @@
         <v>259</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C87" t="n">
         <v>48.6</v>
@@ -10224,10 +10055,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B88" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C88" t="n">
         <v>61.3</v>
@@ -10259,10 +10090,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C89" t="n">
         <v>61.4</v>
@@ -10297,7 +10128,7 @@
         <v>260</v>
       </c>
       <c r="B90" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C90" t="n">
         <v>45.8</v>
@@ -10332,7 +10163,7 @@
         <v>261</v>
       </c>
       <c r="B91" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C91" t="n">
         <v>67.2</v>
@@ -10367,7 +10198,7 @@
         <v>262</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C92" t="n">
         <v>58.2</v>
@@ -10402,7 +10233,7 @@
         <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C93" t="n">
         <v>52.6</v>
@@ -10437,7 +10268,7 @@
         <v>264</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C94" t="n">
         <v>57.9</v>
@@ -10472,7 +10303,7 @@
         <v>265</v>
       </c>
       <c r="B95" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C95" t="n">
         <v>46.2</v>
@@ -10505,7 +10336,7 @@
         <v>266</v>
       </c>
       <c r="B96" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C96" t="n">
         <v>74.2</v>
@@ -10540,7 +10371,7 @@
         <v>267</v>
       </c>
       <c r="B97" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C97" t="n">
         <v>64.9</v>
@@ -10575,7 +10406,7 @@
         <v>268</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C98" t="n">
         <v>57.1</v>
@@ -10610,7 +10441,7 @@
         <v>269</v>
       </c>
       <c r="B99" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C99" t="n">
         <v>73.3</v>
@@ -10645,7 +10476,7 @@
         <v>270</v>
       </c>
       <c r="B100" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C100" t="n">
         <v>61.4</v>
@@ -10680,7 +10511,7 @@
         <v>271</v>
       </c>
       <c r="B101" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C101" t="n">
         <v>64.5</v>
@@ -10715,7 +10546,7 @@
         <v>272</v>
       </c>
       <c r="B102" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C102" t="n">
         <v>74.3</v>
@@ -10750,7 +10581,7 @@
         <v>273</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C103" t="n">
         <v>60.6</v>
@@ -10785,7 +10616,7 @@
         <v>274</v>
       </c>
       <c r="B104" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C104" t="n">
         <v>66</v>
@@ -10820,7 +10651,7 @@
         <v>275</v>
       </c>
       <c r="B105" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C105" t="n">
         <v>66.5</v>
@@ -10855,7 +10686,7 @@
         <v>276</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C106" t="n">
         <v>66.2</v>
@@ -10890,7 +10721,7 @@
         <v>277</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C107" t="n">
         <v>64.4</v>
@@ -10925,7 +10756,7 @@
         <v>278</v>
       </c>
       <c r="B108" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C108" t="n">
         <v>33.3</v>
@@ -10960,7 +10791,7 @@
         <v>279</v>
       </c>
       <c r="B109" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C109" t="n">
         <v>60</v>
@@ -10992,10 +10823,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B110" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C110" t="n">
         <v>51.6</v>
@@ -11030,7 +10861,7 @@
         <v>280</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C111" t="n">
         <v>63.2</v>
@@ -11065,7 +10896,7 @@
         <v>281</v>
       </c>
       <c r="B112" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C112" t="n">
         <v>50</v>
@@ -11098,7 +10929,7 @@
         <v>282</v>
       </c>
       <c r="B113" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C113" t="n">
         <v>64.6</v>
@@ -11133,7 +10964,7 @@
         <v>283</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C114" t="n">
         <v>51</v>
@@ -11165,10 +10996,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C115" t="n">
         <v>50.6</v>
@@ -11203,7 +11034,7 @@
         <v>284</v>
       </c>
       <c r="B116" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C116" t="n">
         <v>62.5</v>
@@ -11238,7 +11069,7 @@
         <v>285</v>
       </c>
       <c r="B117" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C117" t="n">
         <v>52.6</v>
@@ -11273,7 +11104,7 @@
         <v>286</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C118" t="n">
         <v>64.4</v>
@@ -11308,7 +11139,7 @@
         <v>287</v>
       </c>
       <c r="B119" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C119" t="n">
         <v>61.5</v>
@@ -11343,7 +11174,7 @@
         <v>288</v>
       </c>
       <c r="B120" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C120" t="n">
         <v>44</v>
@@ -11378,7 +11209,7 @@
         <v>289</v>
       </c>
       <c r="B121" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C121" t="n">
         <v>38.9</v>
@@ -11413,7 +11244,7 @@
         <v>290</v>
       </c>
       <c r="B122" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C122" t="n">
         <v>50</v>
@@ -11448,7 +11279,7 @@
         <v>291</v>
       </c>
       <c r="B123" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C123" t="n">
         <v>56.5</v>
@@ -11483,7 +11314,7 @@
         <v>292</v>
       </c>
       <c r="B124" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C124" t="n">
         <v>57.9</v>
@@ -11518,7 +11349,7 @@
         <v>293</v>
       </c>
       <c r="B125" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C125" t="n">
         <v>77.3</v>
@@ -11553,7 +11384,7 @@
         <v>294</v>
       </c>
       <c r="B126" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C126" t="n">
         <v>71</v>
@@ -11588,7 +11419,7 @@
         <v>295</v>
       </c>
       <c r="B127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C127" t="n">
         <v>61.6</v>
@@ -11623,7 +11454,7 @@
         <v>296</v>
       </c>
       <c r="B128" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C128" t="n">
         <v>61.1</v>
@@ -11658,7 +11489,7 @@
         <v>297</v>
       </c>
       <c r="B129" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C129" t="n">
         <v>60</v>
@@ -11693,7 +11524,7 @@
         <v>221</v>
       </c>
       <c r="B130" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C130" t="n">
         <v>59.3</v>
@@ -11728,7 +11559,7 @@
         <v>298</v>
       </c>
       <c r="B131" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C131" t="n">
         <v>74.7</v>
@@ -11763,7 +11594,7 @@
         <v>299</v>
       </c>
       <c r="B132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C132" t="n">
         <v>77.2</v>
@@ -11798,7 +11629,7 @@
         <v>300</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C133" t="n">
         <v>50</v>
@@ -11833,7 +11664,7 @@
         <v>301</v>
       </c>
       <c r="B134" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C134" t="n">
         <v>61.3</v>
@@ -11868,7 +11699,7 @@
         <v>302</v>
       </c>
       <c r="B135" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C135" t="n">
         <v>65.8</v>
@@ -11903,7 +11734,7 @@
         <v>303</v>
       </c>
       <c r="B136" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C136" t="n">
         <v>49.6</v>
@@ -11938,7 +11769,7 @@
         <v>253</v>
       </c>
       <c r="B137" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C137" t="n">
         <v>66.7</v>
@@ -11973,7 +11804,7 @@
         <v>304</v>
       </c>
       <c r="B138" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C138" t="n">
         <v>69.5</v>
@@ -12008,7 +11839,7 @@
         <v>305</v>
       </c>
       <c r="B139" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C139" t="n">
         <v>60.3</v>

--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -420,9 +420,6 @@
     <t xml:space="preserve">London Majors</t>
   </si>
   <si>
-    <t xml:space="preserve">Christian Inoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cleveland Brownlee</t>
   </si>
   <si>
@@ -436,9 +433,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jaden Babiuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Bubiuk</t>
   </si>
   <si>
     <t xml:space="preserve">Jarrett Burney</t>
@@ -1015,8 +1009,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K173" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K173"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K171" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K171"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -5433,31 +5427,31 @@
         <v>134</v>
       </c>
       <c r="C119" t="n">
-        <v>88.9</v>
+        <v>66.7</v>
       </c>
       <c r="D119" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="E119" t="n">
-        <v>61.6</v>
+        <v>16.7</v>
       </c>
       <c r="F119" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="G119" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J119" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120">
@@ -5468,31 +5462,31 @@
         <v>134</v>
       </c>
       <c r="C120" t="n">
-        <v>66.7</v>
+        <v>68.4</v>
       </c>
       <c r="D120" t="n">
-        <v>50</v>
+        <v>17.2</v>
       </c>
       <c r="E120" t="n">
-        <v>16.7</v>
+        <v>51.2</v>
       </c>
       <c r="F120" t="n">
-        <v>50</v>
+        <v>17.2</v>
       </c>
       <c r="G120" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="I120" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J120" t="n">
-        <v>50</v>
+        <v>38.8</v>
       </c>
       <c r="K120" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="121">
@@ -5503,31 +5497,31 @@
         <v>134</v>
       </c>
       <c r="C121" t="n">
-        <v>67.5</v>
+        <v>73.4</v>
       </c>
       <c r="D121" t="n">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="E121" t="n">
-        <v>50.8</v>
+        <v>53.9</v>
       </c>
       <c r="F121" t="n">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="G121" t="n">
-        <v>13.4</v>
+        <v>29.9</v>
       </c>
       <c r="H121" t="n">
-        <v>13.8</v>
+        <v>8.3</v>
       </c>
       <c r="I121" t="n">
-        <v>34.4</v>
+        <v>42.1</v>
       </c>
       <c r="J121" t="n">
-        <v>36.6</v>
+        <v>27.6</v>
       </c>
       <c r="K121" t="n">
-        <v>49.5</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="122">
@@ -5538,31 +5532,31 @@
         <v>134</v>
       </c>
       <c r="C122" t="n">
-        <v>73.4</v>
+        <v>79.6</v>
       </c>
       <c r="D122" t="n">
-        <v>19.5</v>
+        <v>29.4</v>
       </c>
       <c r="E122" t="n">
-        <v>53.9</v>
+        <v>50.2</v>
       </c>
       <c r="F122" t="n">
-        <v>19.5</v>
+        <v>29.4</v>
       </c>
       <c r="G122" t="n">
-        <v>29.9</v>
+        <v>26.4</v>
       </c>
       <c r="H122" t="n">
-        <v>8.3</v>
+        <v>6.3</v>
       </c>
       <c r="I122" t="n">
-        <v>42.1</v>
+        <v>43.2</v>
       </c>
       <c r="J122" t="n">
-        <v>27.6</v>
+        <v>25.2</v>
       </c>
       <c r="K122" t="n">
-        <v>48.7</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="123">
@@ -5573,31 +5567,31 @@
         <v>134</v>
       </c>
       <c r="C123" t="n">
-        <v>79.6</v>
+        <v>59.7</v>
       </c>
       <c r="D123" t="n">
-        <v>29.4</v>
+        <v>25.2</v>
       </c>
       <c r="E123" t="n">
-        <v>50.2</v>
+        <v>34.5</v>
       </c>
       <c r="F123" t="n">
-        <v>29.4</v>
+        <v>25.2</v>
       </c>
       <c r="G123" t="n">
-        <v>26.4</v>
+        <v>25</v>
       </c>
       <c r="H123" t="n">
-        <v>6.3</v>
+        <v>9.7</v>
       </c>
       <c r="I123" t="n">
-        <v>43.2</v>
+        <v>61.7</v>
       </c>
       <c r="J123" t="n">
-        <v>25.2</v>
+        <v>15</v>
       </c>
       <c r="K123" t="n">
-        <v>35.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="124">
@@ -5608,31 +5602,31 @@
         <v>134</v>
       </c>
       <c r="C124" t="n">
-        <v>60</v>
+        <v>58.1</v>
       </c>
       <c r="D124" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E124" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F124" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G124" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H124" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I124" t="n">
+        <v>63</v>
+      </c>
+      <c r="J124" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K124" t="n">
         <v>24.6</v>
-      </c>
-      <c r="E124" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="F124" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G124" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H124" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I124" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J124" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K124" t="n">
-        <v>44.8</v>
       </c>
     </row>
     <row r="125">
@@ -5643,31 +5637,31 @@
         <v>134</v>
       </c>
       <c r="C125" t="n">
-        <v>50</v>
+        <v>67.9</v>
       </c>
       <c r="D125" t="n">
-        <v>30.8</v>
+        <v>15.2</v>
       </c>
       <c r="E125" t="n">
-        <v>19.2</v>
+        <v>52.7</v>
       </c>
       <c r="F125" t="n">
-        <v>30.8</v>
+        <v>15.2</v>
       </c>
       <c r="G125" t="n">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
       <c r="H125" t="n">
-        <v>20</v>
+        <v>13.6</v>
       </c>
       <c r="I125" t="n">
-        <v>100</v>
+        <v>44.8</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="K125" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126">
@@ -5678,31 +5672,31 @@
         <v>134</v>
       </c>
       <c r="C126" t="n">
-        <v>58.1</v>
+        <v>80</v>
       </c>
       <c r="D126" t="n">
-        <v>17.7</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="n">
-        <v>40.4</v>
+        <v>68.9</v>
       </c>
       <c r="F126" t="n">
-        <v>17.7</v>
+        <v>11.1</v>
       </c>
       <c r="G126" t="n">
-        <v>9.9</v>
+        <v>39.5</v>
       </c>
       <c r="H126" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="I126" t="n">
-        <v>63</v>
+        <v>63.6</v>
       </c>
       <c r="J126" t="n">
-        <v>14.2</v>
+        <v>9.1</v>
       </c>
       <c r="K126" t="n">
-        <v>24.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="127">
@@ -5713,31 +5707,31 @@
         <v>134</v>
       </c>
       <c r="C127" t="n">
-        <v>67.9</v>
+        <v>68.5</v>
       </c>
       <c r="D127" t="n">
-        <v>15.2</v>
+        <v>26.7</v>
       </c>
       <c r="E127" t="n">
-        <v>52.7</v>
+        <v>41.8</v>
       </c>
       <c r="F127" t="n">
-        <v>15.2</v>
+        <v>26.7</v>
       </c>
       <c r="G127" t="n">
-        <v>23.3</v>
+        <v>20.2</v>
       </c>
       <c r="H127" t="n">
-        <v>13.6</v>
+        <v>4</v>
       </c>
       <c r="I127" t="n">
-        <v>44.8</v>
+        <v>37.7</v>
       </c>
       <c r="J127" t="n">
-        <v>34.5</v>
+        <v>32.1</v>
       </c>
       <c r="K127" t="n">
-        <v>31</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="128">
@@ -5748,31 +5742,31 @@
         <v>134</v>
       </c>
       <c r="C128" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="E128" t="n">
-        <v>68.9</v>
+        <v>43.3</v>
       </c>
       <c r="F128" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="G128" t="n">
-        <v>39.5</v>
+        <v>14.8</v>
       </c>
       <c r="H128" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I128" t="n">
+        <v>60</v>
+      </c>
+      <c r="J128" t="n">
+        <v>30</v>
+      </c>
+      <c r="K128" t="n">
         <v>10</v>
-      </c>
-      <c r="I128" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J128" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K128" t="n">
-        <v>45.5</v>
       </c>
     </row>
     <row r="129">
@@ -5783,31 +5777,31 @@
         <v>134</v>
       </c>
       <c r="C129" t="n">
-        <v>68.5</v>
+        <v>59.3</v>
       </c>
       <c r="D129" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="E129" t="n">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="F129" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="G129" t="n">
-        <v>20.2</v>
+        <v>14.9</v>
       </c>
       <c r="H129" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I129" t="n">
-        <v>37.7</v>
+        <v>50</v>
       </c>
       <c r="J129" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="K129" t="n">
-        <v>36.5</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="130">
@@ -5818,31 +5812,31 @@
         <v>134</v>
       </c>
       <c r="C130" t="n">
-        <v>70</v>
+        <v>73.8</v>
       </c>
       <c r="D130" t="n">
-        <v>26.7</v>
+        <v>18.3</v>
       </c>
       <c r="E130" t="n">
-        <v>43.3</v>
+        <v>55.5</v>
       </c>
       <c r="F130" t="n">
-        <v>26.7</v>
+        <v>18.3</v>
       </c>
       <c r="G130" t="n">
-        <v>14.8</v>
+        <v>33.2</v>
       </c>
       <c r="H130" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="I130" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J130" t="n">
-        <v>30</v>
+        <v>21.2</v>
       </c>
       <c r="K130" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131">
@@ -5853,31 +5847,31 @@
         <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>59.3</v>
+        <v>77.9</v>
       </c>
       <c r="D131" t="n">
-        <v>18.2</v>
+        <v>22.3</v>
       </c>
       <c r="E131" t="n">
-        <v>41.1</v>
+        <v>55.6</v>
       </c>
       <c r="F131" t="n">
-        <v>18.2</v>
+        <v>22.3</v>
       </c>
       <c r="G131" t="n">
-        <v>14.9</v>
+        <v>29.2</v>
       </c>
       <c r="H131" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="I131" t="n">
-        <v>50</v>
+        <v>38.9</v>
       </c>
       <c r="J131" t="n">
-        <v>31.2</v>
+        <v>28.6</v>
       </c>
       <c r="K131" t="n">
-        <v>51.6</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="132">
@@ -5888,31 +5882,31 @@
         <v>134</v>
       </c>
       <c r="C132" t="n">
-        <v>73.8</v>
+        <v>77.4</v>
       </c>
       <c r="D132" t="n">
-        <v>18.3</v>
+        <v>22.6</v>
       </c>
       <c r="E132" t="n">
-        <v>55.5</v>
+        <v>54.8</v>
       </c>
       <c r="F132" t="n">
-        <v>18.3</v>
+        <v>22.6</v>
       </c>
       <c r="G132" t="n">
-        <v>33.2</v>
+        <v>24.2</v>
       </c>
       <c r="H132" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="I132" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="J132" t="n">
-        <v>21.2</v>
+        <v>32.6</v>
       </c>
       <c r="K132" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="133">
@@ -5923,31 +5917,31 @@
         <v>134</v>
       </c>
       <c r="C133" t="n">
-        <v>77.9</v>
+        <v>68.2</v>
       </c>
       <c r="D133" t="n">
-        <v>22.3</v>
+        <v>15.9</v>
       </c>
       <c r="E133" t="n">
-        <v>55.6</v>
+        <v>52.3</v>
       </c>
       <c r="F133" t="n">
-        <v>22.3</v>
+        <v>15.9</v>
       </c>
       <c r="G133" t="n">
-        <v>29.2</v>
+        <v>23.8</v>
       </c>
       <c r="H133" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="I133" t="n">
-        <v>38.9</v>
+        <v>46.2</v>
       </c>
       <c r="J133" t="n">
-        <v>28.6</v>
+        <v>17.9</v>
       </c>
       <c r="K133" t="n">
-        <v>41.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="134">
@@ -5955,104 +5949,104 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C134" t="n">
-        <v>77.4</v>
+        <v>58.2</v>
       </c>
       <c r="D134" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="E134" t="n">
-        <v>54.8</v>
+        <v>36.5</v>
       </c>
       <c r="F134" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="G134" t="n">
-        <v>24.2</v>
+        <v>23.1</v>
       </c>
       <c r="H134" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="I134" t="n">
-        <v>41.3</v>
+        <v>34.6</v>
       </c>
       <c r="J134" t="n">
-        <v>32.6</v>
+        <v>15.4</v>
       </c>
       <c r="K134" t="n">
-        <v>47.8</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135" t="s">
         <v>151</v>
       </c>
-      <c r="B135" t="s">
-        <v>134</v>
-      </c>
       <c r="C135" t="n">
-        <v>68.2</v>
+        <v>66.7</v>
       </c>
       <c r="D135" t="n">
-        <v>15.9</v>
+        <v>60</v>
       </c>
       <c r="E135" t="n">
-        <v>52.3</v>
+        <v>6.7</v>
       </c>
       <c r="F135" t="n">
-        <v>15.9</v>
+        <v>60</v>
       </c>
       <c r="G135" t="n">
-        <v>23.8</v>
+        <v>33.3</v>
       </c>
       <c r="H135" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="I135" t="n">
-        <v>46.2</v>
+        <v>25</v>
       </c>
       <c r="J135" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="K135" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B136" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C136" t="n">
-        <v>58.2</v>
+        <v>66.2</v>
       </c>
       <c r="D136" t="n">
-        <v>21.7</v>
+        <v>15.2</v>
       </c>
       <c r="E136" t="n">
-        <v>36.5</v>
+        <v>51</v>
       </c>
       <c r="F136" t="n">
-        <v>21.7</v>
+        <v>15.2</v>
       </c>
       <c r="G136" t="n">
-        <v>23.1</v>
+        <v>14.9</v>
       </c>
       <c r="H136" t="n">
         <v>8.1</v>
       </c>
       <c r="I136" t="n">
-        <v>34.6</v>
+        <v>48.9</v>
       </c>
       <c r="J136" t="n">
-        <v>15.4</v>
+        <v>21.1</v>
       </c>
       <c r="K136" t="n">
-        <v>23.1</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="137">
@@ -6060,31 +6054,31 @@
         <v>154</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C137" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="D137" t="n">
-        <v>60</v>
+        <v>13.3</v>
       </c>
       <c r="E137" t="n">
-        <v>6.7</v>
+        <v>21.7</v>
       </c>
       <c r="F137" t="n">
-        <v>60</v>
+        <v>13.3</v>
       </c>
       <c r="G137" t="n">
         <v>33.3</v>
       </c>
       <c r="H137" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J137" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -6095,34 +6089,34 @@
         <v>155</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C138" t="n">
-        <v>66.2</v>
+        <v>72.5</v>
       </c>
       <c r="D138" t="n">
-        <v>15.2</v>
+        <v>20.1</v>
       </c>
       <c r="E138" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="F138" t="n">
-        <v>15.2</v>
+        <v>20.1</v>
       </c>
       <c r="G138" t="n">
-        <v>14.9</v>
+        <v>26.6</v>
       </c>
       <c r="H138" t="n">
-        <v>8.1</v>
+        <v>10.9</v>
       </c>
       <c r="I138" t="n">
-        <v>48.9</v>
+        <v>44.3</v>
       </c>
       <c r="J138" t="n">
-        <v>21.1</v>
+        <v>28.6</v>
       </c>
       <c r="K138" t="n">
-        <v>46.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="139">
@@ -6130,34 +6124,34 @@
         <v>156</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C139" t="n">
-        <v>35</v>
+        <v>74.4</v>
       </c>
       <c r="D139" t="n">
-        <v>13.3</v>
+        <v>25.8</v>
       </c>
       <c r="E139" t="n">
-        <v>21.7</v>
+        <v>48.6</v>
       </c>
       <c r="F139" t="n">
-        <v>13.3</v>
+        <v>25.8</v>
       </c>
       <c r="G139" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>9.8</v>
       </c>
       <c r="I139" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="140">
@@ -6165,34 +6159,34 @@
         <v>157</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C140" t="n">
-        <v>72.5</v>
+        <v>48.1</v>
       </c>
       <c r="D140" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="E140" t="n">
-        <v>52.4</v>
+        <v>23.1</v>
       </c>
       <c r="F140" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="G140" t="n">
-        <v>26.6</v>
+        <v>15.4</v>
       </c>
       <c r="H140" t="n">
-        <v>10.9</v>
+        <v>18.8</v>
       </c>
       <c r="I140" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="J140" t="n">
-        <v>28.6</v>
+        <v>22.2</v>
       </c>
       <c r="K140" t="n">
-        <v>34.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="141">
@@ -6200,34 +6194,34 @@
         <v>158</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C141" t="n">
-        <v>74.4</v>
+        <v>70</v>
       </c>
       <c r="D141" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>48.6</v>
+        <v>70</v>
       </c>
       <c r="F141" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>30.8</v>
+        <v>42.9</v>
       </c>
       <c r="H141" t="n">
-        <v>9.8</v>
+        <v>11.1</v>
       </c>
       <c r="I141" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J141" t="n">
-        <v>26.2</v>
+        <v>50</v>
       </c>
       <c r="K141" t="n">
-        <v>31.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -6235,34 +6229,34 @@
         <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C142" t="n">
-        <v>48.1</v>
+        <v>66.5</v>
       </c>
       <c r="D142" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E142" t="n">
-        <v>23.1</v>
+        <v>42.3</v>
       </c>
       <c r="F142" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="G142" t="n">
-        <v>15.4</v>
+        <v>27.5</v>
       </c>
       <c r="H142" t="n">
-        <v>18.8</v>
+        <v>9.6</v>
       </c>
       <c r="I142" t="n">
-        <v>44.4</v>
+        <v>56</v>
       </c>
       <c r="J142" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="K142" t="n">
-        <v>11.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="143">
@@ -6270,34 +6264,34 @@
         <v>160</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C143" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>42.9</v>
+        <v>18.2</v>
       </c>
       <c r="H143" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
+        <v>75</v>
+      </c>
+      <c r="J143" t="n">
         <v>25</v>
       </c>
-      <c r="J143" t="n">
-        <v>50</v>
-      </c>
       <c r="K143" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -6305,34 +6299,34 @@
         <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C144" t="n">
-        <v>66.5</v>
+        <v>85.7</v>
       </c>
       <c r="D144" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="E144" t="n">
-        <v>42.3</v>
+        <v>60.7</v>
       </c>
       <c r="F144" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="G144" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="H144" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
       <c r="J144" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>29.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="145">
@@ -6340,34 +6334,34 @@
         <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C145" t="n">
-        <v>66.7</v>
+        <v>59</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="E145" t="n">
-        <v>66.7</v>
+        <v>45.2</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="G145" t="n">
-        <v>18.2</v>
+        <v>27</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I145" t="n">
-        <v>75</v>
+        <v>78.6</v>
       </c>
       <c r="J145" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="146">
@@ -6375,34 +6369,34 @@
         <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C146" t="n">
-        <v>85.7</v>
+        <v>67.4</v>
       </c>
       <c r="D146" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="E146" t="n">
-        <v>60.7</v>
+        <v>41.7</v>
       </c>
       <c r="F146" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="G146" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H146" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I146" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="J146" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K146" t="n">
         <v>37.5</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="147">
@@ -6410,34 +6404,34 @@
         <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C147" t="n">
-        <v>59</v>
+        <v>66.4</v>
       </c>
       <c r="D147" t="n">
-        <v>13.8</v>
+        <v>22</v>
       </c>
       <c r="E147" t="n">
-        <v>45.2</v>
+        <v>44.4</v>
       </c>
       <c r="F147" t="n">
-        <v>13.8</v>
+        <v>22</v>
       </c>
       <c r="G147" t="n">
-        <v>27</v>
+        <v>21.1</v>
       </c>
       <c r="H147" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="I147" t="n">
-        <v>78.6</v>
+        <v>63</v>
       </c>
       <c r="J147" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="K147" t="n">
-        <v>42.9</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="148">
@@ -6445,34 +6439,34 @@
         <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C148" t="n">
-        <v>67.4</v>
+        <v>80</v>
       </c>
       <c r="D148" t="n">
-        <v>25.7</v>
+        <v>33.8</v>
       </c>
       <c r="E148" t="n">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
       <c r="F148" t="n">
-        <v>25.7</v>
+        <v>33.8</v>
       </c>
       <c r="G148" t="n">
-        <v>29.5</v>
+        <v>33.8</v>
       </c>
       <c r="H148" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="I148" t="n">
-        <v>39.8</v>
+        <v>44</v>
       </c>
       <c r="J148" t="n">
-        <v>22.7</v>
+        <v>20</v>
       </c>
       <c r="K148" t="n">
-        <v>37.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149">
@@ -6480,34 +6474,34 @@
         <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C149" t="n">
-        <v>66.4</v>
+        <v>57.3</v>
       </c>
       <c r="D149" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E149" t="n">
-        <v>44.4</v>
+        <v>45.3</v>
       </c>
       <c r="F149" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G149" t="n">
-        <v>21.1</v>
+        <v>13</v>
       </c>
       <c r="H149" t="n">
-        <v>4.4</v>
+        <v>10.3</v>
       </c>
       <c r="I149" t="n">
-        <v>63</v>
+        <v>56.1</v>
       </c>
       <c r="J149" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K149" t="n">
-        <v>31.3</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="150">
@@ -6515,34 +6509,34 @@
         <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C150" t="n">
-        <v>80</v>
+        <v>63.2</v>
       </c>
       <c r="D150" t="n">
-        <v>33.8</v>
+        <v>45</v>
       </c>
       <c r="E150" t="n">
-        <v>46.2</v>
+        <v>18.2</v>
       </c>
       <c r="F150" t="n">
-        <v>33.8</v>
+        <v>45</v>
       </c>
       <c r="G150" t="n">
-        <v>33.8</v>
+        <v>26.9</v>
       </c>
       <c r="H150" t="n">
-        <v>5.4</v>
+        <v>7.7</v>
       </c>
       <c r="I150" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K150" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151">
@@ -6550,34 +6544,34 @@
         <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C151" t="n">
-        <v>57.3</v>
+        <v>74</v>
       </c>
       <c r="D151" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E151" t="n">
-        <v>45.3</v>
+        <v>63</v>
       </c>
       <c r="F151" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G151" t="n">
-        <v>13</v>
+        <v>19.9</v>
       </c>
       <c r="H151" t="n">
-        <v>10.3</v>
+        <v>15.6</v>
       </c>
       <c r="I151" t="n">
-        <v>56.1</v>
+        <v>31.9</v>
       </c>
       <c r="J151" t="n">
-        <v>14</v>
+        <v>37.2</v>
       </c>
       <c r="K151" t="n">
-        <v>34.3</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="152">
@@ -6585,34 +6579,34 @@
         <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C152" t="n">
-        <v>63.2</v>
+        <v>59.2</v>
       </c>
       <c r="D152" t="n">
-        <v>45</v>
+        <v>11.3</v>
       </c>
       <c r="E152" t="n">
-        <v>18.2</v>
+        <v>47.9</v>
       </c>
       <c r="F152" t="n">
-        <v>45</v>
+        <v>11.3</v>
       </c>
       <c r="G152" t="n">
-        <v>26.9</v>
+        <v>28.2</v>
       </c>
       <c r="H152" t="n">
-        <v>7.7</v>
+        <v>11.7</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="J152" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="K152" t="n">
-        <v>25</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="153">
@@ -6620,34 +6614,34 @@
         <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C153" t="n">
-        <v>74</v>
+        <v>72.1</v>
       </c>
       <c r="D153" t="n">
-        <v>11</v>
+        <v>25.4</v>
       </c>
       <c r="E153" t="n">
-        <v>63</v>
+        <v>46.7</v>
       </c>
       <c r="F153" t="n">
-        <v>11</v>
+        <v>25.4</v>
       </c>
       <c r="G153" t="n">
-        <v>19.9</v>
+        <v>10</v>
       </c>
       <c r="H153" t="n">
-        <v>15.6</v>
+        <v>4.9</v>
       </c>
       <c r="I153" t="n">
-        <v>31.9</v>
+        <v>46.2</v>
       </c>
       <c r="J153" t="n">
-        <v>37.2</v>
+        <v>22.1</v>
       </c>
       <c r="K153" t="n">
-        <v>40.7</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="154">
@@ -6655,104 +6649,104 @@
         <v>171</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C154" t="n">
-        <v>59.2</v>
+        <v>70.5</v>
       </c>
       <c r="D154" t="n">
-        <v>11.3</v>
+        <v>20.5</v>
       </c>
       <c r="E154" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="F154" t="n">
-        <v>11.3</v>
+        <v>20.5</v>
       </c>
       <c r="G154" t="n">
-        <v>28.2</v>
+        <v>37.7</v>
       </c>
       <c r="H154" t="n">
-        <v>11.7</v>
+        <v>9.2</v>
       </c>
       <c r="I154" t="n">
-        <v>61.9</v>
+        <v>51.9</v>
       </c>
       <c r="J154" t="n">
-        <v>28.6</v>
+        <v>21.2</v>
       </c>
       <c r="K154" t="n">
-        <v>36.6</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>173</v>
+      </c>
+      <c r="B155" t="s">
         <v>172</v>
       </c>
-      <c r="B155" t="s">
-        <v>153</v>
-      </c>
       <c r="C155" t="n">
-        <v>72.1</v>
+        <v>71.2</v>
       </c>
       <c r="D155" t="n">
-        <v>25.4</v>
+        <v>17.3</v>
       </c>
       <c r="E155" t="n">
-        <v>46.7</v>
+        <v>53.9</v>
       </c>
       <c r="F155" t="n">
-        <v>25.4</v>
+        <v>17.3</v>
       </c>
       <c r="G155" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="H155" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="I155" t="n">
-        <v>46.2</v>
+        <v>56.8</v>
       </c>
       <c r="J155" t="n">
-        <v>22.1</v>
+        <v>16.8</v>
       </c>
       <c r="K155" t="n">
-        <v>27.9</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B156" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C156" t="n">
-        <v>70.5</v>
+        <v>64.6</v>
       </c>
       <c r="D156" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E156" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="F156" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="G156" t="n">
         <v>37.7</v>
       </c>
       <c r="H156" t="n">
-        <v>9.2</v>
+        <v>12.5</v>
       </c>
       <c r="I156" t="n">
-        <v>51.9</v>
+        <v>29.6</v>
       </c>
       <c r="J156" t="n">
-        <v>21.2</v>
+        <v>48.1</v>
       </c>
       <c r="K156" t="n">
-        <v>39.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="157">
@@ -6760,34 +6754,34 @@
         <v>175</v>
       </c>
       <c r="B157" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C157" t="n">
-        <v>71.2</v>
+        <v>62.5</v>
       </c>
       <c r="D157" t="n">
-        <v>17.3</v>
+        <v>18.3</v>
       </c>
       <c r="E157" t="n">
-        <v>53.9</v>
+        <v>44.2</v>
       </c>
       <c r="F157" t="n">
-        <v>17.3</v>
+        <v>18.3</v>
       </c>
       <c r="G157" t="n">
-        <v>15.3</v>
+        <v>33.3</v>
       </c>
       <c r="H157" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="I157" t="n">
-        <v>56.8</v>
+        <v>29.6</v>
       </c>
       <c r="J157" t="n">
-        <v>16.8</v>
+        <v>29.6</v>
       </c>
       <c r="K157" t="n">
-        <v>38.9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158">
@@ -6795,34 +6789,34 @@
         <v>176</v>
       </c>
       <c r="B158" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C158" t="n">
-        <v>64.6</v>
+        <v>67.9</v>
       </c>
       <c r="D158" t="n">
-        <v>16.7</v>
+        <v>13.1</v>
       </c>
       <c r="E158" t="n">
-        <v>47.9</v>
+        <v>54.8</v>
       </c>
       <c r="F158" t="n">
-        <v>16.7</v>
+        <v>13.1</v>
       </c>
       <c r="G158" t="n">
-        <v>37.7</v>
+        <v>10.5</v>
       </c>
       <c r="H158" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="I158" t="n">
-        <v>29.6</v>
+        <v>55.4</v>
       </c>
       <c r="J158" t="n">
-        <v>48.1</v>
+        <v>19.2</v>
       </c>
       <c r="K158" t="n">
-        <v>38.5</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="159">
@@ -6830,34 +6824,34 @@
         <v>177</v>
       </c>
       <c r="B159" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C159" t="n">
-        <v>62.5</v>
+        <v>79.4</v>
       </c>
       <c r="D159" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="E159" t="n">
-        <v>44.2</v>
+        <v>60.6</v>
       </c>
       <c r="F159" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="G159" t="n">
-        <v>33.3</v>
+        <v>23.6</v>
       </c>
       <c r="H159" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="I159" t="n">
-        <v>29.6</v>
+        <v>35.2</v>
       </c>
       <c r="J159" t="n">
-        <v>29.6</v>
+        <v>36.9</v>
       </c>
       <c r="K159" t="n">
-        <v>32</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="160">
@@ -6865,34 +6859,34 @@
         <v>178</v>
       </c>
       <c r="B160" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C160" t="n">
-        <v>67.9</v>
+        <v>62.3</v>
       </c>
       <c r="D160" t="n">
-        <v>13.1</v>
+        <v>17.9</v>
       </c>
       <c r="E160" t="n">
-        <v>54.8</v>
+        <v>44.4</v>
       </c>
       <c r="F160" t="n">
-        <v>13.1</v>
+        <v>17.9</v>
       </c>
       <c r="G160" t="n">
-        <v>10.5</v>
+        <v>26.5</v>
       </c>
       <c r="H160" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="I160" t="n">
-        <v>55.4</v>
+        <v>51.2</v>
       </c>
       <c r="J160" t="n">
-        <v>19.2</v>
+        <v>25</v>
       </c>
       <c r="K160" t="n">
-        <v>34.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="161">
@@ -6900,34 +6894,34 @@
         <v>179</v>
       </c>
       <c r="B161" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C161" t="n">
-        <v>79.4</v>
+        <v>75</v>
       </c>
       <c r="D161" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>60.6</v>
+        <v>75</v>
       </c>
       <c r="F161" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>23.6</v>
+        <v>66.7</v>
       </c>
       <c r="H161" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>35.2</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>36.9</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>42.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6935,34 +6929,34 @@
         <v>180</v>
       </c>
       <c r="B162" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C162" t="n">
-        <v>62.3</v>
+        <v>80.2</v>
       </c>
       <c r="D162" t="n">
-        <v>17.9</v>
+        <v>27</v>
       </c>
       <c r="E162" t="n">
-        <v>44.4</v>
+        <v>53.2</v>
       </c>
       <c r="F162" t="n">
-        <v>17.9</v>
+        <v>27</v>
       </c>
       <c r="G162" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="H162" t="n">
-        <v>13.2</v>
+        <v>5.3</v>
       </c>
       <c r="I162" t="n">
-        <v>51.2</v>
+        <v>46.4</v>
       </c>
       <c r="J162" t="n">
-        <v>25</v>
+        <v>34.8</v>
       </c>
       <c r="K162" t="n">
-        <v>21.1</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="163">
@@ -6970,34 +6964,34 @@
         <v>181</v>
       </c>
       <c r="B163" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C163" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E163" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G163" t="n">
-        <v>66.7</v>
+        <v>14.5</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="164">
@@ -7005,34 +6999,34 @@
         <v>182</v>
       </c>
       <c r="B164" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C164" t="n">
-        <v>80.2</v>
+        <v>61.5</v>
       </c>
       <c r="D164" t="n">
-        <v>27</v>
+        <v>18.4</v>
       </c>
       <c r="E164" t="n">
-        <v>53.2</v>
+        <v>43.1</v>
       </c>
       <c r="F164" t="n">
-        <v>27</v>
+        <v>18.4</v>
       </c>
       <c r="G164" t="n">
-        <v>27</v>
+        <v>11.3</v>
       </c>
       <c r="H164" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="I164" t="n">
-        <v>46.4</v>
+        <v>57.1</v>
       </c>
       <c r="J164" t="n">
-        <v>34.8</v>
+        <v>18.6</v>
       </c>
       <c r="K164" t="n">
-        <v>38.2</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="165">
@@ -7040,34 +7034,34 @@
         <v>183</v>
       </c>
       <c r="B165" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C165" t="n">
-        <v>59</v>
+        <v>72.3</v>
       </c>
       <c r="D165" t="n">
-        <v>16</v>
+        <v>14.7</v>
       </c>
       <c r="E165" t="n">
-        <v>43</v>
+        <v>57.6</v>
       </c>
       <c r="F165" t="n">
-        <v>16</v>
+        <v>14.7</v>
       </c>
       <c r="G165" t="n">
-        <v>14.5</v>
+        <v>28.4</v>
       </c>
       <c r="H165" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="I165" t="n">
-        <v>37.5</v>
+        <v>32.1</v>
       </c>
       <c r="J165" t="n">
-        <v>28.8</v>
+        <v>34.9</v>
       </c>
       <c r="K165" t="n">
-        <v>52</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="166">
@@ -7075,34 +7069,34 @@
         <v>184</v>
       </c>
       <c r="B166" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C166" t="n">
-        <v>61.5</v>
+        <v>76.4</v>
       </c>
       <c r="D166" t="n">
-        <v>18.4</v>
+        <v>26.7</v>
       </c>
       <c r="E166" t="n">
-        <v>43.1</v>
+        <v>49.7</v>
       </c>
       <c r="F166" t="n">
-        <v>18.4</v>
+        <v>26.7</v>
       </c>
       <c r="G166" t="n">
-        <v>11.3</v>
+        <v>40.7</v>
       </c>
       <c r="H166" t="n">
-        <v>8.6</v>
+        <v>8.8</v>
       </c>
       <c r="I166" t="n">
-        <v>57.1</v>
+        <v>43.8</v>
       </c>
       <c r="J166" t="n">
-        <v>18.6</v>
+        <v>28.1</v>
       </c>
       <c r="K166" t="n">
-        <v>31.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="167">
@@ -7110,34 +7104,34 @@
         <v>185</v>
       </c>
       <c r="B167" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C167" t="n">
-        <v>72.3</v>
+        <v>74.6</v>
       </c>
       <c r="D167" t="n">
-        <v>14.7</v>
+        <v>20.3</v>
       </c>
       <c r="E167" t="n">
-        <v>57.6</v>
+        <v>54.3</v>
       </c>
       <c r="F167" t="n">
-        <v>14.7</v>
+        <v>20.3</v>
       </c>
       <c r="G167" t="n">
-        <v>28.4</v>
+        <v>23.5</v>
       </c>
       <c r="H167" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="I167" t="n">
-        <v>32.1</v>
+        <v>29</v>
       </c>
       <c r="J167" t="n">
-        <v>34.9</v>
+        <v>32.7</v>
       </c>
       <c r="K167" t="n">
-        <v>54.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="168">
@@ -7145,177 +7139,107 @@
         <v>186</v>
       </c>
       <c r="B168" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C168" t="n">
-        <v>76.4</v>
+        <v>37.5</v>
       </c>
       <c r="D168" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="E168" t="n">
-        <v>49.7</v>
+        <v>4.2</v>
       </c>
       <c r="F168" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="G168" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="I168" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="J168" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="K168" t="n">
-        <v>56.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I168"/>
+      <c r="J168"/>
+      <c r="K168"/>
     </row>
     <row r="169">
       <c r="A169" t="s">
         <v>187</v>
       </c>
       <c r="B169" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C169" t="n">
-        <v>74.6</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>20.3</v>
+        <v>33.3</v>
       </c>
       <c r="E169" t="n">
-        <v>54.3</v>
+        <v>-33.3</v>
       </c>
       <c r="F169" t="n">
-        <v>20.3</v>
+        <v>33.3</v>
       </c>
       <c r="G169" t="n">
-        <v>23.5</v>
+        <v>100</v>
       </c>
       <c r="H169" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I169" t="n">
-        <v>29</v>
-      </c>
-      <c r="J169" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="K169" t="n">
-        <v>47.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I169"/>
+      <c r="J169"/>
+      <c r="K169"/>
     </row>
     <row r="170">
       <c r="A170" t="s">
         <v>188</v>
       </c>
       <c r="B170" t="s">
-        <v>174</v>
-      </c>
-      <c r="C170" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D170" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E170" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F170" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" t="n">
-        <v>0</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C170"/>
+      <c r="D170"/>
+      <c r="E170"/>
+      <c r="F170"/>
+      <c r="G170"/>
+      <c r="H170"/>
       <c r="I170"/>
       <c r="J170"/>
       <c r="K170"/>
     </row>
     <row r="171">
-      <c r="A171" t="s">
+      <c r="A171"/>
+      <c r="B171" t="s">
         <v>189</v>
       </c>
-      <c r="B171" t="s">
-        <v>174</v>
-      </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>69.3</v>
       </c>
       <c r="D171" t="n">
-        <v>33.3</v>
+        <v>21.3</v>
       </c>
       <c r="E171" t="n">
-        <v>-33.3</v>
+        <v>48.3</v>
       </c>
       <c r="F171" t="n">
-        <v>33.3</v>
+        <v>21.3</v>
       </c>
       <c r="G171" t="n">
-        <v>100</v>
+        <v>27.2</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171"/>
-      <c r="J171"/>
-      <c r="K171"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>190</v>
-      </c>
-      <c r="B172" t="s">
-        <v>174</v>
-      </c>
-      <c r="C172"/>
-      <c r="D172"/>
-      <c r="E172"/>
-      <c r="F172"/>
-      <c r="G172"/>
-      <c r="H172"/>
-      <c r="I172"/>
-      <c r="J172"/>
-      <c r="K172"/>
-    </row>
-    <row r="173">
-      <c r="A173"/>
-      <c r="B173" t="s">
-        <v>191</v>
-      </c>
-      <c r="C173" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="D173" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E173" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="F173" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G173" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H173" t="n">
         <v>9.7</v>
       </c>
-      <c r="I173" t="n">
-        <v>48</v>
-      </c>
-      <c r="J173" t="n">
-        <v>24</v>
-      </c>
-      <c r="K173" t="n">
-        <v>39.8</v>
+      <c r="I171" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="K171" t="n">
+        <v>39.2</v>
       </c>
     </row>
   </sheetData>
@@ -7347,22 +7271,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7371,18 +7295,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7417,7 +7341,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7452,7 +7376,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7557,7 +7481,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7592,7 +7516,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7627,7 +7551,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7697,7 +7621,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7732,7 +7656,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7767,7 +7691,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7802,7 +7726,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7837,7 +7761,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -7905,7 +7829,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -7940,7 +7864,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -7975,7 +7899,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -8080,7 +8004,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -8115,7 +8039,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -8150,7 +8074,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -8185,7 +8109,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -8220,7 +8144,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -8255,7 +8179,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
@@ -8290,7 +8214,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
@@ -8325,7 +8249,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -8360,7 +8284,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -8395,7 +8319,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -8430,7 +8354,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -8465,7 +8389,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -8500,7 +8424,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
@@ -8535,7 +8459,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -8570,7 +8494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
@@ -8640,7 +8564,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
@@ -8710,7 +8634,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
@@ -8745,7 +8669,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -8780,7 +8704,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
@@ -8815,7 +8739,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
@@ -8883,7 +8807,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B45" t="s">
         <v>47</v>
@@ -8918,7 +8842,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s">
         <v>47</v>
@@ -8953,7 +8877,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B47" t="s">
         <v>47</v>
@@ -8988,7 +8912,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B48" t="s">
         <v>47</v>
@@ -9023,7 +8947,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B49" t="s">
         <v>47</v>
@@ -9058,7 +8982,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s">
         <v>47</v>
@@ -9093,7 +9017,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B51" t="s">
         <v>47</v>
@@ -9126,7 +9050,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B52" t="s">
         <v>47</v>
@@ -9161,7 +9085,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B53" t="s">
         <v>70</v>
@@ -9196,7 +9120,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B54" t="s">
         <v>70</v>
@@ -9231,7 +9155,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s">
         <v>70</v>
@@ -9266,7 +9190,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B56" t="s">
         <v>70</v>
@@ -9334,7 +9258,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s">
         <v>70</v>
@@ -9369,7 +9293,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s">
         <v>70</v>
@@ -9439,7 +9363,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B61" t="s">
         <v>70</v>
@@ -9474,7 +9398,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B62" t="s">
         <v>70</v>
@@ -9509,7 +9433,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B63" t="s">
         <v>70</v>
@@ -9544,7 +9468,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B64" t="s">
         <v>70</v>
@@ -9579,7 +9503,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B65" t="s">
         <v>70</v>
@@ -9684,7 +9608,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B68" t="s">
         <v>70</v>
@@ -9719,7 +9643,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B69" t="s">
         <v>70</v>
@@ -9789,7 +9713,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B71" t="s">
         <v>96</v>
@@ -9824,7 +9748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B72" t="s">
         <v>96</v>
@@ -9859,7 +9783,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B73" t="s">
         <v>96</v>
@@ -9894,7 +9818,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s">
         <v>96</v>
@@ -9929,7 +9853,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B75" t="s">
         <v>96</v>
@@ -9964,7 +9888,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B76" t="s">
         <v>96</v>
@@ -9999,7 +9923,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B77" t="s">
         <v>96</v>
@@ -10034,7 +9958,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s">
         <v>96</v>
@@ -10069,7 +9993,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s">
         <v>96</v>
@@ -10104,7 +10028,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B80" t="s">
         <v>96</v>
@@ -10139,7 +10063,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s">
         <v>96</v>
@@ -10174,7 +10098,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
         <v>96</v>
@@ -10209,7 +10133,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
         <v>96</v>
@@ -10244,7 +10168,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B84" t="s">
         <v>96</v>
@@ -10279,7 +10203,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s">
         <v>113</v>
@@ -10314,7 +10238,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s">
         <v>113</v>
@@ -10349,7 +10273,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B87" t="s">
         <v>113</v>
@@ -10384,7 +10308,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B88" t="s">
         <v>113</v>
@@ -10417,7 +10341,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B89" t="s">
         <v>113</v>
@@ -10452,7 +10376,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B90" t="s">
         <v>113</v>
@@ -10557,7 +10481,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B93" t="s">
         <v>113</v>
@@ -10592,7 +10516,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B94" t="s">
         <v>113</v>
@@ -10627,7 +10551,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B95" t="s">
         <v>113</v>
@@ -10662,7 +10586,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B96" t="s">
         <v>113</v>
@@ -10697,7 +10621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B97" t="s">
         <v>113</v>
@@ -10732,7 +10656,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B98" t="s">
         <v>113</v>
@@ -10767,7 +10691,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B99" t="s">
         <v>134</v>
@@ -10802,7 +10726,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B100" t="s">
         <v>134</v>
@@ -10837,7 +10761,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B101" t="s">
         <v>134</v>
@@ -10872,7 +10796,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B102" t="s">
         <v>134</v>
@@ -10907,7 +10831,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B103" t="s">
         <v>134</v>
@@ -10963,7 +10887,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B105" t="s">
         <v>134</v>
@@ -10998,7 +10922,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B106" t="s">
         <v>134</v>
@@ -11033,7 +10957,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B107" t="s">
         <v>134</v>
@@ -11068,7 +10992,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B108" t="s">
         <v>134</v>
@@ -11103,7 +11027,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B109" t="s">
         <v>134</v>
@@ -11138,7 +11062,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B110" t="s">
         <v>134</v>
@@ -11173,7 +11097,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B111" t="s">
         <v>134</v>
@@ -11208,10 +11132,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B112" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C112" t="n">
         <v>33.3</v>
@@ -11243,10 +11167,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B113" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C113" t="n">
         <v>60.9</v>
@@ -11278,10 +11202,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C114" t="n">
         <v>51.6</v>
@@ -11313,10 +11237,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C115" t="n">
         <v>63.2</v>
@@ -11348,10 +11272,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B116" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C116" t="n">
         <v>50</v>
@@ -11381,10 +11305,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B117" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C117" t="n">
         <v>60</v>
@@ -11416,10 +11340,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B118" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C118" t="n">
         <v>50</v>
@@ -11451,10 +11375,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B119" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C119" t="n">
         <v>50.6</v>
@@ -11486,10 +11410,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B120" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C120" t="n">
         <v>58.6</v>
@@ -11521,10 +11445,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B121" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C121" t="n">
         <v>52.6</v>
@@ -11556,10 +11480,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B122" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C122" t="n">
         <v>63.1</v>
@@ -11591,10 +11515,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B123" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C123" t="n">
         <v>64.9</v>
@@ -11626,10 +11550,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B124" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C124" t="n">
         <v>44</v>
@@ -11661,10 +11585,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B125" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C125" t="n">
         <v>38.9</v>
@@ -11696,10 +11620,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B126" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C126" t="n">
         <v>50</v>
@@ -11731,10 +11655,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B127" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C127" t="n">
         <v>55.1</v>
@@ -11766,10 +11690,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B128" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C128" t="n">
         <v>57.9</v>
@@ -11801,10 +11725,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B129" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C129" t="n">
         <v>40</v>
@@ -11836,10 +11760,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B130" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C130" t="n">
         <v>61.7</v>
@@ -11871,10 +11795,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B131" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C131" t="n">
         <v>71</v>
@@ -11906,10 +11830,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B132" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C132" t="n">
         <v>64.1</v>
@@ -11941,10 +11865,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B133" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C133" t="n">
         <v>61.1</v>
@@ -11976,10 +11900,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B134" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C134" t="n">
         <v>58.8</v>
@@ -12011,10 +11935,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C135" t="n">
         <v>62.7</v>
@@ -12046,10 +11970,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C136" t="n">
         <v>77.6</v>
@@ -12081,10 +12005,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B137" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C137" t="n">
         <v>74.2</v>
@@ -12116,10 +12040,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B138" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C138" t="n">
         <v>50</v>
@@ -12151,10 +12075,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B139" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C139" t="n">
         <v>61.3</v>
@@ -12186,10 +12110,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B140" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C140" t="n">
         <v>65.8</v>
@@ -12221,10 +12145,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B141" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C141" t="n">
         <v>49.2</v>
@@ -12256,10 +12180,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B142" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C142" t="n">
         <v>66.7</v>
@@ -12291,10 +12215,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B143" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C143" t="n">
         <v>70.6</v>
@@ -12326,10 +12250,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B144" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C144" t="n">
         <v>61</v>
@@ -12362,7 +12286,7 @@
     <row r="145">
       <c r="A145"/>
       <c r="B145" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C145" t="n">
         <v>57.7</v>

--- a/cbl-new/data/summary2026.xlsx
+++ b/cbl-new/data/summary2026.xlsx
@@ -189,391 +189,391 @@
     <t xml:space="preserve">Evan Morrison</t>
   </si>
   <si>
+    <t xml:space="preserve">Iyad Ansari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Valle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julien Monks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kian Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee Kucera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Chernesky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsuki Fukuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Constantineau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Mackie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Morin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Richards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yushin Ohta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andy Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guelph Royals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antony Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Patterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carson Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claudio Custodio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conner Morro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damon Topolie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deivis Nadal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drew Donaldson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin Torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garrett Takamatsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleyvin Pineda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.D. Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Sanford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeff MacLeod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Kush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Boscarino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcos Castillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miguel Hiraldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathaniel Ochoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Dos Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taeg Gollert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Mascai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anderson Feliz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton Cardinals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angel Guerrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Nicoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Dominguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champ Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dario Borrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darlin German</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Magill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremie Veilleux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jommer Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk Gibson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reyny Reyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanner Rempel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor Nicoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breidy Encarnacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchener Panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ernesto Punales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Cooke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Cabral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malik Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mateo Zeppieri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Fabian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Hoyt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Boughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petey Kiefer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Gross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuele Bruno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Lawson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yosuke Fujie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yosuke Fukie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yosvani Penalver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yunior Ibarra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Skansi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Thuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London Majors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Inoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleveland Brownlee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristian Inoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Draayers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Drayyers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduardo De Oleo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Babiuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarrett Burney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis Jean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maikol Escotto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberto Caro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryder Hancock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starling Joseph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Lenihan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucker Zdunich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Whittle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Sitarenios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto Maple Leafs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Sterritt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brando Leroux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Tomkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crixtian Taveras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dennis Dei Baning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dionysius Chialtas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drew Howard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JJ Dutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Bonzon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jj Dutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Poapst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Knecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Brandt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Cecchetto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spenser Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vasilios Kaloudis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasiel Puig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yolki Pena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yordan Manduley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Hupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welland Jackfish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Luther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryce Arnold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carson Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiki Abe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gianfranco Morello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Greyson Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyad Ansari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Valle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julien Monks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kian Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee Kucera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Chernesky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsuki Fukuda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Constantineau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Mackie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Morin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Richards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yushin Ohta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andy Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guelph Royals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antony Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Patterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carson Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claudio Custodio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conner Morro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damon Topolie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deivis Nadal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drew Donaldson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franklin Torres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garrett Takamatsu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gleyvin Pineda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J.D. Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Sanford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeff MacLeod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Kush</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Boscarino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcos Castillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miguel Hiraldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathaniel Ochoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Dos Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taeg Gollert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Mascai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anderson Feliz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamilton Cardinals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angel Guerrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Nicoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Dominguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champ Garner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dario Borrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darlin German</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Magill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremie Veilleux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jommer Hernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirk Gibson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reyny Reyes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanner Rempel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor Nicoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breidy Encarnacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchener Panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ernesto Punales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Cooke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Cabral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malik Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mateo Zeppieri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Fabian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Hoyt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Boughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petey Kiefer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Gross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuele Bruno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Lawson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yosuke Fujie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yosuke Fukie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yosvani Penalver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yunior Ibarra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Skansi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Thuss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London Majors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Inoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleveland Brownlee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristian Inoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Draayers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Drayyers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eduardo De Oleo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Babiuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarrett Burney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Lewis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis Jean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maikol Escotto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberto Caro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryder Hancock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starling Joseph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Lenihan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucker Zdunich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Whittle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Sitarenios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto Maple Leafs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Sterritt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brando Leroux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Tomkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crixtian Taveras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dennis Dei Baning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dionysius Chialtas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drew Howard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JJ Dutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Bonzon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jj Dutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Poapst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Knecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Brandt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mike Cecchetto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spenser Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vasilios Kaloudis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yasiel Puig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yolki Pena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yordan Manduley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Hupe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welland Jackfish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Luther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryce Arnold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carson Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daiki Abe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gianfranco Morello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marco</t>
   </si>
   <si>
     <t xml:space="preserve">James Smibert</t>
@@ -1458,31 +1458,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="D4" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="E4" t="n">
-        <v>47.1</v>
+        <v>45.9</v>
       </c>
       <c r="F4" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="G4" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>44.2</v>
+        <v>43.6</v>
       </c>
       <c r="J4" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="K4" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="5">
@@ -1493,22 +1493,22 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>67.3</v>
       </c>
       <c r="D5" t="n">
-        <v>16.3</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="F5" t="n">
-        <v>16.3</v>
+        <v>17.4</v>
       </c>
       <c r="G5" t="n">
-        <v>40.7</v>
+        <v>41.1</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
         <v>62.1</v>
@@ -1528,31 +1528,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>80.4</v>
+        <v>79.7</v>
       </c>
       <c r="D6" t="n">
-        <v>16.4</v>
+        <v>17.3</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>62.4</v>
       </c>
       <c r="F6" t="n">
-        <v>16.4</v>
+        <v>17.3</v>
       </c>
       <c r="G6" t="n">
-        <v>39.1</v>
+        <v>40.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="K6" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="7">
@@ -1563,31 +1563,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>66.7</v>
+        <v>67.5</v>
       </c>
       <c r="D7" t="n">
-        <v>16.9</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="n">
-        <v>49.8</v>
+        <v>48.7</v>
       </c>
       <c r="F7" t="n">
-        <v>16.9</v>
+        <v>18.8</v>
       </c>
       <c r="G7" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="H7" t="n">
-        <v>9.1</v>
+        <v>8.3</v>
       </c>
       <c r="I7" t="n">
-        <v>28.6</v>
+        <v>32.3</v>
       </c>
       <c r="J7" t="n">
-        <v>42.9</v>
+        <v>38.7</v>
       </c>
       <c r="K7" t="n">
-        <v>57.1</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="8">
@@ -1668,31 +1668,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>67.3</v>
+        <v>67.7</v>
       </c>
       <c r="D10" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="E10" t="n">
-        <v>47.4</v>
+        <v>48.5</v>
       </c>
       <c r="F10" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="G10" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="H10" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>40.9</v>
       </c>
       <c r="J10" t="n">
-        <v>35.2</v>
+        <v>33.6</v>
       </c>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -1771,31 +1771,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.9</v>
+        <v>63.2</v>
       </c>
       <c r="D13" t="n">
-        <v>17.6</v>
+        <v>20.2</v>
       </c>
       <c r="E13" t="n">
-        <v>46.3</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>17.6</v>
+        <v>20.2</v>
       </c>
       <c r="G13" t="n">
-        <v>28.1</v>
+        <v>26</v>
       </c>
       <c r="H13" t="n">
         <v>16.7</v>
       </c>
       <c r="I13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="14">
@@ -1806,31 +1806,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>73.3</v>
+        <v>72.4</v>
       </c>
       <c r="D14" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="E14" t="n">
-        <v>57.5</v>
+        <v>55.9</v>
       </c>
       <c r="F14" t="n">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="G14" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="H14" t="n">
-        <v>8.8</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>30.3</v>
+        <v>32.6</v>
       </c>
       <c r="J14" t="n">
-        <v>36</v>
+        <v>34.8</v>
       </c>
       <c r="K14" t="n">
-        <v>43.8</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="15">
@@ -1841,31 +1841,31 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>70.4</v>
+        <v>71.2</v>
       </c>
       <c r="D15" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="E15" t="n">
-        <v>47.8</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="G15" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="H15" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I15" t="n">
-        <v>64.5</v>
+        <v>64.2</v>
       </c>
       <c r="J15" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="K15" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="16">
@@ -1876,31 +1876,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>74.2</v>
+        <v>73.1</v>
       </c>
       <c r="D16" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="E16" t="n">
-        <v>55.9</v>
+        <v>54.3</v>
       </c>
       <c r="F16" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="G16" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="H16" t="n">
-        <v>9.8</v>
+        <v>9.4</v>
       </c>
       <c r="I16" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
       <c r="J16" t="n">
         <v>25.6</v>
       </c>
       <c r="K16" t="n">
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="17">
@@ -1911,31 +1911,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>75.4</v>
       </c>
       <c r="D17" t="n">
-        <v>28.4</v>
+        <v>27.9</v>
       </c>
       <c r="E17" t="n">
-        <v>45.6</v>
+        <v>47.5</v>
       </c>
       <c r="F17" t="n">
-        <v>28.4</v>
+        <v>27.9</v>
       </c>
       <c r="G17" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="H17" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I17" t="n">
-        <v>39.5</v>
+        <v>41.5</v>
       </c>
       <c r="J17" t="n">
-        <v>28.9</v>
+        <v>26.8</v>
       </c>
       <c r="K17" t="n">
-        <v>32.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="18">
@@ -1981,31 +1981,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>78.9</v>
+        <v>77.9</v>
       </c>
       <c r="D19" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="E19" t="n">
-        <v>52.7</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="G19" t="n">
-        <v>34.4</v>
+        <v>34.1</v>
       </c>
       <c r="H19" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="n">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="J19" t="n">
-        <v>36.5</v>
+        <v>35.6</v>
       </c>
       <c r="K19" t="n">
-        <v>43.5</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="20">
@@ -2019,28 +2019,28 @@
         <v>66.1</v>
       </c>
       <c r="D20" t="n">
-        <v>19.6</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>46.5</v>
+        <v>48.1</v>
       </c>
       <c r="F20" t="n">
-        <v>19.6</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>44.6</v>
+        <v>47</v>
       </c>
       <c r="H20" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I20" t="n">
         <v>33.3</v>
       </c>
       <c r="J20" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="K20" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="21">
@@ -2051,31 +2051,31 @@
         <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3</v>
+        <v>76.2</v>
       </c>
       <c r="D21" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="E21" t="n">
-        <v>51.6</v>
+        <v>52.7</v>
       </c>
       <c r="F21" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="G21" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="H21" t="n">
-        <v>8.3</v>
+        <v>8.7</v>
       </c>
       <c r="I21" t="n">
-        <v>34.8</v>
+        <v>35.6</v>
       </c>
       <c r="J21" t="n">
-        <v>31.5</v>
+        <v>33.3</v>
       </c>
       <c r="K21" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="22">
@@ -2086,31 +2086,31 @@
         <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>67.8</v>
+        <v>66.9</v>
       </c>
       <c r="D22" t="n">
         <v>16.8</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
       <c r="F22" t="n">
         <v>16.8</v>
       </c>
       <c r="G22" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="H22" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="I22" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="K22" t="n">
-        <v>37.8</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="23">
@@ -2121,22 +2121,22 @@
         <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>64.3</v>
+        <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="E23" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="F23" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="G23" t="n">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
         <v>51.9</v>
@@ -2226,31 +2226,31 @@
         <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>77.4</v>
+        <v>78</v>
       </c>
       <c r="D26" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="E26" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="F26" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="G26" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>25.8</v>
+        <v>27.9</v>
       </c>
       <c r="J26" t="n">
-        <v>22.7</v>
+        <v>21.3</v>
       </c>
       <c r="K26" t="n">
-        <v>46.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="27">
@@ -2261,31 +2261,31 @@
         <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>75.6</v>
+        <v>75.7</v>
       </c>
       <c r="D27" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="E27" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="F27" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="G27" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I27" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
       <c r="J27" t="n">
         <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="28">
@@ -2331,31 +2331,31 @@
         <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="D29" t="n">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>61.7</v>
       </c>
       <c r="F29" t="n">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="G29" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="H29" t="n">
-        <v>12.2</v>
+        <v>13.6</v>
       </c>
       <c r="I29" t="n">
-        <v>47.1</v>
+        <v>43.3</v>
       </c>
       <c r="J29" t="n">
-        <v>35.3</v>
+        <v>36.7</v>
       </c>
       <c r="K29" t="n">
-        <v>66.7</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="30">
@@ -2366,31 +2366,31 @@
         <v>31</v>
       </c>
       <c r="C30" t="n">
-        <v>68.7</v>
+        <v>68.4</v>
       </c>
       <c r="D30" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="E30" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="F30" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="G30" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="H30" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="I30" t="n">
-        <v>41.6</v>
+        <v>42.2</v>
       </c>
       <c r="J30" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>40.7</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="31">
@@ -2436,31 +2436,31 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>68.7</v>
       </c>
       <c r="D32" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="E32" t="n">
-        <v>41.4</v>
+        <v>40.1</v>
       </c>
       <c r="F32" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="G32" t="n">
         <v>23.9</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I32" t="n">
-        <v>45.8</v>
+        <v>44.4</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="K32" t="n">
-        <v>31.9</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="33">
@@ -2541,31 +2541,31 @@
         <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>75.6</v>
+        <v>75.7</v>
       </c>
       <c r="D35" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="E35" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="F35" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="G35" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="H35" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I35" t="n">
-        <v>45.1</v>
+        <v>45.6</v>
       </c>
       <c r="J35" t="n">
-        <v>25.6</v>
+        <v>26.6</v>
       </c>
       <c r="K35" t="n">
-        <v>45.1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="36">
@@ -2576,31 +2576,31 @@
         <v>48</v>
       </c>
       <c r="C36" t="n">
-        <v>75.3</v>
+        <v>74.9</v>
       </c>
       <c r="D36" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="E36" t="n">
         <v>54.5</v>
       </c>
       <c r="F36" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="G36" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="I36" t="n">
-        <v>60.3</v>
+        <v>60.7</v>
       </c>
       <c r="J36" t="n">
-        <v>22.2</v>
+        <v>21.3</v>
       </c>
       <c r="K36" t="n">
-        <v>41.3</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="37">
@@ -2646,31 +2646,31 @@
         <v>48</v>
       </c>
       <c r="C38" t="n">
-        <v>56.2</v>
+        <v>59.1</v>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="E38" t="n">
-        <v>43.7</v>
+        <v>44.8</v>
       </c>
       <c r="F38" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="G38" t="n">
-        <v>18.8</v>
+        <v>23.8</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I38" t="n">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -2716,22 +2716,22 @@
         <v>48</v>
       </c>
       <c r="C40" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>65.7</v>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="G40" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I40" t="n">
         <v>100</v>
@@ -2821,31 +2821,31 @@
         <v>48</v>
       </c>
       <c r="C43" t="n">
-        <v>77.2</v>
+        <v>81.1</v>
       </c>
       <c r="D43" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="E43" t="n">
-        <v>58.8</v>
+        <v>63.3</v>
       </c>
       <c r="F43" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="G43" t="n">
-        <v>30.8</v>
+        <v>28.4</v>
       </c>
       <c r="H43" t="n">
-        <v>12.9</v>
+        <v>9.7</v>
       </c>
       <c r="I43" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="J43" t="n">
-        <v>21.1</v>
+        <v>22.5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -2920,31 +2920,31 @@
         <v>48</v>
       </c>
       <c r="C46" t="n">
-        <v>80</v>
+        <v>72.1</v>
       </c>
       <c r="D46" t="n">
-        <v>26.4</v>
+        <v>25.3</v>
       </c>
       <c r="E46" t="n">
-        <v>53.6</v>
+        <v>46.8</v>
       </c>
       <c r="F46" t="n">
-        <v>26.4</v>
+        <v>25.3</v>
       </c>
       <c r="G46" t="n">
-        <v>27.6</v>
+        <v>25.5</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="I46" t="n">
-        <v>47.9</v>
+        <v>32.1</v>
       </c>
       <c r="J46" t="n">
-        <v>32.2</v>
+        <v>41.1</v>
       </c>
       <c r="K46" t="n">
-        <v>38.7</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="47">
@@ -2954,32 +2954,28 @@
       <c r="B47" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="n">
-        <v>71.4</v>
-      </c>
+      <c r="C47"/>
       <c r="D47" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E47" t="n">
-        <v>46.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E47"/>
       <c r="F47" t="n">
-        <v>24.8</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>40.4</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>35.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -2989,28 +2985,32 @@
       <c r="B48" t="s">
         <v>48</v>
       </c>
-      <c r="C48"/>
+      <c r="C48" t="n">
+        <v>67.1</v>
+      </c>
       <c r="D48" t="n">
-        <v>100</v>
-      </c>
-      <c r="E48"/>
+        <v>22.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>44.6</v>
+      </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="49">
@@ -3021,31 +3021,31 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>67.6</v>
+        <v>77.8</v>
       </c>
       <c r="D49" t="n">
-        <v>23.5</v>
+        <v>21.8</v>
       </c>
       <c r="E49" t="n">
-        <v>44.1</v>
+        <v>56</v>
       </c>
       <c r="F49" t="n">
-        <v>23.5</v>
+        <v>21.8</v>
       </c>
       <c r="G49" t="n">
-        <v>19.4</v>
+        <v>41.9</v>
       </c>
       <c r="H49" t="n">
-        <v>6.9</v>
+        <v>9.8</v>
       </c>
       <c r="I49" t="n">
-        <v>53.1</v>
+        <v>55.6</v>
       </c>
       <c r="J49" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="K49" t="n">
-        <v>26.6</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="50">
@@ -3056,31 +3056,31 @@
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>77.8</v>
+        <v>80.1</v>
       </c>
       <c r="D50" t="n">
-        <v>21.8</v>
+        <v>41.3</v>
       </c>
       <c r="E50" t="n">
-        <v>56</v>
+        <v>38.8</v>
       </c>
       <c r="F50" t="n">
-        <v>21.8</v>
+        <v>41.3</v>
       </c>
       <c r="G50" t="n">
-        <v>41.9</v>
+        <v>36.6</v>
       </c>
       <c r="H50" t="n">
-        <v>9.8</v>
+        <v>3.7</v>
       </c>
       <c r="I50" t="n">
-        <v>55.6</v>
+        <v>43.2</v>
       </c>
       <c r="J50" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="K50" t="n">
-        <v>25.9</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="51">
@@ -3091,31 +3091,31 @@
         <v>48</v>
       </c>
       <c r="C51" t="n">
-        <v>79.4</v>
+        <v>75</v>
       </c>
       <c r="D51" t="n">
-        <v>40.2</v>
+        <v>41.7</v>
       </c>
       <c r="E51" t="n">
-        <v>39.2</v>
+        <v>33.3</v>
       </c>
       <c r="F51" t="n">
-        <v>40.2</v>
+        <v>41.7</v>
       </c>
       <c r="G51" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="H51" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="52">
@@ -3126,31 +3126,31 @@
         <v>48</v>
       </c>
       <c r="C52" t="n">
-        <v>75</v>
+        <v>50.7</v>
       </c>
       <c r="D52" t="n">
-        <v>41.7</v>
+        <v>17.9</v>
       </c>
       <c r="E52" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="F52" t="n">
-        <v>41.7</v>
+        <v>17.9</v>
       </c>
       <c r="G52" t="n">
-        <v>66.7</v>
+        <v>18.3</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="K52" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="53">
@@ -3161,31 +3161,31 @@
         <v>48</v>
       </c>
       <c r="C53" t="n">
-        <v>50.7</v>
+        <v>72.9</v>
       </c>
       <c r="D53" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="E53" t="n">
-        <v>32.8</v>
+        <v>55.2</v>
       </c>
       <c r="F53" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="G53" t="n">
-        <v>18.3</v>
+        <v>33.6</v>
       </c>
       <c r="H53" t="n">
-        <v>17.1</v>
+        <v>10.6</v>
       </c>
       <c r="I53" t="n">
-        <v>38.5</v>
+        <v>47.7</v>
       </c>
       <c r="J53" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="K53" t="n">
-        <v>16.7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
@@ -3196,31 +3196,31 @@
         <v>48</v>
       </c>
       <c r="C54" t="n">
-        <v>72.5</v>
+        <v>63.7</v>
       </c>
       <c r="D54" t="n">
-        <v>17.7</v>
+        <v>22.8</v>
       </c>
       <c r="E54" t="n">
-        <v>54.8</v>
+        <v>40.9</v>
       </c>
       <c r="F54" t="n">
-        <v>17.7</v>
+        <v>22.8</v>
       </c>
       <c r="G54" t="n">
-        <v>32.6</v>
+        <v>51.6</v>
       </c>
       <c r="H54" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="I54" t="n">
-        <v>49.1</v>
+        <v>53.3</v>
       </c>
       <c r="J54" t="n">
-        <v>30.6</v>
+        <v>23.3</v>
       </c>
       <c r="K54" t="n">
-        <v>27.8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="55">
@@ -3231,31 +3231,31 @@
         <v>48</v>
       </c>
       <c r="C55" t="n">
-        <v>62.4</v>
+        <v>72.5</v>
       </c>
       <c r="D55" t="n">
-        <v>23.4</v>
+        <v>14</v>
       </c>
       <c r="E55" t="n">
-        <v>39</v>
+        <v>58.5</v>
       </c>
       <c r="F55" t="n">
-        <v>23.4</v>
+        <v>14</v>
       </c>
       <c r="G55" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="H55" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="I55" t="n">
-        <v>53.3</v>
+        <v>63.9</v>
       </c>
       <c r="J55" t="n">
-        <v>23.3</v>
+        <v>15.7</v>
       </c>
       <c r="K55" t="n">
-        <v>37.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="56">
@@ -3266,31 +3266,31 @@
         <v>48</v>
       </c>
       <c r="C56" t="n">
-        <v>73.6</v>
+        <v>69.3</v>
       </c>
       <c r="D56" t="n">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="n">
-        <v>60.3</v>
+        <v>54.7</v>
       </c>
       <c r="F56" t="n">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="G56" t="n">
-        <v>19.1</v>
+        <v>26.3</v>
       </c>
       <c r="H56" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="I56" t="n">
-        <v>64.3</v>
+        <v>38.8</v>
       </c>
       <c r="J56" t="n">
-        <v>16.7</v>
+        <v>32.8</v>
       </c>
       <c r="K56" t="n">
-        <v>23.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="57">
@@ -3301,31 +3301,31 @@
         <v>48</v>
       </c>
       <c r="C57" t="n">
-        <v>69.3</v>
+        <v>73</v>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>9.8</v>
       </c>
       <c r="E57" t="n">
-        <v>54.7</v>
+        <v>63.2</v>
       </c>
       <c r="F57" t="n">
-        <v>14.6</v>
+        <v>9.8</v>
       </c>
       <c r="G57" t="n">
-        <v>26.3</v>
+        <v>24.5</v>
       </c>
       <c r="H57" t="n">
-        <v>9.5</v>
+        <v>12.3</v>
       </c>
       <c r="I57" t="n">
-        <v>38.8</v>
+        <v>58.3</v>
       </c>
       <c r="J57" t="n">
-        <v>32.8</v>
+        <v>19.4</v>
       </c>
       <c r="K57" t="n">
-        <v>38.8</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="58">
@@ -3335,33 +3335,15 @@
       <c r="B58" t="s">
         <v>48</v>
       </c>
-      <c r="C58" t="n">
-        <v>71.9</v>
-      </c>
-      <c r="D58" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="E58" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>9.8</v>
-      </c>
-      <c r="G58" t="n">
-        <v>24</v>
-      </c>
-      <c r="H58" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="J58" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K58" t="n">
-        <v>31.4</v>
-      </c>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
@@ -3370,84 +3352,102 @@
       <c r="B59" t="s">
         <v>48</v>
       </c>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
+      <c r="C59" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>38</v>
+      </c>
+      <c r="H59" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>24</v>
+      </c>
+      <c r="J59" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>46.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C60" t="n">
-        <v>75.2</v>
+        <v>79.5</v>
       </c>
       <c r="D60" t="n">
-        <v>13.8</v>
+        <v>25.8</v>
       </c>
       <c r="E60" t="n">
-        <v>61.4</v>
+        <v>53.7</v>
       </c>
       <c r="F60" t="n">
-        <v>13.8</v>
+        <v>25.8</v>
       </c>
       <c r="G60" t="n">
-        <v>38.9</v>
+        <v>30.6</v>
       </c>
       <c r="H60" t="n">
-        <v>15.6</v>
+        <v>9.9</v>
       </c>
       <c r="I60" t="n">
-        <v>23.5</v>
+        <v>53.4</v>
       </c>
       <c r="J60" t="n">
-        <v>39.2</v>
+        <v>17.8</v>
       </c>
       <c r="K60" t="n">
-        <v>45.1</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" t="s">
         <v>73</v>
       </c>
-      <c r="B61" t="s">
-        <v>74</v>
-      </c>
       <c r="C61" t="n">
-        <v>79.5</v>
+        <v>76.9</v>
       </c>
       <c r="D61" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="E61" t="n">
-        <v>53.7</v>
+        <v>50.6</v>
       </c>
       <c r="F61" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="G61" t="n">
-        <v>30.6</v>
+        <v>25.1</v>
       </c>
       <c r="H61" t="n">
-        <v>9.9</v>
+        <v>5.3</v>
       </c>
       <c r="I61" t="n">
-        <v>53.4</v>
+        <v>42.5</v>
       </c>
       <c r="J61" t="n">
-        <v>17.8</v>
+        <v>20.9</v>
       </c>
       <c r="K61" t="n">
-        <v>39.7</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="62">
@@ -3455,34 +3455,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C62" t="n">
-        <v>76.9</v>
+        <v>62.8</v>
       </c>
       <c r="D62" t="n">
-        <v>26.3</v>
+        <v>14.1</v>
       </c>
       <c r="E62" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="F62" t="n">
-        <v>26.3</v>
+        <v>14.1</v>
       </c>
       <c r="G62" t="n">
-        <v>25.1</v>
+        <v>27.2</v>
       </c>
       <c r="H62" t="n">
-        <v>5.3</v>
+        <v>10.8</v>
       </c>
       <c r="I62" t="n">
-        <v>42.5</v>
+        <v>53.3</v>
       </c>
       <c r="J62" t="n">
-        <v>20.9</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>30.1</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="63">
@@ -3490,34 +3490,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" t="n">
-        <v>62.8</v>
+        <v>66.7</v>
       </c>
       <c r="D63" t="n">
-        <v>14.1</v>
+        <v>22.2</v>
       </c>
       <c r="E63" t="n">
-        <v>48.7</v>
+        <v>44.5</v>
       </c>
       <c r="F63" t="n">
-        <v>14.1</v>
+        <v>22.2</v>
       </c>
       <c r="G63" t="n">
-        <v>27.2</v>
+        <v>43.3</v>
       </c>
       <c r="H63" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="I63" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
-        <v>38.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3525,98 +3525,98 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" t="n">
+        <v>40</v>
+      </c>
+      <c r="D64" t="n">
+        <v>50</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F64" t="n">
+        <v>50</v>
+      </c>
+      <c r="G64" t="n">
         <v>66.7</v>
       </c>
-      <c r="D64" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E64" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F64" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G64" t="n">
-        <v>43.3</v>
-      </c>
       <c r="H64" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I64" t="n">
-        <v>50</v>
-      </c>
-      <c r="J64" t="n">
-        <v>50</v>
-      </c>
-      <c r="K64" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C65" t="n">
-        <v>40</v>
+        <v>70.5</v>
       </c>
       <c r="D65" t="n">
-        <v>50</v>
+        <v>36.7</v>
       </c>
       <c r="E65" t="n">
-        <v>-10</v>
+        <v>33.8</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>36.7</v>
       </c>
       <c r="G65" t="n">
-        <v>66.7</v>
+        <v>21.2</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
+        <v>4.2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J65" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K65" t="n">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="n">
-        <v>70.5</v>
+        <v>57.1</v>
       </c>
       <c r="D66" t="n">
-        <v>36.7</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="n">
-        <v>33.8</v>
+        <v>44.6</v>
       </c>
       <c r="F66" t="n">
-        <v>36.7</v>
+        <v>12.5</v>
       </c>
       <c r="G66" t="n">
-        <v>21.2</v>
+        <v>14.3</v>
       </c>
       <c r="H66" t="n">
-        <v>4.2</v>
+        <v>16.7</v>
       </c>
       <c r="I66" t="n">
-        <v>38.9</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>41.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67">
@@ -3624,34 +3624,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E67" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F67" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G67" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="H67" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I67" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K67" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68">
@@ -3659,34 +3659,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D68" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F68" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G68" t="n">
-        <v>38.1</v>
+        <v>41.2</v>
       </c>
       <c r="H68" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I68" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="J68" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -3694,34 +3694,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" t="n">
-        <v>72.4</v>
+        <v>56.2</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="E69" t="n">
-        <v>62.4</v>
+        <v>41.7</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="G69" t="n">
-        <v>41.2</v>
+        <v>13.2</v>
       </c>
       <c r="H69" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>45.7</v>
       </c>
       <c r="J69" t="n">
-        <v>30</v>
+        <v>22.9</v>
       </c>
       <c r="K69" t="n">
-        <v>30</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="70">
@@ -3729,34 +3729,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>56.2</v>
+        <v>71.7</v>
       </c>
       <c r="D70" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="E70" t="n">
-        <v>41.7</v>
+        <v>52.2</v>
       </c>
       <c r="F70" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="G70" t="n">
-        <v>13.2</v>
+        <v>25.7</v>
       </c>
       <c r="H70" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="I70" t="n">
-        <v>45.7</v>
+        <v>42.6</v>
       </c>
       <c r="J70" t="n">
-        <v>22.9</v>
+        <v>27</v>
       </c>
       <c r="K70" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71">
@@ -3764,34 +3764,28 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="D71" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E71" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F71" t="n">
-        <v>19.5</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>25.7</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>42.6</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -3799,28 +3793,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C72" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
+        <v>74.7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>15.2</v>
+      </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>52.3</v>
       </c>
       <c r="J72" t="n">
-        <v>50</v>
+        <v>13.6</v>
       </c>
       <c r="K72" t="n">
-        <v>50</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="73">
@@ -3828,34 +3828,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" t="n">
-        <v>74.7</v>
+        <v>100</v>
       </c>
       <c r="D73" t="n">
-        <v>15.2</v>
+        <v>50</v>
       </c>
       <c r="E73" t="n">
-        <v>59.5</v>
+        <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>15.2</v>
+        <v>50</v>
       </c>
       <c r="G73" t="n">
-        <v>28.2</v>
+        <v>25</v>
       </c>
       <c r="H73" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>52.3</v>
+        <v>100</v>
       </c>
       <c r="J73" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>37.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -3863,19 +3863,19 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D74" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G74" t="n">
         <v>25</v>
@@ -3884,13 +3884,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
@@ -3898,34 +3898,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C75" t="n">
-        <v>33.3</v>
+        <v>76.8</v>
       </c>
       <c r="D75" t="n">
-        <v>33.3</v>
+        <v>8.9</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>67.9</v>
       </c>
       <c r="F75" t="n">
-        <v>33.3</v>
+        <v>8.9</v>
       </c>
       <c r="G75" t="n">
-        <v>25</v>
+        <v>34.2</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="I75" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="76">
@@ -3933,34 +3933,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C76" t="n">
-        <v>76.8</v>
+        <v>69.6</v>
       </c>
       <c r="D76" t="n">
-        <v>8.9</v>
+        <v>33.3</v>
       </c>
       <c r="E76" t="n">
-        <v>67.9</v>
+        <v>36.3</v>
       </c>
       <c r="F76" t="n">
-        <v>8.9</v>
+        <v>33.3</v>
       </c>
       <c r="G76" t="n">
-        <v>34.2</v>
+        <v>20</v>
       </c>
       <c r="H76" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="I76" t="n">
-        <v>75</v>
+        <v>46.2</v>
       </c>
       <c r="J76" t="n">
-        <v>12.5</v>
+        <v>30.8</v>
       </c>
       <c r="K76" t="n">
-        <v>31.2</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="77">
@@ -3968,34 +3968,34 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C77" t="n">
-        <v>69.6</v>
+        <v>67.7</v>
       </c>
       <c r="D77" t="n">
-        <v>33.3</v>
+        <v>16.2</v>
       </c>
       <c r="E77" t="n">
-        <v>36.3</v>
+        <v>51.5</v>
       </c>
       <c r="F77" t="n">
-        <v>33.3</v>
+        <v>16.2</v>
       </c>
       <c r="G77" t="n">
-        <v>20</v>
+        <v>42.2</v>
       </c>
       <c r="H77" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I77" t="n">
-        <v>46.2</v>
+        <v>35</v>
       </c>
       <c r="J77" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="K77" t="n">
-        <v>53.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
@@ -4003,34 +4003,34 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C78" t="n">
-        <v>67.7</v>
+        <v>68.6</v>
       </c>
       <c r="D78" t="n">
-        <v>16.2</v>
+        <v>31.8</v>
       </c>
       <c r="E78" t="n">
-        <v>51.5</v>
+        <v>36.8</v>
       </c>
       <c r="F78" t="n">
-        <v>16.2</v>
+        <v>31.8</v>
       </c>
       <c r="G78" t="n">
-        <v>42.2</v>
+        <v>11.1</v>
       </c>
       <c r="H78" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="I78" t="n">
-        <v>35</v>
+        <v>47.6</v>
       </c>
       <c r="J78" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="K78" t="n">
-        <v>45</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="79">
@@ -4038,34 +4038,34 @@
         <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C79" t="n">
-        <v>68.6</v>
+        <v>66.4</v>
       </c>
       <c r="D79" t="n">
-        <v>31.8</v>
+        <v>12.6</v>
       </c>
       <c r="E79" t="n">
-        <v>36.8</v>
+        <v>53.8</v>
       </c>
       <c r="F79" t="n">
-        <v>31.8</v>
+        <v>12.6</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1</v>
+        <v>28.1</v>
       </c>
       <c r="H79" t="n">
-        <v>3.4</v>
+        <v>13.8</v>
       </c>
       <c r="I79" t="n">
-        <v>47.6</v>
+        <v>39.4</v>
       </c>
       <c r="J79" t="n">
-        <v>28.6</v>
+        <v>36.5</v>
       </c>
       <c r="K79" t="n">
-        <v>38.1</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="80">
@@ -4073,34 +4073,34 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C80" t="n">
-        <v>66.4</v>
+        <v>81.3</v>
       </c>
       <c r="D80" t="n">
-        <v>12.6</v>
+        <v>25.3</v>
       </c>
       <c r="E80" t="n">
-        <v>53.8</v>
+        <v>56</v>
       </c>
       <c r="F80" t="n">
-        <v>12.6</v>
+        <v>25.3</v>
       </c>
       <c r="G80" t="n">
-        <v>28.1</v>
+        <v>26.2</v>
       </c>
       <c r="H80" t="n">
-        <v>13.8</v>
+        <v>5.7</v>
       </c>
       <c r="I80" t="n">
-        <v>39.4</v>
+        <v>43.7</v>
       </c>
       <c r="J80" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="K80" t="n">
-        <v>45.6</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="81">
@@ -4108,34 +4108,34 @@
         <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C81" t="n">
-        <v>81.3</v>
+        <v>76.5</v>
       </c>
       <c r="D81" t="n">
-        <v>25.3</v>
+        <v>19</v>
       </c>
       <c r="E81" t="n">
-        <v>56</v>
+        <v>57.5</v>
       </c>
       <c r="F81" t="n">
-        <v>25.3</v>
+        <v>19</v>
       </c>
       <c r="G81" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="H81" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="I81" t="n">
-        <v>43.7</v>
+        <v>46.9</v>
       </c>
       <c r="J81" t="n">
-        <v>35.2</v>
+        <v>31.2</v>
       </c>
       <c r="K81" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="82">
@@ -4143,34 +4143,34 @@
         <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C82" t="n">
-        <v>76.5</v>
+        <v>56.9</v>
       </c>
       <c r="D82" t="n">
-        <v>19</v>
+        <v>10.3</v>
       </c>
       <c r="E82" t="n">
-        <v>57.5</v>
+        <v>46.6</v>
       </c>
       <c r="F82" t="n">
-        <v>19</v>
+        <v>10.3</v>
       </c>
       <c r="G82" t="n">
-        <v>25.6</v>
+        <v>29.5</v>
       </c>
       <c r="H82" t="n">
-        <v>14</v>
+        <v>18.2</v>
       </c>
       <c r="I82" t="n">
-        <v>46.9</v>
+        <v>44.6</v>
       </c>
       <c r="J82" t="n">
-        <v>31.2</v>
+        <v>28.9</v>
       </c>
       <c r="K82" t="n">
-        <v>45.5</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="83">
@@ -4178,34 +4178,34 @@
         <v>96</v>
       </c>
       <c r="B83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C83" t="n">
-        <v>56.9</v>
+        <v>66.7</v>
       </c>
       <c r="D83" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>46.6</v>
+        <v>66.7</v>
       </c>
       <c r="F83" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>29.5</v>
+        <v>26.7</v>
       </c>
       <c r="H83" t="n">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
       <c r="I83" t="n">
-        <v>44.6</v>
+        <v>27.3</v>
       </c>
       <c r="J83" t="n">
-        <v>28.9</v>
+        <v>36.4</v>
       </c>
       <c r="K83" t="n">
-        <v>26.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="84">
@@ -4213,34 +4213,34 @@
         <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C84" t="n">
-        <v>66.7</v>
+        <v>75.6</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="E84" t="n">
-        <v>66.7</v>
+        <v>56.7</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="G84" t="n">
-        <v>26.7</v>
+        <v>33.4</v>
       </c>
       <c r="H84" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="I84" t="n">
-        <v>27.3</v>
+        <v>39.6</v>
       </c>
       <c r="J84" t="n">
-        <v>36.4</v>
+        <v>31.9</v>
       </c>
       <c r="K84" t="n">
-        <v>54.5</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="85">
@@ -4248,69 +4248,69 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C85" t="n">
-        <v>75.6</v>
+        <v>85.7</v>
       </c>
       <c r="D85" t="n">
-        <v>18.9</v>
+        <v>15.3</v>
       </c>
       <c r="E85" t="n">
-        <v>56.7</v>
+        <v>70.4</v>
       </c>
       <c r="F85" t="n">
-        <v>18.9</v>
+        <v>15.3</v>
       </c>
       <c r="G85" t="n">
-        <v>33.4</v>
+        <v>37.7</v>
       </c>
       <c r="H85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="I85" t="n">
-        <v>39.6</v>
+        <v>38.9</v>
       </c>
       <c r="J85" t="n">
-        <v>31.9</v>
+        <v>41.7</v>
       </c>
       <c r="K85" t="n">
-        <v>55.4</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" t="s">
         <v>99</v>
       </c>
-      <c r="B86" t="s">
-        <v>100</v>
-      </c>
       <c r="C86" t="n">
-        <v>85.7</v>
+        <v>73</v>
       </c>
       <c r="D86" t="n">
-        <v>15.3</v>
+        <v>29</v>
       </c>
       <c r="E86" t="n">
-        <v>70.4</v>
+        <v>44</v>
       </c>
       <c r="F86" t="n">
-        <v>15.3</v>
+        <v>29</v>
       </c>
       <c r="G86" t="n">
-        <v>37.7</v>
+        <v>21</v>
       </c>
       <c r="H86" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="I86" t="n">
-        <v>38.9</v>
+        <v>61.1</v>
       </c>
       <c r="J86" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="K86" t="n">
-        <v>47.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="87">
@@ -4318,34 +4318,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C87" t="n">
-        <v>75.3</v>
+        <v>76.8</v>
       </c>
       <c r="D87" t="n">
-        <v>29.7</v>
+        <v>25.1</v>
       </c>
       <c r="E87" t="n">
-        <v>45.6</v>
+        <v>51.7</v>
       </c>
       <c r="F87" t="n">
-        <v>29.7</v>
+        <v>25.1</v>
       </c>
       <c r="G87" t="n">
-        <v>20.4</v>
+        <v>31.5</v>
       </c>
       <c r="H87" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="I87" t="n">
-        <v>60</v>
+        <v>42.5</v>
       </c>
       <c r="J87" t="n">
-        <v>17.1</v>
+        <v>23.1</v>
       </c>
       <c r="K87" t="n">
-        <v>44.1</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="88">
@@ -4353,34 +4353,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C88" t="n">
-        <v>76.8</v>
+        <v>76.3</v>
       </c>
       <c r="D88" t="n">
-        <v>24.7</v>
+        <v>23.3</v>
       </c>
       <c r="E88" t="n">
-        <v>52.1</v>
+        <v>53</v>
       </c>
       <c r="F88" t="n">
-        <v>24.7</v>
+        <v>23.3</v>
       </c>
       <c r="G88" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H88" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="I88" t="n">
-        <v>42.7</v>
+        <v>46.8</v>
       </c>
       <c r="J88" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="K88" t="n">
-        <v>54.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="89">
@@ -4388,34 +4388,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89" t="n">
-        <v>77</v>
+        <v>71.4</v>
       </c>
       <c r="D89" t="n">
-        <v>23.9</v>
+        <v>14.3</v>
       </c>
       <c r="E89" t="n">
-        <v>53.1</v>
+        <v>57.1</v>
       </c>
       <c r="F89" t="n">
-        <v>23.9</v>
+        <v>14.3</v>
       </c>
       <c r="G89" t="n">
-        <v>24</v>
+        <v>25.6</v>
       </c>
       <c r="H89" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I89" t="n">
-        <v>46.2</v>
+        <v>53.3</v>
       </c>
       <c r="J89" t="n">
-        <v>22.7</v>
+        <v>13.3</v>
       </c>
       <c r="K89" t="n">
-        <v>47.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="90">
@@ -4423,34 +4423,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C90" t="n">
-        <v>71.4</v>
+        <v>78.7</v>
       </c>
       <c r="D90" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="E90" t="n">
-        <v>57.1</v>
+        <v>50.1</v>
       </c>
       <c r="F90" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="G90" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="H90" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="I90" t="n">
-        <v>53.3</v>
+        <v>48</v>
       </c>
       <c r="J90" t="n">
-        <v>13.3</v>
+        <v>26</v>
       </c>
       <c r="K90" t="n">
-        <v>26.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
@@ -4458,34 +4458,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C91" t="n">
-        <v>78.8</v>
+        <v>76.5</v>
       </c>
       <c r="D91" t="n">
-        <v>28.1</v>
+        <v>32.8</v>
       </c>
       <c r="E91" t="n">
-        <v>50.7</v>
+        <v>43.7</v>
       </c>
       <c r="F91" t="n">
-        <v>28.1</v>
+        <v>32.8</v>
       </c>
       <c r="G91" t="n">
-        <v>21.6</v>
+        <v>25.2</v>
       </c>
       <c r="H91" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I91" t="n">
-        <v>43.2</v>
+        <v>44.3</v>
       </c>
       <c r="J91" t="n">
-        <v>29.5</v>
+        <v>25.9</v>
       </c>
       <c r="K91" t="n">
-        <v>38.6</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="92">
@@ -4493,34 +4493,34 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C92" t="n">
-        <v>77.2</v>
+        <v>72.8</v>
       </c>
       <c r="D92" t="n">
-        <v>31.3</v>
+        <v>18.3</v>
       </c>
       <c r="E92" t="n">
-        <v>45.9</v>
+        <v>54.5</v>
       </c>
       <c r="F92" t="n">
-        <v>31.3</v>
+        <v>18.3</v>
       </c>
       <c r="G92" t="n">
-        <v>24.9</v>
+        <v>29.5</v>
       </c>
       <c r="H92" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="I92" t="n">
-        <v>45.4</v>
+        <v>33.6</v>
       </c>
       <c r="J92" t="n">
-        <v>24.3</v>
+        <v>33.6</v>
       </c>
       <c r="K92" t="n">
-        <v>54.7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93">
@@ -4528,34 +4528,34 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C93" t="n">
-        <v>72.8</v>
+        <v>73.4</v>
       </c>
       <c r="D93" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="E93" t="n">
-        <v>54.8</v>
+        <v>56.7</v>
       </c>
       <c r="F93" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="G93" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="H93" t="n">
-        <v>9.8</v>
+        <v>6.7</v>
       </c>
       <c r="I93" t="n">
-        <v>34.2</v>
+        <v>51.6</v>
       </c>
       <c r="J93" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="K93" t="n">
-        <v>33.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="94">
@@ -4563,34 +4563,34 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C94" t="n">
-        <v>75.3</v>
+        <v>68.2</v>
       </c>
       <c r="D94" t="n">
-        <v>17.7</v>
+        <v>27.5</v>
       </c>
       <c r="E94" t="n">
-        <v>57.6</v>
+        <v>40.7</v>
       </c>
       <c r="F94" t="n">
-        <v>17.7</v>
+        <v>27.5</v>
       </c>
       <c r="G94" t="n">
-        <v>28.6</v>
+        <v>38.3</v>
       </c>
       <c r="H94" t="n">
-        <v>7.1</v>
+        <v>16.1</v>
       </c>
       <c r="I94" t="n">
-        <v>51.7</v>
+        <v>61.5</v>
       </c>
       <c r="J94" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="K94" t="n">
-        <v>32.9</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="95">
@@ -4598,34 +4598,34 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C95" t="n">
-        <v>68.8</v>
+        <v>76</v>
       </c>
       <c r="D95" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E95" t="n">
-        <v>41.8</v>
+        <v>53</v>
       </c>
       <c r="F95" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G95" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="H95" t="n">
-        <v>17.9</v>
+        <v>9.3</v>
       </c>
       <c r="I95" t="n">
-        <v>63.6</v>
+        <v>46.4</v>
       </c>
       <c r="J95" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="K95" t="n">
-        <v>54.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="96">
@@ -4633,34 +4633,34 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>76</v>
+        <v>70.8</v>
       </c>
       <c r="D96" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="E96" t="n">
-        <v>53</v>
+        <v>47.9</v>
       </c>
       <c r="F96" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="G96" t="n">
-        <v>41.7</v>
+        <v>27</v>
       </c>
       <c r="H96" t="n">
-        <v>9.3</v>
+        <v>4.1</v>
       </c>
       <c r="I96" t="n">
-        <v>46.4</v>
+        <v>67.6</v>
       </c>
       <c r="J96" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>35.7</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="97">
@@ -4668,34 +4668,34 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C97" t="n">
-        <v>70.8</v>
+        <v>70</v>
       </c>
       <c r="D97" t="n">
-        <v>22.9</v>
+        <v>25.1</v>
       </c>
       <c r="E97" t="n">
-        <v>47.9</v>
+        <v>44.9</v>
       </c>
       <c r="F97" t="n">
-        <v>22.9</v>
+        <v>25.1</v>
       </c>
       <c r="G97" t="n">
-        <v>27</v>
+        <v>19.3</v>
       </c>
       <c r="H97" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="I97" t="n">
-        <v>67.6</v>
+        <v>50.8</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="K97" t="n">
-        <v>41.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="98">
@@ -4703,34 +4703,34 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C98" t="n">
-        <v>70.9</v>
+        <v>72.5</v>
       </c>
       <c r="D98" t="n">
-        <v>23.2</v>
+        <v>32.4</v>
       </c>
       <c r="E98" t="n">
-        <v>47.7</v>
+        <v>40.1</v>
       </c>
       <c r="F98" t="n">
-        <v>23.2</v>
+        <v>32.4</v>
       </c>
       <c r="G98" t="n">
-        <v>18.2</v>
+        <v>26</v>
       </c>
       <c r="H98" t="n">
-        <v>6</v>
+        <v>9.3</v>
       </c>
       <c r="I98" t="n">
-        <v>51.2</v>
+        <v>44.4</v>
       </c>
       <c r="J98" t="n">
-        <v>23.6</v>
+        <v>37</v>
       </c>
       <c r="K98" t="n">
-        <v>38.6</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="99">
@@ -4738,34 +4738,34 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C99" t="n">
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="D99" t="n">
-        <v>32.4</v>
+        <v>16.2</v>
       </c>
       <c r="E99" t="n">
-        <v>40.1</v>
+        <v>63.8</v>
       </c>
       <c r="F99" t="n">
-        <v>32.4</v>
+        <v>16.2</v>
       </c>
       <c r="G99" t="n">
-        <v>26</v>
+        <v>30.2</v>
       </c>
       <c r="H99" t="n">
-        <v>9.3</v>
+        <v>13.3</v>
       </c>
       <c r="I99" t="n">
-        <v>44.4</v>
+        <v>71.4</v>
       </c>
       <c r="J99" t="n">
-        <v>37</v>
+        <v>9.5</v>
       </c>
       <c r="K99" t="n">
-        <v>55.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="100">
@@ -4773,34 +4773,34 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>80</v>
+        <v>70.2</v>
       </c>
       <c r="D100" t="n">
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="E100" t="n">
-        <v>63.8</v>
+        <v>54.7</v>
       </c>
       <c r="F100" t="n">
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="G100" t="n">
-        <v>30.2</v>
+        <v>25.9</v>
       </c>
       <c r="H100" t="n">
-        <v>13.3</v>
+        <v>10.6</v>
       </c>
       <c r="I100" t="n">
-        <v>71.4</v>
+        <v>53.2</v>
       </c>
       <c r="J100" t="n">
-        <v>9.5</v>
+        <v>16.9</v>
       </c>
       <c r="K100" t="n">
-        <v>23.8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="101">
@@ -4808,89 +4808,89 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
+        <v>116</v>
+      </c>
+      <c r="C101" t="n">
+        <v>50</v>
+      </c>
+      <c r="D101" t="n">
+        <v>50</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>50</v>
+      </c>
+      <c r="G101" t="n">
         <v>100</v>
       </c>
-      <c r="C101" t="n">
-        <v>70.4</v>
-      </c>
-      <c r="D101" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="E101" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="F101" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="G101" t="n">
-        <v>25.5</v>
-      </c>
       <c r="H101" t="n">
-        <v>11</v>
-      </c>
-      <c r="I101" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="J101" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K101" t="n">
-        <v>39</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>117</v>
+      </c>
+      <c r="B102" t="s">
         <v>116</v>
       </c>
-      <c r="B102" t="s">
-        <v>117</v>
-      </c>
       <c r="C102" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F102" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G102" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
         <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C103" t="n">
-        <v>100</v>
+        <v>71.4</v>
       </c>
       <c r="D103" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E103" t="n">
-        <v>40</v>
+        <v>51.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G103" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -4907,34 +4907,34 @@
         <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C104" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D104" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>51.4</v>
+        <v>75</v>
       </c>
       <c r="F104" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="H104" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105">
@@ -4942,34 +4942,34 @@
         <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C105" t="n">
-        <v>75</v>
+        <v>51.1</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="E105" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="G105" t="n">
-        <v>40</v>
+        <v>16.3</v>
       </c>
       <c r="H105" t="n">
-        <v>25</v>
+        <v>15.2</v>
       </c>
       <c r="I105" t="n">
-        <v>100</v>
+        <v>47.6</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K105" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="106">
@@ -4977,34 +4977,34 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C106" t="n">
-        <v>51.1</v>
+        <v>60.9</v>
       </c>
       <c r="D106" t="n">
-        <v>28.1</v>
+        <v>47.1</v>
       </c>
       <c r="E106" t="n">
-        <v>23</v>
+        <v>13.8</v>
       </c>
       <c r="F106" t="n">
-        <v>28.1</v>
+        <v>47.1</v>
       </c>
       <c r="G106" t="n">
-        <v>16.3</v>
+        <v>35.5</v>
       </c>
       <c r="H106" t="n">
-        <v>15.2</v>
+        <v>2.5</v>
       </c>
       <c r="I106" t="n">
-        <v>47.6</v>
+        <v>41.7</v>
       </c>
       <c r="J106" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K106" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="107">
@@ -5012,34 +5012,34 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C107" t="n">
-        <v>60.9</v>
+        <v>77.4</v>
       </c>
       <c r="D107" t="n">
-        <v>47.1</v>
+        <v>33.3</v>
       </c>
       <c r="E107" t="n">
-        <v>13.8</v>
+        <v>44.1</v>
       </c>
       <c r="F107" t="n">
-        <v>47.1</v>
+        <v>33.3</v>
       </c>
       <c r="G107" t="n">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="H107" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="I107" t="n">
-        <v>41.7</v>
+        <v>60.8</v>
       </c>
       <c r="J107" t="n">
-        <v>25</v>
+        <v>9.8</v>
       </c>
       <c r="K107" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
@@ -5047,34 +5047,34 @@
         <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C108" t="n">
-        <v>77.4</v>
+        <v>69.8</v>
       </c>
       <c r="D108" t="n">
-        <v>33.3</v>
+        <v>16.8</v>
       </c>
       <c r="E108" t="n">
-        <v>44.1</v>
+        <v>53</v>
       </c>
       <c r="F108" t="n">
-        <v>33.3</v>
+        <v>16.8</v>
       </c>
       <c r="G108" t="n">
-        <v>38.1</v>
+        <v>14.9</v>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>9.8</v>
       </c>
       <c r="I108" t="n">
-        <v>60.8</v>
+        <v>48</v>
       </c>
       <c r="J108" t="n">
-        <v>9.8</v>
+        <v>21.3</v>
       </c>
       <c r="K108" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109">
@@ -5082,34 +5082,34 @@
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C109" t="n">
-        <v>70.8</v>
+        <v>66.7</v>
       </c>
       <c r="D109" t="n">
-        <v>17.5</v>
+        <v>9.7</v>
       </c>
       <c r="E109" t="n">
-        <v>53.3</v>
+        <v>57</v>
       </c>
       <c r="F109" t="n">
-        <v>17.5</v>
+        <v>9.7</v>
       </c>
       <c r="G109" t="n">
-        <v>15.2</v>
+        <v>32.1</v>
       </c>
       <c r="H109" t="n">
-        <v>8.9</v>
+        <v>18.6</v>
       </c>
       <c r="I109" t="n">
-        <v>48.4</v>
+        <v>23.9</v>
       </c>
       <c r="J109" t="n">
-        <v>20.2</v>
+        <v>37</v>
       </c>
       <c r="K109" t="n">
-        <v>26.8</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="110">
@@ -5117,34 +5117,34 @@
         <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C110" t="n">
-        <v>66.3</v>
+        <v>62.4</v>
       </c>
       <c r="D110" t="n">
-        <v>9.7</v>
+        <v>17.7</v>
       </c>
       <c r="E110" t="n">
-        <v>56.6</v>
+        <v>44.7</v>
       </c>
       <c r="F110" t="n">
-        <v>9.7</v>
+        <v>17.7</v>
       </c>
       <c r="G110" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="H110" t="n">
-        <v>19.2</v>
+        <v>3.4</v>
       </c>
       <c r="I110" t="n">
-        <v>24.2</v>
+        <v>45.3</v>
       </c>
       <c r="J110" t="n">
-        <v>36.3</v>
+        <v>20.8</v>
       </c>
       <c r="K110" t="n">
-        <v>36.7</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="111">
@@ -5152,34 +5152,34 @@
         <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C111" t="n">
-        <v>62.4</v>
+        <v>71.4</v>
       </c>
       <c r="D111" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>44.7</v>
+        <v>71.4</v>
       </c>
       <c r="F111" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>31.4</v>
+        <v>33.3</v>
       </c>
       <c r="H111" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>45.3</v>
+        <v>50</v>
       </c>
       <c r="J111" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5187,34 +5187,26 @@
         <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
-      </c>
-      <c r="C112" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
       <c r="G112" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113">
@@ -5222,26 +5214,34 @@
         <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
-      </c>
-      <c r="C113"/>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
+        <v>116</v>
+      </c>
+      <c r="C113" t="n">
+        <v>73.1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>49</v>
+      </c>
+      <c r="F113" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G113" t="n">
-        <v>16.7</v>
+        <v>21.7</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I113" t="n">
-        <v>100</v>
+        <v>46.1</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="K113" t="n">
-        <v>100</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="114">
@@ -5249,34 +5249,34 @@
         <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C114" t="n">
-        <v>72.3</v>
+        <v>77.5</v>
       </c>
       <c r="D114" t="n">
-        <v>24.1</v>
+        <v>31.4</v>
       </c>
       <c r="E114" t="n">
-        <v>48.2</v>
+        <v>46.1</v>
       </c>
       <c r="F114" t="n">
-        <v>24.1</v>
+        <v>31.4</v>
       </c>
       <c r="G114" t="n">
-        <v>21.5</v>
+        <v>32.5</v>
       </c>
       <c r="H114" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="I114" t="n">
-        <v>46.4</v>
+        <v>39</v>
       </c>
       <c r="J114" t="n">
-        <v>24.8</v>
+        <v>30</v>
       </c>
       <c r="K114" t="n">
-        <v>39.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115">
@@ -5284,34 +5284,34 @@
         <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C115" t="n">
-        <v>78.2</v>
+        <v>71.4</v>
       </c>
       <c r="D115" t="n">
-        <v>31.5</v>
+        <v>35.7</v>
       </c>
       <c r="E115" t="n">
-        <v>46.7</v>
+        <v>35.7</v>
       </c>
       <c r="F115" t="n">
-        <v>31.5</v>
+        <v>35.7</v>
       </c>
       <c r="G115" t="n">
-        <v>32.8</v>
+        <v>5.3</v>
       </c>
       <c r="H115" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I115" t="n">
-        <v>38.4</v>
+        <v>42.9</v>
       </c>
       <c r="J115" t="n">
-        <v>30.3</v>
+        <v>14.3</v>
       </c>
       <c r="K115" t="n">
-        <v>49.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="116">
@@ -5319,34 +5319,34 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C116" t="n">
-        <v>71.4</v>
+        <v>60.2</v>
       </c>
       <c r="D116" t="n">
-        <v>35.7</v>
+        <v>18.1</v>
       </c>
       <c r="E116" t="n">
-        <v>35.7</v>
+        <v>42.1</v>
       </c>
       <c r="F116" t="n">
-        <v>35.7</v>
+        <v>18.1</v>
       </c>
       <c r="G116" t="n">
-        <v>5.3</v>
+        <v>30.3</v>
       </c>
       <c r="H116" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="I116" t="n">
-        <v>42.9</v>
+        <v>25.8</v>
       </c>
       <c r="J116" t="n">
-        <v>14.3</v>
+        <v>45.2</v>
       </c>
       <c r="K116" t="n">
-        <v>33.3</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="117">
@@ -5354,34 +5354,34 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C117" t="n">
-        <v>59.9</v>
+        <v>75.4</v>
       </c>
       <c r="D117" t="n">
-        <v>17.5</v>
+        <v>21.6</v>
       </c>
       <c r="E117" t="n">
-        <v>42.4</v>
+        <v>53.8</v>
       </c>
       <c r="F117" t="n">
-        <v>17.5</v>
+        <v>21.6</v>
       </c>
       <c r="G117" t="n">
-        <v>30</v>
+        <v>35.7</v>
       </c>
       <c r="H117" t="n">
-        <v>6.8</v>
+        <v>8.8</v>
       </c>
       <c r="I117" t="n">
-        <v>27.6</v>
+        <v>41.5</v>
       </c>
       <c r="J117" t="n">
-        <v>44.8</v>
+        <v>26.8</v>
       </c>
       <c r="K117" t="n">
-        <v>36.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="118">
@@ -5389,34 +5389,26 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
-      </c>
-      <c r="C118" t="n">
-        <v>76.4</v>
-      </c>
-      <c r="D118" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E118" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="F118" t="n">
-        <v>21.8</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
       <c r="G118" t="n">
-        <v>35.6</v>
+        <v>8.3</v>
       </c>
       <c r="H118" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>41.2</v>
+        <v>25</v>
       </c>
       <c r="J118" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="K118" t="n">
-        <v>47.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119">
@@ -5424,26 +5416,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
-      </c>
-      <c r="C119"/>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
+        <v>116</v>
+      </c>
+      <c r="C119" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="D119" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E119" t="n">
+        <v>50</v>
+      </c>
+      <c r="F119" t="n">
+        <v>15.7</v>
+      </c>
       <c r="G119" t="n">
-        <v>8.3</v>
+        <v>18.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>9.8</v>
       </c>
       <c r="I119" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J119" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="K119" t="n">
-        <v>25</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="120">
@@ -5451,34 +5451,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C120" t="n">
-        <v>65.9</v>
+        <v>64.2</v>
       </c>
       <c r="D120" t="n">
-        <v>16.2</v>
+        <v>19.7</v>
       </c>
       <c r="E120" t="n">
-        <v>49.7</v>
+        <v>44.5</v>
       </c>
       <c r="F120" t="n">
-        <v>16.2</v>
+        <v>19.7</v>
       </c>
       <c r="G120" t="n">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="H120" t="n">
-        <v>10.1</v>
+        <v>9.7</v>
       </c>
       <c r="I120" t="n">
-        <v>38.9</v>
+        <v>43.5</v>
       </c>
       <c r="J120" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="K120" t="n">
-        <v>43.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121">
@@ -5486,34 +5486,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C121" t="n">
-        <v>63.7</v>
+        <v>64.4</v>
       </c>
       <c r="D121" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="E121" t="n">
-        <v>43.8</v>
+        <v>44.7</v>
       </c>
       <c r="F121" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="G121" t="n">
-        <v>16.9</v>
+        <v>25.2</v>
       </c>
       <c r="H121" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="I121" t="n">
-        <v>43.4</v>
+        <v>49.5</v>
       </c>
       <c r="J121" t="n">
-        <v>21.2</v>
+        <v>25.3</v>
       </c>
       <c r="K121" t="n">
-        <v>38.9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122">
@@ -5521,69 +5521,61 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C122" t="n">
-        <v>64.3</v>
+        <v>64.4</v>
       </c>
       <c r="D122" t="n">
-        <v>20.3</v>
+        <v>39.7</v>
       </c>
       <c r="E122" t="n">
-        <v>44</v>
+        <v>24.7</v>
       </c>
       <c r="F122" t="n">
-        <v>20.3</v>
+        <v>39.7</v>
       </c>
       <c r="G122" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="H122" t="n">
-        <v>8.7</v>
+        <v>7.1</v>
       </c>
       <c r="I122" t="n">
-        <v>49.4</v>
+        <v>40</v>
       </c>
       <c r="J122" t="n">
-        <v>25.8</v>
+        <v>30</v>
       </c>
       <c r="K122" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>139</v>
+      </c>
+      <c r="B123" t="s">
         <v>138</v>
       </c>
-      <c r="B123" t="s">
-        <v>139</v>
-      </c>
-      <c r="C123" t="n">
-        <v>64.4</v>
-      </c>
-      <c r="D123" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="E123" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F123" t="n">
-        <v>39.7</v>
-      </c>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
       <c r="G123" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J123" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K123" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124">
@@ -5591,14 +5583,22 @@
         <v>140</v>
       </c>
       <c r="B124" t="s">
-        <v>139</v>
-      </c>
-      <c r="C124"/>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
+        <v>138</v>
+      </c>
+      <c r="C124" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D124" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F124" t="n">
+        <v>50</v>
+      </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5607,10 +5607,10 @@
         <v>50</v>
       </c>
       <c r="J124" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K124" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125">
@@ -5618,34 +5618,34 @@
         <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C125" t="n">
-        <v>66.7</v>
+        <v>69.7</v>
       </c>
       <c r="D125" t="n">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="E125" t="n">
-        <v>16.7</v>
+        <v>53.2</v>
       </c>
       <c r="F125" t="n">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="G125" t="n">
-        <v>50</v>
+        <v>13.1</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="I125" t="n">
-        <v>50</v>
+        <v>34.2</v>
       </c>
       <c r="J125" t="n">
-        <v>50</v>
+        <v>36.8</v>
       </c>
       <c r="K125" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="126">
@@ -5653,34 +5653,34 @@
         <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C126" t="n">
-        <v>70.1</v>
+        <v>72.6</v>
       </c>
       <c r="D126" t="n">
-        <v>17.1</v>
+        <v>19.7</v>
       </c>
       <c r="E126" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="F126" t="n">
-        <v>17.1</v>
+        <v>19.7</v>
       </c>
       <c r="G126" t="n">
-        <v>14.2</v>
+        <v>29.1</v>
       </c>
       <c r="H126" t="n">
-        <v>11.6</v>
+        <v>7.5</v>
       </c>
       <c r="I126" t="n">
-        <v>34.2</v>
+        <v>42.4</v>
       </c>
       <c r="J126" t="n">
-        <v>35.1</v>
+        <v>24.7</v>
       </c>
       <c r="K126" t="n">
-        <v>51.8</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="127">
@@ -5688,34 +5688,34 @@
         <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C127" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D127" t="n">
-        <v>19.7</v>
+        <v>71.4</v>
       </c>
       <c r="E127" t="n">
-        <v>52.3</v>
+        <v>28.6</v>
       </c>
       <c r="F127" t="n">
-        <v>19.7</v>
+        <v>71.4</v>
       </c>
       <c r="G127" t="n">
-        <v>29.8</v>
+        <v>27.3</v>
       </c>
       <c r="H127" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>42.7</v>
+        <v>100</v>
       </c>
       <c r="J127" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>47.6</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="128">
@@ -5723,34 +5723,34 @@
         <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C128" t="n">
-        <v>100</v>
+        <v>79.1</v>
       </c>
       <c r="D128" t="n">
-        <v>71.4</v>
+        <v>29.7</v>
       </c>
       <c r="E128" t="n">
-        <v>28.6</v>
+        <v>49.4</v>
       </c>
       <c r="F128" t="n">
-        <v>71.4</v>
+        <v>29.7</v>
       </c>
       <c r="G128" t="n">
-        <v>27.3</v>
+        <v>26</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I128" t="n">
-        <v>100</v>
+        <v>43.5</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K128" t="n">
-        <v>66.7</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="129">
@@ -5758,34 +5758,34 @@
         <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C129" t="n">
-        <v>78.8</v>
+        <v>59.7</v>
       </c>
       <c r="D129" t="n">
-        <v>30.6</v>
+        <v>25.2</v>
       </c>
       <c r="E129" t="n">
-        <v>48.2</v>
+        <v>34.5</v>
       </c>
       <c r="F129" t="n">
-        <v>30.6</v>
+        <v>25.2</v>
       </c>
       <c r="G129" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
       <c r="H129" t="n">
-        <v>6.2</v>
+        <v>9.7</v>
       </c>
       <c r="I129" t="n">
-        <v>44.3</v>
+        <v>61.7</v>
       </c>
       <c r="J129" t="n">
-        <v>24.6</v>
+        <v>15</v>
       </c>
       <c r="K129" t="n">
-        <v>37.2</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="130">
@@ -5793,34 +5793,34 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C130" t="n">
-        <v>59.7</v>
+        <v>58.9</v>
       </c>
       <c r="D130" t="n">
-        <v>25.2</v>
+        <v>17</v>
       </c>
       <c r="E130" t="n">
-        <v>34.5</v>
+        <v>41.9</v>
       </c>
       <c r="F130" t="n">
-        <v>25.2</v>
+        <v>17</v>
       </c>
       <c r="G130" t="n">
-        <v>25</v>
+        <v>10.3</v>
       </c>
       <c r="H130" t="n">
-        <v>9.7</v>
+        <v>10.9</v>
       </c>
       <c r="I130" t="n">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="J130" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="K130" t="n">
-        <v>46.7</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="131">
@@ -5828,34 +5828,34 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C131" t="n">
-        <v>58.6</v>
+        <v>69.4</v>
       </c>
       <c r="D131" t="n">
-        <v>17.5</v>
+        <v>13.4</v>
       </c>
       <c r="E131" t="n">
-        <v>41.1</v>
+        <v>56</v>
       </c>
       <c r="F131" t="n">
-        <v>17.5</v>
+        <v>13.4</v>
       </c>
       <c r="G131" t="n">
-        <v>10</v>
+        <v>26.9</v>
       </c>
       <c r="H131" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="I131" t="n">
-        <v>61.3</v>
+        <v>36.4</v>
       </c>
       <c r="J131" t="n">
-        <v>16.8</v>
+        <v>36.4</v>
       </c>
       <c r="K131" t="n">
-        <v>25</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="132">
@@ -5863,34 +5863,34 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C132" t="n">
-        <v>69.7</v>
+        <v>80</v>
       </c>
       <c r="D132" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="n">
-        <v>55.3</v>
+        <v>68.9</v>
       </c>
       <c r="F132" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="G132" t="n">
-        <v>27.5</v>
+        <v>39.5</v>
       </c>
       <c r="H132" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I132" t="n">
-        <v>34.9</v>
+        <v>63.6</v>
       </c>
       <c r="J132" t="n">
-        <v>41.9</v>
+        <v>9.1</v>
       </c>
       <c r="K132" t="n">
-        <v>30.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="133">
@@ -5898,34 +5898,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C133" t="n">
-        <v>80</v>
+        <v>67.6</v>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>26.9</v>
       </c>
       <c r="E133" t="n">
-        <v>68.9</v>
+        <v>40.7</v>
       </c>
       <c r="F133" t="n">
-        <v>11.1</v>
+        <v>26.9</v>
       </c>
       <c r="G133" t="n">
-        <v>39.5</v>
+        <v>20.9</v>
       </c>
       <c r="H133" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="I133" t="n">
-        <v>63.6</v>
+        <v>36.6</v>
       </c>
       <c r="J133" t="n">
-        <v>9.1</v>
+        <v>32.6</v>
       </c>
       <c r="K133" t="n">
-        <v>45.5</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="134">
@@ -5933,34 +5933,34 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C134" t="n">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="D134" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="E134" t="n">
-        <v>41.2</v>
+        <v>43.3</v>
       </c>
       <c r="F134" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G134" t="n">
-        <v>20.8</v>
+        <v>14.8</v>
       </c>
       <c r="H134" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="I134" t="n">
-        <v>35.8</v>
+        <v>60</v>
       </c>
       <c r="J134" t="n">
-        <v>32.9</v>
+        <v>30</v>
       </c>
       <c r="K134" t="n">
-        <v>38.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
@@ -5968,34 +5968,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C135" t="n">
-        <v>70</v>
+        <v>59.3</v>
       </c>
       <c r="D135" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="E135" t="n">
-        <v>43.3</v>
+        <v>41.1</v>
       </c>
       <c r="F135" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="G135" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H135" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I135" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J135" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="K135" t="n">
-        <v>10</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="136">
@@ -6003,34 +6003,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C136" t="n">
-        <v>59.3</v>
+        <v>74.1</v>
       </c>
       <c r="D136" t="n">
         <v>18.2</v>
       </c>
       <c r="E136" t="n">
-        <v>41.1</v>
+        <v>55.9</v>
       </c>
       <c r="F136" t="n">
         <v>18.2</v>
       </c>
       <c r="G136" t="n">
-        <v>14.9</v>
+        <v>33.6</v>
       </c>
       <c r="H136" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="I136" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="J136" t="n">
-        <v>31.2</v>
+        <v>20.9</v>
       </c>
       <c r="K136" t="n">
-        <v>51.6</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="137">
@@ -6038,34 +6038,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C137" t="n">
-        <v>74.8</v>
+        <v>78.9</v>
       </c>
       <c r="D137" t="n">
-        <v>18.8</v>
+        <v>21.4</v>
       </c>
       <c r="E137" t="n">
-        <v>56</v>
+        <v>57.5</v>
       </c>
       <c r="F137" t="n">
-        <v>18.8</v>
+        <v>21.4</v>
       </c>
       <c r="G137" t="n">
-        <v>33.1</v>
+        <v>27.5</v>
       </c>
       <c r="H137" t="n">
-        <v>13.2</v>
+        <v>8.2</v>
       </c>
       <c r="I137" t="n">
-        <v>50.5</v>
+        <v>39.6</v>
       </c>
       <c r="J137" t="n">
-        <v>21.6</v>
+        <v>29.9</v>
       </c>
       <c r="K137" t="n">
-        <v>40.2</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="138">
@@ -6073,34 +6073,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C138" t="n">
-        <v>78.1</v>
+        <v>77</v>
       </c>
       <c r="D138" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="E138" t="n">
-        <v>56.7</v>
+        <v>54.4</v>
       </c>
       <c r="F138" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="G138" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="H138" t="n">
-        <v>8.7</v>
+        <v>6.3</v>
       </c>
       <c r="I138" t="n">
-        <v>39.2</v>
+        <v>41.3</v>
       </c>
       <c r="J138" t="n">
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="K138" t="n">
-        <v>40.8</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="139">
@@ -6108,34 +6108,34 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C139" t="n">
-        <v>77.2</v>
+        <v>68.5</v>
       </c>
       <c r="D139" t="n">
-        <v>22.8</v>
+        <v>16.4</v>
       </c>
       <c r="E139" t="n">
-        <v>54.4</v>
+        <v>52.1</v>
       </c>
       <c r="F139" t="n">
-        <v>22.8</v>
+        <v>16.4</v>
       </c>
       <c r="G139" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="H139" t="n">
-        <v>6.8</v>
+        <v>8.8</v>
       </c>
       <c r="I139" t="n">
-        <v>40.4</v>
+        <v>47.5</v>
       </c>
       <c r="J139" t="n">
-        <v>31.1</v>
+        <v>17.5</v>
       </c>
       <c r="K139" t="n">
-        <v>47.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="140">
@@ -6143,69 +6143,69 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="C140" t="n">
-        <v>68.5</v>
+        <v>58.2</v>
       </c>
       <c r="D140" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="E140" t="n">
-        <v>52.1</v>
+        <v>36.5</v>
       </c>
       <c r="F140" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="G140" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="H140" t="n">
-        <v>8.8</v>
+        <v>8.1</v>
       </c>
       <c r="I140" t="n">
-        <v>47.5</v>
+        <v>34.6</v>
       </c>
       <c r="J140" t="n">
-        <v>17.5</v>
+        <v>15.4</v>
       </c>
       <c r="K140" t="n">
-        <v>32.5</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B141" t="s">
         <v>157</v>
       </c>
-      <c r="B141" t="s">
-        <v>158</v>
-      </c>
       <c r="C141" t="n">
-        <v>58.2</v>
+        <v>66.7</v>
       </c>
       <c r="D141" t="n">
-        <v>21.7</v>
+        <v>60</v>
       </c>
       <c r="E141" t="n">
-        <v>36.5</v>
+        <v>6.7</v>
       </c>
       <c r="F141" t="n">
-        <v>21.7</v>
+        <v>60</v>
       </c>
       <c r="G141" t="n">
-        <v>23.1</v>
+        <v>33.3</v>
       </c>
       <c r="H141" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="I141" t="n">
-        <v>34.6</v>
+        <v>25</v>
       </c>
       <c r="J141" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="K141" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6213,34 +6213,34 @@
         <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C142" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="D142" t="n">
-        <v>60</v>
+        <v>15.2</v>
       </c>
       <c r="E142" t="n">
-        <v>6.7</v>
+        <v>51</v>
       </c>
       <c r="F142" t="n">
-        <v>60</v>
+        <v>15.2</v>
       </c>
       <c r="G142" t="n">
-        <v>33.3</v>
+        <v>14.9</v>
       </c>
       <c r="H142" t="n">
-        <v>11.1</v>
+        <v>8.1</v>
       </c>
       <c r="I142" t="n">
-        <v>25</v>
+        <v>48.9</v>
       </c>
       <c r="J142" t="n">
-        <v>25</v>
+        <v>21.1</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="143">
@@ -6248,34 +6248,34 @@
         <v>160</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C143" t="n">
-        <v>66.2</v>
+        <v>35</v>
       </c>
       <c r="D143" t="n">
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="E143" t="n">
-        <v>51</v>
+        <v>21.7</v>
       </c>
       <c r="F143" t="n">
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="G143" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="H143" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="J143" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>46.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -6283,34 +6283,34 @@
         <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C144" t="n">
-        <v>35</v>
+        <v>72.9</v>
       </c>
       <c r="D144" t="n">
-        <v>13.3</v>
+        <v>20.5</v>
       </c>
       <c r="E144" t="n">
-        <v>21.7</v>
+        <v>52.4</v>
       </c>
       <c r="F144" t="n">
-        <v>13.3</v>
+        <v>20.5</v>
       </c>
       <c r="G144" t="n">
-        <v>33.3</v>
+        <v>25.8</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I144" t="n">
-        <v>50</v>
+        <v>45.9</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="145">
@@ -6318,34 +6318,34 @@
         <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C145" t="n">
-        <v>72.9</v>
+        <v>74.1</v>
       </c>
       <c r="D145" t="n">
-        <v>20.5</v>
+        <v>26</v>
       </c>
       <c r="E145" t="n">
-        <v>52.4</v>
+        <v>48.1</v>
       </c>
       <c r="F145" t="n">
-        <v>20.5</v>
+        <v>26</v>
       </c>
       <c r="G145" t="n">
-        <v>25.8</v>
+        <v>31</v>
       </c>
       <c r="H145" t="n">
-        <v>10.5</v>
+        <v>9.8</v>
       </c>
       <c r="I145" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="J145" t="n">
-        <v>28.4</v>
+        <v>25.9</v>
       </c>
       <c r="K145" t="n">
-        <v>36.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="146">
@@ -6353,34 +6353,34 @@
         <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C146" t="n">
-        <v>74.1</v>
+        <v>48.1</v>
       </c>
       <c r="D146" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E146" t="n">
-        <v>48.1</v>
+        <v>23.1</v>
       </c>
       <c r="F146" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G146" t="n">
-        <v>31</v>
+        <v>15.4</v>
       </c>
       <c r="H146" t="n">
-        <v>9.8</v>
+        <v>18.8</v>
       </c>
       <c r="I146" t="n">
-        <v>45.7</v>
+        <v>44.4</v>
       </c>
       <c r="J146" t="n">
-        <v>25.9</v>
+        <v>22.2</v>
       </c>
       <c r="K146" t="n">
-        <v>31.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="147">
@@ -6388,34 +6388,34 @@
         <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C147" t="n">
-        <v>48.1</v>
+        <v>75</v>
       </c>
       <c r="D147" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="E147" t="n">
-        <v>23.1</v>
+        <v>61.7</v>
       </c>
       <c r="F147" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="G147" t="n">
+        <v>40</v>
+      </c>
+      <c r="H147" t="n">
         <v>15.4</v>
       </c>
-      <c r="H147" t="n">
-        <v>18.8</v>
-      </c>
       <c r="I147" t="n">
-        <v>44.4</v>
+        <v>28.6</v>
       </c>
       <c r="J147" t="n">
-        <v>22.2</v>
+        <v>57.1</v>
       </c>
       <c r="K147" t="n">
-        <v>11.1</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="148">
@@ -6423,34 +6423,34 @@
         <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C148" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D148" t="n">
-        <v>13.3</v>
+        <v>23.7</v>
       </c>
       <c r="E148" t="n">
-        <v>61.7</v>
+        <v>43</v>
       </c>
       <c r="F148" t="n">
-        <v>13.3</v>
+        <v>23.7</v>
       </c>
       <c r="G148" t="n">
-        <v>40</v>
+        <v>27.4</v>
       </c>
       <c r="H148" t="n">
-        <v>15.4</v>
+        <v>9.4</v>
       </c>
       <c r="I148" t="n">
-        <v>28.6</v>
+        <v>55.2</v>
       </c>
       <c r="J148" t="n">
-        <v>57.1</v>
+        <v>13.8</v>
       </c>
       <c r="K148" t="n">
-        <v>42.9</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="149">
@@ -6458,34 +6458,34 @@
         <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C149" t="n">
         <v>66.7</v>
       </c>
       <c r="D149" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>43</v>
+        <v>66.7</v>
       </c>
       <c r="F149" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>27.4</v>
+        <v>18.2</v>
       </c>
       <c r="H149" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="J149" t="n">
-        <v>13.8</v>
+        <v>25</v>
       </c>
       <c r="K149" t="n">
-        <v>28.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6493,34 +6493,34 @@
         <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C150" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D150" t="n">
+        <v>25</v>
+      </c>
+      <c r="E150" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F150" t="n">
+        <v>25</v>
+      </c>
+      <c r="G150" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
         <v>66.7</v>
       </c>
-      <c r="D150" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" t="n">
-        <v>75</v>
-      </c>
       <c r="J150" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151">
@@ -6528,34 +6528,34 @@
         <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C151" t="n">
-        <v>85.7</v>
+        <v>60</v>
       </c>
       <c r="D151" t="n">
-        <v>25</v>
+        <v>13.8</v>
       </c>
       <c r="E151" t="n">
-        <v>60.7</v>
+        <v>46.2</v>
       </c>
       <c r="F151" t="n">
-        <v>25</v>
+        <v>13.8</v>
       </c>
       <c r="G151" t="n">
-        <v>37.5</v>
+        <v>26.3</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I151" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K151" t="n">
-        <v>100</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="152">
@@ -6563,34 +6563,34 @@
         <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C152" t="n">
-        <v>60</v>
+        <v>67.1</v>
       </c>
       <c r="D152" t="n">
-        <v>13.8</v>
+        <v>25.7</v>
       </c>
       <c r="E152" t="n">
-        <v>46.2</v>
+        <v>41.4</v>
       </c>
       <c r="F152" t="n">
-        <v>13.8</v>
+        <v>25.7</v>
       </c>
       <c r="G152" t="n">
-        <v>26.3</v>
+        <v>29.8</v>
       </c>
       <c r="H152" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="I152" t="n">
-        <v>80</v>
+        <v>38.9</v>
       </c>
       <c r="J152" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="K152" t="n">
-        <v>46.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="153">
@@ -6598,34 +6598,34 @@
         <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C153" t="n">
-        <v>67.1</v>
+        <v>66.2</v>
       </c>
       <c r="D153" t="n">
-        <v>25.7</v>
+        <v>21.7</v>
       </c>
       <c r="E153" t="n">
-        <v>41.4</v>
+        <v>44.5</v>
       </c>
       <c r="F153" t="n">
-        <v>25.7</v>
+        <v>21.7</v>
       </c>
       <c r="G153" t="n">
-        <v>29.8</v>
+        <v>21</v>
       </c>
       <c r="H153" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="I153" t="n">
-        <v>38.9</v>
+        <v>62.1</v>
       </c>
       <c r="J153" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="K153" t="n">
-        <v>36.7</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="154">
@@ -6633,34 +6633,34 @@
         <v>171</v>
       </c>
       <c r="B154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C154" t="n">
-        <v>66.2</v>
+        <v>80</v>
       </c>
       <c r="D154" t="n">
-        <v>21.7</v>
+        <v>33.8</v>
       </c>
       <c r="E154" t="n">
-        <v>44.5</v>
+        <v>46.2</v>
       </c>
       <c r="F154" t="n">
-        <v>21.7</v>
+        <v>33.8</v>
       </c>
       <c r="G154" t="n">
-        <v>21</v>
+        <v>33.8</v>
       </c>
       <c r="H154" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="I154" t="n">
-        <v>62.1</v>
+        <v>44</v>
       </c>
       <c r="J154" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="K154" t="n">
-        <v>32.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155">
@@ -6668,34 +6668,34 @@
         <v>172</v>
       </c>
       <c r="B155" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C155" t="n">
-        <v>80</v>
+        <v>57.4</v>
       </c>
       <c r="D155" t="n">
-        <v>33.8</v>
+        <v>11.8</v>
       </c>
       <c r="E155" t="n">
-        <v>46.2</v>
+        <v>45.6</v>
       </c>
       <c r="F155" t="n">
-        <v>33.8</v>
+        <v>11.8</v>
       </c>
       <c r="G155" t="n">
-        <v>33.8</v>
+        <v>12.6</v>
       </c>
       <c r="H155" t="n">
-        <v>5.4</v>
+        <v>10.7</v>
       </c>
       <c r="I155" t="n">
-        <v>44</v>
+        <v>55.5</v>
       </c>
       <c r="J155" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="K155" t="n">
-        <v>44</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="156">
@@ -6703,34 +6703,34 @@
         <v>173</v>
       </c>
       <c r="B156" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C156" t="n">
-        <v>57.4</v>
+        <v>63.2</v>
       </c>
       <c r="D156" t="n">
-        <v>11.8</v>
+        <v>45</v>
       </c>
       <c r="E156" t="n">
-        <v>45.6</v>
+        <v>18.2</v>
       </c>
       <c r="F156" t="n">
-        <v>11.8</v>
+        <v>45</v>
       </c>
       <c r="G156" t="n">
-        <v>12.6</v>
+        <v>26.9</v>
       </c>
       <c r="H156" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="I156" t="n">
-        <v>55.5</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="K156" t="n">
-        <v>34.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157">
@@ -6738,34 +6738,34 @@
         <v>174</v>
       </c>
       <c r="B157" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C157" t="n">
-        <v>63.2</v>
+        <v>73.7</v>
       </c>
       <c r="D157" t="n">
-        <v>45</v>
+        <v>10.8</v>
       </c>
       <c r="E157" t="n">
-        <v>18.2</v>
+        <v>62.9</v>
       </c>
       <c r="F157" t="n">
-        <v>45</v>
+        <v>10.8</v>
       </c>
       <c r="G157" t="n">
-        <v>26.9</v>
+        <v>19.7</v>
       </c>
       <c r="H157" t="n">
-        <v>7.7</v>
+        <v>16</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="J157" t="n">
-        <v>25</v>
+        <v>38.3</v>
       </c>
       <c r="K157" t="n">
-        <v>25</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="158">
@@ -6773,34 +6773,34 @@
         <v>175</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C158" t="n">
-        <v>73.7</v>
+        <v>59.7</v>
       </c>
       <c r="D158" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
       <c r="E158" t="n">
-        <v>62.9</v>
+        <v>47.2</v>
       </c>
       <c r="F158" t="n">
-        <v>10.8</v>
+        <v>12.5</v>
       </c>
       <c r="G158" t="n">
-        <v>19.7</v>
+        <v>26.7</v>
       </c>
       <c r="H158" t="n">
-        <v>16</v>
+        <v>13.6</v>
       </c>
       <c r="I158" t="n">
-        <v>31.3</v>
+        <v>60</v>
       </c>
       <c r="J158" t="n">
-        <v>38.3</v>
+        <v>28.9</v>
       </c>
       <c r="K158" t="n">
-        <v>40.9</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="159">
@@ -6808,34 +6808,34 @@
         <v>176</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C159" t="n">
-        <v>59.7</v>
+        <v>72.6</v>
       </c>
       <c r="D159" t="n">
-        <v>12.5</v>
+        <v>24.8</v>
       </c>
       <c r="E159" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="F159" t="n">
-        <v>12.5</v>
+        <v>24.8</v>
       </c>
       <c r="G159" t="n">
-        <v>26.7</v>
+        <v>10.3</v>
       </c>
       <c r="H159" t="n">
-        <v>13.6</v>
+        <v>4.8</v>
       </c>
       <c r="I159" t="n">
-        <v>60</v>
+        <v>45.3</v>
       </c>
       <c r="J159" t="n">
-        <v>28.9</v>
+        <v>23.6</v>
       </c>
       <c r="K159" t="n">
-        <v>36.4</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="160">
@@ -6843,69 +6843,69 @@
         <v>177</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C160" t="n">
-        <v>72.6</v>
+        <v>70.5</v>
       </c>
       <c r="D160" t="n">
-        <v>24.8</v>
+        <v>20.5</v>
       </c>
       <c r="E160" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="F160" t="n">
-        <v>24.8</v>
+        <v>20.5</v>
       </c>
       <c r="G160" t="n">
-        <v>10.3</v>
+        <v>37.7</v>
       </c>
       <c r="H160" t="n">
-        <v>4.8</v>
+        <v>9.2</v>
       </c>
       <c r="I160" t="n">
-        <v>45.3</v>
+        <v>51.9</v>
       </c>
       <c r="J160" t="n">
-        <v>23.6</v>
+        <v>21.2</v>
       </c>
       <c r="K160" t="n">
-        <v>28.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
+        <v>179</v>
+      </c>
+      <c r="B161" t="s">
         <v>178</v>
       </c>
-      <c r="B161" t="s">
-        <v>179</v>
-      </c>
       <c r="C161" t="n">
-        <v>70.5</v>
+        <v>72</v>
       </c>
       <c r="D161" t="n">
-        <v>20.5</v>
+        <v>17.3</v>
       </c>
       <c r="E161" t="n">
-        <v>50</v>
+        <v>54.7</v>
       </c>
       <c r="F161" t="n">
-        <v>20.5</v>
+        <v>17.3</v>
       </c>
       <c r="G161" t="n">
-        <v>37.7</v>
+        <v>14.8</v>
       </c>
       <c r="H161" t="n">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="I161" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="J161" t="n">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
       <c r="K161" t="n">
-        <v>39.1</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="162">
@@ -6913,34 +6913,34 @@
         <v>180</v>
       </c>
       <c r="B162" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C162" t="n">
-        <v>72.4</v>
+        <v>64.6</v>
       </c>
       <c r="D162" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E162" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="F162" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="G162" t="n">
-        <v>14.3</v>
+        <v>37.7</v>
       </c>
       <c r="H162" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="I162" t="n">
-        <v>53</v>
+        <v>29.6</v>
       </c>
       <c r="J162" t="n">
-        <v>16.2</v>
+        <v>48.1</v>
       </c>
       <c r="K162" t="n">
-        <v>34.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="163">
@@ -6948,34 +6948,34 @@
         <v>181</v>
       </c>
       <c r="B163" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C163" t="n">
-        <v>64.6</v>
+        <v>59.8</v>
       </c>
       <c r="D163" t="n">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="E163" t="n">
-        <v>47.9</v>
+        <v>40.3</v>
       </c>
       <c r="F163" t="n">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="G163" t="n">
-        <v>37.7</v>
+        <v>29.8</v>
       </c>
       <c r="H163" t="n">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="I163" t="n">
-        <v>29.6</v>
+        <v>32.4</v>
       </c>
       <c r="J163" t="n">
-        <v>48.1</v>
+        <v>26.5</v>
       </c>
       <c r="K163" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="164">
@@ -6983,34 +6983,34 @@
         <v>182</v>
       </c>
       <c r="B164" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C164" t="n">
-        <v>60</v>
+        <v>64.1</v>
       </c>
       <c r="D164" t="n">
-        <v>19.5</v>
+        <v>12.9</v>
       </c>
       <c r="E164" t="n">
-        <v>40.5</v>
+        <v>51.2</v>
       </c>
       <c r="F164" t="n">
-        <v>19.5</v>
+        <v>12.9</v>
       </c>
       <c r="G164" t="n">
-        <v>30.2</v>
+        <v>11.2</v>
       </c>
       <c r="H164" t="n">
-        <v>14.7</v>
+        <v>15.8</v>
       </c>
       <c r="I164" t="n">
-        <v>32.4</v>
+        <v>56.1</v>
       </c>
       <c r="J164" t="n">
-        <v>26.5</v>
+        <v>18.2</v>
       </c>
       <c r="K164" t="n">
-        <v>37.5</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="165">
@@ -7018,34 +7018,34 @@
         <v>183</v>
       </c>
       <c r="B165" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C165" t="n">
-        <v>65.2</v>
+        <v>80.6</v>
       </c>
       <c r="D165" t="n">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="E165" t="n">
-        <v>52.2</v>
+        <v>63.9</v>
       </c>
       <c r="F165" t="n">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="G165" t="n">
-        <v>11.3</v>
+        <v>23.3</v>
       </c>
       <c r="H165" t="n">
-        <v>15.8</v>
+        <v>9.1</v>
       </c>
       <c r="I165" t="n">
-        <v>55.4</v>
+        <v>32.9</v>
       </c>
       <c r="J165" t="n">
-        <v>18.2</v>
+        <v>36.4</v>
       </c>
       <c r="K165" t="n">
-        <v>31.9</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="166">
@@ -7053,34 +7053,34 @@
         <v>184</v>
       </c>
       <c r="B166" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C166" t="n">
-        <v>80.3</v>
+        <v>63.6</v>
       </c>
       <c r="D166" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="E166" t="n">
-        <v>63.4</v>
+        <v>46</v>
       </c>
       <c r="F166" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="G166" t="n">
-        <v>24</v>
+        <v>27.4</v>
       </c>
       <c r="H166" t="n">
-        <v>9.7</v>
+        <v>12.9</v>
       </c>
       <c r="I166" t="n">
-        <v>32.1</v>
+        <v>47.8</v>
       </c>
       <c r="J166" t="n">
-        <v>37.2</v>
+        <v>27.8</v>
       </c>
       <c r="K166" t="n">
-        <v>42.4</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="167">
@@ -7088,34 +7088,34 @@
         <v>185</v>
       </c>
       <c r="B167" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C167" t="n">
-        <v>63.2</v>
+        <v>75</v>
       </c>
       <c r="D167" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>45.7</v>
+        <v>75</v>
       </c>
       <c r="F167" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>26.8</v>
+        <v>66.7</v>
       </c>
       <c r="H167" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -7123,34 +7123,34 @@
         <v>186</v>
       </c>
       <c r="B168" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C168" t="n">
-        <v>75</v>
+        <v>80.5</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="E168" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="G168" t="n">
-        <v>66.7</v>
+        <v>27.6</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="169">
@@ -7158,34 +7158,34 @@
         <v>187</v>
       </c>
       <c r="B169" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C169" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="D169" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="E169" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="F169" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="G169" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="H169" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="I169" t="n">
-        <v>37.7</v>
+        <v>38.3</v>
       </c>
       <c r="J169" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
       <c r="K169" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="170">
@@ -7193,16 +7193,16 @@
         <v>188</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C170" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="D170" t="n">
         <v>17.7</v>
       </c>
       <c r="E170" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
         <v>17.7</v>
@@ -7214,13 +7214,13 @@
         <v>8.5</v>
       </c>
       <c r="I170" t="n">
-        <v>56.3</v>
+        <v>57.6</v>
       </c>
       <c r="J170" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="K170" t="n">
-        <v>30.1</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="171">
@@ -7228,34 +7228,34 @@
         <v>189</v>
       </c>
       <c r="B171" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C171" t="n">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="D171" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="E171" t="n">
         <v>56.8</v>
       </c>
       <c r="F171" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="G171" t="n">
-        <v>28.1</v>
+        <v>27.3</v>
       </c>
       <c r="H171" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="I171" t="n">
-        <v>32.3</v>
+        <v>31.7</v>
       </c>
       <c r="J171" t="n">
-        <v>34.7</v>
+        <v>35.7</v>
       </c>
       <c r="K171" t="n">
-        <v>52.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="172">
@@ -7263,7 +7263,7 @@
         <v>190</v>
       </c>
       <c r="B172" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C172" t="n">
         <v>77.5</v>
@@ -7298,34 +7298,34 @@
         <v>191</v>
       </c>
       <c r="B173" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C173" t="n">
-        <v>73.1</v>
+        <v>72.7</v>
       </c>
       <c r="D173" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="E173" t="n">
-        <v>54.2</v>
+        <v>54.6</v>
       </c>
       <c r="F173" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="G173" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="H173" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I173" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="J173" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="K173" t="n">
-        <v>45.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="174">
@@ -7333,7 +7333,7 @@
         <v>192</v>
       </c>
       <c r="B174" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C174" t="n">
         <v>37.5</v>
@@ -7362,7 +7362,7 @@
         <v>193</v>
       </c>
       <c r="B175" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -7392,31 +7392,31 @@
         <v>194</v>
       </c>
       <c r="C176" t="n">
-        <v>69.3</v>
+        <v>69.4</v>
       </c>
       <c r="D176" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="E176" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="F176" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="G176" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="H176" t="n">
-        <v>9.3</v>
+        <v>9.4</v>
       </c>
       <c r="I176" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="J176" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="K176" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
     </row>
   </sheetData>
@@ -7492,28 +7492,28 @@
         <v>67.1</v>
       </c>
       <c r="D2" t="n">
-        <v>61.8</v>
+        <v>60.8</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="F2" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="G2" t="n">
-        <v>11.6</v>
+        <v>13.3</v>
       </c>
       <c r="H2" t="n">
-        <v>33.3</v>
+        <v>34.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>48.3</v>
+        <v>47.2</v>
       </c>
       <c r="K2" t="n">
-        <v>34.8</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="3">
@@ -7524,31 +7524,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>62.3</v>
       </c>
       <c r="D3" t="n">
         <v>64.5</v>
       </c>
       <c r="E3" t="n">
-        <v>19.5</v>
+        <v>18.1</v>
       </c>
       <c r="F3" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>36.6</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>15.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="4">
@@ -7594,36 +7594,36 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>58.4</v>
+        <v>57.9</v>
       </c>
       <c r="D5" t="n">
-        <v>59.9</v>
+        <v>60.2</v>
       </c>
       <c r="E5" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="F5" t="n">
-        <v>40.3</v>
+        <v>41.8</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H5" t="n">
-        <v>46.3</v>
+        <v>45.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.7</v>
       </c>
       <c r="J5" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="K5" t="n">
-        <v>7.5</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7699,31 +7699,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>67.6</v>
+        <v>68.4</v>
       </c>
       <c r="D8" t="n">
-        <v>69.3</v>
+        <v>69.8</v>
       </c>
       <c r="E8" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="F8" t="n">
-        <v>34.3</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
         <v>41.3</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>26.6</v>
+        <v>28.2</v>
       </c>
       <c r="K8" t="n">
-        <v>14.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="9">
@@ -7804,7 +7804,7 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="D11" t="n">
         <v>64.5</v>
@@ -7813,22 +7813,22 @@
         <v>13.9</v>
       </c>
       <c r="F11" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="K11" t="n">
-        <v>9.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="12">
@@ -7874,31 +7874,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>59.5</v>
+        <v>60.3</v>
       </c>
       <c r="D13" t="n">
-        <v>61.5</v>
+        <v>61.7</v>
       </c>
       <c r="E13" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>50.8</v>
+        <v>52.3</v>
       </c>
       <c r="G13" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="H13" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="K13" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="14">
@@ -7909,31 +7909,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>48.8</v>
+        <v>51.6</v>
       </c>
       <c r="D14" t="n">
-        <v>51.1</v>
+        <v>53.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9.8</v>
+        <v>10.3</v>
       </c>
       <c r="F14" t="n">
-        <v>41.7</v>
+        <v>39.4</v>
       </c>
       <c r="G14" t="n">
-        <v>18.6</v>
+        <v>14.8</v>
       </c>
       <c r="H14" t="n">
-        <v>42.1</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
-        <v>24.2</v>
+        <v>21.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
@@ -7944,31 +7944,31 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>59.2</v>
+        <v>58.9</v>
       </c>
       <c r="D15" t="n">
-        <v>63.6</v>
+        <v>63.9</v>
       </c>
       <c r="E15" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="F15" t="n">
-        <v>47.4</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>8.2</v>
+        <v>7.7</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="K15" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="16">
@@ -8257,31 +8257,31 @@
         <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>39.4</v>
+        <v>37.5</v>
       </c>
       <c r="D24" t="n">
-        <v>50.3</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="F24" t="n">
-        <v>57.5</v>
+        <v>57.1</v>
       </c>
       <c r="G24" t="n">
-        <v>20.3</v>
+        <v>25.5</v>
       </c>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>23.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>40.4</v>
+        <v>43.1</v>
       </c>
       <c r="K24" t="n">
-        <v>15.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -8362,31 +8362,31 @@
         <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>57.6</v>
+        <v>58.2</v>
       </c>
       <c r="D27" t="n">
-        <v>59.9</v>
+        <v>60.2</v>
       </c>
       <c r="E27" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="F27" t="n">
-        <v>55.4</v>
+        <v>53.2</v>
       </c>
       <c r="G27" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="H27" t="n">
-        <v>57.7</v>
+        <v>55.9</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="K27" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="28">
@@ -8607,31 +8607,31 @@
         <v>31</v>
       </c>
       <c r="C34" t="n">
-        <v>52.7</v>
+        <v>55</v>
       </c>
       <c r="D34" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="E34" t="n">
-        <v>16.5</v>
+        <v>17.9</v>
       </c>
       <c r="F34" t="n">
-        <v>38.6</v>
+        <v>40</v>
       </c>
       <c r="G34" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H34" t="n">
-        <v>42.6</v>
+        <v>43.1</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="35">
@@ -8887,31 +8887,31 @@
         <v>48</v>
       </c>
       <c r="C42" t="n">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
       <c r="D42" t="n">
-        <v>64.4</v>
+        <v>64.3</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="F42" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="G42" t="n">
-        <v>8.3</v>
+        <v>8.6</v>
       </c>
       <c r="H42" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="I42" t="n">
         <v>1.9</v>
       </c>
       <c r="J42" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="43">
@@ -8951,7 +8951,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
@@ -9060,31 +9060,31 @@
         <v>48</v>
       </c>
       <c r="C47" t="n">
-        <v>60.5</v>
+        <v>62.7</v>
       </c>
       <c r="D47" t="n">
-        <v>64.9</v>
+        <v>66.2</v>
       </c>
       <c r="E47" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="F47" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H47" t="n">
-        <v>32.7</v>
+        <v>36.6</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="48">
@@ -9130,31 +9130,31 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>58.2</v>
+        <v>54.9</v>
       </c>
       <c r="D49" t="n">
         <v>65.4</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="F49" t="n">
-        <v>39.6</v>
+        <v>36.4</v>
       </c>
       <c r="G49" t="n">
-        <v>8</v>
+        <v>8.8</v>
       </c>
       <c r="H49" t="n">
-        <v>43.1</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="K49" t="n">
-        <v>13.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="50">
@@ -9265,7 +9265,7 @@
         <v>241</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" t="n">
         <v>60</v>
@@ -9300,7 +9300,7 @@
         <v>242</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" t="n">
         <v>74.1</v>
@@ -9335,7 +9335,7 @@
         <v>243</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" t="n">
         <v>55.4</v>
@@ -9370,7 +9370,7 @@
         <v>244</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C56" t="n">
         <v>66.7</v>
@@ -9400,10 +9400,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C57" t="n">
         <v>62.2</v>
@@ -9438,7 +9438,7 @@
         <v>245</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C58" t="n">
         <v>65.6</v>
@@ -9473,7 +9473,7 @@
         <v>246</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C59" t="n">
         <v>58.8</v>
@@ -9505,10 +9505,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C60" t="n">
         <v>73.1</v>
@@ -9543,7 +9543,7 @@
         <v>247</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C61" t="n">
         <v>62</v>
@@ -9578,7 +9578,7 @@
         <v>248</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C62" t="n">
         <v>62.4</v>
@@ -9613,7 +9613,7 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" t="n">
         <v>60</v>
@@ -9648,7 +9648,7 @@
         <v>250</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" t="n">
         <v>62.9</v>
@@ -9683,7 +9683,7 @@
         <v>251</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C65" t="n">
         <v>68.1</v>
@@ -9715,10 +9715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="n">
         <v>30</v>
@@ -9750,10 +9750,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" t="n">
         <v>40</v>
@@ -9788,7 +9788,7 @@
         <v>252</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" t="n">
         <v>43.8</v>
@@ -9823,7 +9823,7 @@
         <v>253</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" t="n">
         <v>68.4</v>
@@ -9855,10 +9855,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" t="n">
         <v>62.5</v>
@@ -9893,34 +9893,34 @@
         <v>254</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C71" t="n">
-        <v>70.5</v>
+        <v>70.9</v>
       </c>
       <c r="D71" t="n">
-        <v>68.8</v>
+        <v>68.4</v>
       </c>
       <c r="E71" t="n">
-        <v>16.9</v>
+        <v>19.9</v>
       </c>
       <c r="F71" t="n">
-        <v>45.1</v>
+        <v>46.3</v>
       </c>
       <c r="G71" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H71" t="n">
-        <v>47.6</v>
+        <v>49.5</v>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
       <c r="K71" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="72">
@@ -9928,7 +9928,7 @@
         <v>255</v>
       </c>
       <c r="B72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C72" t="n">
         <v>55.4</v>
@@ -9963,7 +9963,7 @@
         <v>256</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C73" t="n">
         <v>54.4</v>
@@ -9998,34 +9998,34 @@
         <v>257</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C74" t="n">
-        <v>55</v>
+        <v>55.8</v>
       </c>
       <c r="D74" t="n">
-        <v>64.4</v>
+        <v>63.6</v>
       </c>
       <c r="E74" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="F74" t="n">
-        <v>41.2</v>
+        <v>40.5</v>
       </c>
       <c r="G74" t="n">
-        <v>7.7</v>
+        <v>8.3</v>
       </c>
       <c r="H74" t="n">
-        <v>47.3</v>
+        <v>50</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="K74" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="75">
@@ -10033,7 +10033,7 @@
         <v>229</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C75" t="n">
         <v>53.1</v>
@@ -10068,34 +10068,34 @@
         <v>258</v>
       </c>
       <c r="B76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="D76" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="E76" t="n">
-        <v>23.6</v>
+        <v>25.9</v>
       </c>
       <c r="F76" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="G76" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="H76" t="n">
-        <v>44.9</v>
+        <v>45.3</v>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
-        <v>25.9</v>
+        <v>26.4</v>
       </c>
       <c r="K76" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="77">
@@ -10103,34 +10103,34 @@
         <v>259</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C77" t="n">
         <v>62.8</v>
       </c>
       <c r="D77" t="n">
-        <v>65.1</v>
+        <v>65.5</v>
       </c>
       <c r="E77" t="n">
-        <v>26.1</v>
+        <v>26.5</v>
       </c>
       <c r="F77" t="n">
-        <v>56</v>
+        <v>55.2</v>
       </c>
       <c r="G77" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H77" t="n">
-        <v>48.8</v>
+        <v>46.7</v>
       </c>
       <c r="I77" t="n">
         <v>0.6</v>
       </c>
       <c r="J77" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="K77" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="78">
@@ -10138,7 +10138,7 @@
         <v>260</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C78" t="n">
         <v>60.5</v>
@@ -10173,7 +10173,7 @@
         <v>261</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C79" t="n">
         <v>51.6</v>
@@ -10208,34 +10208,34 @@
         <v>262</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C80" t="n">
-        <v>61.7</v>
+        <v>63.2</v>
       </c>
       <c r="D80" t="n">
-        <v>61.7</v>
+        <v>60.9</v>
       </c>
       <c r="E80" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="F80" t="n">
-        <v>34.3</v>
+        <v>30</v>
       </c>
       <c r="G80" t="n">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="H80" t="n">
-        <v>33.3</v>
+        <v>29.3</v>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="K80" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="81">
@@ -10243,7 +10243,7 @@
         <v>263</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C81" t="n">
         <v>66</v>
@@ -10278,34 +10278,34 @@
         <v>264</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C82" t="n">
-        <v>62.7</v>
+        <v>63.1</v>
       </c>
       <c r="D82" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="E82" t="n">
-        <v>21.8</v>
+        <v>20.7</v>
       </c>
       <c r="F82" t="n">
-        <v>52.3</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
-        <v>8.1</v>
+        <v>8.2</v>
       </c>
       <c r="H82" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="K82" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="83">
@@ -10313,7 +10313,7 @@
         <v>265</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C83" t="n">
         <v>71.4</v>
@@ -10348,34 +10348,34 @@
         <v>266</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C84" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="D84" t="n">
-        <v>64.1</v>
+        <v>64.2</v>
       </c>
       <c r="E84" t="n">
-        <v>21.5</v>
+        <v>20.2</v>
       </c>
       <c r="F84" t="n">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="H84" t="n">
         <v>57.1</v>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>24</v>
       </c>
       <c r="K84" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="85">
@@ -10383,7 +10383,7 @@
         <v>267</v>
       </c>
       <c r="B85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" t="n">
         <v>42</v>
@@ -10418,7 +10418,7 @@
         <v>268</v>
       </c>
       <c r="B86" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C86" t="n">
         <v>61.7</v>
@@ -10453,7 +10453,7 @@
         <v>204</v>
       </c>
       <c r="B87" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C87" t="n">
         <v>56.4</v>
@@ -10488,7 +10488,7 @@
         <v>269</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C88" t="n">
         <v>28.6</v>
@@ -10521,7 +10521,7 @@
         <v>270</v>
       </c>
       <c r="B89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C89" t="n">
         <v>61.9</v>
@@ -10556,7 +10556,7 @@
         <v>217</v>
       </c>
       <c r="B90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C90" t="n">
         <v>48.6</v>
@@ -10588,10 +10588,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C91" t="n">
         <v>59.3</v>
@@ -10623,10 +10623,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C92" t="n">
         <v>61.1</v>
@@ -10661,7 +10661,7 @@
         <v>271</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C93" t="n">
         <v>53.6</v>
@@ -10696,7 +10696,7 @@
         <v>272</v>
       </c>
       <c r="B94" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C94" t="n">
         <v>66</v>
@@ -10731,34 +10731,34 @@
         <v>273</v>
       </c>
       <c r="B95" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C95" t="n">
-        <v>55.7</v>
+        <v>53.7</v>
       </c>
       <c r="D95" t="n">
-        <v>60.7</v>
+        <v>60.2</v>
       </c>
       <c r="E95" t="n">
-        <v>22</v>
+        <v>19.4</v>
       </c>
       <c r="F95" t="n">
-        <v>39.7</v>
+        <v>38.7</v>
       </c>
       <c r="G95" t="n">
         <v>7.6</v>
       </c>
       <c r="H95" t="n">
-        <v>54.9</v>
+        <v>54.1</v>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="K95" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="96">
@@ -10766,34 +10766,34 @@
         <v>274</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C96" t="n">
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
       <c r="D96" t="n">
-        <v>54.5</v>
+        <v>54.9</v>
       </c>
       <c r="E96" t="n">
-        <v>21.5</v>
+        <v>20.2</v>
       </c>
       <c r="F96" t="n">
-        <v>39.3</v>
+        <v>40.9</v>
       </c>
       <c r="G96" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="H96" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J96" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="K96" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="97">
@@ -10801,7 +10801,7 @@
         <v>275</v>
       </c>
       <c r="B97" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C97" t="n">
         <v>57.9</v>
@@ -10836,7 +10836,7 @@
         <v>276</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C98" t="n">
         <v>57.1</v>
@@ -10871,34 +10871,34 @@
         <v>277</v>
       </c>
       <c r="B99" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C99" t="n">
-        <v>67.9</v>
+        <v>66.1</v>
       </c>
       <c r="D99" t="n">
-        <v>71.3</v>
+        <v>70.3</v>
       </c>
       <c r="E99" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
       <c r="F99" t="n">
-        <v>39.3</v>
+        <v>38.7</v>
       </c>
       <c r="G99" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H99" t="n">
-        <v>42.1</v>
+        <v>42.9</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K99" t="n">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="100">
@@ -10906,7 +10906,7 @@
         <v>278</v>
       </c>
       <c r="B100" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C100" t="n">
         <v>60.4</v>
@@ -10941,7 +10941,7 @@
         <v>279</v>
       </c>
       <c r="B101" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C101" t="n">
         <v>58.1</v>
@@ -10976,34 +10976,34 @@
         <v>280</v>
       </c>
       <c r="B102" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C102" t="n">
-        <v>72.2</v>
+        <v>69.6</v>
       </c>
       <c r="D102" t="n">
-        <v>63.9</v>
+        <v>64.6</v>
       </c>
       <c r="E102" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="F102" t="n">
-        <v>33.3</v>
+        <v>36.8</v>
       </c>
       <c r="G102" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H102" t="n">
-        <v>45</v>
+        <v>42.4</v>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
-        <v>19.8</v>
+        <v>21.4</v>
       </c>
       <c r="K102" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="103">
@@ -11011,42 +11011,42 @@
         <v>281</v>
       </c>
       <c r="B103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C103" t="n">
-        <v>59.3</v>
+        <v>59</v>
       </c>
       <c r="D103" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="E103" t="n">
-        <v>25.7</v>
+        <v>24.6</v>
       </c>
       <c r="F103" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="G103" t="n">
-        <v>9.9</v>
+        <v>9.8</v>
       </c>
       <c r="H103" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I103" t="n">
         <v>0.8</v>
       </c>
       <c r="J103" t="n">
-        <v>31.9</v>
+        <v>30.3</v>
       </c>
       <c r="K103" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -11067,34 +11067,34 @@
         <v>282</v>
       </c>
       <c r="B105" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C105" t="n">
-        <v>65.3</v>
+        <v>62.7</v>
       </c>
       <c r="D105" t="n">
-        <v>67.3</v>
+        <v>65.9</v>
       </c>
       <c r="E105" t="n">
-        <v>31.2</v>
+        <v>27.8</v>
       </c>
       <c r="F105" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="G105" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H105" t="n">
-        <v>59.6</v>
+        <v>58.8</v>
       </c>
       <c r="I105" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J105" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="K105" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="106">
@@ -11102,34 +11102,34 @@
         <v>283</v>
       </c>
       <c r="B106" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C106" t="n">
-        <v>69.6</v>
+        <v>67</v>
       </c>
       <c r="D106" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E106" t="n">
-        <v>23.3</v>
+        <v>19.1</v>
       </c>
       <c r="F106" t="n">
-        <v>43.8</v>
+        <v>42.5</v>
       </c>
       <c r="G106" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="H106" t="n">
-        <v>63.9</v>
+        <v>57.1</v>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J106" t="n">
-        <v>27</v>
+        <v>27.9</v>
       </c>
       <c r="K106" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="107">
@@ -11137,7 +11137,7 @@
         <v>284</v>
       </c>
       <c r="B107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C107" t="n">
         <v>60.6</v>
@@ -11172,34 +11172,34 @@
         <v>285</v>
       </c>
       <c r="B108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C108" t="n">
-        <v>65.3</v>
+        <v>64.9</v>
       </c>
       <c r="D108" t="n">
-        <v>66</v>
+        <v>65.9</v>
       </c>
       <c r="E108" t="n">
-        <v>28.3</v>
+        <v>28.6</v>
       </c>
       <c r="F108" t="n">
-        <v>55.3</v>
+        <v>54.3</v>
       </c>
       <c r="G108" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H108" t="n">
         <v>48.8</v>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J108" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="K108" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109">
@@ -11207,34 +11207,34 @@
         <v>286</v>
       </c>
       <c r="B109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C109" t="n">
-        <v>66.1</v>
+        <v>67</v>
       </c>
       <c r="D109" t="n">
-        <v>65.6</v>
+        <v>66</v>
       </c>
       <c r="E109" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="F109" t="n">
-        <v>36.8</v>
+        <v>35.4</v>
       </c>
       <c r="G109" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H109" t="n">
-        <v>44.9</v>
+        <v>43.4</v>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="K109" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="110">
@@ -11242,7 +11242,7 @@
         <v>287</v>
       </c>
       <c r="B110" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C110" t="n">
         <v>65.1</v>
@@ -11277,34 +11277,34 @@
         <v>288</v>
       </c>
       <c r="B111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C111" t="n">
-        <v>61.6</v>
+        <v>62.7</v>
       </c>
       <c r="D111" t="n">
-        <v>61.9</v>
+        <v>62.2</v>
       </c>
       <c r="E111" t="n">
         <v>13.3</v>
       </c>
       <c r="F111" t="n">
-        <v>58.6</v>
+        <v>58.9</v>
       </c>
       <c r="G111" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="H111" t="n">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>35.6</v>
       </c>
       <c r="K111" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="112">
@@ -11312,7 +11312,7 @@
         <v>289</v>
       </c>
       <c r="B112" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C112" t="n">
         <v>33.3</v>
@@ -11347,7 +11347,7 @@
         <v>290</v>
       </c>
       <c r="B113" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C113" t="n">
         <v>57.4</v>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>156</v>
+      </c>
+      <c r="B114" t="s">
         <v>157</v>
-      </c>
-      <c r="B114" t="s">
-        <v>158</v>
       </c>
       <c r="C114" t="n">
         <v>51.6</v>
@@ -11417,7 +11417,7 @@
         <v>291</v>
       </c>
       <c r="B115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C115" t="n">
         <v>64.9</v>
@@ -11452,7 +11452,7 @@
         <v>292</v>
       </c>
       <c r="B116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C116" t="n">
         <v>50</v>
@@ -11485,7 +11485,7 @@
         <v>293</v>
       </c>
       <c r="B117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C117" t="n">
         <v>59.3</v>
@@ -11520,7 +11520,7 @@
         <v>294</v>
       </c>
       <c r="B118" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C118" t="n">
         <v>46.6</v>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C119" t="n">
         <v>50.6</v>
@@ -11590,7 +11590,7 @@
         <v>295</v>
       </c>
       <c r="B120" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C120" t="n">
         <v>58.6</v>
@@ -11625,7 +11625,7 @@
         <v>296</v>
       </c>
       <c r="B121" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C121" t="n">
         <v>52.6</v>
@@ -11660,7 +11660,7 @@
         <v>297</v>
       </c>
       <c r="B122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C122" t="n">
         <v>63.1</v>
@@ -11695,7 +11695,7 @@
         <v>298</v>
       </c>
       <c r="B123" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C123" t="n">
         <v>66.9</v>
@@ -11730,7 +11730,7 @@
         <v>299</v>
       </c>
       <c r="B124" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C124" t="n">
         <v>44</v>
@@ -11765,7 +11765,7 @@
         <v>300</v>
       </c>
       <c r="B125" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C125" t="n">
         <v>38.9</v>
@@ -11800,7 +11800,7 @@
         <v>301</v>
       </c>
       <c r="B126" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C126" t="n">
         <v>50</v>
@@ -11835,7 +11835,7 @@
         <v>302</v>
       </c>
       <c r="B127" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C127" t="n">
         <v>55.1</v>
@@ -11870,7 +11870,7 @@
         <v>303</v>
       </c>
       <c r="B128" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C128" t="n">
         <v>57.9</v>
@@ -11905,7 +11905,7 @@
         <v>304</v>
       </c>
       <c r="B129" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C129" t="n">
         <v>40</v>
@@ -11940,7 +11940,7 @@
         <v>305</v>
       </c>
       <c r="B130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C130" t="n">
         <v>61.7</v>
@@ -11975,7 +11975,7 @@
         <v>306</v>
       </c>
       <c r="B131" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C131" t="n">
         <v>63.6</v>
@@ -12010,42 +12010,42 @@
         <v>307</v>
       </c>
       <c r="B132" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C132" t="n">
-        <v>64.5</v>
+        <v>63.2</v>
       </c>
       <c r="D132" t="n">
-        <v>67.1</v>
+        <v>66.4</v>
       </c>
       <c r="E132" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="F132" t="n">
-        <v>35.3</v>
+        <v>39</v>
       </c>
       <c r="G132" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H132" t="n">
-        <v>45.4</v>
+        <v>46.6</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="K132" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C133" t="n">
         <v>80</v>
@@ -12078,7 +12078,7 @@
         <v>308</v>
       </c>
       <c r="B134" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C134" t="n">
         <v>60.2</v>
@@ -12113,7 +12113,7 @@
         <v>309</v>
       </c>
       <c r="B135" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C135" t="n">
         <v>58.1</v>
@@ -12148,34 +12148,34 @@
         <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C136" t="n">
-        <v>60.3</v>
+        <v>58.3</v>
       </c>
       <c r="D136" t="n">
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="E136" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="F136" t="n">
-        <v>38.3</v>
+        <v>37.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.7</v>
+        <v>10.5</v>
       </c>
       <c r="H136" t="n">
-        <v>32.4</v>
+        <v>33.7</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J136" t="n">
         <v>26.6</v>
       </c>
       <c r="K136" t="n">
-        <v>10.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="137">
@@ -12183,34 +12183,34 @@
         <v>310</v>
       </c>
       <c r="B137" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C137" t="n">
-        <v>74.6</v>
+        <v>73.8</v>
       </c>
       <c r="D137" t="n">
-        <v>66.4</v>
+        <v>66.2</v>
       </c>
       <c r="E137" t="n">
-        <v>30</v>
+        <v>29.1</v>
       </c>
       <c r="F137" t="n">
-        <v>62.1</v>
+        <v>60.9</v>
       </c>
       <c r="G137" t="n">
         <v>4</v>
       </c>
       <c r="H137" t="n">
-        <v>38.1</v>
+        <v>40.6</v>
       </c>
       <c r="I137" t="n">
         <v>2.4</v>
       </c>
       <c r="J137" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="K137" t="n">
-        <v>39.5</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="138">
@@ -12218,7 +12218,7 @@
         <v>311</v>
       </c>
       <c r="B138" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C138" t="n">
         <v>73.7</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="B139" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C139" t="n">
         <v>66.7</v>
@@ -12286,7 +12286,7 @@
         <v>312</v>
       </c>
       <c r="B140" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C140" t="n">
         <v>50</v>
@@ -12321,7 +12321,7 @@
         <v>313</v>
       </c>
       <c r="B141" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C141" t="n">
         <v>61.3</v>
@@ -12356,7 +12356,7 @@
         <v>314</v>
       </c>
       <c r="B142" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C142" t="n">
         <v>65.8</v>
@@ -12391,7 +12391,7 @@
         <v>315</v>
       </c>
       <c r="B143" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C143" t="n">
         <v>49.4</v>
@@ -12426,7 +12426,7 @@
         <v>265</v>
       </c>
       <c r="B144" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C144" t="n">
         <v>66.7</v>
@@ -12461,34 +12461,34 @@
         <v>316</v>
       </c>
       <c r="B145" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C145" t="n">
-        <v>70.6</v>
+        <v>69.5</v>
       </c>
       <c r="D145" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="E145" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="F145" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="G145" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H145" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="K145" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="146">
@@ -12496,7 +12496,7 @@
         <v>317</v>
       </c>
       <c r="B146" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C146" t="n">
         <v>59.5</v>
@@ -12532,13 +12532,13 @@
         <v>194</v>
       </c>
       <c r="C147" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="D147" t="n">
         <v>60.4</v>
       </c>
       <c r="E147" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F147" t="n">
         <v>38.9</v>
@@ -12547,7 +12547,7 @@
         <v>11.6</v>
       </c>
       <c r="H147" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="I147" t="n">
         <v>3.3</v>
